--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB06CFC-3BAB-4478-AA7B-43D6A8569CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CEC02E9-FC1C-4E4A-8248-41A1EAB59399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="71">
   <si>
     <t>Booking</t>
   </si>
@@ -233,6 +233,12 @@
   </si>
   <si>
     <t>Nabeel Traders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aqib </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qamar Ijaz </t>
   </si>
 </sst>
 </file>
@@ -3714,7 +3720,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE3A274-C162-4D95-8CE5-F3DF4FC60319}">
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -3750,21 +3756,21 @@
     </row>
     <row r="2" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="91">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>1</v>
+        <v>3.7037037037037035E-2</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F2" s="89">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="G2" s="114" t="s">
         <v>34</v>
@@ -3840,7 +3846,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="29" t="s">
         <v>20</v>
       </c>
@@ -3851,7 +3857,7 @@
         <v>21</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="E4" s="47" t="s">
         <v>22</v>
@@ -3864,39 +3870,36 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>271+8+7+21+1+8+16</f>
-        <v>332</v>
+        <v>8</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.55333333333333334</v>
-      </c>
-      <c r="K4" s="7">
-        <v>550</v>
-      </c>
+        <v>1.3333333333333334E-2</v>
+      </c>
+      <c r="K4" s="7"/>
       <c r="L4" s="8">
-        <v>353.52499999999998</v>
+        <v>7.5</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.64277272727272727</v>
+        <v>0</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>196.47500000000002</v>
-      </c>
-      <c r="O4" s="10" t="e">
+        <v>-7.5</v>
+      </c>
+      <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>#DIV/0!</v>
+        <v>-0.28846153846153844</v>
       </c>
       <c r="P4" s="68">
-        <f t="shared" ref="P4:P12" si="2">L4/I4</f>
-        <v>1.0648343373493976</v>
+        <f t="shared" ref="P4:P13" si="2">L4/I4</f>
+        <v>0.9375</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
     </row>
-    <row r="5" spans="1:18" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="35" t="s">
         <v>20</v>
       </c>
@@ -3906,8 +3909,8 @@
       <c r="C5" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="16" t="s">
-        <v>19</v>
+      <c r="D5" s="47" t="s">
+        <v>70</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>22</v>
@@ -3920,39 +3923,36 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <f>277+21+18+15+30</f>
-        <v>361</v>
+        <v>2</v>
       </c>
       <c r="J5" s="69">
-        <f t="shared" ref="J5:J28" si="3">IFERROR(I5/G5,0)</f>
-        <v>0.60166666666666668</v>
-      </c>
-      <c r="K5" s="11">
-        <v>450</v>
-      </c>
+        <f t="shared" ref="J5:J29" si="3">IFERROR(I5/G5,0)</f>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="K5" s="11"/>
       <c r="L5" s="12">
-        <v>205.95</v>
+        <v>6</v>
       </c>
       <c r="M5" s="70">
-        <f t="shared" ref="M5:M28" si="4">IFERROR(L5/K5,0)</f>
-        <v>0.45766666666666667</v>
+        <f t="shared" ref="M5:M29" si="4">IFERROR(L5/K5,0)</f>
+        <v>0</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>244.05</v>
-      </c>
-      <c r="O5" s="14" t="e">
+        <v>-6</v>
+      </c>
+      <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-0.23076923076923078</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>0.57049861495844867</v>
+        <v>3</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
     </row>
-    <row r="6" spans="1:18" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="35" t="s">
         <v>20</v>
       </c>
@@ -3962,8 +3962,8 @@
       <c r="C6" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="16" t="s">
-        <v>19</v>
+      <c r="D6" s="47" t="s">
+        <v>70</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>22</v>
@@ -3976,39 +3976,36 @@
       </c>
       <c r="H6" s="71"/>
       <c r="I6" s="12">
-        <f>117+5+5+8+8+5+2</f>
-        <v>150</v>
+        <v>7</v>
       </c>
       <c r="J6" s="69">
         <f t="shared" si="3"/>
-        <v>0.25</v>
-      </c>
-      <c r="K6" s="11">
-        <v>550</v>
-      </c>
+        <v>1.1666666666666667E-2</v>
+      </c>
+      <c r="K6" s="11"/>
       <c r="L6" s="12">
-        <v>212.72499999999999</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="M6" s="70">
         <f t="shared" si="4"/>
-        <v>0.38677272727272727</v>
+        <v>0</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="0"/>
-        <v>337.27499999999998</v>
-      </c>
-      <c r="O6" s="14" t="e">
+        <v>-4.6500000000000004</v>
+      </c>
+      <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-0.17884615384615385</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
-        <v>1.4181666666666666</v>
+        <v>0.66428571428571437</v>
       </c>
       <c r="Q6" s="14"/>
       <c r="R6" s="34"/>
     </row>
-    <row r="7" spans="1:18" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="35" t="s">
         <v>20</v>
       </c>
@@ -4018,8 +4015,8 @@
       <c r="C7" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="16" t="s">
-        <v>19</v>
+      <c r="D7" s="47" t="s">
+        <v>70</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>22</v>
@@ -4032,39 +4029,36 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>121+5+6+4+8+2</f>
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>0.24333333333333335</v>
-      </c>
-      <c r="K7" s="11">
-        <v>400</v>
-      </c>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K7" s="11"/>
       <c r="L7" s="12">
-        <v>180.4</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>0.45100000000000001</v>
+        <v>0</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>219.6</v>
-      </c>
-      <c r="O7" s="14" t="e">
+        <v>-4.9000000000000004</v>
+      </c>
+      <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-0.18846153846153849</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.2356164383561645</v>
+        <v>1.6333333333333335</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
     </row>
-    <row r="8" spans="1:18" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="35" t="s">
         <v>20</v>
       </c>
@@ -4074,8 +4068,8 @@
       <c r="C8" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="16" t="s">
-        <v>19</v>
+      <c r="D8" s="47" t="s">
+        <v>70</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>22</v>
@@ -4088,39 +4082,36 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <f>85+5+5+8+3+2+5</f>
-        <v>113</v>
+        <v>4</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>0.18833333333333332</v>
-      </c>
-      <c r="K8" s="11">
-        <v>575</v>
-      </c>
+        <v>6.6666666666666671E-3</v>
+      </c>
+      <c r="K8" s="11"/>
       <c r="L8" s="12">
-        <v>126.65</v>
+        <v>2.1749999999999998</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>0.2202608695652174</v>
+        <v>0</v>
       </c>
       <c r="N8" s="12">
-        <f t="shared" ref="N8:N28" si="5">K8-L8</f>
-        <v>448.35</v>
-      </c>
-      <c r="O8" s="14" t="e">
-        <f t="shared" ref="O8:O28" si="6">N8/$D$2</f>
-        <v>#DIV/0!</v>
+        <f t="shared" ref="N8:N29" si="5">K8-L8</f>
+        <v>-2.1749999999999998</v>
+      </c>
+      <c r="O8" s="14">
+        <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
+        <v>-8.3653846153846148E-2</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.1207964601769913</v>
+        <v>0.54374999999999996</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
     </row>
-    <row r="9" spans="1:18" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="35" t="s">
         <v>20</v>
       </c>
@@ -4130,53 +4121,50 @@
       <c r="C9" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="16" t="s">
-        <v>19</v>
+      <c r="D9" s="47" t="s">
+        <v>70</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="G9" s="11">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="H9" s="71"/>
       <c r="I9" s="12">
-        <f>73+3+5+1+7+5+4</f>
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="J9" s="69">
         <f t="shared" si="3"/>
-        <v>0.49</v>
-      </c>
-      <c r="K9" s="11">
-        <v>3000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K9" s="11"/>
       <c r="L9" s="12">
-        <v>1940.925</v>
+        <v>0</v>
       </c>
       <c r="M9" s="70">
         <f t="shared" si="4"/>
-        <v>0.64697499999999997</v>
+        <v>0</v>
       </c>
       <c r="N9" s="12">
         <f t="shared" si="5"/>
-        <v>1059.075</v>
-      </c>
-      <c r="O9" s="14" t="e">
+        <v>0</v>
+      </c>
+      <c r="O9" s="14">
         <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P9" s="71" t="e">
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
-      </c>
-      <c r="P9" s="71">
-        <f t="shared" si="2"/>
-        <v>19.805357142857144</v>
       </c>
       <c r="Q9" s="14"/>
       <c r="R9" s="34"/>
     </row>
-    <row r="10" spans="1:18" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="35" t="s">
         <v>20</v>
       </c>
@@ -4186,54 +4174,50 @@
       <c r="C10" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="16" t="s">
-        <v>19</v>
+      <c r="D10" s="47" t="s">
+        <v>70</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="G10" s="11">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="12">
-        <f>219+20+7</f>
-        <v>246</v>
+        <v>1</v>
       </c>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>0.41</v>
-      </c>
-      <c r="K10" s="11">
-        <v>650</v>
-      </c>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K10" s="11"/>
       <c r="L10" s="12">
-        <f>371+7+20+7</f>
-        <v>405</v>
+        <v>51</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>0.62307692307692308</v>
+        <v>0</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>245</v>
-      </c>
-      <c r="O10" s="14" t="e">
+        <v>-51</v>
+      </c>
+      <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1.9615384615384615</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>1.6463414634146341</v>
+        <v>51</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
     </row>
-    <row r="11" spans="1:18" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A11" s="35" t="s">
         <v>20</v>
       </c>
@@ -4243,54 +4227,50 @@
       <c r="C11" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="16" t="s">
-        <v>19</v>
+      <c r="D11" s="47" t="s">
+        <v>70</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G11" s="11">
         <v>600</v>
       </c>
       <c r="H11" s="71"/>
       <c r="I11" s="12">
-        <f>156+20+20</f>
-        <v>196</v>
+        <v>13</v>
       </c>
       <c r="J11" s="69">
         <f t="shared" si="3"/>
-        <v>0.32666666666666666</v>
-      </c>
-      <c r="K11" s="11">
-        <v>550</v>
-      </c>
+        <v>2.1666666666666667E-2</v>
+      </c>
+      <c r="K11" s="11"/>
       <c r="L11" s="12">
-        <f>199+20+25</f>
-        <v>244</v>
+        <v>14</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="4"/>
-        <v>0.44363636363636366</v>
+        <v>0</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="5"/>
-        <v>306</v>
-      </c>
-      <c r="O11" s="14" t="e">
+        <v>-14</v>
+      </c>
+      <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-0.53846153846153844</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
-        <v>1.2448979591836735</v>
+        <v>1.0769230769230769</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="34"/>
     </row>
-    <row r="12" spans="1:18" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="35" t="s">
         <v>20</v>
       </c>
@@ -4300,54 +4280,50 @@
       <c r="C12" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="16" t="s">
-        <v>19</v>
+      <c r="D12" s="47" t="s">
+        <v>70</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G12" s="11">
         <v>600</v>
       </c>
       <c r="H12" s="71"/>
       <c r="I12" s="12">
-        <f>139+10</f>
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="J12" s="69">
         <f t="shared" si="3"/>
-        <v>0.24833333333333332</v>
-      </c>
-      <c r="K12" s="11">
-        <v>450</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K12" s="11"/>
       <c r="L12" s="12">
-        <f>126+2</f>
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="M12" s="70">
         <f t="shared" si="4"/>
-        <v>0.28444444444444444</v>
+        <v>0</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="5"/>
-        <v>322</v>
-      </c>
-      <c r="O12" s="14" t="e">
+        <v>0</v>
+      </c>
+      <c r="O12" s="14">
         <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P12" s="71" t="e">
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
-      </c>
-      <c r="P12" s="71">
-        <f t="shared" si="2"/>
-        <v>0.85906040268456374</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="34"/>
     </row>
-    <row r="13" spans="1:18" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A13" s="35" t="s">
         <v>20</v>
       </c>
@@ -4357,49 +4333,50 @@
       <c r="C13" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="16" t="s">
-        <v>19</v>
+      <c r="D13" s="47" t="s">
+        <v>70</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="100" t="s">
-        <v>66</v>
+      <c r="F13" s="17" t="s">
+        <v>65</v>
       </c>
       <c r="G13" s="11">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H13" s="71"/>
       <c r="I13" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J13" s="69">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="11">
-        <v>100</v>
-      </c>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K13" s="11"/>
       <c r="L13" s="12">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="M13" s="70">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O13" s="14" t="e">
+        <v>-3</v>
+      </c>
+      <c r="O13" s="14">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P13" s="71"/>
+        <v>-0.11538461538461539</v>
+      </c>
+      <c r="P13" s="71">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
       <c r="Q13" s="14"/>
       <c r="R13" s="34"/>
     </row>
-    <row r="14" spans="1:18" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="35" t="s">
         <v>20</v>
       </c>
@@ -4409,16 +4386,18 @@
       <c r="C14" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="16" t="s">
-        <v>19</v>
+      <c r="D14" s="47" t="s">
+        <v>70</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F14" s="100" t="s">
-        <v>67</v>
-      </c>
-      <c r="G14" s="11"/>
+        <v>66</v>
+      </c>
+      <c r="G14" s="11">
+        <v>0</v>
+      </c>
       <c r="H14" s="71"/>
       <c r="I14" s="12"/>
       <c r="J14" s="69">
@@ -4435,9 +4414,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O14" s="14" t="e">
+      <c r="O14" s="14">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="P14" s="71"/>
       <c r="Q14" s="14"/>
@@ -4453,14 +4432,14 @@
       <c r="C15" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="16" t="s">
-        <v>19</v>
+      <c r="D15" s="47" t="s">
+        <v>70</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="101" t="s">
-        <v>68</v>
+      <c r="F15" s="100" t="s">
+        <v>67</v>
       </c>
       <c r="G15" s="11"/>
       <c r="H15" s="71"/>
@@ -4479,183 +4458,172 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O15" s="14" t="e">
+      <c r="O15" s="14">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="P15" s="71"/>
       <c r="Q15" s="14"/>
       <c r="R15" s="34"/>
     </row>
-    <row r="16" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A16" s="35" t="s">
         <v>20</v>
       </c>
       <c r="B16" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="51" t="s">
+      <c r="C16" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="105" t="s">
+      <c r="D16" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="101" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="69">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="11"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="70">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="14">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="14"/>
+      <c r="R16" s="34"/>
+    </row>
+    <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="106"/>
-      <c r="F16" s="107"/>
-      <c r="G16" s="40">
-        <f>SUM(G4:G13)</f>
-        <v>5000</v>
-      </c>
-      <c r="H16" s="41">
-        <f>SUM(H4:H12)</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="41">
-        <f>SUM(I4:I12)</f>
-        <v>1791</v>
-      </c>
-      <c r="J16" s="75">
+      <c r="E17" s="106"/>
+      <c r="F17" s="107"/>
+      <c r="G17" s="40">
+        <f>SUM(G4:G14)</f>
+        <v>5600</v>
+      </c>
+      <c r="H17" s="41">
+        <f>SUM(H4:H13)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="41">
+        <f>SUM(I4:I13)</f>
+        <v>41</v>
+      </c>
+      <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>0.35820000000000002</v>
-      </c>
-      <c r="K16" s="76">
-        <f>SUM(K4:K15)</f>
-        <v>7275</v>
-      </c>
-      <c r="L16" s="77">
-        <f>SUM(L4:L15)</f>
-        <v>3897.1750000000002</v>
-      </c>
-      <c r="M16" s="78">
+        <v>7.3214285714285716E-3</v>
+      </c>
+      <c r="K17" s="76">
+        <f>SUM(K4:K16)</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="77">
+        <f>SUM(L4:L16)</f>
+        <v>93.224999999999994</v>
+      </c>
+      <c r="M17" s="78">
         <f t="shared" si="4"/>
-        <v>0.53569415807560139</v>
-      </c>
-      <c r="N16" s="77">
+        <v>0</v>
+      </c>
+      <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>3377.8249999999998</v>
-      </c>
-      <c r="O16" s="79" t="e">
+        <v>-93.224999999999994</v>
+      </c>
+      <c r="O17" s="79">
         <f t="shared" si="6"/>
+        <v>-3.585576923076923</v>
+      </c>
+      <c r="P17" s="80">
+        <f>L17/I17</f>
+        <v>2.2737804878048777</v>
+      </c>
+      <c r="Q17" s="43" t="e">
+        <f>AVERAGE(Q4:Q16)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P16" s="80">
-        <f>L16/I16</f>
-        <v>2.1759771077610273</v>
-      </c>
-      <c r="Q16" s="43" t="e">
-        <f>AVERAGE(Q4:Q15)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R16" s="44"/>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A17" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="16" t="s">
+      <c r="R17" s="44"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A18" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D18" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E18" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="95" t="s">
+      <c r="F18" s="95" t="s">
         <v>56</v>
       </c>
-      <c r="G17" s="7">
-        <v>1</v>
-      </c>
-      <c r="H17" s="96"/>
-      <c r="I17" s="8">
-        <v>1</v>
-      </c>
-      <c r="J17" s="81">
+      <c r="G18" s="7">
+        <v>1</v>
+      </c>
+      <c r="H18" s="96"/>
+      <c r="I18" s="8">
+        <v>1</v>
+      </c>
+      <c r="J18" s="81">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="K17" s="7">
+      <c r="K18" s="7">
         <v>600</v>
       </c>
-      <c r="L17" s="8">
+      <c r="L18" s="8">
         <v>174.3</v>
       </c>
-      <c r="M17" s="82">
+      <c r="M18" s="82">
         <f t="shared" si="4"/>
         <v>0.29050000000000004</v>
       </c>
-      <c r="N17" s="8">
+      <c r="N18" s="8">
         <f t="shared" si="5"/>
         <v>425.7</v>
       </c>
-      <c r="O17" s="10" t="e">
+      <c r="O18" s="10">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P17" s="96">
-        <f t="shared" ref="P17:P21" si="7">L17/I17</f>
+        <v>16.373076923076923</v>
+      </c>
+      <c r="P18" s="96">
+        <f t="shared" ref="P18:P22" si="7">L18/I18</f>
         <v>174.3</v>
       </c>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="34"/>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A18" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="97" t="s">
-        <v>28</v>
-      </c>
-      <c r="G18" s="11">
-        <v>1</v>
-      </c>
-      <c r="H18" s="71"/>
-      <c r="I18" s="12">
-        <v>1</v>
-      </c>
-      <c r="J18" s="69">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="K18" s="11">
-        <v>600</v>
-      </c>
-      <c r="L18" s="12">
-        <v>174.3</v>
-      </c>
-      <c r="M18" s="70">
-        <f t="shared" si="4"/>
-        <v>0.29050000000000004</v>
-      </c>
-      <c r="N18" s="12">
-        <f t="shared" si="5"/>
-        <v>425.7</v>
-      </c>
-      <c r="O18" s="14" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P18" s="71">
-        <f t="shared" si="7"/>
-        <v>174.3</v>
-      </c>
-      <c r="Q18" s="14"/>
+      <c r="Q18" s="10"/>
       <c r="R18" s="34"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.35">
@@ -4675,7 +4643,7 @@
         <v>27</v>
       </c>
       <c r="F19" s="97" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G19" s="11">
         <v>1</v>
@@ -4702,9 +4670,9 @@
         <f t="shared" si="5"/>
         <v>425.7</v>
       </c>
-      <c r="O19" s="14" t="e">
+      <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>16.373076923076923</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4730,7 +4698,7 @@
         <v>27</v>
       </c>
       <c r="F20" s="97" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G20" s="11">
         <v>1</v>
@@ -4757,9 +4725,9 @@
         <f t="shared" si="5"/>
         <v>425.7</v>
       </c>
-      <c r="O20" s="14" t="e">
+      <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>16.373076923076923</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4768,7 +4736,7 @@
       <c r="Q20" s="14"/>
       <c r="R20" s="34"/>
     </row>
-    <row r="21" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A21" s="35" t="s">
         <v>20</v>
       </c>
@@ -4778,51 +4746,49 @@
       <c r="C21" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E21" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="F21" s="98" t="s">
-        <v>38</v>
-      </c>
-      <c r="G21" s="36">
-        <v>1</v>
-      </c>
-      <c r="H21" s="74"/>
-      <c r="I21" s="37">
-        <v>1</v>
-      </c>
-      <c r="J21" s="72">
+      <c r="F21" s="97" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" s="11">
+        <v>1</v>
+      </c>
+      <c r="H21" s="71"/>
+      <c r="I21" s="12">
+        <v>1</v>
+      </c>
+      <c r="J21" s="69">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="K21" s="92">
+      <c r="K21" s="11">
         <v>600</v>
       </c>
-      <c r="L21" s="93">
+      <c r="L21" s="12">
         <v>174.3</v>
       </c>
-      <c r="M21" s="73">
+      <c r="M21" s="70">
         <f t="shared" si="4"/>
         <v>0.29050000000000004</v>
       </c>
-      <c r="N21" s="93">
+      <c r="N21" s="12">
         <f t="shared" si="5"/>
         <v>425.7</v>
       </c>
-      <c r="O21" s="94" t="e">
+      <c r="O21" s="14">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P21" s="74">
+        <v>16.373076923076923</v>
+      </c>
+      <c r="P21" s="71">
         <f t="shared" si="7"/>
         <v>174.3</v>
       </c>
-      <c r="Q21" s="39">
-        <v>1</v>
-      </c>
+      <c r="Q21" s="14"/>
       <c r="R21" s="34"/>
     </row>
     <row r="22" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4832,166 +4798,168 @@
       <c r="B22" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="51" t="s">
+      <c r="C22" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="105" t="s">
+      <c r="D22" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="98" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" s="36">
+        <v>1</v>
+      </c>
+      <c r="H22" s="74"/>
+      <c r="I22" s="37">
+        <v>1</v>
+      </c>
+      <c r="J22" s="72">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="K22" s="92">
+        <v>600</v>
+      </c>
+      <c r="L22" s="93">
+        <v>174.3</v>
+      </c>
+      <c r="M22" s="73">
+        <f t="shared" si="4"/>
+        <v>0.29050000000000004</v>
+      </c>
+      <c r="N22" s="93">
+        <f t="shared" si="5"/>
+        <v>425.7</v>
+      </c>
+      <c r="O22" s="94">
+        <f t="shared" si="6"/>
+        <v>16.373076923076923</v>
+      </c>
+      <c r="P22" s="74">
+        <f t="shared" si="7"/>
+        <v>174.3</v>
+      </c>
+      <c r="Q22" s="39">
+        <v>1</v>
+      </c>
+      <c r="R22" s="34"/>
+    </row>
+    <row r="23" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="106"/>
-      <c r="F22" s="107"/>
-      <c r="G22" s="40">
-        <f>SUM(G17:G21)</f>
+      <c r="E23" s="106"/>
+      <c r="F23" s="107"/>
+      <c r="G23" s="40">
+        <f>SUM(G18:G22)</f>
         <v>5</v>
       </c>
-      <c r="H22" s="41">
-        <f t="shared" ref="H22:I22" si="8">SUM(H17:H21)</f>
-        <v>0</v>
-      </c>
-      <c r="I22" s="41">
+      <c r="H23" s="41">
+        <f t="shared" ref="H23:I23" si="8">SUM(H18:H22)</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="41">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="J22" s="75">
+      <c r="J23" s="75">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="K22" s="76">
+      <c r="K23" s="76">
         <v>600</v>
       </c>
-      <c r="L22" s="77">
+      <c r="L23" s="77">
         <v>174.3</v>
       </c>
-      <c r="M22" s="78">
+      <c r="M23" s="78">
         <f t="shared" si="4"/>
         <v>0.29050000000000004</v>
       </c>
-      <c r="N22" s="77">
+      <c r="N23" s="77">
         <f t="shared" si="5"/>
         <v>425.7</v>
       </c>
-      <c r="O22" s="79" t="e">
+      <c r="O23" s="79">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P22" s="80">
-        <f>L22/I22</f>
+        <v>16.373076923076923</v>
+      </c>
+      <c r="P23" s="80">
+        <f>L23/I23</f>
         <v>34.86</v>
       </c>
-      <c r="Q22" s="43">
-        <f>AVERAGE(Q17:Q21)</f>
-        <v>1</v>
-      </c>
-      <c r="R22" s="44"/>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A23" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="16" t="s">
+      <c r="Q23" s="43">
+        <f>AVERAGE(Q18:Q22)</f>
+        <v>1</v>
+      </c>
+      <c r="R23" s="44"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A24" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D24" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E24" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="95" t="s">
+      <c r="F24" s="95" t="s">
         <v>39</v>
       </c>
-      <c r="G23" s="7">
-        <v>1</v>
-      </c>
-      <c r="H23" s="96"/>
-      <c r="I23" s="8">
-        <v>1</v>
-      </c>
-      <c r="J23" s="81">
+      <c r="G24" s="7">
+        <v>1</v>
+      </c>
+      <c r="H24" s="96"/>
+      <c r="I24" s="8">
+        <v>1</v>
+      </c>
+      <c r="J24" s="81">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="K23" s="7">
+      <c r="K24" s="7">
         <v>600</v>
       </c>
-      <c r="L23" s="8">
+      <c r="L24" s="8">
         <v>174.3</v>
       </c>
-      <c r="M23" s="82">
+      <c r="M24" s="82">
         <f t="shared" si="4"/>
         <v>0.29050000000000004</v>
       </c>
-      <c r="N23" s="8">
+      <c r="N24" s="8">
         <f t="shared" si="5"/>
         <v>425.7</v>
       </c>
-      <c r="O23" s="10" t="e">
+      <c r="O24" s="10">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P23" s="96">
-        <f t="shared" ref="P23:P26" si="9">L23/I23</f>
+        <v>16.373076923076923</v>
+      </c>
+      <c r="P24" s="96">
+        <f t="shared" ref="P24:P27" si="9">L24/I24</f>
         <v>174.3</v>
       </c>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="34"/>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A24" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="97" t="s">
-        <v>57</v>
-      </c>
-      <c r="G24" s="11">
-        <v>1</v>
-      </c>
-      <c r="H24" s="71"/>
-      <c r="I24" s="12">
-        <v>1</v>
-      </c>
-      <c r="J24" s="69">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="K24" s="11">
-        <v>600</v>
-      </c>
-      <c r="L24" s="12">
-        <v>174.3</v>
-      </c>
-      <c r="M24" s="70">
-        <f t="shared" si="4"/>
-        <v>0.29050000000000004</v>
-      </c>
-      <c r="N24" s="12">
-        <f t="shared" si="5"/>
-        <v>425.7</v>
-      </c>
-      <c r="O24" s="14" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P24" s="71">
-        <f t="shared" si="9"/>
-        <v>174.3</v>
-      </c>
-      <c r="Q24" s="14"/>
+      <c r="Q24" s="10"/>
       <c r="R24" s="34"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.35">
@@ -5011,7 +4979,7 @@
         <v>32</v>
       </c>
       <c r="F25" s="97" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="G25" s="11">
         <v>1</v>
@@ -5038,9 +5006,9 @@
         <f t="shared" si="5"/>
         <v>425.7</v>
       </c>
-      <c r="O25" s="14" t="e">
+      <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>16.373076923076923</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5049,7 +5017,7 @@
       <c r="Q25" s="14"/>
       <c r="R25" s="34"/>
     </row>
-    <row r="26" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A26" s="35" t="s">
         <v>20</v>
       </c>
@@ -5059,169 +5027,224 @@
       <c r="C26" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="E26" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F26" s="98" t="s">
-        <v>58</v>
-      </c>
-      <c r="G26" s="36">
-        <v>1</v>
-      </c>
-      <c r="H26" s="74"/>
-      <c r="I26" s="37">
-        <v>1</v>
-      </c>
-      <c r="J26" s="72">
+      <c r="F26" s="97" t="s">
+        <v>40</v>
+      </c>
+      <c r="G26" s="11">
+        <v>1</v>
+      </c>
+      <c r="H26" s="71"/>
+      <c r="I26" s="12">
+        <v>1</v>
+      </c>
+      <c r="J26" s="69">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="K26" s="92">
+      <c r="K26" s="11">
         <v>600</v>
       </c>
-      <c r="L26" s="93">
+      <c r="L26" s="12">
         <v>174.3</v>
       </c>
-      <c r="M26" s="73">
+      <c r="M26" s="70">
         <f t="shared" si="4"/>
         <v>0.29050000000000004</v>
       </c>
-      <c r="N26" s="93">
+      <c r="N26" s="12">
         <f t="shared" si="5"/>
         <v>425.7</v>
       </c>
-      <c r="O26" s="94" t="e">
+      <c r="O26" s="14">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P26" s="74">
+        <v>16.373076923076923</v>
+      </c>
+      <c r="P26" s="71">
         <f t="shared" si="9"/>
         <v>174.3</v>
       </c>
-      <c r="Q26" s="39">
-        <v>1</v>
-      </c>
+      <c r="Q26" s="14"/>
       <c r="R26" s="34"/>
     </row>
     <row r="27" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="54" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="55" t="s">
+      <c r="B27" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="105" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="106"/>
-      <c r="F27" s="107"/>
-      <c r="G27" s="40">
-        <f>SUM(G23:G26)</f>
-        <v>4</v>
-      </c>
-      <c r="H27" s="80"/>
-      <c r="I27" s="41">
-        <f t="shared" ref="I27" si="10">SUM(I23:I26)</f>
-        <v>4</v>
-      </c>
-      <c r="J27" s="75">
+      <c r="D27" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" s="98" t="s">
+        <v>58</v>
+      </c>
+      <c r="G27" s="36">
+        <v>1</v>
+      </c>
+      <c r="H27" s="74"/>
+      <c r="I27" s="37">
+        <v>1</v>
+      </c>
+      <c r="J27" s="72">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="K27" s="76">
+      <c r="K27" s="92">
         <v>600</v>
       </c>
-      <c r="L27" s="77">
+      <c r="L27" s="93">
         <v>174.3</v>
       </c>
-      <c r="M27" s="78">
+      <c r="M27" s="73">
         <f t="shared" si="4"/>
         <v>0.29050000000000004</v>
       </c>
-      <c r="N27" s="77">
+      <c r="N27" s="93">
         <f t="shared" si="5"/>
         <v>425.7</v>
       </c>
-      <c r="O27" s="79" t="e">
+      <c r="O27" s="94">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P27" s="80">
-        <f>L27/I27</f>
-        <v>43.575000000000003</v>
-      </c>
-      <c r="Q27" s="43">
-        <f>AVERAGE(Q23:Q26)</f>
-        <v>1</v>
-      </c>
-      <c r="R27" s="44"/>
+        <v>16.373076923076923</v>
+      </c>
+      <c r="P27" s="74">
+        <f t="shared" si="9"/>
+        <v>174.3</v>
+      </c>
+      <c r="Q27" s="39">
+        <v>1</v>
+      </c>
+      <c r="R27" s="34"/>
     </row>
     <row r="28" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="45" t="s">
-        <v>20</v>
-      </c>
-      <c r="B28" s="56" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" s="57"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="20">
-        <f>+G27+G22+G16</f>
-        <v>5009</v>
-      </c>
-      <c r="H28" s="21">
-        <f t="shared" ref="H28:I28" si="11">+H27+H22+H16</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="21">
-        <f t="shared" si="11"/>
-        <v>1800</v>
-      </c>
-      <c r="J28" s="83">
+      <c r="A28" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" s="54" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="105" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="106"/>
+      <c r="F28" s="107"/>
+      <c r="G28" s="40">
+        <f>SUM(G24:G27)</f>
+        <v>4</v>
+      </c>
+      <c r="H28" s="80"/>
+      <c r="I28" s="41">
+        <f t="shared" ref="I28" si="10">SUM(I24:I27)</f>
+        <v>4</v>
+      </c>
+      <c r="J28" s="75">
         <f t="shared" si="3"/>
-        <v>0.35935316430425235</v>
-      </c>
-      <c r="K28" s="84">
+        <v>1</v>
+      </c>
+      <c r="K28" s="76">
         <v>600</v>
       </c>
-      <c r="L28" s="85">
+      <c r="L28" s="77">
         <v>174.3</v>
       </c>
-      <c r="M28" s="86">
+      <c r="M28" s="78">
         <f t="shared" si="4"/>
         <v>0.29050000000000004</v>
       </c>
-      <c r="N28" s="85">
+      <c r="N28" s="77">
         <f t="shared" si="5"/>
         <v>425.7</v>
       </c>
-      <c r="O28" s="87" t="e">
+      <c r="O28" s="79">
         <f t="shared" si="6"/>
+        <v>16.373076923076923</v>
+      </c>
+      <c r="P28" s="80">
+        <f>L28/I28</f>
+        <v>43.575000000000003</v>
+      </c>
+      <c r="Q28" s="43">
+        <f>AVERAGE(Q24:Q27)</f>
+        <v>1</v>
+      </c>
+      <c r="R28" s="44"/>
+    </row>
+    <row r="29" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="56" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="20">
+        <f>+G28+G23+G17</f>
+        <v>5609</v>
+      </c>
+      <c r="H29" s="21">
+        <f t="shared" ref="H29:I29" si="11">+H28+H23+H17</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="21">
+        <f t="shared" si="11"/>
+        <v>50</v>
+      </c>
+      <c r="J29" s="83">
+        <f t="shared" si="3"/>
+        <v>8.9142449634515963E-3</v>
+      </c>
+      <c r="K29" s="84">
+        <v>600</v>
+      </c>
+      <c r="L29" s="85">
+        <v>174.3</v>
+      </c>
+      <c r="M29" s="86">
+        <f t="shared" si="4"/>
+        <v>0.29050000000000004</v>
+      </c>
+      <c r="N29" s="85">
+        <f t="shared" si="5"/>
+        <v>425.7</v>
+      </c>
+      <c r="O29" s="87">
+        <f t="shared" si="6"/>
+        <v>16.373076923076923</v>
+      </c>
+      <c r="P29" s="88">
+        <f>L29/I29</f>
+        <v>3.4860000000000002</v>
+      </c>
+      <c r="Q29" s="23" t="e">
+        <f>AVERAGE(Q28,Q17,Q23)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P28" s="88">
-        <f>L28/I28</f>
-        <v>9.6833333333333341E-2</v>
-      </c>
-      <c r="Q28" s="23" t="e">
-        <f>AVERAGE(Q27,Q16,Q22)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R28" s="34"/>
+      <c r="R29" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D28:F28"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="G2:J2"/>
     <mergeCell ref="K2:O2"/>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CEC02E9-FC1C-4E4A-8248-41A1EAB59399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB00E23-06DB-4D86-BE8B-86336C76FCE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="75">
   <si>
     <t>Booking</t>
   </si>
@@ -187,9 +187,6 @@
     <t>Productive Shop</t>
   </si>
   <si>
-    <t>Yasir</t>
-  </si>
-  <si>
     <t>Jabbar</t>
   </si>
   <si>
@@ -217,12 +214,6 @@
     <t xml:space="preserve">Qasim Khan </t>
   </si>
   <si>
-    <t>Kasoor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nabeel Traders </t>
-  </si>
-  <si>
     <t xml:space="preserve">Yasir </t>
   </si>
   <si>
@@ -239,6 +230,27 @@
   </si>
   <si>
     <t xml:space="preserve">Qamar Ijaz </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zeshan </t>
+  </si>
+  <si>
+    <t>Umair Rehman</t>
+  </si>
+  <si>
+    <t>Shakoor Husain</t>
+  </si>
+  <si>
+    <t>Vacant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aqeel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qasim </t>
+  </si>
+  <si>
+    <t>SD</t>
   </si>
 </sst>
 </file>
@@ -1562,7 +1574,7 @@
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="89">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="G2" s="114" t="s">
         <v>2</v>
@@ -1681,7 +1693,7 @@
         <v>22</v>
       </c>
       <c r="F4" s="48" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="G4" s="30">
         <v>50</v>
@@ -1690,50 +1702,50 @@
         <v>40</v>
       </c>
       <c r="I4" s="12">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J4" s="32">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.18</v>
+        <v>0.34</v>
       </c>
       <c r="K4" s="30">
         <v>40</v>
       </c>
       <c r="L4" s="12">
-        <v>10.5</v>
+        <v>13.6</v>
       </c>
       <c r="M4" s="32">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.26250000000000001</v>
+        <v>0.33999999999999997</v>
       </c>
       <c r="N4" s="90">
         <f>IFERROR(L4/I4,0)</f>
-        <v>1.1666666666666667</v>
+        <v>0.79999999999999993</v>
       </c>
       <c r="O4" s="33"/>
       <c r="P4" s="30">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q4" s="31">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R4" s="32">
         <f>IFERROR(Q4/P4,0)</f>
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="S4" s="30">
-        <v>60</v>
+        <v>9.375</v>
       </c>
       <c r="T4" s="31">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="U4" s="32">
         <f>IFERROR(T4/S4,0)</f>
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="V4" s="90">
         <f>IFERROR(T4/Q4,0)</f>
-        <v>60</v>
+        <v>1.8</v>
       </c>
       <c r="W4" s="33"/>
       <c r="X4" s="34"/>
@@ -1764,50 +1776,50 @@
         <v>45</v>
       </c>
       <c r="I5" s="12">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="J5" s="13">
         <f t="shared" ref="J5:J32" si="0">IFERROR(I5/G5,0)</f>
-        <v>0.54</v>
+        <v>0.12</v>
       </c>
       <c r="K5" s="11">
         <v>30</v>
       </c>
       <c r="L5" s="12">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M5" s="13">
         <f t="shared" ref="M5:M32" si="1">IFERROR(L5/K5,0)</f>
-        <v>0.33333333333333331</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="N5" s="11">
         <f t="shared" ref="N5:N32" si="2">IFERROR(L5/I5,0)</f>
-        <v>0.37037037037037035</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="11">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="Q5" s="12">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="R5" s="13">
         <f t="shared" ref="R5:R32" si="3">IFERROR(Q5/P5,0)</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="S5" s="11">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="T5" s="12">
-        <v>8</v>
+        <v>9.9</v>
       </c>
       <c r="U5" s="13">
         <f t="shared" ref="U5:U32" si="4">IFERROR(T5/S5,0)</f>
-        <v>0.84210526315789469</v>
+        <v>0.9</v>
       </c>
       <c r="V5" s="11">
         <f t="shared" ref="V5:V32" si="5">IFERROR(T5/Q5,0)</f>
-        <v>0.44444444444444442</v>
+        <v>2.4750000000000001</v>
       </c>
       <c r="W5" s="14"/>
       <c r="X5" s="34"/>
@@ -1829,7 +1841,7 @@
         <v>22</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G6" s="11">
         <v>50</v>
@@ -1838,50 +1850,50 @@
         <v>40</v>
       </c>
       <c r="I6" s="12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J6" s="13">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="K6" s="11">
         <v>25</v>
       </c>
       <c r="L6" s="12">
-        <v>15.25</v>
+        <v>12.025</v>
       </c>
       <c r="M6" s="13">
         <f t="shared" si="1"/>
-        <v>0.61</v>
+        <v>0.48100000000000004</v>
       </c>
       <c r="N6" s="11">
         <f t="shared" si="2"/>
-        <v>2.1785714285714284</v>
+        <v>1.503125</v>
       </c>
       <c r="O6" s="14"/>
       <c r="P6" s="11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q6" s="12">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R6" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="S6" s="11">
-        <v>16.8</v>
+        <v>6.5</v>
       </c>
       <c r="T6" s="12">
-        <v>14.8</v>
+        <v>6.5</v>
       </c>
       <c r="U6" s="13">
         <f t="shared" si="4"/>
-        <v>0.88095238095238093</v>
+        <v>1</v>
       </c>
       <c r="V6" s="11">
         <f t="shared" si="5"/>
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="W6" s="14"/>
       <c r="X6" s="34"/>
@@ -1903,7 +1915,7 @@
         <v>22</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G7" s="11">
         <v>50</v>
@@ -1912,48 +1924,50 @@
         <v>45</v>
       </c>
       <c r="I7" s="12">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>0.04</v>
       </c>
       <c r="K7" s="11">
         <v>30</v>
       </c>
       <c r="L7" s="12">
-        <v>10.1</v>
+        <v>1.4</v>
       </c>
       <c r="M7" s="13">
         <f t="shared" si="1"/>
-        <v>0.33666666666666667</v>
+        <v>4.6666666666666662E-2</v>
       </c>
       <c r="N7" s="11">
         <f t="shared" si="2"/>
-        <v>1.1222222222222222</v>
+        <v>0.7</v>
       </c>
       <c r="O7" s="14"/>
       <c r="P7" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="12"/>
+        <v>4</v>
+      </c>
+      <c r="Q7" s="12">
+        <v>4</v>
+      </c>
       <c r="R7" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" s="11">
-        <v>2</v>
+        <v>6.3</v>
       </c>
       <c r="T7" s="12">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="U7" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1.575</v>
       </c>
       <c r="W7" s="14"/>
       <c r="X7" s="34"/>
@@ -1975,7 +1989,7 @@
         <v>22</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G8" s="11">
         <v>50</v>
@@ -1984,50 +1998,50 @@
         <v>40</v>
       </c>
       <c r="I8" s="12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="K8" s="11">
         <v>20</v>
       </c>
       <c r="L8" s="12">
-        <v>7.25</v>
+        <v>6.3</v>
       </c>
       <c r="M8" s="13">
         <f t="shared" si="1"/>
-        <v>0.36249999999999999</v>
+        <v>0.315</v>
       </c>
       <c r="N8" s="11">
         <f t="shared" si="2"/>
-        <v>1.2083333333333333</v>
+        <v>1.26</v>
       </c>
       <c r="O8" s="14"/>
       <c r="P8" s="11">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q8" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R8" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="S8" s="11">
-        <v>6.55</v>
+        <v>5.7750000000000004</v>
       </c>
       <c r="T8" s="12">
-        <v>5.65</v>
+        <v>5.4749999999999996</v>
       </c>
       <c r="U8" s="13">
         <f t="shared" si="4"/>
-        <v>0.86259541984732835</v>
+        <v>0.94805194805194792</v>
       </c>
       <c r="V8" s="11">
         <f t="shared" si="5"/>
-        <v>1.8833333333333335</v>
+        <v>1.095</v>
       </c>
       <c r="W8" s="14"/>
       <c r="X8" s="34"/>
@@ -2049,59 +2063,57 @@
         <v>22</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="G9" s="11">
         <v>50</v>
       </c>
       <c r="H9" s="71">
-        <v>10</v>
-      </c>
-      <c r="I9" s="12">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I9" s="12"/>
       <c r="J9" s="13">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="K9" s="11">
         <v>80</v>
       </c>
       <c r="L9" s="12">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="M9" s="13">
         <f t="shared" si="1"/>
-        <v>1.3625</v>
+        <v>0</v>
       </c>
       <c r="N9" s="11">
         <f t="shared" si="2"/>
-        <v>18.166666666666668</v>
+        <v>0</v>
       </c>
       <c r="O9" s="14"/>
       <c r="P9" s="11">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="12">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R9" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" s="11">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="T9" s="12">
-        <v>100.5</v>
+        <v>0</v>
       </c>
       <c r="U9" s="13">
         <f t="shared" si="4"/>
-        <v>0.81048387096774188</v>
+        <v>0</v>
       </c>
       <c r="V9" s="11">
         <f t="shared" si="5"/>
-        <v>14.357142857142858</v>
+        <v>0</v>
       </c>
       <c r="W9" s="14"/>
       <c r="X9" s="34"/>
@@ -2123,59 +2135,59 @@
         <v>22</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G10" s="11">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H10" s="71">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="I10" s="12">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J10" s="13">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="K10" s="11">
         <v>20</v>
       </c>
       <c r="L10" s="12">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="M10" s="13">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>2.25</v>
       </c>
       <c r="N10" s="11">
         <f t="shared" si="2"/>
-        <v>1.2</v>
+        <v>15</v>
       </c>
       <c r="O10" s="14"/>
       <c r="P10" s="11">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q10" s="12">
         <v>7</v>
       </c>
       <c r="R10" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="S10" s="11">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="T10" s="12">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="U10" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.88235294117647056</v>
       </c>
       <c r="V10" s="11">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>8.5714285714285712</v>
       </c>
       <c r="W10" s="14"/>
       <c r="X10" s="34"/>
@@ -2197,7 +2209,7 @@
         <v>22</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="G11" s="11">
         <v>50</v>
@@ -2206,11 +2218,11 @@
         <v>40</v>
       </c>
       <c r="I11" s="12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J11" s="13">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="K11" s="11">
         <v>20</v>
@@ -2224,24 +2236,24 @@
       </c>
       <c r="N11" s="11">
         <f t="shared" si="2"/>
-        <v>1.4285714285714286</v>
+        <v>1.1111111111111112</v>
       </c>
       <c r="O11" s="14"/>
       <c r="P11" s="11">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="Q11" s="12">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="R11" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="S11" s="11">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="T11" s="12">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="U11" s="13">
         <f t="shared" si="4"/>
@@ -2249,7 +2261,7 @@
       </c>
       <c r="V11" s="11">
         <f t="shared" si="5"/>
-        <v>1.25</v>
+        <v>1.0769230769230769</v>
       </c>
       <c r="W11" s="14"/>
       <c r="X11" s="34"/>
@@ -2271,7 +2283,7 @@
         <v>22</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="G12" s="11">
         <v>50</v>
@@ -2280,50 +2292,50 @@
         <v>40</v>
       </c>
       <c r="I12" s="12">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J12" s="13">
         <f t="shared" si="0"/>
-        <v>0.36</v>
+        <v>0.18</v>
       </c>
       <c r="K12" s="11">
         <v>30</v>
       </c>
       <c r="L12" s="12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M12" s="13">
         <f t="shared" si="1"/>
-        <v>0.3</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="N12" s="11">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="O12" s="14"/>
       <c r="P12" s="11">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q12" s="12">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R12" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="S12" s="11">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="T12" s="12">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U12" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.8125</v>
       </c>
       <c r="V12" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1.1818181818181819</v>
       </c>
       <c r="W12" s="14"/>
       <c r="X12" s="34"/>
@@ -2345,7 +2357,7 @@
         <v>22</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G13" s="11"/>
       <c r="H13" s="71"/>
@@ -2365,21 +2377,29 @@
         <v>0</v>
       </c>
       <c r="O13" s="14"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="12"/>
+      <c r="P13" s="11">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="12">
+        <v>3</v>
+      </c>
       <c r="R13" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S13" s="11"/>
-      <c r="T13" s="12"/>
+        <v>1</v>
+      </c>
+      <c r="S13" s="11">
+        <v>3</v>
+      </c>
+      <c r="T13" s="12">
+        <v>3</v>
+      </c>
       <c r="U13" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" s="14"/>
       <c r="X13" s="34"/>
@@ -2401,7 +2421,7 @@
         <v>22</v>
       </c>
       <c r="F14" s="49" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="71"/>
@@ -2751,19 +2771,19 @@
       <c r="F20" s="104"/>
       <c r="G20" s="40">
         <f>SUM(G4:G19)</f>
-        <v>450</v>
+        <v>410</v>
       </c>
       <c r="H20" s="41">
         <f>SUM(H4:H19)</f>
-        <v>345</v>
+        <v>300</v>
       </c>
       <c r="I20" s="41">
         <f>SUM(I4:I19)</f>
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="J20" s="42">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0.14390243902439023</v>
       </c>
       <c r="K20" s="40">
         <f>SUM(K4:K12)</f>
@@ -2771,15 +2791,15 @@
       </c>
       <c r="L20" s="40">
         <f>SUM(L4:L12)</f>
-        <v>193.1</v>
+        <v>101.32499999999999</v>
       </c>
       <c r="M20" s="42">
         <f t="shared" si="1"/>
-        <v>0.65457627118644068</v>
+        <v>0.34347457627118638</v>
       </c>
       <c r="N20" s="40">
         <f t="shared" si="2"/>
-        <v>1.9505050505050505</v>
+        <v>1.7173728813559319</v>
       </c>
       <c r="O20" s="43">
         <f>AVERAGE(O4:O19)</f>
@@ -2787,31 +2807,31 @@
       </c>
       <c r="P20" s="40">
         <f>SUM(P4:P19)</f>
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="Q20" s="41">
         <f>SUM(Q4:Q19)</f>
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="R20" s="42">
         <f t="shared" si="3"/>
-        <v>0.98461538461538467</v>
+        <v>0.83823529411764708</v>
       </c>
       <c r="S20" s="40">
         <f>SUM(S4:S19)</f>
-        <v>250.85</v>
+        <v>139.94999999999999</v>
       </c>
       <c r="T20" s="41">
         <f>SUM(T4:T19)</f>
-        <v>220.95</v>
+        <v>127.175</v>
       </c>
       <c r="U20" s="42">
         <f t="shared" si="4"/>
-        <v>0.88080526210882992</v>
+        <v>0.90871739907109683</v>
       </c>
       <c r="V20" s="40">
         <f t="shared" si="5"/>
-        <v>3.4523437499999998</v>
+        <v>2.231140350877193</v>
       </c>
       <c r="W20" s="43">
         <f>AVERAGE(W4:W19)</f>
@@ -2836,7 +2856,7 @@
         <v>27</v>
       </c>
       <c r="F21" s="52" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G21" s="7">
         <v>1</v>
@@ -3347,7 +3367,7 @@
         <v>32</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G28" s="11">
         <v>1</v>
@@ -3487,7 +3507,7 @@
         <v>32</v>
       </c>
       <c r="F30" s="53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G30" s="36">
         <v>1</v>
@@ -3636,19 +3656,19 @@
       <c r="F32" s="57"/>
       <c r="G32" s="20">
         <f>+G31+G26+G20</f>
-        <v>459</v>
+        <v>419</v>
       </c>
       <c r="H32" s="21">
         <f t="shared" ref="H32:I32" si="12">+H31+H26+H20</f>
-        <v>345</v>
+        <v>300</v>
       </c>
       <c r="I32" s="21">
         <f t="shared" si="12"/>
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="J32" s="22">
         <f t="shared" si="0"/>
-        <v>0.21568627450980393</v>
+        <v>0.14081145584725538</v>
       </c>
       <c r="K32" s="20">
         <v>1</v>
@@ -3662,7 +3682,7 @@
       </c>
       <c r="N32" s="20">
         <f t="shared" si="2"/>
-        <v>1.0101010101010102E-2</v>
+        <v>1.6949152542372881E-2</v>
       </c>
       <c r="O32" s="23">
         <f>AVERAGE(O31,O20,O26)</f>
@@ -3670,31 +3690,31 @@
       </c>
       <c r="P32" s="20">
         <f>+P31+P26+P20</f>
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="Q32" s="21">
         <f t="shared" ref="Q32" si="13">+Q31+Q26+Q20</f>
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="R32" s="22">
         <f t="shared" si="3"/>
-        <v>0.98648648648648651</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S32" s="20">
         <f>+S31+S26+S20</f>
-        <v>259.85000000000002</v>
+        <v>148.94999999999999</v>
       </c>
       <c r="T32" s="21">
         <f t="shared" ref="T32" si="14">+T31+T26+T20</f>
-        <v>229.95</v>
+        <v>136.17500000000001</v>
       </c>
       <c r="U32" s="22">
         <f t="shared" si="4"/>
-        <v>0.88493361554743111</v>
+        <v>0.9142329640819068</v>
       </c>
       <c r="V32" s="20">
         <f t="shared" si="5"/>
-        <v>3.15</v>
+        <v>2.063257575757576</v>
       </c>
       <c r="W32" s="23">
         <f>AVERAGE(W31,W20,W26)</f>
@@ -3759,18 +3779,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>3.7037037037037035E-2</v>
+        <v>7.407407407407407E-2</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" s="89">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="G2" s="114" t="s">
         <v>34</v>
@@ -3857,7 +3877,7 @@
         <v>21</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E4" s="47" t="s">
         <v>22</v>
@@ -3870,15 +3890,16 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <v>8</v>
+        <f>8+5</f>
+        <v>13</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>1.3333333333333334E-2</v>
+        <v>2.1666666666666667E-2</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="8">
-        <v>7.5</v>
+        <v>16.5</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
@@ -3886,15 +3907,15 @@
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>-7.5</v>
+        <v>-16.5</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>-0.28846153846153844</v>
+        <v>-0.66</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P13" si="2">L4/I4</f>
-        <v>0.9375</v>
+        <v>1.2692307692307692</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3910,7 +3931,7 @@
         <v>21</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>22</v>
@@ -3923,15 +3944,16 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <v>2</v>
+        <f>2+4</f>
+        <v>6</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J29" si="3">IFERROR(I5/G5,0)</f>
-        <v>3.3333333333333335E-3</v>
+        <v>0.01</v>
       </c>
       <c r="K5" s="11"/>
       <c r="L5" s="12">
-        <v>6</v>
+        <v>15.9</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M29" si="4">IFERROR(L5/K5,0)</f>
@@ -3939,15 +3961,15 @@
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>-6</v>
+        <v>-15.9</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>-0.23076923076923078</v>
+        <v>-0.63600000000000001</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -3963,28 +3985,29 @@
         <v>21</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G6" s="11">
         <v>600</v>
       </c>
       <c r="H6" s="71"/>
       <c r="I6" s="12">
-        <v>7</v>
+        <f>7+5</f>
+        <v>12</v>
       </c>
       <c r="J6" s="69">
         <f t="shared" si="3"/>
-        <v>1.1666666666666667E-2</v>
+        <v>0.02</v>
       </c>
       <c r="K6" s="11"/>
       <c r="L6" s="12">
-        <v>4.6500000000000004</v>
+        <v>11.15</v>
       </c>
       <c r="M6" s="70">
         <f t="shared" si="4"/>
@@ -3992,15 +4015,15 @@
       </c>
       <c r="N6" s="12">
         <f t="shared" si="0"/>
-        <v>-4.6500000000000004</v>
+        <v>-11.15</v>
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>-0.17884615384615385</v>
+        <v>-0.44600000000000001</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
-        <v>0.66428571428571437</v>
+        <v>0.9291666666666667</v>
       </c>
       <c r="Q6" s="14"/>
       <c r="R6" s="34"/>
@@ -4016,28 +4039,29 @@
         <v>21</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G7" s="11">
         <v>600</v>
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <v>3</v>
+        <f>3+4</f>
+        <v>7</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>5.0000000000000001E-3</v>
+        <v>1.1666666666666667E-2</v>
       </c>
       <c r="K7" s="11"/>
       <c r="L7" s="12">
-        <v>4.9000000000000004</v>
+        <v>11.2</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
@@ -4045,15 +4069,15 @@
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>-4.9000000000000004</v>
+        <v>-11.2</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>-0.18846153846153849</v>
+        <v>-0.44799999999999995</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.6333333333333335</v>
+        <v>1.5999999999999999</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4069,28 +4093,29 @@
         <v>21</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G8" s="11">
         <v>600</v>
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <v>4</v>
+        <f>4+5</f>
+        <v>9</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>6.6666666666666671E-3</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="K8" s="11"/>
       <c r="L8" s="12">
-        <v>2.1749999999999998</v>
+        <v>7.65</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
@@ -4098,15 +4123,15 @@
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N29" si="5">K8-L8</f>
-        <v>-2.1749999999999998</v>
+        <v>-7.65</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
-        <v>-8.3653846153846148E-2</v>
+        <v>-0.30599999999999999</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>0.54374999999999996</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4122,13 +4147,13 @@
         <v>21</v>
       </c>
       <c r="D9" s="47" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G9" s="11">
         <v>600</v>
@@ -4150,7 +4175,6 @@
         <v>0</v>
       </c>
       <c r="N9" s="12">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O9" s="14">
@@ -4175,7 +4199,7 @@
         <v>21</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>22</v>
@@ -4188,15 +4212,16 @@
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="12">
-        <v>1</v>
+        <f>1+4</f>
+        <v>5</v>
       </c>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>5.0000000000000001E-3</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="K10" s="11"/>
       <c r="L10" s="12">
-        <v>51</v>
+        <v>65.625</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
@@ -4204,15 +4229,15 @@
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>-51</v>
+        <v>-65.625</v>
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>-1.9615384615384615</v>
+        <v>-2.625</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>13.125</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
@@ -4228,24 +4253,25 @@
         <v>21</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G11" s="11">
         <v>600</v>
       </c>
       <c r="H11" s="71"/>
       <c r="I11" s="12">
-        <v>13</v>
+        <f>13+12</f>
+        <v>25</v>
       </c>
       <c r="J11" s="69">
         <f t="shared" si="3"/>
-        <v>2.1666666666666667E-2</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="K11" s="11"/>
       <c r="L11" s="12">
@@ -4261,11 +4287,11 @@
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>-0.53846153846153844</v>
+        <v>-0.56000000000000005</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
-        <v>1.0769230769230769</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="34"/>
@@ -4281,28 +4307,28 @@
         <v>21</v>
       </c>
       <c r="D12" s="47" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G12" s="11">
         <v>600</v>
       </c>
       <c r="H12" s="71"/>
       <c r="I12" s="12">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J12" s="69">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.1666666666666667E-2</v>
       </c>
       <c r="K12" s="11"/>
       <c r="L12" s="12">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M12" s="70">
         <f t="shared" si="4"/>
@@ -4310,15 +4336,15 @@
       </c>
       <c r="N12" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P12" s="71" t="e">
+        <v>-0.52</v>
+      </c>
+      <c r="P12" s="71">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="34"/>
@@ -4334,24 +4360,24 @@
         <v>21</v>
       </c>
       <c r="D13" s="47" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G13" s="11">
         <v>600</v>
       </c>
       <c r="H13" s="71"/>
       <c r="I13" s="12">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J13" s="69">
         <f t="shared" si="3"/>
-        <v>5.0000000000000001E-3</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="K13" s="11"/>
       <c r="L13" s="12">
@@ -4367,11 +4393,11 @@
       </c>
       <c r="O13" s="14">
         <f t="shared" si="6"/>
-        <v>-0.11538461538461539</v>
+        <v>-0.12</v>
       </c>
       <c r="P13" s="71">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="Q13" s="14"/>
       <c r="R13" s="34"/>
@@ -4387,13 +4413,13 @@
         <v>21</v>
       </c>
       <c r="D14" s="47" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F14" s="100" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G14" s="11">
         <v>0</v>
@@ -4433,13 +4459,13 @@
         <v>21</v>
       </c>
       <c r="D15" s="47" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F15" s="100" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G15" s="11"/>
       <c r="H15" s="71"/>
@@ -4477,13 +4503,13 @@
         <v>21</v>
       </c>
       <c r="D16" s="47" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E16" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F16" s="101" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G16" s="11"/>
       <c r="H16" s="71"/>
@@ -4535,11 +4561,11 @@
       </c>
       <c r="I17" s="41">
         <f>SUM(I4:I13)</f>
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>7.3214285714285716E-3</v>
+        <v>1.8749999999999999E-2</v>
       </c>
       <c r="K17" s="76">
         <f>SUM(K4:K16)</f>
@@ -4547,7 +4573,7 @@
       </c>
       <c r="L17" s="77">
         <f>SUM(L4:L16)</f>
-        <v>93.224999999999994</v>
+        <v>158.02500000000001</v>
       </c>
       <c r="M17" s="78">
         <f t="shared" si="4"/>
@@ -4555,15 +4581,15 @@
       </c>
       <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>-93.224999999999994</v>
+        <v>-158.02500000000001</v>
       </c>
       <c r="O17" s="79">
         <f t="shared" si="6"/>
-        <v>-3.585576923076923</v>
+        <v>-6.3210000000000006</v>
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>2.2737804878048777</v>
+        <v>1.5050000000000001</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -4588,7 +4614,7 @@
         <v>27</v>
       </c>
       <c r="F18" s="95" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G18" s="7">
         <v>1</v>
@@ -4617,7 +4643,7 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="6"/>
-        <v>16.373076923076923</v>
+        <v>17.027999999999999</v>
       </c>
       <c r="P18" s="96">
         <f t="shared" ref="P18:P22" si="7">L18/I18</f>
@@ -4672,7 +4698,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>16.373076923076923</v>
+        <v>17.027999999999999</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4727,7 +4753,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>16.373076923076923</v>
+        <v>17.027999999999999</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4782,7 +4808,7 @@
       </c>
       <c r="O21" s="14">
         <f t="shared" si="6"/>
-        <v>16.373076923076923</v>
+        <v>17.027999999999999</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="7"/>
@@ -4837,7 +4863,7 @@
       </c>
       <c r="O22" s="94">
         <f t="shared" si="6"/>
-        <v>16.373076923076923</v>
+        <v>17.027999999999999</v>
       </c>
       <c r="P22" s="74">
         <f t="shared" si="7"/>
@@ -4895,7 +4921,7 @@
       </c>
       <c r="O23" s="79">
         <f t="shared" si="6"/>
-        <v>16.373076923076923</v>
+        <v>17.027999999999999</v>
       </c>
       <c r="P23" s="80">
         <f>L23/I23</f>
@@ -4953,7 +4979,7 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="6"/>
-        <v>16.373076923076923</v>
+        <v>17.027999999999999</v>
       </c>
       <c r="P24" s="96">
         <f t="shared" ref="P24:P27" si="9">L24/I24</f>
@@ -4979,7 +5005,7 @@
         <v>32</v>
       </c>
       <c r="F25" s="97" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G25" s="11">
         <v>1</v>
@@ -5008,7 +5034,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>16.373076923076923</v>
+        <v>17.027999999999999</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5063,7 +5089,7 @@
       </c>
       <c r="O26" s="14">
         <f t="shared" si="6"/>
-        <v>16.373076923076923</v>
+        <v>17.027999999999999</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="9"/>
@@ -5089,7 +5115,7 @@
         <v>32</v>
       </c>
       <c r="F27" s="98" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G27" s="36">
         <v>1</v>
@@ -5118,7 +5144,7 @@
       </c>
       <c r="O27" s="94">
         <f t="shared" si="6"/>
-        <v>16.373076923076923</v>
+        <v>17.027999999999999</v>
       </c>
       <c r="P27" s="74">
         <f t="shared" si="9"/>
@@ -5173,7 +5199,7 @@
       </c>
       <c r="O28" s="79">
         <f t="shared" si="6"/>
-        <v>16.373076923076923</v>
+        <v>17.027999999999999</v>
       </c>
       <c r="P28" s="80">
         <f>L28/I28</f>
@@ -5206,11 +5232,11 @@
       </c>
       <c r="I29" s="21">
         <f t="shared" si="11"/>
-        <v>50</v>
+        <v>114</v>
       </c>
       <c r="J29" s="83">
         <f t="shared" si="3"/>
-        <v>8.9142449634515963E-3</v>
+        <v>2.0324478516669638E-2</v>
       </c>
       <c r="K29" s="84">
         <v>600</v>
@@ -5228,11 +5254,11 @@
       </c>
       <c r="O29" s="87">
         <f t="shared" si="6"/>
-        <v>16.373076923076923</v>
+        <v>17.027999999999999</v>
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>
-        <v>3.4860000000000002</v>
+        <v>1.5289473684210528</v>
       </c>
       <c r="Q29" s="23" t="e">
         <f>AVERAGE(Q28,Q17,Q23)</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB00E23-06DB-4D86-BE8B-86336C76FCE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CACB445-C54C-42E2-988D-95579D7D9DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="75">
   <si>
     <t>Booking</t>
   </si>
@@ -226,9 +226,6 @@
     <t>Nabeel Traders</t>
   </si>
   <si>
-    <t xml:space="preserve">Aqib </t>
-  </si>
-  <si>
     <t xml:space="preserve">Qamar Ijaz </t>
   </si>
   <si>
@@ -251,6 +248,9 @@
   </si>
   <si>
     <t>SD</t>
+  </si>
+  <si>
+    <t>Leave</t>
   </si>
 </sst>
 </file>
@@ -1574,7 +1574,7 @@
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="89">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="G2" s="114" t="s">
         <v>2</v>
@@ -1693,7 +1693,7 @@
         <v>22</v>
       </c>
       <c r="F4" s="48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G4" s="30">
         <v>50</v>
@@ -1702,50 +1702,50 @@
         <v>40</v>
       </c>
       <c r="I4" s="12">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J4" s="32">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.34</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="K4" s="30">
         <v>40</v>
       </c>
       <c r="L4" s="12">
-        <v>13.6</v>
+        <v>16.875</v>
       </c>
       <c r="M4" s="32">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.33999999999999997</v>
+        <v>0.421875</v>
       </c>
       <c r="N4" s="90">
         <f>IFERROR(L4/I4,0)</f>
-        <v>0.79999999999999993</v>
+        <v>1.2053571428571428</v>
       </c>
       <c r="O4" s="33"/>
       <c r="P4" s="30">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="Q4" s="31">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="R4" s="32">
         <f>IFERROR(Q4/P4,0)</f>
-        <v>0.83333333333333337</v>
+        <v>0.88235294117647056</v>
       </c>
       <c r="S4" s="30">
-        <v>9.375</v>
+        <v>13.6</v>
       </c>
       <c r="T4" s="31">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U4" s="32">
         <f>IFERROR(T4/S4,0)</f>
-        <v>0.96</v>
+        <v>0.80882352941176472</v>
       </c>
       <c r="V4" s="90">
         <f>IFERROR(T4/Q4,0)</f>
-        <v>1.8</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="W4" s="33"/>
       <c r="X4" s="34"/>
@@ -1786,40 +1786,40 @@
         <v>30</v>
       </c>
       <c r="L5" s="12">
-        <v>5</v>
+        <v>8.625</v>
       </c>
       <c r="M5" s="13">
         <f t="shared" ref="M5:M32" si="1">IFERROR(L5/K5,0)</f>
-        <v>0.16666666666666666</v>
+        <v>0.28749999999999998</v>
       </c>
       <c r="N5" s="11">
         <f t="shared" ref="N5:N32" si="2">IFERROR(L5/I5,0)</f>
-        <v>0.83333333333333337</v>
+        <v>1.4375</v>
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q5" s="12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R5" s="13">
         <f t="shared" ref="R5:R32" si="3">IFERROR(Q5/P5,0)</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="S5" s="11">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T5" s="12">
-        <v>9.9</v>
+        <v>3</v>
       </c>
       <c r="U5" s="13">
         <f t="shared" ref="U5:U32" si="4">IFERROR(T5/S5,0)</f>
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="V5" s="11">
         <f t="shared" ref="V5:V32" si="5">IFERROR(T5/Q5,0)</f>
-        <v>2.4750000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="W5" s="14"/>
       <c r="X5" s="34"/>
@@ -1841,7 +1841,7 @@
         <v>22</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G6" s="11">
         <v>50</v>
@@ -1850,50 +1850,50 @@
         <v>40</v>
       </c>
       <c r="I6" s="12">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J6" s="13">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="K6" s="11">
         <v>25</v>
       </c>
       <c r="L6" s="12">
-        <v>12.025</v>
+        <v>5</v>
       </c>
       <c r="M6" s="13">
         <f t="shared" si="1"/>
-        <v>0.48100000000000004</v>
+        <v>0.2</v>
       </c>
       <c r="N6" s="11">
         <f t="shared" si="2"/>
-        <v>1.503125</v>
+        <v>1.25</v>
       </c>
       <c r="O6" s="14"/>
       <c r="P6" s="11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q6" s="12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R6" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="S6" s="11">
-        <v>6.5</v>
+        <v>12.025</v>
       </c>
       <c r="T6" s="12">
-        <v>6.5</v>
+        <v>9.9250000000000007</v>
       </c>
       <c r="U6" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.82536382536382535</v>
       </c>
       <c r="V6" s="11">
         <f t="shared" si="5"/>
-        <v>1.3</v>
+        <v>1.6541666666666668</v>
       </c>
       <c r="W6" s="14"/>
       <c r="X6" s="34"/>
@@ -1924,42 +1924,42 @@
         <v>45</v>
       </c>
       <c r="I7" s="12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="0"/>
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="K7" s="11">
         <v>30</v>
       </c>
       <c r="L7" s="12">
-        <v>1.4</v>
+        <v>5.9</v>
       </c>
       <c r="M7" s="13">
         <f t="shared" si="1"/>
-        <v>4.6666666666666662E-2</v>
+        <v>0.19666666666666668</v>
       </c>
       <c r="N7" s="11">
         <f t="shared" si="2"/>
-        <v>0.7</v>
+        <v>1.4750000000000001</v>
       </c>
       <c r="O7" s="14"/>
       <c r="P7" s="11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R7" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="S7" s="11">
-        <v>6.3</v>
+        <v>1.4</v>
       </c>
       <c r="T7" s="12">
-        <v>6.3</v>
+        <v>1.4</v>
       </c>
       <c r="U7" s="13">
         <f t="shared" si="4"/>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="V7" s="11">
         <f t="shared" si="5"/>
-        <v>1.575</v>
+        <v>0.7</v>
       </c>
       <c r="W7" s="14"/>
       <c r="X7" s="34"/>
@@ -1998,50 +1998,50 @@
         <v>40</v>
       </c>
       <c r="I8" s="12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K8" s="11">
         <v>20</v>
       </c>
       <c r="L8" s="12">
-        <v>6.3</v>
+        <v>5.7</v>
       </c>
       <c r="M8" s="13">
         <f t="shared" si="1"/>
-        <v>0.315</v>
+        <v>0.28500000000000003</v>
       </c>
       <c r="N8" s="11">
         <f t="shared" si="2"/>
-        <v>1.26</v>
+        <v>0.81428571428571428</v>
       </c>
       <c r="O8" s="14"/>
       <c r="P8" s="11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q8" s="12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R8" s="13">
         <f t="shared" si="3"/>
-        <v>0.83333333333333337</v>
+        <v>0.6</v>
       </c>
       <c r="S8" s="11">
-        <v>5.7750000000000004</v>
+        <v>6.3</v>
       </c>
       <c r="T8" s="12">
-        <v>5.4749999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="U8" s="13">
         <f t="shared" si="4"/>
-        <v>0.94805194805194792</v>
+        <v>0.68253968253968256</v>
       </c>
       <c r="V8" s="11">
         <f t="shared" si="5"/>
-        <v>1.095</v>
+        <v>1.4333333333333333</v>
       </c>
       <c r="W8" s="14"/>
       <c r="X8" s="34"/>
@@ -2063,7 +2063,7 @@
         <v>22</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G9" s="11">
         <v>50</v>
@@ -2079,9 +2079,7 @@
       <c r="K9" s="11">
         <v>80</v>
       </c>
-      <c r="L9" s="12">
-        <v>0</v>
-      </c>
+      <c r="L9" s="12"/>
       <c r="M9" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2091,9 +2089,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="14"/>
-      <c r="P9" s="11">
-        <v>0</v>
-      </c>
+      <c r="P9" s="11"/>
       <c r="Q9" s="12">
         <v>0</v>
       </c>
@@ -2135,7 +2131,7 @@
         <v>22</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G10" s="11">
         <v>10</v>
@@ -2144,50 +2140,50 @@
         <v>10</v>
       </c>
       <c r="I10" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J10" s="13">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K10" s="11">
         <v>20</v>
       </c>
       <c r="L10" s="12">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M10" s="13">
         <f t="shared" si="1"/>
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="N10" s="11">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O10" s="14"/>
       <c r="P10" s="11">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Q10" s="12">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R10" s="13">
         <f t="shared" si="3"/>
-        <v>0.63636363636363635</v>
+        <v>1</v>
       </c>
       <c r="S10" s="11">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="T10" s="12">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="U10" s="13">
         <f t="shared" si="4"/>
-        <v>0.88235294117647056</v>
+        <v>1</v>
       </c>
       <c r="V10" s="11">
         <f t="shared" si="5"/>
-        <v>8.5714285714285712</v>
+        <v>15</v>
       </c>
       <c r="W10" s="14"/>
       <c r="X10" s="34"/>
@@ -2209,7 +2205,7 @@
         <v>22</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G11" s="11">
         <v>50</v>
@@ -2218,11 +2214,11 @@
         <v>40</v>
       </c>
       <c r="I11" s="12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J11" s="13">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="K11" s="11">
         <v>20</v>
@@ -2236,24 +2232,24 @@
       </c>
       <c r="N11" s="11">
         <f t="shared" si="2"/>
-        <v>1.1111111111111112</v>
+        <v>1.25</v>
       </c>
       <c r="O11" s="14"/>
       <c r="P11" s="11">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q11" s="12">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="R11" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="S11" s="11">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T11" s="12">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="U11" s="13">
         <f t="shared" si="4"/>
@@ -2261,7 +2257,7 @@
       </c>
       <c r="V11" s="11">
         <f t="shared" si="5"/>
-        <v>1.0769230769230769</v>
+        <v>1.1111111111111112</v>
       </c>
       <c r="W11" s="14"/>
       <c r="X11" s="34"/>
@@ -2283,7 +2279,7 @@
         <v>22</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G12" s="11">
         <v>50</v>
@@ -2292,50 +2288,50 @@
         <v>40</v>
       </c>
       <c r="I12" s="12">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="J12" s="13">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>0.44</v>
       </c>
       <c r="K12" s="11">
         <v>30</v>
       </c>
       <c r="L12" s="12">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="M12" s="13">
         <f t="shared" si="1"/>
-        <v>0.26666666666666666</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="N12" s="11">
         <f t="shared" si="2"/>
-        <v>0.88888888888888884</v>
+        <v>1.2727272727272727</v>
       </c>
       <c r="O12" s="14"/>
       <c r="P12" s="11">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q12" s="12">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="R12" s="13">
         <f t="shared" si="3"/>
-        <v>0.73333333333333328</v>
+        <v>1</v>
       </c>
       <c r="S12" s="11">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T12" s="12">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="U12" s="13">
         <f t="shared" si="4"/>
-        <v>0.8125</v>
+        <v>1</v>
       </c>
       <c r="V12" s="11">
         <f t="shared" si="5"/>
-        <v>1.1818181818181819</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="W12" s="14"/>
       <c r="X12" s="34"/>
@@ -2361,13 +2357,17 @@
       </c>
       <c r="G13" s="11"/>
       <c r="H13" s="71"/>
-      <c r="I13" s="12"/>
+      <c r="I13" s="12">
+        <v>0</v>
+      </c>
       <c r="J13" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K13" s="11"/>
-      <c r="L13" s="12"/>
+      <c r="L13" s="12">
+        <v>0</v>
+      </c>
       <c r="M13" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2421,7 +2421,7 @@
         <v>22</v>
       </c>
       <c r="F14" s="49" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="71"/>
@@ -2779,11 +2779,11 @@
       </c>
       <c r="I20" s="41">
         <f>SUM(I4:I19)</f>
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J20" s="42">
         <f t="shared" si="0"/>
-        <v>0.14390243902439023</v>
+        <v>0.15853658536585366</v>
       </c>
       <c r="K20" s="40">
         <f>SUM(K4:K12)</f>
@@ -2791,15 +2791,15 @@
       </c>
       <c r="L20" s="40">
         <f>SUM(L4:L12)</f>
-        <v>101.32499999999999</v>
+        <v>80.099999999999994</v>
       </c>
       <c r="M20" s="42">
         <f t="shared" si="1"/>
-        <v>0.34347457627118638</v>
+        <v>0.27152542372881355</v>
       </c>
       <c r="N20" s="40">
         <f t="shared" si="2"/>
-        <v>1.7173728813559319</v>
+        <v>1.2323076923076923</v>
       </c>
       <c r="O20" s="43">
         <f>AVERAGE(O4:O19)</f>
@@ -2807,31 +2807,31 @@
       </c>
       <c r="P20" s="40">
         <f>SUM(P4:P19)</f>
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="Q20" s="41">
         <f>SUM(Q4:Q19)</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R20" s="42">
         <f t="shared" si="3"/>
-        <v>0.83823529411764708</v>
+        <v>0.90322580645161288</v>
       </c>
       <c r="S20" s="40">
         <f>SUM(S4:S19)</f>
-        <v>139.94999999999999</v>
+        <v>104.32499999999999</v>
       </c>
       <c r="T20" s="41">
         <f>SUM(T4:T19)</f>
-        <v>127.175</v>
+        <v>95.625</v>
       </c>
       <c r="U20" s="42">
         <f t="shared" si="4"/>
-        <v>0.90871739907109683</v>
+        <v>0.91660675772825317</v>
       </c>
       <c r="V20" s="40">
         <f t="shared" si="5"/>
-        <v>2.231140350877193</v>
+        <v>1.7075892857142858</v>
       </c>
       <c r="W20" s="43">
         <f>AVERAGE(W4:W19)</f>
@@ -3664,11 +3664,11 @@
       </c>
       <c r="I32" s="21">
         <f t="shared" si="12"/>
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J32" s="22">
         <f t="shared" si="0"/>
-        <v>0.14081145584725538</v>
+        <v>0.15513126491646778</v>
       </c>
       <c r="K32" s="20">
         <v>1</v>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="N32" s="20">
         <f t="shared" si="2"/>
-        <v>1.6949152542372881E-2</v>
+        <v>1.5384615384615385E-2</v>
       </c>
       <c r="O32" s="23">
         <f>AVERAGE(O31,O20,O26)</f>
@@ -3690,31 +3690,31 @@
       </c>
       <c r="P32" s="20">
         <f>+P31+P26+P20</f>
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="Q32" s="21">
         <f t="shared" ref="Q32" si="13">+Q31+Q26+Q20</f>
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R32" s="22">
         <f t="shared" si="3"/>
-        <v>0.8571428571428571</v>
+        <v>0.91549295774647887</v>
       </c>
       <c r="S32" s="20">
         <f>+S31+S26+S20</f>
-        <v>148.94999999999999</v>
+        <v>113.32499999999999</v>
       </c>
       <c r="T32" s="21">
         <f t="shared" ref="T32" si="14">+T31+T26+T20</f>
-        <v>136.17500000000001</v>
+        <v>104.625</v>
       </c>
       <c r="U32" s="22">
         <f t="shared" si="4"/>
-        <v>0.9142329640819068</v>
+        <v>0.92322964923891471</v>
       </c>
       <c r="V32" s="20">
         <f t="shared" si="5"/>
-        <v>2.063257575757576</v>
+        <v>1.6096153846153847</v>
       </c>
       <c r="W32" s="23">
         <f>AVERAGE(W31,W20,W26)</f>
@@ -3749,7 +3749,8 @@
     <col min="4" max="4" width="18.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.7265625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="6.26953125" style="24" customWidth="1"/>
+    <col min="7" max="7" width="6.26953125" style="24" customWidth="1"/>
+    <col min="8" max="8" width="6.26953125" style="24" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="10.54296875" customWidth="1"/>
     <col min="10" max="10" width="5.54296875" customWidth="1"/>
     <col min="11" max="11" width="8.1796875" bestFit="1" customWidth="1"/>
@@ -3779,18 +3780,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>7.407407407407407E-2</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F2" s="89">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="G2" s="114" t="s">
         <v>34</v>
@@ -3877,7 +3878,7 @@
         <v>21</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E4" s="47" t="s">
         <v>22</v>
@@ -3890,32 +3891,33 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>8+5</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>2.1666666666666667E-2</v>
-      </c>
-      <c r="K4" s="7"/>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="K4" s="7">
+        <v>600</v>
+      </c>
       <c r="L4" s="8">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0</v>
+        <v>1.8333333333333333E-2</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>-16.5</v>
+        <v>589</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>-0.66</v>
+        <v>24.541666666666668</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P13" si="2">L4/I4</f>
-        <v>1.2692307692307692</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3931,7 +3933,7 @@
         <v>21</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>22</v>
@@ -3944,32 +3946,33 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <f>2+4</f>
         <v>6</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J29" si="3">IFERROR(I5/G5,0)</f>
         <v>0.01</v>
       </c>
-      <c r="K5" s="11"/>
+      <c r="K5" s="11">
+        <v>500</v>
+      </c>
       <c r="L5" s="12">
-        <v>15.9</v>
+        <v>3</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M29" si="4">IFERROR(L5/K5,0)</f>
-        <v>0</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>-15.9</v>
+        <v>497</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>-0.63600000000000001</v>
+        <v>20.708333333333332</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>2.65</v>
+        <v>0.5</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -3985,7 +3988,7 @@
         <v>21</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>22</v>
@@ -3998,32 +4001,33 @@
       </c>
       <c r="H6" s="71"/>
       <c r="I6" s="12">
-        <f>7+5</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J6" s="69">
         <f t="shared" si="3"/>
-        <v>0.02</v>
-      </c>
-      <c r="K6" s="11"/>
+        <v>0.01</v>
+      </c>
+      <c r="K6" s="11">
+        <v>500</v>
+      </c>
       <c r="L6" s="12">
-        <v>11.15</v>
+        <v>9.9250000000000007</v>
       </c>
       <c r="M6" s="70">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.9850000000000003E-2</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="0"/>
-        <v>-11.15</v>
+        <v>490.07499999999999</v>
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>-0.44600000000000001</v>
+        <v>20.419791666666665</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
-        <v>0.9291666666666667</v>
+        <v>1.6541666666666668</v>
       </c>
       <c r="Q6" s="14"/>
       <c r="R6" s="34"/>
@@ -4039,7 +4043,7 @@
         <v>21</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>22</v>
@@ -4052,32 +4056,33 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>3+4</f>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>1.1666666666666667E-2</v>
-      </c>
-      <c r="K7" s="11"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="K7" s="11">
+        <v>400</v>
+      </c>
       <c r="L7" s="12">
-        <v>11.2</v>
+        <v>1.4</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3.4999999999999996E-3</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>-11.2</v>
+        <v>398.6</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>-0.44799999999999995</v>
+        <v>16.608333333333334</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.5999999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4093,7 +4098,7 @@
         <v>21</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>22</v>
@@ -4106,32 +4111,33 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <f>4+5</f>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="K8" s="11"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K8" s="11">
+        <v>400</v>
+      </c>
       <c r="L8" s="12">
-        <v>7.65</v>
+        <v>4.3</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.0749999999999999E-2</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N29" si="5">K8-L8</f>
-        <v>-7.65</v>
+        <v>395.7</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
-        <v>-0.30599999999999999</v>
+        <v>16.487500000000001</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>0.85000000000000009</v>
+        <v>1.4333333333333333</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4147,21 +4153,19 @@
         <v>21</v>
       </c>
       <c r="D9" s="47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G9" s="11">
         <v>600</v>
       </c>
       <c r="H9" s="71"/>
-      <c r="I9" s="12">
-        <v>0</v>
-      </c>
+      <c r="I9" s="12"/>
       <c r="J9" s="69">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4199,7 +4203,7 @@
         <v>21</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>22</v>
@@ -4212,32 +4216,33 @@
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="12">
-        <f>1+4</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="K10" s="11"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="K10" s="11">
+        <v>2500</v>
+      </c>
       <c r="L10" s="12">
-        <v>65.625</v>
+        <v>23.75</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9.4999999999999998E-3</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>-65.625</v>
+        <v>2476.25</v>
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>-2.625</v>
+        <v>103.17708333333333</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>13.125</v>
+        <v>7.916666666666667</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
@@ -4253,7 +4258,7 @@
         <v>21</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>22</v>
@@ -4266,32 +4271,33 @@
       </c>
       <c r="H11" s="71"/>
       <c r="I11" s="12">
-        <f>13+12</f>
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="J11" s="69">
         <f t="shared" si="3"/>
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="K11" s="11"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="K11" s="11">
+        <v>500</v>
+      </c>
       <c r="L11" s="12">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="5"/>
-        <v>-14</v>
+        <v>490</v>
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>-0.56000000000000005</v>
+        <v>20.416666666666668</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
-        <v>0.56000000000000005</v>
+        <v>1.1111111111111112</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="34"/>
@@ -4307,7 +4313,7 @@
         <v>21</v>
       </c>
       <c r="D12" s="47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>22</v>
@@ -4320,31 +4326,33 @@
       </c>
       <c r="H12" s="71"/>
       <c r="I12" s="12">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J12" s="69">
         <f t="shared" si="3"/>
-        <v>2.1666666666666667E-2</v>
-      </c>
-      <c r="K12" s="11"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="K12" s="11">
+        <v>500</v>
+      </c>
       <c r="L12" s="12">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M12" s="70">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.6E-2</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="5"/>
-        <v>-13</v>
+        <v>492</v>
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>-0.52</v>
+        <v>20.5</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="34"/>
@@ -4360,7 +4368,7 @@
         <v>21</v>
       </c>
       <c r="D13" s="47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>22</v>
@@ -4373,15 +4381,17 @@
       </c>
       <c r="H13" s="71"/>
       <c r="I13" s="12">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J13" s="69">
         <f t="shared" si="3"/>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="K13" s="11"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="11">
+        <v>400</v>
+      </c>
       <c r="L13" s="12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M13" s="70">
         <f t="shared" si="4"/>
@@ -4389,18 +4399,20 @@
       </c>
       <c r="N13" s="12">
         <f t="shared" si="5"/>
-        <v>-3</v>
+        <v>400</v>
       </c>
       <c r="O13" s="14">
         <f t="shared" si="6"/>
-        <v>-0.12</v>
-      </c>
-      <c r="P13" s="71">
+        <v>16.666666666666668</v>
+      </c>
+      <c r="P13" s="71" t="e">
         <f t="shared" si="2"/>
-        <v>0.2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="Q13" s="14"/>
-      <c r="R13" s="34"/>
+      <c r="R13" s="14" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="14" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="35" t="s">
@@ -4413,7 +4425,7 @@
         <v>21</v>
       </c>
       <c r="D14" s="47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>22</v>
@@ -4459,7 +4471,7 @@
         <v>21</v>
       </c>
       <c r="D15" s="47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>22</v>
@@ -4503,7 +4515,7 @@
         <v>21</v>
       </c>
       <c r="D16" s="47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E16" s="16" t="s">
         <v>22</v>
@@ -4561,35 +4573,35 @@
       </c>
       <c r="I17" s="41">
         <f>SUM(I4:I13)</f>
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>1.8749999999999999E-2</v>
+        <v>9.464285714285715E-3</v>
       </c>
       <c r="K17" s="76">
         <f>SUM(K4:K16)</f>
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="L17" s="77">
         <f>SUM(L4:L16)</f>
-        <v>158.02500000000001</v>
+        <v>71.375</v>
       </c>
       <c r="M17" s="78">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.132936507936508E-2</v>
       </c>
       <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>-158.02500000000001</v>
+        <v>6228.625</v>
       </c>
       <c r="O17" s="79">
         <f t="shared" si="6"/>
-        <v>-6.3210000000000006</v>
+        <v>259.52604166666669</v>
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>1.5050000000000001</v>
+        <v>1.3466981132075471</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -4643,7 +4655,7 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="6"/>
-        <v>17.027999999999999</v>
+        <v>17.737500000000001</v>
       </c>
       <c r="P18" s="96">
         <f t="shared" ref="P18:P22" si="7">L18/I18</f>
@@ -4698,7 +4710,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>17.027999999999999</v>
+        <v>17.737500000000001</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4753,7 +4765,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>17.027999999999999</v>
+        <v>17.737500000000001</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4808,7 +4820,7 @@
       </c>
       <c r="O21" s="14">
         <f t="shared" si="6"/>
-        <v>17.027999999999999</v>
+        <v>17.737500000000001</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="7"/>
@@ -4863,7 +4875,7 @@
       </c>
       <c r="O22" s="94">
         <f t="shared" si="6"/>
-        <v>17.027999999999999</v>
+        <v>17.737500000000001</v>
       </c>
       <c r="P22" s="74">
         <f t="shared" si="7"/>
@@ -4921,7 +4933,7 @@
       </c>
       <c r="O23" s="79">
         <f t="shared" si="6"/>
-        <v>17.027999999999999</v>
+        <v>17.737500000000001</v>
       </c>
       <c r="P23" s="80">
         <f>L23/I23</f>
@@ -4979,7 +4991,7 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="6"/>
-        <v>17.027999999999999</v>
+        <v>17.737500000000001</v>
       </c>
       <c r="P24" s="96">
         <f t="shared" ref="P24:P27" si="9">L24/I24</f>
@@ -5034,7 +5046,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>17.027999999999999</v>
+        <v>17.737500000000001</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5089,7 +5101,7 @@
       </c>
       <c r="O26" s="14">
         <f t="shared" si="6"/>
-        <v>17.027999999999999</v>
+        <v>17.737500000000001</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="9"/>
@@ -5144,7 +5156,7 @@
       </c>
       <c r="O27" s="94">
         <f t="shared" si="6"/>
-        <v>17.027999999999999</v>
+        <v>17.737500000000001</v>
       </c>
       <c r="P27" s="74">
         <f t="shared" si="9"/>
@@ -5199,7 +5211,7 @@
       </c>
       <c r="O28" s="79">
         <f t="shared" si="6"/>
-        <v>17.027999999999999</v>
+        <v>17.737500000000001</v>
       </c>
       <c r="P28" s="80">
         <f>L28/I28</f>
@@ -5232,11 +5244,11 @@
       </c>
       <c r="I29" s="21">
         <f t="shared" si="11"/>
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="J29" s="83">
         <f t="shared" si="3"/>
-        <v>2.0324478516669638E-2</v>
+        <v>1.1053663754679978E-2</v>
       </c>
       <c r="K29" s="84">
         <v>600</v>
@@ -5254,11 +5266,11 @@
       </c>
       <c r="O29" s="87">
         <f t="shared" si="6"/>
-        <v>17.027999999999999</v>
+        <v>17.737500000000001</v>
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>
-        <v>1.5289473684210528</v>
+        <v>2.8112903225806454</v>
       </c>
       <c r="Q29" s="23" t="e">
         <f>AVERAGE(Q28,Q17,Q23)</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CACB445-C54C-42E2-988D-95579D7D9DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DB6FFF-EBFF-4B76-AC56-78B8D8C2B4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="74">
   <si>
     <t>Booking</t>
   </si>
@@ -248,9 +248,6 @@
   </si>
   <si>
     <t>SD</t>
-  </si>
-  <si>
-    <t>Leave</t>
   </si>
 </sst>
 </file>
@@ -1574,7 +1571,7 @@
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="89">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="G2" s="114" t="s">
         <v>2</v>
@@ -1702,50 +1699,50 @@
         <v>40</v>
       </c>
       <c r="I4" s="12">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J4" s="32">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.28000000000000003</v>
+        <v>0.18</v>
       </c>
       <c r="K4" s="30">
         <v>40</v>
       </c>
       <c r="L4" s="12">
-        <v>16.875</v>
+        <v>17.875</v>
       </c>
       <c r="M4" s="32">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.421875</v>
+        <v>0.44687500000000002</v>
       </c>
       <c r="N4" s="90">
         <f>IFERROR(L4/I4,0)</f>
-        <v>1.2053571428571428</v>
+        <v>1.9861111111111112</v>
       </c>
       <c r="O4" s="33"/>
       <c r="P4" s="30">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q4" s="31">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R4" s="32">
         <f>IFERROR(Q4/P4,0)</f>
-        <v>0.88235294117647056</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="S4" s="30">
-        <v>13.6</v>
+        <v>16.875</v>
       </c>
       <c r="T4" s="31">
-        <v>11</v>
+        <v>10.875</v>
       </c>
       <c r="U4" s="32">
         <f>IFERROR(T4/S4,0)</f>
-        <v>0.80882352941176472</v>
+        <v>0.64444444444444449</v>
       </c>
       <c r="V4" s="90">
         <f>IFERROR(T4/Q4,0)</f>
-        <v>0.73333333333333328</v>
+        <v>0.83653846153846156</v>
       </c>
       <c r="W4" s="33"/>
       <c r="X4" s="34"/>
@@ -1776,50 +1773,50 @@
         <v>45</v>
       </c>
       <c r="I5" s="12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J5" s="13">
         <f t="shared" ref="J5:J32" si="0">IFERROR(I5/G5,0)</f>
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="K5" s="11">
         <v>30</v>
       </c>
       <c r="L5" s="12">
-        <v>8.625</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M5" s="13">
         <f t="shared" ref="M5:M32" si="1">IFERROR(L5/K5,0)</f>
-        <v>0.28749999999999998</v>
+        <v>0.16999999999999998</v>
       </c>
       <c r="N5" s="11">
         <f t="shared" ref="N5:N32" si="2">IFERROR(L5/I5,0)</f>
-        <v>1.4375</v>
+        <v>1.02</v>
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="11">
         <v>6</v>
       </c>
       <c r="Q5" s="12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R5" s="13">
         <f t="shared" ref="R5:R32" si="3">IFERROR(Q5/P5,0)</f>
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="S5" s="11">
-        <v>5</v>
+        <v>8.625</v>
       </c>
       <c r="T5" s="12">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="U5" s="13">
         <f t="shared" ref="U5:U32" si="4">IFERROR(T5/S5,0)</f>
-        <v>0.6</v>
+        <v>0.76521739130434774</v>
       </c>
       <c r="V5" s="11">
         <f t="shared" ref="V5:V32" si="5">IFERROR(T5/Q5,0)</f>
-        <v>0.5</v>
+        <v>1.3199999999999998</v>
       </c>
       <c r="W5" s="14"/>
       <c r="X5" s="34"/>
@@ -1850,50 +1847,50 @@
         <v>40</v>
       </c>
       <c r="I6" s="12">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J6" s="13">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="K6" s="11">
         <v>25</v>
       </c>
       <c r="L6" s="12">
-        <v>5</v>
+        <v>7.45</v>
       </c>
       <c r="M6" s="13">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0.29799999999999999</v>
       </c>
       <c r="N6" s="11">
         <f t="shared" si="2"/>
-        <v>1.25</v>
+        <v>0.93125000000000002</v>
       </c>
       <c r="O6" s="14"/>
       <c r="P6" s="11">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q6" s="12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R6" s="13">
         <f t="shared" si="3"/>
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="S6" s="11">
-        <v>12.025</v>
+        <v>5</v>
       </c>
       <c r="T6" s="12">
-        <v>9.9250000000000007</v>
+        <v>4.25</v>
       </c>
       <c r="U6" s="13">
         <f t="shared" si="4"/>
-        <v>0.82536382536382535</v>
+        <v>0.85</v>
       </c>
       <c r="V6" s="11">
         <f t="shared" si="5"/>
-        <v>1.6541666666666668</v>
+        <v>1.0625</v>
       </c>
       <c r="W6" s="14"/>
       <c r="X6" s="34"/>
@@ -1924,50 +1921,50 @@
         <v>45</v>
       </c>
       <c r="I7" s="12">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K7" s="11">
         <v>30</v>
       </c>
       <c r="L7" s="12">
-        <v>5.9</v>
+        <v>11.05</v>
       </c>
       <c r="M7" s="13">
         <f t="shared" si="1"/>
-        <v>0.19666666666666668</v>
+        <v>0.36833333333333335</v>
       </c>
       <c r="N7" s="11">
         <f t="shared" si="2"/>
-        <v>1.4750000000000001</v>
+        <v>1.5785714285714287</v>
       </c>
       <c r="O7" s="14"/>
       <c r="P7" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q7" s="12">
         <v>2</v>
       </c>
       <c r="R7" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="S7" s="11">
-        <v>1.4</v>
+        <v>5.9</v>
       </c>
       <c r="T7" s="12">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="U7" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.50847457627118642</v>
       </c>
       <c r="V7" s="11">
         <f t="shared" si="5"/>
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="W7" s="14"/>
       <c r="X7" s="34"/>
@@ -1998,50 +1995,50 @@
         <v>40</v>
       </c>
       <c r="I8" s="12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="K8" s="11">
         <v>20</v>
       </c>
       <c r="L8" s="12">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="M8" s="13">
         <f t="shared" si="1"/>
-        <v>0.28500000000000003</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="N8" s="11">
         <f t="shared" si="2"/>
-        <v>0.81428571428571428</v>
+        <v>0.72222222222222221</v>
       </c>
       <c r="O8" s="14"/>
       <c r="P8" s="11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q8" s="12">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R8" s="13">
         <f t="shared" si="3"/>
-        <v>0.6</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S8" s="11">
-        <v>6.3</v>
+        <v>5.7</v>
       </c>
       <c r="T8" s="12">
-        <v>4.3</v>
+        <v>4.95</v>
       </c>
       <c r="U8" s="13">
         <f t="shared" si="4"/>
-        <v>0.68253968253968256</v>
+        <v>0.86842105263157898</v>
       </c>
       <c r="V8" s="11">
         <f t="shared" si="5"/>
-        <v>1.4333333333333333</v>
+        <v>0.82500000000000007</v>
       </c>
       <c r="W8" s="14"/>
       <c r="X8" s="34"/>
@@ -2140,50 +2137,42 @@
         <v>10</v>
       </c>
       <c r="I10" s="12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J10" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K10" s="11">
         <v>20</v>
       </c>
       <c r="L10" s="12">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M10" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N10" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="O10" s="14"/>
-      <c r="P10" s="11">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="12">
-        <v>3</v>
-      </c>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="12"/>
       <c r="R10" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="S10" s="11">
-        <v>45</v>
-      </c>
-      <c r="T10" s="12">
-        <v>45</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S10" s="11"/>
+      <c r="T10" s="12"/>
       <c r="U10" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="11">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W10" s="14"/>
       <c r="X10" s="34"/>
@@ -2214,50 +2203,42 @@
         <v>40</v>
       </c>
       <c r="I11" s="12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J11" s="13">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K11" s="11">
         <v>20</v>
       </c>
       <c r="L11" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M11" s="13">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="N11" s="11">
         <f t="shared" si="2"/>
-        <v>1.25</v>
+        <v>1.2857142857142858</v>
       </c>
       <c r="O11" s="14"/>
-      <c r="P11" s="11">
-        <v>9</v>
-      </c>
-      <c r="Q11" s="12">
-        <v>9</v>
-      </c>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="12"/>
       <c r="R11" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="S11" s="11">
-        <v>10</v>
-      </c>
-      <c r="T11" s="12">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S11" s="11"/>
+      <c r="T11" s="12"/>
       <c r="U11" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="11">
         <f t="shared" si="5"/>
-        <v>1.1111111111111112</v>
+        <v>0</v>
       </c>
       <c r="W11" s="14"/>
       <c r="X11" s="34"/>
@@ -2288,50 +2269,42 @@
         <v>40</v>
       </c>
       <c r="I12" s="12">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J12" s="13">
         <f t="shared" si="0"/>
-        <v>0.44</v>
+        <v>0.12</v>
       </c>
       <c r="K12" s="11">
         <v>30</v>
       </c>
       <c r="L12" s="12">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="M12" s="13">
         <f t="shared" si="1"/>
-        <v>0.93333333333333335</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="N12" s="11">
         <f t="shared" si="2"/>
-        <v>1.2727272727272727</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="O12" s="14"/>
-      <c r="P12" s="11">
-        <v>9</v>
-      </c>
-      <c r="Q12" s="12">
-        <v>9</v>
-      </c>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="12"/>
       <c r="R12" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="S12" s="11">
-        <v>8</v>
-      </c>
-      <c r="T12" s="12">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S12" s="11"/>
+      <c r="T12" s="12"/>
       <c r="U12" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="11">
         <f t="shared" si="5"/>
-        <v>0.88888888888888884</v>
+        <v>0</v>
       </c>
       <c r="W12" s="14"/>
       <c r="X12" s="34"/>
@@ -2355,51 +2328,49 @@
       <c r="F13" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="71"/>
+      <c r="G13" s="11">
+        <v>50</v>
+      </c>
+      <c r="H13" s="71">
+        <v>45</v>
+      </c>
       <c r="I13" s="12">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J13" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="11"/>
+        <v>0.12</v>
+      </c>
+      <c r="K13" s="11">
+        <v>30</v>
+      </c>
       <c r="L13" s="12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M13" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="N13" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="O13" s="14"/>
-      <c r="P13" s="11">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="12">
-        <v>3</v>
-      </c>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="12"/>
       <c r="R13" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="S13" s="11">
-        <v>3</v>
-      </c>
-      <c r="T13" s="12">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S13" s="11"/>
+      <c r="T13" s="12"/>
       <c r="U13" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="11">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" s="14"/>
       <c r="X13" s="34"/>
@@ -2771,19 +2742,19 @@
       <c r="F20" s="104"/>
       <c r="G20" s="40">
         <f>SUM(G4:G19)</f>
-        <v>410</v>
+        <v>460</v>
       </c>
       <c r="H20" s="41">
         <f>SUM(H4:H19)</f>
-        <v>300</v>
+        <v>345</v>
       </c>
       <c r="I20" s="41">
         <f>SUM(I4:I19)</f>
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="J20" s="42">
         <f t="shared" si="0"/>
-        <v>0.15853658536585366</v>
+        <v>0.13478260869565217</v>
       </c>
       <c r="K20" s="40">
         <f>SUM(K4:K12)</f>
@@ -2791,15 +2762,15 @@
       </c>
       <c r="L20" s="40">
         <f>SUM(L4:L12)</f>
-        <v>80.099999999999994</v>
+        <v>118.97499999999999</v>
       </c>
       <c r="M20" s="42">
         <f t="shared" si="1"/>
-        <v>0.27152542372881355</v>
+        <v>0.40330508474576271</v>
       </c>
       <c r="N20" s="40">
         <f t="shared" si="2"/>
-        <v>1.2323076923076923</v>
+        <v>1.9189516129032258</v>
       </c>
       <c r="O20" s="43">
         <f>AVERAGE(O4:O19)</f>
@@ -2807,31 +2778,31 @@
       </c>
       <c r="P20" s="40">
         <f>SUM(P4:P19)</f>
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="Q20" s="41">
         <f>SUM(Q4:Q19)</f>
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="R20" s="42">
         <f t="shared" si="3"/>
-        <v>0.90322580645161288</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S20" s="40">
         <f>SUM(S4:S19)</f>
-        <v>104.32499999999999</v>
+        <v>42.1</v>
       </c>
       <c r="T20" s="41">
         <f>SUM(T4:T19)</f>
-        <v>95.625</v>
+        <v>29.675000000000001</v>
       </c>
       <c r="U20" s="42">
         <f t="shared" si="4"/>
-        <v>0.91660675772825317</v>
+        <v>0.70486935866983369</v>
       </c>
       <c r="V20" s="40">
         <f t="shared" si="5"/>
-        <v>1.7075892857142858</v>
+        <v>0.98916666666666664</v>
       </c>
       <c r="W20" s="43">
         <f>AVERAGE(W4:W19)</f>
@@ -3656,19 +3627,19 @@
       <c r="F32" s="57"/>
       <c r="G32" s="20">
         <f>+G31+G26+G20</f>
-        <v>419</v>
+        <v>469</v>
       </c>
       <c r="H32" s="21">
         <f t="shared" ref="H32:I32" si="12">+H31+H26+H20</f>
-        <v>300</v>
+        <v>345</v>
       </c>
       <c r="I32" s="21">
         <f t="shared" si="12"/>
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="J32" s="22">
         <f t="shared" si="0"/>
-        <v>0.15513126491646778</v>
+        <v>0.13219616204690832</v>
       </c>
       <c r="K32" s="20">
         <v>1</v>
@@ -3682,7 +3653,7 @@
       </c>
       <c r="N32" s="20">
         <f t="shared" si="2"/>
-        <v>1.5384615384615385E-2</v>
+        <v>1.6129032258064516E-2</v>
       </c>
       <c r="O32" s="23">
         <f>AVERAGE(O31,O20,O26)</f>
@@ -3690,31 +3661,31 @@
       </c>
       <c r="P32" s="20">
         <f>+P31+P26+P20</f>
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="Q32" s="21">
         <f t="shared" ref="Q32" si="13">+Q31+Q26+Q20</f>
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="R32" s="22">
         <f t="shared" si="3"/>
-        <v>0.91549295774647887</v>
+        <v>0.88636363636363635</v>
       </c>
       <c r="S32" s="20">
         <f>+S31+S26+S20</f>
-        <v>113.32499999999999</v>
+        <v>51.1</v>
       </c>
       <c r="T32" s="21">
         <f t="shared" ref="T32" si="14">+T31+T26+T20</f>
-        <v>104.625</v>
+        <v>38.674999999999997</v>
       </c>
       <c r="U32" s="22">
         <f t="shared" si="4"/>
-        <v>0.92322964923891471</v>
+        <v>0.75684931506849307</v>
       </c>
       <c r="V32" s="20">
         <f t="shared" si="5"/>
-        <v>1.6096153846153847</v>
+        <v>0.99166666666666659</v>
       </c>
       <c r="W32" s="23">
         <f>AVERAGE(W31,W20,W26)</f>
@@ -3780,18 +3751,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.1111111111111111</v>
+        <v>0.14814814814814814</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F2" s="89">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="G2" s="114" t="s">
         <v>34</v>
@@ -3891,33 +3862,34 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <v>15</v>
+        <f>15+13</f>
+        <v>28</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>2.5000000000000001E-2</v>
+        <v>4.6666666666666669E-2</v>
       </c>
       <c r="K4" s="7">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="L4" s="8">
-        <v>11</v>
+        <v>38.375</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>1.8333333333333333E-2</v>
+        <v>8.5277777777777772E-2</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>589</v>
+        <v>411.625</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>24.541666666666668</v>
+        <v>17.896739130434781</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P13" si="2">L4/I4</f>
-        <v>0.73333333333333328</v>
+        <v>1.3705357142857142</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3946,33 +3918,34 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <v>6</v>
+        <f>6+5</f>
+        <v>11</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J29" si="3">IFERROR(I5/G5,0)</f>
-        <v>0.01</v>
+        <v>1.8333333333333333E-2</v>
       </c>
       <c r="K5" s="11">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="L5" s="12">
-        <v>3</v>
+        <v>25.5</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M29" si="4">IFERROR(L5/K5,0)</f>
-        <v>6.0000000000000001E-3</v>
+        <v>7.2857142857142856E-2</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>497</v>
+        <v>324.5</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>20.708333333333332</v>
+        <v>14.108695652173912</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>2.3181818181818183</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -4001,33 +3974,34 @@
       </c>
       <c r="H6" s="71"/>
       <c r="I6" s="12">
-        <v>6</v>
+        <f>6+4</f>
+        <v>10</v>
       </c>
       <c r="J6" s="69">
         <f t="shared" si="3"/>
-        <v>0.01</v>
+        <v>1.6666666666666666E-2</v>
       </c>
       <c r="K6" s="11">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="L6" s="12">
-        <v>9.9250000000000007</v>
+        <v>25.324999999999999</v>
       </c>
       <c r="M6" s="70">
         <f t="shared" si="4"/>
-        <v>1.9850000000000003E-2</v>
+        <v>7.2357142857142856E-2</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="0"/>
-        <v>490.07499999999999</v>
+        <v>324.67500000000001</v>
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>20.419791666666665</v>
+        <v>14.116304347826087</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
-        <v>1.6541666666666668</v>
+        <v>2.5324999999999998</v>
       </c>
       <c r="Q6" s="14"/>
       <c r="R6" s="34"/>
@@ -4056,33 +4030,34 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <v>2</v>
+        <f>2+2</f>
+        <v>4</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>3.3333333333333335E-3</v>
+        <v>6.6666666666666671E-3</v>
       </c>
       <c r="K7" s="11">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="L7" s="12">
-        <v>1.4</v>
+        <v>15.6</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>3.4999999999999996E-3</v>
+        <v>6.2399999999999997E-2</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>398.6</v>
+        <v>234.4</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>16.608333333333334</v>
+        <v>10.191304347826087</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4111,33 +4086,34 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <v>3</v>
+        <f>3+6</f>
+        <v>9</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>5.0000000000000001E-3</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="K8" s="11">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="L8" s="12">
-        <v>4.3</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>1.0749999999999999E-2</v>
+        <v>6.7599999999999993E-2</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N29" si="5">K8-L8</f>
-        <v>395.7</v>
+        <v>233.1</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
-        <v>16.487500000000001</v>
+        <v>10.134782608695652</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.4333333333333333</v>
+        <v>1.8777777777777775</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4170,7 +4146,9 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K9" s="11"/>
+      <c r="K9" s="11">
+        <v>150</v>
+      </c>
       <c r="L9" s="12">
         <v>0</v>
       </c>
@@ -4223,26 +4201,26 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="K10" s="11">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="L10" s="12">
-        <v>23.75</v>
+        <v>140</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>9.4999999999999998E-3</v>
+        <v>6.0869565217391307E-2</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>2476.25</v>
+        <v>2160</v>
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>103.17708333333333</v>
+        <v>93.913043478260875</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>7.916666666666667</v>
+        <v>46.666666666666664</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
@@ -4278,26 +4256,26 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="K11" s="11">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="L11" s="12">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="4"/>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>432</v>
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>20.416666666666668</v>
+        <v>18.782608695652176</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
-        <v>1.1111111111111112</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="34"/>
@@ -4333,26 +4311,26 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="K12" s="11">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="L12" s="12">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M12" s="70">
         <f t="shared" si="4"/>
-        <v>1.6E-2</v>
+        <v>0.04</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="5"/>
-        <v>492</v>
+        <v>288</v>
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>20.5</v>
+        <v>12.521739130434783</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
-        <v>0.88888888888888884</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="34"/>
@@ -4388,31 +4366,29 @@
         <v>0</v>
       </c>
       <c r="K13" s="11">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="L13" s="12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M13" s="70">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.6E-2</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="5"/>
-        <v>400</v>
+        <v>246</v>
       </c>
       <c r="O13" s="14">
         <f t="shared" si="6"/>
-        <v>16.666666666666668</v>
+        <v>10.695652173913043</v>
       </c>
       <c r="P13" s="71" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q13" s="14"/>
-      <c r="R13" s="14" t="s">
-        <v>74</v>
-      </c>
+      <c r="R13" s="14"/>
     </row>
     <row r="14" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="35" t="s">
@@ -4573,35 +4549,35 @@
       </c>
       <c r="I17" s="41">
         <f>SUM(I4:I13)</f>
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>9.464285714285715E-3</v>
+        <v>1.4821428571428572E-2</v>
       </c>
       <c r="K17" s="76">
         <f>SUM(K4:K16)</f>
-        <v>6300</v>
+        <v>5100</v>
       </c>
       <c r="L17" s="77">
         <f>SUM(L4:L16)</f>
-        <v>71.375</v>
+        <v>295.7</v>
       </c>
       <c r="M17" s="78">
         <f t="shared" si="4"/>
-        <v>1.132936507936508E-2</v>
+        <v>5.7980392156862744E-2</v>
       </c>
       <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>6228.625</v>
+        <v>4804.3</v>
       </c>
       <c r="O17" s="79">
         <f t="shared" si="6"/>
-        <v>259.52604166666669</v>
+        <v>208.88260869565218</v>
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>1.3466981132075471</v>
+        <v>3.5626506024096383</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -4655,7 +4631,7 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="6"/>
-        <v>17.737500000000001</v>
+        <v>18.508695652173913</v>
       </c>
       <c r="P18" s="96">
         <f t="shared" ref="P18:P22" si="7">L18/I18</f>
@@ -4710,7 +4686,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>17.737500000000001</v>
+        <v>18.508695652173913</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4765,7 +4741,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>17.737500000000001</v>
+        <v>18.508695652173913</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4820,7 +4796,7 @@
       </c>
       <c r="O21" s="14">
         <f t="shared" si="6"/>
-        <v>17.737500000000001</v>
+        <v>18.508695652173913</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="7"/>
@@ -4875,7 +4851,7 @@
       </c>
       <c r="O22" s="94">
         <f t="shared" si="6"/>
-        <v>17.737500000000001</v>
+        <v>18.508695652173913</v>
       </c>
       <c r="P22" s="74">
         <f t="shared" si="7"/>
@@ -4933,7 +4909,7 @@
       </c>
       <c r="O23" s="79">
         <f t="shared" si="6"/>
-        <v>17.737500000000001</v>
+        <v>18.508695652173913</v>
       </c>
       <c r="P23" s="80">
         <f>L23/I23</f>
@@ -4991,7 +4967,7 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="6"/>
-        <v>17.737500000000001</v>
+        <v>18.508695652173913</v>
       </c>
       <c r="P24" s="96">
         <f t="shared" ref="P24:P27" si="9">L24/I24</f>
@@ -5046,7 +5022,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>17.737500000000001</v>
+        <v>18.508695652173913</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5101,7 +5077,7 @@
       </c>
       <c r="O26" s="14">
         <f t="shared" si="6"/>
-        <v>17.737500000000001</v>
+        <v>18.508695652173913</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="9"/>
@@ -5156,7 +5132,7 @@
       </c>
       <c r="O27" s="94">
         <f t="shared" si="6"/>
-        <v>17.737500000000001</v>
+        <v>18.508695652173913</v>
       </c>
       <c r="P27" s="74">
         <f t="shared" si="9"/>
@@ -5211,7 +5187,7 @@
       </c>
       <c r="O28" s="79">
         <f t="shared" si="6"/>
-        <v>17.737500000000001</v>
+        <v>18.508695652173913</v>
       </c>
       <c r="P28" s="80">
         <f>L28/I28</f>
@@ -5244,11 +5220,11 @@
       </c>
       <c r="I29" s="21">
         <f t="shared" si="11"/>
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="J29" s="83">
         <f t="shared" si="3"/>
-        <v>1.1053663754679978E-2</v>
+        <v>1.6402210732750937E-2</v>
       </c>
       <c r="K29" s="84">
         <v>600</v>
@@ -5266,11 +5242,11 @@
       </c>
       <c r="O29" s="87">
         <f t="shared" si="6"/>
-        <v>17.737500000000001</v>
+        <v>18.508695652173913</v>
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>
-        <v>2.8112903225806454</v>
+        <v>1.8945652173913046</v>
       </c>
       <c r="Q29" s="23" t="e">
         <f>AVERAGE(Q28,Q17,Q23)</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DB6FFF-EBFF-4B76-AC56-78B8D8C2B4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C043925-7C2D-4335-B550-67BD62CC4CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -247,7 +247,7 @@
     <t xml:space="preserve">Qasim </t>
   </si>
   <si>
-    <t>SD</t>
+    <t>Sohail Kasoor SD</t>
   </si>
 </sst>
 </file>
@@ -1532,7 +1532,7 @@
     <col min="10" max="10" width="5.54296875" customWidth="1"/>
     <col min="11" max="11" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.81640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5.26953125" customWidth="1"/>
     <col min="15" max="15" width="8.54296875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="7.7265625" bestFit="1" customWidth="1"/>
@@ -1571,7 +1571,7 @@
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="89">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="G2" s="114" t="s">
         <v>2</v>
@@ -1673,7 +1673,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="29" t="s">
         <v>20</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>21</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="E4" s="47" t="s">
         <v>22</v>
@@ -1699,55 +1699,55 @@
         <v>40</v>
       </c>
       <c r="I4" s="12">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J4" s="32">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="K4" s="30">
         <v>40</v>
       </c>
       <c r="L4" s="12">
-        <v>17.875</v>
+        <v>7</v>
       </c>
       <c r="M4" s="32">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.44687500000000002</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="N4" s="90">
         <f>IFERROR(L4/I4,0)</f>
-        <v>1.9861111111111112</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="O4" s="33"/>
       <c r="P4" s="30">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Q4" s="31">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="R4" s="32">
         <f>IFERROR(Q4/P4,0)</f>
-        <v>0.9285714285714286</v>
+        <v>1</v>
       </c>
       <c r="S4" s="30">
-        <v>16.875</v>
+        <v>17.875</v>
       </c>
       <c r="T4" s="31">
-        <v>10.875</v>
+        <v>17.875</v>
       </c>
       <c r="U4" s="32">
         <f>IFERROR(T4/S4,0)</f>
-        <v>0.64444444444444449</v>
+        <v>1</v>
       </c>
       <c r="V4" s="90">
         <f>IFERROR(T4/Q4,0)</f>
-        <v>0.83653846153846156</v>
+        <v>1.9861111111111112</v>
       </c>
       <c r="W4" s="33"/>
       <c r="X4" s="34"/>
     </row>
-    <row r="5" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="35" t="s">
         <v>20</v>
       </c>
@@ -1757,8 +1757,8 @@
       <c r="C5" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="16" t="s">
-        <v>19</v>
+      <c r="D5" s="47" t="s">
+        <v>66</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>22</v>
@@ -1773,55 +1773,55 @@
         <v>45</v>
       </c>
       <c r="I5" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J5" s="13">
         <f t="shared" ref="J5:J32" si="0">IFERROR(I5/G5,0)</f>
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="K5" s="11">
         <v>30</v>
       </c>
       <c r="L5" s="12">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="M5" s="13">
+        <v>9</v>
+      </c>
+      <c r="M5" s="70">
         <f t="shared" ref="M5:M32" si="1">IFERROR(L5/K5,0)</f>
-        <v>0.16999999999999998</v>
-      </c>
-      <c r="N5" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="N5" s="71">
         <f t="shared" ref="N5:N32" si="2">IFERROR(L5/I5,0)</f>
-        <v>1.02</v>
+        <v>2.25</v>
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q5" s="12">
         <v>5</v>
       </c>
       <c r="R5" s="13">
         <f t="shared" ref="R5:R32" si="3">IFERROR(Q5/P5,0)</f>
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="S5" s="11">
-        <v>8.625</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="T5" s="12">
-        <v>6.6</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="U5" s="13">
         <f t="shared" ref="U5:U32" si="4">IFERROR(T5/S5,0)</f>
-        <v>0.76521739130434774</v>
+        <v>1</v>
       </c>
       <c r="V5" s="11">
         <f t="shared" ref="V5:V32" si="5">IFERROR(T5/Q5,0)</f>
-        <v>1.3199999999999998</v>
+        <v>1.02</v>
       </c>
       <c r="W5" s="14"/>
       <c r="X5" s="34"/>
     </row>
-    <row r="6" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="35" t="s">
         <v>20</v>
       </c>
@@ -1831,8 +1831,8 @@
       <c r="C6" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="16" t="s">
-        <v>19</v>
+      <c r="D6" s="47" t="s">
+        <v>66</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>22</v>
@@ -1846,56 +1846,54 @@
       <c r="H6" s="71">
         <v>40</v>
       </c>
-      <c r="I6" s="12">
-        <v>8</v>
-      </c>
+      <c r="I6" s="12"/>
       <c r="J6" s="13">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="K6" s="11">
         <v>25</v>
       </c>
       <c r="L6" s="12">
-        <v>7.45</v>
-      </c>
-      <c r="M6" s="13">
+        <v>0</v>
+      </c>
+      <c r="M6" s="70">
         <f t="shared" si="1"/>
-        <v>0.29799999999999999</v>
-      </c>
-      <c r="N6" s="11">
+        <v>0</v>
+      </c>
+      <c r="N6" s="71">
         <f t="shared" si="2"/>
-        <v>0.93125000000000002</v>
+        <v>0</v>
       </c>
       <c r="O6" s="14"/>
       <c r="P6" s="11">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q6" s="12">
         <v>4</v>
       </c>
       <c r="R6" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="S6" s="11">
-        <v>5</v>
+        <v>7.45</v>
       </c>
       <c r="T6" s="12">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="U6" s="13">
         <f t="shared" si="4"/>
-        <v>0.85</v>
+        <v>0.53691275167785235</v>
       </c>
       <c r="V6" s="11">
         <f t="shared" si="5"/>
-        <v>1.0625</v>
+        <v>1</v>
       </c>
       <c r="W6" s="14"/>
       <c r="X6" s="34"/>
     </row>
-    <row r="7" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="35" t="s">
         <v>20</v>
       </c>
@@ -1905,8 +1903,8 @@
       <c r="C7" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="16" t="s">
-        <v>19</v>
+      <c r="D7" s="47" t="s">
+        <v>66</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>22</v>
@@ -1921,55 +1919,55 @@
         <v>45</v>
       </c>
       <c r="I7" s="12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="K7" s="11">
         <v>30</v>
       </c>
       <c r="L7" s="12">
-        <v>11.05</v>
-      </c>
-      <c r="M7" s="13">
+        <v>7</v>
+      </c>
+      <c r="M7" s="70">
         <f t="shared" si="1"/>
-        <v>0.36833333333333335</v>
-      </c>
-      <c r="N7" s="11">
+        <v>0.23333333333333334</v>
+      </c>
+      <c r="N7" s="71">
         <f t="shared" si="2"/>
-        <v>1.5785714285714287</v>
+        <v>1.1666666666666667</v>
       </c>
       <c r="O7" s="14"/>
       <c r="P7" s="11">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q7" s="12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R7" s="13">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S7" s="11">
-        <v>5.9</v>
+        <v>11.05</v>
       </c>
       <c r="T7" s="12">
-        <v>3</v>
+        <v>5.05</v>
       </c>
       <c r="U7" s="13">
         <f t="shared" si="4"/>
-        <v>0.50847457627118642</v>
+        <v>0.45701357466063341</v>
       </c>
       <c r="V7" s="11">
         <f t="shared" si="5"/>
-        <v>1.5</v>
+        <v>0.84166666666666667</v>
       </c>
       <c r="W7" s="14"/>
       <c r="X7" s="34"/>
     </row>
-    <row r="8" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="35" t="s">
         <v>20</v>
       </c>
@@ -1979,8 +1977,8 @@
       <c r="C8" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="16" t="s">
-        <v>19</v>
+      <c r="D8" s="47" t="s">
+        <v>66</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>22</v>
@@ -1995,55 +1993,55 @@
         <v>40</v>
       </c>
       <c r="I8" s="12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K8" s="11">
         <v>20</v>
       </c>
       <c r="L8" s="12">
-        <v>6.5</v>
-      </c>
-      <c r="M8" s="13">
+        <v>4.75</v>
+      </c>
+      <c r="M8" s="70">
         <f t="shared" si="1"/>
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="N8" s="11">
+        <v>0.23749999999999999</v>
+      </c>
+      <c r="N8" s="71">
         <f t="shared" si="2"/>
-        <v>0.72222222222222221</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="O8" s="14"/>
       <c r="P8" s="11">
+        <v>9</v>
+      </c>
+      <c r="Q8" s="12">
         <v>7</v>
-      </c>
-      <c r="Q8" s="12">
-        <v>6</v>
       </c>
       <c r="R8" s="13">
         <f t="shared" si="3"/>
-        <v>0.8571428571428571</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="S8" s="11">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="T8" s="12">
-        <v>4.95</v>
+        <v>5.15</v>
       </c>
       <c r="U8" s="13">
         <f t="shared" si="4"/>
-        <v>0.86842105263157898</v>
+        <v>0.79230769230769238</v>
       </c>
       <c r="V8" s="11">
         <f t="shared" si="5"/>
-        <v>0.82500000000000007</v>
+        <v>0.73571428571428577</v>
       </c>
       <c r="W8" s="14"/>
       <c r="X8" s="34"/>
     </row>
-    <row r="9" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="35" t="s">
         <v>20</v>
       </c>
@@ -2053,8 +2051,8 @@
       <c r="C9" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="16" t="s">
-        <v>19</v>
+      <c r="D9" s="47" t="s">
+        <v>66</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>22</v>
@@ -2076,20 +2074,20 @@
       <c r="K9" s="11">
         <v>80</v>
       </c>
-      <c r="L9" s="12"/>
-      <c r="M9" s="13">
+      <c r="L9" s="12">
+        <v>0</v>
+      </c>
+      <c r="M9" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N9" s="11">
+      <c r="N9" s="71">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O9" s="14"/>
       <c r="P9" s="11"/>
-      <c r="Q9" s="12">
-        <v>0</v>
-      </c>
+      <c r="Q9" s="12"/>
       <c r="R9" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2111,7 +2109,7 @@
       <c r="W9" s="14"/>
       <c r="X9" s="34"/>
     </row>
-    <row r="10" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="35" t="s">
         <v>20</v>
       </c>
@@ -2121,8 +2119,8 @@
       <c r="C10" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="16" t="s">
-        <v>19</v>
+      <c r="D10" s="47" t="s">
+        <v>66</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>22</v>
@@ -2147,37 +2145,45 @@
         <v>20</v>
       </c>
       <c r="L10" s="12">
-        <v>52</v>
-      </c>
-      <c r="M10" s="13">
+        <v>107</v>
+      </c>
+      <c r="M10" s="70">
         <f t="shared" si="1"/>
-        <v>2.6</v>
-      </c>
-      <c r="N10" s="11">
+        <v>5.35</v>
+      </c>
+      <c r="N10" s="71">
         <f t="shared" si="2"/>
-        <v>10.4</v>
+        <v>21.4</v>
       </c>
       <c r="O10" s="14"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="12"/>
+      <c r="P10" s="11">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>4</v>
+      </c>
       <c r="R10" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S10" s="11"/>
-      <c r="T10" s="12"/>
+        <v>1</v>
+      </c>
+      <c r="S10" s="11">
+        <v>60</v>
+      </c>
+      <c r="T10" s="12">
+        <v>52</v>
+      </c>
       <c r="U10" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="V10" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W10" s="14"/>
       <c r="X10" s="34"/>
     </row>
-    <row r="11" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A11" s="35" t="s">
         <v>20</v>
       </c>
@@ -2187,8 +2193,8 @@
       <c r="C11" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="16" t="s">
-        <v>19</v>
+      <c r="D11" s="47" t="s">
+        <v>66</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>22</v>
@@ -2203,25 +2209,25 @@
         <v>40</v>
       </c>
       <c r="I11" s="12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J11" s="13">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="K11" s="11">
         <v>20</v>
       </c>
       <c r="L11" s="12">
-        <v>9</v>
-      </c>
-      <c r="M11" s="13">
+        <v>8</v>
+      </c>
+      <c r="M11" s="70">
         <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="N11" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="N11" s="71">
         <f t="shared" si="2"/>
-        <v>1.2857142857142858</v>
+        <v>0.8</v>
       </c>
       <c r="O11" s="14"/>
       <c r="P11" s="11"/>
@@ -2243,7 +2249,7 @@
       <c r="W11" s="14"/>
       <c r="X11" s="34"/>
     </row>
-    <row r="12" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="35" t="s">
         <v>20</v>
       </c>
@@ -2253,8 +2259,8 @@
       <c r="C12" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="16" t="s">
-        <v>19</v>
+      <c r="D12" s="47" t="s">
+        <v>66</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>22</v>
@@ -2269,25 +2275,25 @@
         <v>40</v>
       </c>
       <c r="I12" s="12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J12" s="13">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="K12" s="11">
         <v>30</v>
       </c>
       <c r="L12" s="12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M12" s="13">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>0.23333333333333334</v>
       </c>
       <c r="N12" s="11">
         <f t="shared" si="2"/>
-        <v>1.6666666666666667</v>
+        <v>0.875</v>
       </c>
       <c r="O12" s="14"/>
       <c r="P12" s="11"/>
@@ -2309,7 +2315,7 @@
       <c r="W12" s="14"/>
       <c r="X12" s="34"/>
     </row>
-    <row r="13" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A13" s="35" t="s">
         <v>20</v>
       </c>
@@ -2319,8 +2325,8 @@
       <c r="C13" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="16" t="s">
-        <v>19</v>
+      <c r="D13" s="47" t="s">
+        <v>66</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>22</v>
@@ -2335,25 +2341,25 @@
         <v>45</v>
       </c>
       <c r="I13" s="12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J13" s="13">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K13" s="11">
         <v>30</v>
       </c>
       <c r="L13" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M13" s="13">
         <f t="shared" si="1"/>
-        <v>0.13333333333333333</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="N13" s="11">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="O13" s="14"/>
       <c r="P13" s="11"/>
@@ -2385,8 +2391,8 @@
       <c r="C14" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="16" t="s">
-        <v>19</v>
+      <c r="D14" s="47" t="s">
+        <v>66</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>22</v>
@@ -2412,21 +2418,29 @@
         <v>0</v>
       </c>
       <c r="O14" s="14"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="12"/>
+      <c r="P14" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="12">
+        <v>1</v>
+      </c>
       <c r="R14" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="11"/>
-      <c r="T14" s="12"/>
+        <v>1</v>
+      </c>
+      <c r="S14" s="11">
+        <v>90</v>
+      </c>
+      <c r="T14" s="12">
+        <v>90</v>
+      </c>
       <c r="U14" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="W14" s="14"/>
       <c r="X14" s="34"/>
@@ -2750,11 +2764,11 @@
       </c>
       <c r="I20" s="41">
         <f>SUM(I4:I19)</f>
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J20" s="42">
         <f t="shared" si="0"/>
-        <v>0.13478260869565217</v>
+        <v>0.12608695652173912</v>
       </c>
       <c r="K20" s="40">
         <f>SUM(K4:K12)</f>
@@ -2762,15 +2776,15 @@
       </c>
       <c r="L20" s="40">
         <f>SUM(L4:L12)</f>
-        <v>118.97499999999999</v>
+        <v>149.75</v>
       </c>
       <c r="M20" s="42">
         <f t="shared" si="1"/>
-        <v>0.40330508474576271</v>
+        <v>0.50762711864406784</v>
       </c>
       <c r="N20" s="40">
         <f t="shared" si="2"/>
-        <v>1.9189516129032258</v>
+        <v>2.5818965517241379</v>
       </c>
       <c r="O20" s="43">
         <f>AVERAGE(O4:O19)</f>
@@ -2778,31 +2792,31 @@
       </c>
       <c r="P20" s="40">
         <f>SUM(P4:P19)</f>
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="Q20" s="41">
         <f>SUM(Q4:Q19)</f>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="R20" s="42">
         <f t="shared" si="3"/>
-        <v>0.8571428571428571</v>
+        <v>0.83720930232558144</v>
       </c>
       <c r="S20" s="40">
         <f>SUM(S4:S19)</f>
-        <v>42.1</v>
+        <v>197.97499999999999</v>
       </c>
       <c r="T20" s="41">
         <f>SUM(T4:T19)</f>
-        <v>29.675000000000001</v>
+        <v>179.17500000000001</v>
       </c>
       <c r="U20" s="42">
         <f t="shared" si="4"/>
-        <v>0.70486935866983369</v>
+        <v>0.90503851496401067</v>
       </c>
       <c r="V20" s="40">
         <f t="shared" si="5"/>
-        <v>0.98916666666666664</v>
+        <v>4.9770833333333337</v>
       </c>
       <c r="W20" s="43">
         <f>AVERAGE(W4:W19)</f>
@@ -3635,11 +3649,11 @@
       </c>
       <c r="I32" s="21">
         <f t="shared" si="12"/>
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J32" s="22">
         <f t="shared" si="0"/>
-        <v>0.13219616204690832</v>
+        <v>0.12366737739872068</v>
       </c>
       <c r="K32" s="20">
         <v>1</v>
@@ -3653,7 +3667,7 @@
       </c>
       <c r="N32" s="20">
         <f t="shared" si="2"/>
-        <v>1.6129032258064516E-2</v>
+        <v>1.7241379310344827E-2</v>
       </c>
       <c r="O32" s="23">
         <f>AVERAGE(O31,O20,O26)</f>
@@ -3661,31 +3675,31 @@
       </c>
       <c r="P32" s="20">
         <f>+P31+P26+P20</f>
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="Q32" s="21">
         <f t="shared" ref="Q32" si="13">+Q31+Q26+Q20</f>
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="R32" s="22">
         <f t="shared" si="3"/>
-        <v>0.88636363636363635</v>
+        <v>0.86538461538461542</v>
       </c>
       <c r="S32" s="20">
         <f>+S31+S26+S20</f>
-        <v>51.1</v>
+        <v>206.97499999999999</v>
       </c>
       <c r="T32" s="21">
         <f t="shared" ref="T32" si="14">+T31+T26+T20</f>
-        <v>38.674999999999997</v>
+        <v>188.17500000000001</v>
       </c>
       <c r="U32" s="22">
         <f t="shared" si="4"/>
-        <v>0.75684931506849307</v>
+        <v>0.90916777388573511</v>
       </c>
       <c r="V32" s="20">
         <f t="shared" si="5"/>
-        <v>0.99166666666666659</v>
+        <v>4.1816666666666666</v>
       </c>
       <c r="W32" s="23">
         <f>AVERAGE(W31,W20,W26)</f>
@@ -3751,18 +3765,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.14814814814814814</v>
+        <v>0.18518518518518517</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2" s="89">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="G2" s="114" t="s">
         <v>34</v>
@@ -3858,38 +3872,38 @@
         <v>23</v>
       </c>
       <c r="G4" s="30">
-        <v>600</v>
+        <v>325</v>
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>15+13</f>
-        <v>28</v>
+        <f>15+13+9</f>
+        <v>37</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>4.6666666666666669E-2</v>
+        <v>0.11384615384615385</v>
       </c>
       <c r="K4" s="7">
         <v>450</v>
       </c>
       <c r="L4" s="8">
-        <v>38.375</v>
+        <v>56.25</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>8.5277777777777772E-2</v>
+        <v>0.125</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>411.625</v>
+        <v>393.75</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>17.896739130434781</v>
+        <v>17.897727272727273</v>
       </c>
       <c r="P4" s="68">
-        <f t="shared" ref="P4:P13" si="2">L4/I4</f>
-        <v>1.3705357142857142</v>
+        <f t="shared" ref="P4:P14" si="2">L4/I4</f>
+        <v>1.5202702702702702</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3914,38 +3928,38 @@
         <v>24</v>
       </c>
       <c r="G5" s="11">
-        <v>600</v>
+        <v>237</v>
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <f>6+5</f>
-        <v>11</v>
+        <f>6+5+5</f>
+        <v>16</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J29" si="3">IFERROR(I5/G5,0)</f>
-        <v>1.8333333333333333E-2</v>
+        <v>6.7510548523206745E-2</v>
       </c>
       <c r="K5" s="11">
         <v>350</v>
       </c>
       <c r="L5" s="12">
-        <v>25.5</v>
+        <v>30.6</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M29" si="4">IFERROR(L5/K5,0)</f>
-        <v>7.2857142857142856E-2</v>
+        <v>8.7428571428571439E-2</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>324.5</v>
+        <v>319.39999999999998</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>14.108695652173912</v>
+        <v>14.518181818181818</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>2.3181818181818183</v>
+        <v>1.9125000000000001</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -3970,38 +3984,38 @@
         <v>58</v>
       </c>
       <c r="G6" s="11">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="H6" s="71"/>
       <c r="I6" s="12">
-        <f>6+4</f>
-        <v>10</v>
+        <f>6+4+4</f>
+        <v>14</v>
       </c>
       <c r="J6" s="69">
         <f t="shared" si="3"/>
-        <v>1.6666666666666666E-2</v>
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="K6" s="11">
         <v>350</v>
       </c>
       <c r="L6" s="12">
-        <v>25.324999999999999</v>
+        <v>29.324999999999999</v>
       </c>
       <c r="M6" s="70">
         <f t="shared" si="4"/>
-        <v>7.2357142857142856E-2</v>
+        <v>8.3785714285714283E-2</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="0"/>
-        <v>324.67500000000001</v>
+        <v>320.67500000000001</v>
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>14.116304347826087</v>
+        <v>14.576136363636364</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
-        <v>2.5324999999999998</v>
+        <v>2.094642857142857</v>
       </c>
       <c r="Q6" s="14"/>
       <c r="R6" s="34"/>
@@ -4026,38 +4040,38 @@
         <v>53</v>
       </c>
       <c r="G7" s="11">
-        <v>600</v>
+        <v>288</v>
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>2+2</f>
-        <v>4</v>
+        <f>2+2+6</f>
+        <v>10</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>6.6666666666666671E-3</v>
+        <v>3.4722222222222224E-2</v>
       </c>
       <c r="K7" s="11">
         <v>250</v>
       </c>
       <c r="L7" s="12">
-        <v>15.6</v>
+        <v>20.65</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>6.2399999999999997E-2</v>
+        <v>8.2599999999999993E-2</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>234.4</v>
+        <v>229.35</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>10.191304347826087</v>
+        <v>10.424999999999999</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>3.9</v>
+        <v>2.0649999999999999</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4082,38 +4096,38 @@
         <v>59</v>
       </c>
       <c r="G8" s="11">
-        <v>600</v>
+        <v>357</v>
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <f>3+6</f>
-        <v>9</v>
+        <f>3+6+7</f>
+        <v>16</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>1.4999999999999999E-2</v>
+        <v>4.4817927170868348E-2</v>
       </c>
       <c r="K8" s="11">
         <v>250</v>
       </c>
       <c r="L8" s="12">
-        <v>16.899999999999999</v>
+        <v>22.05</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>6.7599999999999993E-2</v>
+        <v>8.8200000000000001E-2</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N29" si="5">K8-L8</f>
-        <v>233.1</v>
+        <v>227.95</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
-        <v>10.134782608695652</v>
+        <v>10.361363636363636</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.8777777777777775</v>
+        <v>1.378125</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4138,10 +4152,12 @@
         <v>70</v>
       </c>
       <c r="G9" s="11">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="H9" s="71"/>
-      <c r="I9" s="12"/>
+      <c r="I9" s="12">
+        <v>0</v>
+      </c>
       <c r="J9" s="69">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4190,37 +4206,38 @@
         <v>25</v>
       </c>
       <c r="G10" s="11">
-        <v>200</v>
+        <v>111</v>
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="12">
-        <v>3</v>
+        <f>3+4</f>
+        <v>7</v>
       </c>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>1.4999999999999999E-2</v>
+        <v>6.3063063063063057E-2</v>
       </c>
       <c r="K10" s="11">
         <v>2300</v>
       </c>
       <c r="L10" s="12">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>6.0869565217391307E-2</v>
+        <v>8.3478260869565224E-2</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>2160</v>
+        <v>2108</v>
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>93.913043478260875</v>
+        <v>95.818181818181813</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>46.666666666666664</v>
+        <v>27.428571428571427</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
@@ -4245,7 +4262,7 @@
         <v>60</v>
       </c>
       <c r="G11" s="11">
-        <v>600</v>
+        <v>322</v>
       </c>
       <c r="H11" s="71"/>
       <c r="I11" s="12">
@@ -4253,7 +4270,7 @@
       </c>
       <c r="J11" s="69">
         <f t="shared" si="3"/>
-        <v>1.4999999999999999E-2</v>
+        <v>2.7950310559006212E-2</v>
       </c>
       <c r="K11" s="11">
         <v>450</v>
@@ -4271,7 +4288,7 @@
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>18.782608695652176</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
@@ -4300,7 +4317,7 @@
         <v>61</v>
       </c>
       <c r="G12" s="11">
-        <v>600</v>
+        <v>311</v>
       </c>
       <c r="H12" s="71"/>
       <c r="I12" s="12">
@@ -4308,7 +4325,7 @@
       </c>
       <c r="J12" s="69">
         <f t="shared" si="3"/>
-        <v>1.4999999999999999E-2</v>
+        <v>2.8938906752411574E-2</v>
       </c>
       <c r="K12" s="11">
         <v>300</v>
@@ -4326,7 +4343,7 @@
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>12.521739130434783</v>
+        <v>13.090909090909092</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
@@ -4355,7 +4372,7 @@
         <v>62</v>
       </c>
       <c r="G13" s="11">
-        <v>600</v>
+        <v>140</v>
       </c>
       <c r="H13" s="71"/>
       <c r="I13" s="12">
@@ -4381,7 +4398,7 @@
       </c>
       <c r="O13" s="14">
         <f t="shared" si="6"/>
-        <v>10.695652173913043</v>
+        <v>11.181818181818182</v>
       </c>
       <c r="P13" s="71" t="e">
         <f t="shared" si="2"/>
@@ -4410,29 +4427,36 @@
         <v>63</v>
       </c>
       <c r="G14" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="71"/>
-      <c r="I14" s="12"/>
+      <c r="I14" s="12">
+        <v>1</v>
+      </c>
       <c r="J14" s="69">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="11"/>
-      <c r="L14" s="12"/>
+      <c r="L14" s="12">
+        <v>90</v>
+      </c>
       <c r="M14" s="70">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N14" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="O14" s="14">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P14" s="71"/>
+        <v>-4.0909090909090908</v>
+      </c>
+      <c r="P14" s="71">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
       <c r="Q14" s="14"/>
       <c r="R14" s="34"/>
     </row>
@@ -4541,19 +4565,19 @@
       <c r="F17" s="107"/>
       <c r="G17" s="40">
         <f>SUM(G4:G14)</f>
-        <v>5600</v>
+        <v>2492</v>
       </c>
       <c r="H17" s="41">
         <f>SUM(H4:H13)</f>
         <v>0</v>
       </c>
       <c r="I17" s="41">
-        <f>SUM(I4:I13)</f>
-        <v>83</v>
+        <f>SUM(I4:I14)</f>
+        <v>119</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>1.4821428571428572E-2</v>
+        <v>4.7752808988764044E-2</v>
       </c>
       <c r="K17" s="76">
         <f>SUM(K4:K16)</f>
@@ -4561,23 +4585,23 @@
       </c>
       <c r="L17" s="77">
         <f>SUM(L4:L16)</f>
-        <v>295.7</v>
+        <v>474.875</v>
       </c>
       <c r="M17" s="78">
         <f t="shared" si="4"/>
-        <v>5.7980392156862744E-2</v>
+        <v>9.3112745098039212E-2</v>
       </c>
       <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>4804.3</v>
+        <v>4625.125</v>
       </c>
       <c r="O17" s="79">
         <f t="shared" si="6"/>
-        <v>208.88260869565218</v>
+        <v>210.23295454545453</v>
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>3.5626506024096383</v>
+        <v>3.990546218487395</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -4631,7 +4655,7 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="6"/>
-        <v>18.508695652173913</v>
+        <v>19.349999999999998</v>
       </c>
       <c r="P18" s="96">
         <f t="shared" ref="P18:P22" si="7">L18/I18</f>
@@ -4686,7 +4710,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>18.508695652173913</v>
+        <v>19.349999999999998</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4741,7 +4765,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>18.508695652173913</v>
+        <v>19.349999999999998</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4796,7 +4820,7 @@
       </c>
       <c r="O21" s="14">
         <f t="shared" si="6"/>
-        <v>18.508695652173913</v>
+        <v>19.349999999999998</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="7"/>
@@ -4851,7 +4875,7 @@
       </c>
       <c r="O22" s="94">
         <f t="shared" si="6"/>
-        <v>18.508695652173913</v>
+        <v>19.349999999999998</v>
       </c>
       <c r="P22" s="74">
         <f t="shared" si="7"/>
@@ -4909,7 +4933,7 @@
       </c>
       <c r="O23" s="79">
         <f t="shared" si="6"/>
-        <v>18.508695652173913</v>
+        <v>19.349999999999998</v>
       </c>
       <c r="P23" s="80">
         <f>L23/I23</f>
@@ -4967,7 +4991,7 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="6"/>
-        <v>18.508695652173913</v>
+        <v>19.349999999999998</v>
       </c>
       <c r="P24" s="96">
         <f t="shared" ref="P24:P27" si="9">L24/I24</f>
@@ -5022,7 +5046,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>18.508695652173913</v>
+        <v>19.349999999999998</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5077,7 +5101,7 @@
       </c>
       <c r="O26" s="14">
         <f t="shared" si="6"/>
-        <v>18.508695652173913</v>
+        <v>19.349999999999998</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="9"/>
@@ -5132,7 +5156,7 @@
       </c>
       <c r="O27" s="94">
         <f t="shared" si="6"/>
-        <v>18.508695652173913</v>
+        <v>19.349999999999998</v>
       </c>
       <c r="P27" s="74">
         <f t="shared" si="9"/>
@@ -5187,7 +5211,7 @@
       </c>
       <c r="O28" s="79">
         <f t="shared" si="6"/>
-        <v>18.508695652173913</v>
+        <v>19.349999999999998</v>
       </c>
       <c r="P28" s="80">
         <f>L28/I28</f>
@@ -5212,7 +5236,7 @@
       <c r="F29" s="57"/>
       <c r="G29" s="20">
         <f>+G28+G23+G17</f>
-        <v>5609</v>
+        <v>2501</v>
       </c>
       <c r="H29" s="21">
         <f t="shared" ref="H29:I29" si="11">+H28+H23+H17</f>
@@ -5220,11 +5244,11 @@
       </c>
       <c r="I29" s="21">
         <f t="shared" si="11"/>
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="J29" s="83">
         <f t="shared" si="3"/>
-        <v>1.6402210732750937E-2</v>
+        <v>5.117952818872451E-2</v>
       </c>
       <c r="K29" s="84">
         <v>600</v>
@@ -5242,11 +5266,11 @@
       </c>
       <c r="O29" s="87">
         <f t="shared" si="6"/>
-        <v>18.508695652173913</v>
+        <v>19.349999999999998</v>
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>
-        <v>1.8945652173913046</v>
+        <v>1.3617187500000001</v>
       </c>
       <c r="Q29" s="23" t="e">
         <f>AVERAGE(Q28,Q17,Q23)</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C043925-7C2D-4335-B550-67BD62CC4CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28705802-277D-4156-8D3D-682D5BAD9AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="77">
   <si>
     <t>Booking</t>
   </si>
@@ -248,6 +248,15 @@
   </si>
   <si>
     <t>Sohail Kasoor SD</t>
+  </si>
+  <si>
+    <t>Absent</t>
+  </si>
+  <si>
+    <t>ABSENT</t>
+  </si>
+  <si>
+    <t>Delivery Pending</t>
   </si>
 </sst>
 </file>
@@ -920,7 +929,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1236,6 +1245,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1571,7 +1581,7 @@
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="89">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="G2" s="114" t="s">
         <v>2</v>
@@ -1721,20 +1731,20 @@
       </c>
       <c r="O4" s="33"/>
       <c r="P4" s="30">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q4" s="31">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R4" s="32">
         <f>IFERROR(Q4/P4,0)</f>
         <v>1</v>
       </c>
       <c r="S4" s="30">
-        <v>17.875</v>
+        <v>7</v>
       </c>
       <c r="T4" s="31">
-        <v>17.875</v>
+        <v>7</v>
       </c>
       <c r="U4" s="32">
         <f>IFERROR(T4/S4,0)</f>
@@ -1742,7 +1752,7 @@
       </c>
       <c r="V4" s="90">
         <f>IFERROR(T4/Q4,0)</f>
-        <v>1.9861111111111112</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="W4" s="33"/>
       <c r="X4" s="34"/>
@@ -1783,40 +1793,40 @@
         <v>30</v>
       </c>
       <c r="L5" s="12">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M32" si="1">IFERROR(L5/K5,0)</f>
-        <v>0.3</v>
+        <v>0.18333333333333332</v>
       </c>
       <c r="N5" s="71">
         <f t="shared" ref="N5:N32" si="2">IFERROR(L5/I5,0)</f>
-        <v>2.25</v>
+        <v>1.375</v>
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q5" s="12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R5" s="13">
         <f t="shared" ref="R5:R32" si="3">IFERROR(Q5/P5,0)</f>
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="S5" s="11">
-        <v>5.0999999999999996</v>
+        <v>9</v>
       </c>
       <c r="T5" s="12">
-        <v>5.0999999999999996</v>
+        <v>2.5</v>
       </c>
       <c r="U5" s="13">
         <f t="shared" ref="U5:U32" si="4">IFERROR(T5/S5,0)</f>
-        <v>1</v>
+        <v>0.27777777777777779</v>
       </c>
       <c r="V5" s="11">
         <f t="shared" ref="V5:V32" si="5">IFERROR(T5/Q5,0)</f>
-        <v>1.02</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W5" s="14"/>
       <c r="X5" s="34"/>
@@ -1866,32 +1876,30 @@
         <v>0</v>
       </c>
       <c r="O6" s="14"/>
-      <c r="P6" s="11">
-        <v>8</v>
-      </c>
-      <c r="Q6" s="12">
-        <v>4</v>
-      </c>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="12"/>
       <c r="R6" s="13">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S6" s="11">
-        <v>7.45</v>
+        <v>0</v>
       </c>
       <c r="T6" s="12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U6" s="13">
         <f t="shared" si="4"/>
-        <v>0.53691275167785235</v>
+        <v>0</v>
       </c>
       <c r="V6" s="11">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6" s="14"/>
-      <c r="X6" s="34"/>
+      <c r="X6" s="34" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="7" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="35" t="s">
@@ -1919,50 +1927,50 @@
         <v>45</v>
       </c>
       <c r="I7" s="12">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="K7" s="11">
         <v>30</v>
       </c>
       <c r="L7" s="12">
-        <v>7</v>
+        <v>13.45</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="1"/>
-        <v>0.23333333333333334</v>
+        <v>0.44833333333333331</v>
       </c>
       <c r="N7" s="71">
         <f t="shared" si="2"/>
-        <v>1.1666666666666667</v>
+        <v>1.4944444444444445</v>
       </c>
       <c r="O7" s="14"/>
       <c r="P7" s="11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q7" s="12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R7" s="13">
         <f t="shared" si="3"/>
-        <v>0.8571428571428571</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="S7" s="11">
-        <v>11.05</v>
+        <v>7</v>
       </c>
       <c r="T7" s="12">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="U7" s="13">
         <f t="shared" si="4"/>
-        <v>0.45701357466063341</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="V7" s="11">
         <f t="shared" si="5"/>
-        <v>0.84166666666666667</v>
+        <v>1.25</v>
       </c>
       <c r="W7" s="14"/>
       <c r="X7" s="34"/>
@@ -1993,50 +2001,50 @@
         <v>40</v>
       </c>
       <c r="I8" s="12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="K8" s="11">
         <v>20</v>
       </c>
       <c r="L8" s="12">
-        <v>4.75</v>
+        <v>8.5</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="1"/>
-        <v>0.23749999999999999</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="N8" s="71">
         <f t="shared" si="2"/>
-        <v>0.6785714285714286</v>
+        <v>1.4166666666666667</v>
       </c>
       <c r="O8" s="14"/>
       <c r="P8" s="11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q8" s="12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R8" s="13">
         <f t="shared" si="3"/>
-        <v>0.77777777777777779</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S8" s="11">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="T8" s="12">
-        <v>5.15</v>
+        <v>3.45</v>
       </c>
       <c r="U8" s="13">
         <f t="shared" si="4"/>
-        <v>0.79230769230769238</v>
+        <v>0.72631578947368425</v>
       </c>
       <c r="V8" s="11">
         <f t="shared" si="5"/>
-        <v>0.73571428571428577</v>
+        <v>0.57500000000000007</v>
       </c>
       <c r="W8" s="14"/>
       <c r="X8" s="34"/>
@@ -2135,50 +2143,50 @@
         <v>10</v>
       </c>
       <c r="I10" s="12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10" s="13">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K10" s="11">
         <v>20</v>
       </c>
       <c r="L10" s="12">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="1"/>
-        <v>5.35</v>
+        <v>3.5</v>
       </c>
       <c r="N10" s="71">
         <f t="shared" si="2"/>
-        <v>21.4</v>
+        <v>11.666666666666666</v>
       </c>
       <c r="O10" s="14"/>
       <c r="P10" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q10" s="12">
         <v>4</v>
       </c>
       <c r="R10" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="S10" s="11">
-        <v>60</v>
+        <v>107</v>
       </c>
       <c r="T10" s="12">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="U10" s="13">
         <f t="shared" si="4"/>
-        <v>0.8666666666666667</v>
+        <v>0.67289719626168221</v>
       </c>
       <c r="V10" s="11">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="W10" s="14"/>
       <c r="X10" s="34"/>
@@ -2219,25 +2227,33 @@
         <v>20</v>
       </c>
       <c r="L11" s="12">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="N11" s="71">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="O11" s="14"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="12"/>
+      <c r="P11" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>0</v>
+      </c>
       <c r="R11" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S11" s="11"/>
-      <c r="T11" s="12"/>
+      <c r="S11" s="11">
+        <v>0</v>
+      </c>
+      <c r="T11" s="12">
+        <v>0</v>
+      </c>
       <c r="U11" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -2275,11 +2291,11 @@
         <v>40</v>
       </c>
       <c r="I12" s="12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J12" s="13">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="K12" s="11">
         <v>30</v>
@@ -2293,17 +2309,25 @@
       </c>
       <c r="N12" s="11">
         <f t="shared" si="2"/>
-        <v>0.875</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="O12" s="14"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="12"/>
+      <c r="P12" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>0</v>
+      </c>
       <c r="R12" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S12" s="11"/>
-      <c r="T12" s="12"/>
+      <c r="S12" s="11">
+        <v>0</v>
+      </c>
+      <c r="T12" s="12">
+        <v>0</v>
+      </c>
       <c r="U12" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -2341,35 +2365,43 @@
         <v>45</v>
       </c>
       <c r="I13" s="12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J13" s="13">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="K13" s="11">
         <v>30</v>
       </c>
       <c r="L13" s="12">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M13" s="13">
         <f t="shared" si="1"/>
-        <v>0.16666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="N13" s="11">
         <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
+        <v>1.875</v>
       </c>
       <c r="O13" s="14"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="12"/>
+      <c r="P13" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="12">
+        <v>0</v>
+      </c>
       <c r="R13" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S13" s="11"/>
-      <c r="T13" s="12"/>
+      <c r="S13" s="11">
+        <v>0</v>
+      </c>
+      <c r="T13" s="12">
+        <v>0</v>
+      </c>
       <c r="U13" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -2764,11 +2796,11 @@
       </c>
       <c r="I20" s="41">
         <f>SUM(I4:I19)</f>
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J20" s="42">
         <f t="shared" si="0"/>
-        <v>0.12608695652173912</v>
+        <v>0.13695652173913042</v>
       </c>
       <c r="K20" s="40">
         <f>SUM(K4:K12)</f>
@@ -2776,15 +2808,15 @@
       </c>
       <c r="L20" s="40">
         <f>SUM(L4:L12)</f>
-        <v>149.75</v>
+        <v>123.45</v>
       </c>
       <c r="M20" s="42">
         <f t="shared" si="1"/>
-        <v>0.50762711864406784</v>
+        <v>0.41847457627118645</v>
       </c>
       <c r="N20" s="40">
         <f t="shared" si="2"/>
-        <v>2.5818965517241379</v>
+        <v>1.9595238095238097</v>
       </c>
       <c r="O20" s="43">
         <f>AVERAGE(O4:O19)</f>
@@ -2792,31 +2824,31 @@
       </c>
       <c r="P20" s="40">
         <f>SUM(P4:P19)</f>
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="Q20" s="41">
         <f>SUM(Q4:Q19)</f>
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="R20" s="42">
         <f t="shared" si="3"/>
-        <v>0.83720930232558144</v>
+        <v>0.8529411764705882</v>
       </c>
       <c r="S20" s="40">
         <f>SUM(S4:S19)</f>
-        <v>197.97499999999999</v>
+        <v>224.75</v>
       </c>
       <c r="T20" s="41">
         <f>SUM(T4:T19)</f>
-        <v>179.17500000000001</v>
+        <v>179.95</v>
       </c>
       <c r="U20" s="42">
         <f t="shared" si="4"/>
-        <v>0.90503851496401067</v>
+        <v>0.80066740823136817</v>
       </c>
       <c r="V20" s="40">
         <f t="shared" si="5"/>
-        <v>4.9770833333333337</v>
+        <v>6.205172413793103</v>
       </c>
       <c r="W20" s="43">
         <f>AVERAGE(W4:W19)</f>
@@ -3649,11 +3681,11 @@
       </c>
       <c r="I32" s="21">
         <f t="shared" si="12"/>
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J32" s="22">
         <f t="shared" si="0"/>
-        <v>0.12366737739872068</v>
+        <v>0.13432835820895522</v>
       </c>
       <c r="K32" s="20">
         <v>1</v>
@@ -3667,7 +3699,7 @@
       </c>
       <c r="N32" s="20">
         <f t="shared" si="2"/>
-        <v>1.7241379310344827E-2</v>
+        <v>1.5873015873015872E-2</v>
       </c>
       <c r="O32" s="23">
         <f>AVERAGE(O31,O20,O26)</f>
@@ -3675,31 +3707,31 @@
       </c>
       <c r="P32" s="20">
         <f>+P31+P26+P20</f>
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="Q32" s="21">
         <f t="shared" ref="Q32" si="13">+Q31+Q26+Q20</f>
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="R32" s="22">
         <f t="shared" si="3"/>
-        <v>0.86538461538461542</v>
+        <v>0.88372093023255816</v>
       </c>
       <c r="S32" s="20">
         <f>+S31+S26+S20</f>
-        <v>206.97499999999999</v>
+        <v>233.75</v>
       </c>
       <c r="T32" s="21">
         <f t="shared" ref="T32" si="14">+T31+T26+T20</f>
-        <v>188.17500000000001</v>
+        <v>188.95</v>
       </c>
       <c r="U32" s="22">
         <f t="shared" si="4"/>
-        <v>0.90916777388573511</v>
+        <v>0.80834224598930482</v>
       </c>
       <c r="V32" s="20">
         <f t="shared" si="5"/>
-        <v>4.1816666666666666</v>
+        <v>4.9723684210526313</v>
       </c>
       <c r="W32" s="23">
         <f>AVERAGE(W31,W20,W26)</f>
@@ -3743,7 +3775,7 @@
     <col min="13" max="13" width="7.7265625" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="7.7265625" customWidth="1"/>
     <col min="16" max="16" width="5.26953125" customWidth="1"/>
-    <col min="18" max="18" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3765,18 +3797,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.18518518518518517</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2" s="89">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="G2" s="114" t="s">
         <v>34</v>
@@ -3876,34 +3908,34 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>15+13+9</f>
-        <v>37</v>
+        <f>15+13+9+11</f>
+        <v>48</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.11384615384615385</v>
+        <v>0.14769230769230771</v>
       </c>
       <c r="K4" s="7">
         <v>450</v>
       </c>
       <c r="L4" s="8">
-        <v>56.25</v>
+        <v>63.25</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.125</v>
+        <v>0.14055555555555554</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>393.75</v>
+        <v>386.75</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>17.897727272727273</v>
+        <v>18.416666666666668</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P14" si="2">L4/I4</f>
-        <v>1.5202702702702702</v>
+        <v>1.3177083333333333</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3932,34 +3964,34 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <f>6+5+5</f>
-        <v>16</v>
+        <f>6+5+5+3</f>
+        <v>19</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J29" si="3">IFERROR(I5/G5,0)</f>
-        <v>6.7510548523206745E-2</v>
+        <v>8.0168776371308023E-2</v>
       </c>
       <c r="K5" s="11">
         <v>350</v>
       </c>
       <c r="L5" s="12">
-        <v>30.6</v>
+        <v>33.1</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M29" si="4">IFERROR(L5/K5,0)</f>
-        <v>8.7428571428571439E-2</v>
+        <v>9.457142857142857E-2</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>319.39999999999998</v>
+        <v>316.89999999999998</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>14.518181818181818</v>
+        <v>15.09047619047619</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>1.9125000000000001</v>
+        <v>1.7421052631578948</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -4011,14 +4043,16 @@
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>14.576136363636364</v>
+        <v>15.270238095238096</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
         <v>2.094642857142857</v>
       </c>
       <c r="Q6" s="14"/>
-      <c r="R6" s="34"/>
+      <c r="R6" s="119" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="7" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="35" t="s">
@@ -4044,34 +4078,34 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>2+2+6</f>
-        <v>10</v>
+        <f>2+2+6+4</f>
+        <v>14</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>3.4722222222222224E-2</v>
+        <v>4.8611111111111112E-2</v>
       </c>
       <c r="K7" s="11">
         <v>250</v>
       </c>
       <c r="L7" s="12">
-        <v>20.65</v>
+        <v>25.65</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>8.2599999999999993E-2</v>
+        <v>0.1026</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>229.35</v>
+        <v>224.35</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>10.424999999999999</v>
+        <v>10.683333333333334</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>2.0649999999999999</v>
+        <v>1.8321428571428571</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4100,34 +4134,34 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <f>3+6+7</f>
-        <v>16</v>
+        <f>3+6+7+6</f>
+        <v>22</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>4.4817927170868348E-2</v>
+        <v>6.1624649859943981E-2</v>
       </c>
       <c r="K8" s="11">
         <v>250</v>
       </c>
       <c r="L8" s="12">
-        <v>22.05</v>
+        <v>25.5</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>8.8200000000000001E-2</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N29" si="5">K8-L8</f>
-        <v>227.95</v>
+        <v>224.5</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
-        <v>10.361363636363636</v>
+        <v>10.69047619047619</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.378125</v>
+        <v>1.1590909090909092</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4210,34 +4244,34 @@
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="12">
-        <f>3+4</f>
-        <v>7</v>
+        <f>3+4+4</f>
+        <v>11</v>
       </c>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>6.3063063063063057E-2</v>
+        <v>9.90990990990991E-2</v>
       </c>
       <c r="K10" s="11">
         <v>2300</v>
       </c>
       <c r="L10" s="12">
-        <v>192</v>
+        <v>304</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>8.3478260869565224E-2</v>
+        <v>0.13217391304347825</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>2108</v>
+        <v>1996</v>
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>95.818181818181813</v>
+        <v>95.047619047619051</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>27.428571428571427</v>
+        <v>27.636363636363637</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
@@ -4288,14 +4322,16 @@
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>19.636363636363637</v>
+        <v>20.571428571428573</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Q11" s="14"/>
-      <c r="R11" s="34"/>
+      <c r="R11" s="119" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="12" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="35" t="s">
@@ -4343,14 +4379,16 @@
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>13.090909090909092</v>
+        <v>13.714285714285714</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
         <v>1.3333333333333333</v>
       </c>
       <c r="Q12" s="14"/>
-      <c r="R12" s="34"/>
+      <c r="R12" s="119" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A13" s="35" t="s">
@@ -4398,14 +4436,16 @@
       </c>
       <c r="O13" s="14">
         <f t="shared" si="6"/>
-        <v>11.181818181818182</v>
+        <v>11.714285714285714</v>
       </c>
       <c r="P13" s="71" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q13" s="14"/>
-      <c r="R13" s="14"/>
+      <c r="R13" s="119" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="14" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="35" t="s">
@@ -4451,7 +4491,7 @@
       </c>
       <c r="O14" s="14">
         <f t="shared" si="6"/>
-        <v>-4.0909090909090908</v>
+        <v>-4.2857142857142856</v>
       </c>
       <c r="P14" s="71">
         <f t="shared" si="2"/>
@@ -4573,11 +4613,11 @@
       </c>
       <c r="I17" s="41">
         <f>SUM(I4:I14)</f>
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>4.7752808988764044E-2</v>
+        <v>5.8988764044943819E-2</v>
       </c>
       <c r="K17" s="76">
         <f>SUM(K4:K16)</f>
@@ -4585,23 +4625,23 @@
       </c>
       <c r="L17" s="77">
         <f>SUM(L4:L16)</f>
-        <v>474.875</v>
+        <v>604.82500000000005</v>
       </c>
       <c r="M17" s="78">
         <f t="shared" si="4"/>
-        <v>9.3112745098039212E-2</v>
+        <v>0.11859313725490198</v>
       </c>
       <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>4625.125</v>
+        <v>4495.1750000000002</v>
       </c>
       <c r="O17" s="79">
         <f t="shared" si="6"/>
-        <v>210.23295454545453</v>
+        <v>214.05595238095239</v>
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>3.990546218487395</v>
+        <v>4.1144557823129251</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -4655,7 +4695,7 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="6"/>
-        <v>19.349999999999998</v>
+        <v>20.271428571428572</v>
       </c>
       <c r="P18" s="96">
         <f t="shared" ref="P18:P22" si="7">L18/I18</f>
@@ -4710,7 +4750,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>19.349999999999998</v>
+        <v>20.271428571428572</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4765,7 +4805,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>19.349999999999998</v>
+        <v>20.271428571428572</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4820,7 +4860,7 @@
       </c>
       <c r="O21" s="14">
         <f t="shared" si="6"/>
-        <v>19.349999999999998</v>
+        <v>20.271428571428572</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="7"/>
@@ -4875,7 +4915,7 @@
       </c>
       <c r="O22" s="94">
         <f t="shared" si="6"/>
-        <v>19.349999999999998</v>
+        <v>20.271428571428572</v>
       </c>
       <c r="P22" s="74">
         <f t="shared" si="7"/>
@@ -4933,7 +4973,7 @@
       </c>
       <c r="O23" s="79">
         <f t="shared" si="6"/>
-        <v>19.349999999999998</v>
+        <v>20.271428571428572</v>
       </c>
       <c r="P23" s="80">
         <f>L23/I23</f>
@@ -4991,7 +5031,7 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="6"/>
-        <v>19.349999999999998</v>
+        <v>20.271428571428572</v>
       </c>
       <c r="P24" s="96">
         <f t="shared" ref="P24:P27" si="9">L24/I24</f>
@@ -5046,7 +5086,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>19.349999999999998</v>
+        <v>20.271428571428572</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5101,7 +5141,7 @@
       </c>
       <c r="O26" s="14">
         <f t="shared" si="6"/>
-        <v>19.349999999999998</v>
+        <v>20.271428571428572</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="9"/>
@@ -5156,7 +5196,7 @@
       </c>
       <c r="O27" s="94">
         <f t="shared" si="6"/>
-        <v>19.349999999999998</v>
+        <v>20.271428571428572</v>
       </c>
       <c r="P27" s="74">
         <f t="shared" si="9"/>
@@ -5211,7 +5251,7 @@
       </c>
       <c r="O28" s="79">
         <f t="shared" si="6"/>
-        <v>19.349999999999998</v>
+        <v>20.271428571428572</v>
       </c>
       <c r="P28" s="80">
         <f>L28/I28</f>
@@ -5244,11 +5284,11 @@
       </c>
       <c r="I29" s="21">
         <f t="shared" si="11"/>
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="J29" s="83">
         <f t="shared" si="3"/>
-        <v>5.117952818872451E-2</v>
+        <v>6.2375049980008E-2</v>
       </c>
       <c r="K29" s="84">
         <v>600</v>
@@ -5266,11 +5306,11 @@
       </c>
       <c r="O29" s="87">
         <f t="shared" si="6"/>
-        <v>19.349999999999998</v>
+        <v>20.271428571428572</v>
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>
-        <v>1.3617187500000001</v>
+        <v>1.1173076923076923</v>
       </c>
       <c r="Q29" s="23" t="e">
         <f>AVERAGE(Q28,Q17,Q23)</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28705802-277D-4156-8D3D-682D5BAD9AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D28AD26-DF38-47AC-B15B-90DBAE913E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="79">
   <si>
     <t>Booking</t>
   </si>
@@ -217,12 +217,6 @@
     <t xml:space="preserve">Yasir </t>
   </si>
   <si>
-    <t>Kasur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riwand </t>
-  </si>
-  <si>
     <t>Nabeel Traders</t>
   </si>
   <si>
@@ -257,6 +251,18 @@
   </si>
   <si>
     <t>Delivery Pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Still Pending </t>
+  </si>
+  <si>
+    <t>Abdullah Traders SD</t>
+  </si>
+  <si>
+    <t>Kasur SD</t>
+  </si>
+  <si>
+    <t>Nabeel Traders SD</t>
   </si>
 </sst>
 </file>
@@ -929,7 +935,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1194,6 +1200,13 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1245,7 +1258,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1557,55 +1569,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G1" s="108" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="111" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-      <c r="W1" s="113"/>
+      <c r="G1" s="111" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="114" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
+      <c r="V1" s="115"/>
+      <c r="W1" s="116"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="89">
-        <v>46302</v>
-      </c>
-      <c r="G2" s="114" t="s">
+        <v>46304</v>
+      </c>
+      <c r="G2" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="115" t="s">
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="115"/>
-      <c r="M2" s="116"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="119"/>
       <c r="N2" s="1"/>
       <c r="O2" s="2"/>
-      <c r="P2" s="114" t="s">
+      <c r="P2" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="115"/>
-      <c r="R2" s="116"/>
-      <c r="S2" s="115" t="s">
+      <c r="Q2" s="118"/>
+      <c r="R2" s="119"/>
+      <c r="S2" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="T2" s="115"/>
-      <c r="U2" s="116"/>
+      <c r="T2" s="118"/>
+      <c r="U2" s="119"/>
       <c r="V2" s="1"/>
       <c r="W2" s="2"/>
     </row>
@@ -1694,13 +1706,13 @@
         <v>21</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E4" s="47" t="s">
         <v>22</v>
       </c>
       <c r="F4" s="48" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G4" s="30">
         <v>50</v>
@@ -1709,50 +1721,50 @@
         <v>40</v>
       </c>
       <c r="I4" s="12">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J4" s="32">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="K4" s="30">
         <v>40</v>
       </c>
       <c r="L4" s="12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M4" s="32">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.17499999999999999</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="N4" s="90">
         <f>IFERROR(L4/I4,0)</f>
-        <v>0.63636363636363635</v>
+        <v>1.125</v>
       </c>
       <c r="O4" s="33"/>
       <c r="P4" s="30">
         <v>11</v>
       </c>
       <c r="Q4" s="31">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R4" s="32">
         <f>IFERROR(Q4/P4,0)</f>
-        <v>1</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="S4" s="30">
         <v>7</v>
       </c>
       <c r="T4" s="31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U4" s="32">
         <f>IFERROR(T4/S4,0)</f>
-        <v>1</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="V4" s="90">
         <f>IFERROR(T4/Q4,0)</f>
-        <v>0.63636363636363635</v>
+        <v>0.5</v>
       </c>
       <c r="W4" s="33"/>
       <c r="X4" s="34"/>
@@ -1768,7 +1780,7 @@
         <v>21</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>22</v>
@@ -1783,25 +1795,25 @@
         <v>45</v>
       </c>
       <c r="I5" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5" s="13">
         <f t="shared" ref="J5:J32" si="0">IFERROR(I5/G5,0)</f>
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="K5" s="11">
         <v>30</v>
       </c>
       <c r="L5" s="12">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M32" si="1">IFERROR(L5/K5,0)</f>
-        <v>0.18333333333333332</v>
+        <v>0.2</v>
       </c>
       <c r="N5" s="71">
         <f t="shared" ref="N5:N32" si="2">IFERROR(L5/I5,0)</f>
-        <v>1.375</v>
+        <v>1.2</v>
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="11">
@@ -1815,18 +1827,18 @@
         <v>0.75</v>
       </c>
       <c r="S5" s="11">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="T5" s="12">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="U5" s="13">
         <f t="shared" ref="U5:U32" si="4">IFERROR(T5/S5,0)</f>
-        <v>0.27777777777777779</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="V5" s="11">
         <f t="shared" ref="V5:V32" si="5">IFERROR(T5/Q5,0)</f>
-        <v>0.83333333333333337</v>
+        <v>1.5</v>
       </c>
       <c r="W5" s="14"/>
       <c r="X5" s="34"/>
@@ -1842,13 +1854,13 @@
         <v>21</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G6" s="11">
         <v>50</v>
@@ -1856,7 +1868,9 @@
       <c r="H6" s="71">
         <v>40</v>
       </c>
-      <c r="I6" s="12"/>
+      <c r="I6" s="12">
+        <v>0</v>
+      </c>
       <c r="J6" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1897,8 +1911,8 @@
         <v>0</v>
       </c>
       <c r="W6" s="14"/>
-      <c r="X6" s="34" t="s">
-        <v>74</v>
+      <c r="X6" s="104" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
@@ -1912,7 +1926,7 @@
         <v>21</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>22</v>
@@ -1937,43 +1951,43 @@
         <v>30</v>
       </c>
       <c r="L7" s="12">
-        <v>13.45</v>
+        <v>8.1</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="1"/>
-        <v>0.44833333333333331</v>
+        <v>0.26999999999999996</v>
       </c>
       <c r="N7" s="71">
         <f t="shared" si="2"/>
-        <v>1.4944444444444445</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="O7" s="14"/>
       <c r="P7" s="11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q7" s="12">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R7" s="13">
         <f t="shared" si="3"/>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="S7" s="11">
-        <v>7</v>
+        <v>13.45</v>
       </c>
       <c r="T7" s="12">
-        <v>5</v>
+        <v>13.45</v>
       </c>
       <c r="U7" s="13">
         <f t="shared" si="4"/>
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
       <c r="V7" s="11">
         <f t="shared" si="5"/>
-        <v>1.25</v>
+        <v>1.4944444444444445</v>
       </c>
       <c r="W7" s="14"/>
-      <c r="X7" s="34"/>
+      <c r="X7" s="103"/>
     </row>
     <row r="8" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="35" t="s">
@@ -1986,7 +2000,7 @@
         <v>21</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>22</v>
@@ -2000,54 +2014,50 @@
       <c r="H8" s="71">
         <v>40</v>
       </c>
-      <c r="I8" s="12">
-        <v>6</v>
-      </c>
+      <c r="I8" s="12"/>
       <c r="J8" s="13">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="K8" s="11">
         <v>20</v>
       </c>
-      <c r="L8" s="12">
-        <v>8.5</v>
-      </c>
+      <c r="L8" s="12"/>
       <c r="M8" s="70">
         <f t="shared" si="1"/>
-        <v>0.42499999999999999</v>
+        <v>0</v>
       </c>
       <c r="N8" s="71">
         <f t="shared" si="2"/>
-        <v>1.4166666666666667</v>
+        <v>0</v>
       </c>
       <c r="O8" s="14"/>
       <c r="P8" s="11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q8" s="12">
         <v>6</v>
       </c>
       <c r="R8" s="13">
         <f t="shared" si="3"/>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="S8" s="11">
-        <v>4.75</v>
+        <v>8.5</v>
       </c>
       <c r="T8" s="12">
-        <v>3.45</v>
+        <v>7.9249999999999998</v>
       </c>
       <c r="U8" s="13">
         <f t="shared" si="4"/>
-        <v>0.72631578947368425</v>
+        <v>0.93235294117647061</v>
       </c>
       <c r="V8" s="11">
         <f t="shared" si="5"/>
-        <v>0.57500000000000007</v>
+        <v>1.3208333333333333</v>
       </c>
       <c r="W8" s="14"/>
-      <c r="X8" s="34"/>
+      <c r="X8" s="103"/>
     </row>
     <row r="9" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="35" t="s">
@@ -2060,13 +2070,13 @@
         <v>21</v>
       </c>
       <c r="D9" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G9" s="11">
         <v>50</v>
@@ -2082,9 +2092,7 @@
       <c r="K9" s="11">
         <v>80</v>
       </c>
-      <c r="L9" s="12">
-        <v>0</v>
-      </c>
+      <c r="L9" s="12"/>
       <c r="M9" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2115,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="W9" s="14"/>
-      <c r="X9" s="34"/>
+      <c r="X9" s="103"/>
     </row>
     <row r="10" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="35" t="s">
@@ -2128,13 +2136,13 @@
         <v>21</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G10" s="11">
         <v>10</v>
@@ -2142,54 +2150,50 @@
       <c r="H10" s="71">
         <v>10</v>
       </c>
-      <c r="I10" s="12">
-        <v>6</v>
-      </c>
+      <c r="I10" s="12"/>
       <c r="J10" s="13">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="K10" s="11">
         <v>20</v>
       </c>
-      <c r="L10" s="12">
-        <v>70</v>
-      </c>
+      <c r="L10" s="12"/>
       <c r="M10" s="70">
         <f t="shared" si="1"/>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N10" s="71">
         <f t="shared" si="2"/>
-        <v>11.666666666666666</v>
+        <v>0</v>
       </c>
       <c r="O10" s="14"/>
       <c r="P10" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q10" s="12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R10" s="13">
         <f t="shared" si="3"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="S10" s="11">
-        <v>107</v>
+        <v>69.5</v>
       </c>
       <c r="T10" s="12">
-        <v>72</v>
+        <v>69.5</v>
       </c>
       <c r="U10" s="13">
         <f t="shared" si="4"/>
-        <v>0.67289719626168221</v>
+        <v>1</v>
       </c>
       <c r="V10" s="11">
         <f t="shared" si="5"/>
-        <v>18</v>
+        <v>11.583333333333334</v>
       </c>
       <c r="W10" s="14"/>
-      <c r="X10" s="34"/>
+      <c r="X10" s="103"/>
     </row>
     <row r="11" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A11" s="35" t="s">
@@ -2202,54 +2206,46 @@
         <v>21</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G11" s="11">
         <v>50</v>
       </c>
-      <c r="H11" s="71">
-        <v>40</v>
-      </c>
-      <c r="I11" s="12">
-        <v>10</v>
-      </c>
+      <c r="H11" s="71"/>
+      <c r="I11" s="12"/>
       <c r="J11" s="13">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K11" s="11">
         <v>20</v>
       </c>
-      <c r="L11" s="12">
-        <v>12</v>
-      </c>
+      <c r="L11" s="12"/>
       <c r="M11" s="70">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N11" s="71">
         <f t="shared" si="2"/>
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O11" s="14"/>
       <c r="P11" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="12">
-        <v>0</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="Q11" s="12"/>
       <c r="R11" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S11" s="11">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T11" s="12">
         <v>0</v>
@@ -2263,7 +2259,9 @@
         <v>0</v>
       </c>
       <c r="W11" s="14"/>
-      <c r="X11" s="34"/>
+      <c r="X11" s="104" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="12" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="35" t="s">
@@ -2276,54 +2274,46 @@
         <v>21</v>
       </c>
       <c r="D12" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G12" s="11">
         <v>50</v>
       </c>
-      <c r="H12" s="71">
-        <v>40</v>
-      </c>
-      <c r="I12" s="12">
-        <v>9</v>
-      </c>
+      <c r="H12" s="71"/>
+      <c r="I12" s="12"/>
       <c r="J12" s="13">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="K12" s="11">
         <v>30</v>
       </c>
-      <c r="L12" s="12">
-        <v>7</v>
-      </c>
+      <c r="L12" s="12"/>
       <c r="M12" s="13">
         <f t="shared" si="1"/>
-        <v>0.23333333333333334</v>
+        <v>0</v>
       </c>
       <c r="N12" s="11">
         <f t="shared" si="2"/>
-        <v>0.77777777777777779</v>
+        <v>0</v>
       </c>
       <c r="O12" s="14"/>
       <c r="P12" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="12">
-        <v>0</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="Q12" s="12"/>
       <c r="R12" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S12" s="11">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T12" s="12">
         <v>0</v>
@@ -2337,7 +2327,9 @@
         <v>0</v>
       </c>
       <c r="W12" s="14"/>
-      <c r="X12" s="34"/>
+      <c r="X12" s="104" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="13" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A13" s="35" t="s">
@@ -2350,7 +2342,7 @@
         <v>21</v>
       </c>
       <c r="D13" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>22</v>
@@ -2361,43 +2353,35 @@
       <c r="G13" s="11">
         <v>50</v>
       </c>
-      <c r="H13" s="71">
-        <v>45</v>
-      </c>
-      <c r="I13" s="12">
-        <v>8</v>
-      </c>
+      <c r="H13" s="71"/>
+      <c r="I13" s="12"/>
       <c r="J13" s="13">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="K13" s="11">
         <v>30</v>
       </c>
-      <c r="L13" s="12">
-        <v>15</v>
-      </c>
+      <c r="L13" s="12"/>
       <c r="M13" s="13">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N13" s="11">
         <f t="shared" si="2"/>
-        <v>1.875</v>
+        <v>0</v>
       </c>
       <c r="O13" s="14"/>
       <c r="P13" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="12">
-        <v>0</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="Q13" s="12"/>
       <c r="R13" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S13" s="11">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="T13" s="12">
         <v>0</v>
@@ -2411,9 +2395,11 @@
         <v>0</v>
       </c>
       <c r="W13" s="14"/>
-      <c r="X13" s="34"/>
-    </row>
-    <row r="14" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="X13" s="104" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="35" t="s">
         <v>20</v>
       </c>
@@ -2424,15 +2410,17 @@
         <v>21</v>
       </c>
       <c r="D14" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F14" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="G14" s="11"/>
+        <v>71</v>
+      </c>
+      <c r="G14" s="11">
+        <v>1</v>
+      </c>
       <c r="H14" s="71"/>
       <c r="I14" s="12"/>
       <c r="J14" s="13">
@@ -2475,7 +2463,7 @@
         <v>90</v>
       </c>
       <c r="W14" s="14"/>
-      <c r="X14" s="34"/>
+      <c r="X14" s="103"/>
     </row>
     <row r="15" spans="1:24" ht="16.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15" s="35" t="s">
@@ -2709,7 +2697,7 @@
       <c r="W18" s="14"/>
       <c r="X18" s="34"/>
     </row>
-    <row r="19" spans="1:24" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A19" s="35" t="s">
         <v>20</v>
       </c>
@@ -2725,27 +2713,33 @@
       <c r="E19" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="50"/>
-      <c r="G19" s="36"/>
+      <c r="F19" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="36">
+        <v>1</v>
+      </c>
       <c r="H19" s="74"/>
-      <c r="I19" s="37"/>
+      <c r="I19" s="37">
+        <v>1</v>
+      </c>
       <c r="J19" s="38">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="36">
         <v>1</v>
       </c>
       <c r="L19" s="37">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="M19" s="38">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="N19" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O19" s="39">
         <v>1</v>
@@ -2781,74 +2775,74 @@
       <c r="C20" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="102" t="s">
+      <c r="D20" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="103"/>
-      <c r="F20" s="104"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="107"/>
       <c r="G20" s="40">
         <f>SUM(G4:G19)</f>
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H20" s="41">
         <f>SUM(H4:H19)</f>
-        <v>345</v>
+        <v>220</v>
       </c>
       <c r="I20" s="41">
         <f>SUM(I4:I19)</f>
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="J20" s="42">
         <f t="shared" si="0"/>
-        <v>0.13695652173913042</v>
+        <v>4.9783549783549784E-2</v>
       </c>
       <c r="K20" s="40">
-        <f>SUM(K4:K12)</f>
-        <v>295</v>
+        <f t="shared" ref="K20:L20" si="6">SUM(K4:K19)</f>
+        <v>330</v>
       </c>
       <c r="L20" s="40">
-        <f>SUM(L4:L12)</f>
-        <v>123.45</v>
+        <f t="shared" si="6"/>
+        <v>227.1</v>
       </c>
       <c r="M20" s="42">
         <f t="shared" si="1"/>
-        <v>0.41847457627118645</v>
+        <v>0.68818181818181812</v>
       </c>
       <c r="N20" s="40">
         <f t="shared" si="2"/>
-        <v>1.9595238095238097</v>
+        <v>9.8739130434782609</v>
       </c>
       <c r="O20" s="43">
         <f>AVERAGE(O4:O19)</f>
         <v>1</v>
       </c>
       <c r="P20" s="40">
-        <f>SUM(P4:P19)</f>
-        <v>34</v>
+        <f t="shared" ref="P20" si="7">SUM(P4:P19)</f>
+        <v>64</v>
       </c>
       <c r="Q20" s="41">
-        <f>SUM(Q4:Q19)</f>
-        <v>29</v>
+        <f t="shared" ref="Q20" si="8">SUM(Q4:Q19)</f>
+        <v>35</v>
       </c>
       <c r="R20" s="42">
         <f t="shared" si="3"/>
-        <v>0.8529411764705882</v>
+        <v>0.546875</v>
       </c>
       <c r="S20" s="40">
-        <f>SUM(S4:S19)</f>
-        <v>224.75</v>
+        <f t="shared" ref="S20" si="9">SUM(S4:S19)</f>
+        <v>227.95</v>
       </c>
       <c r="T20" s="41">
-        <f>SUM(T4:T19)</f>
-        <v>179.95</v>
+        <f t="shared" ref="T20" si="10">SUM(T4:T19)</f>
+        <v>190.375</v>
       </c>
       <c r="U20" s="42">
         <f t="shared" si="4"/>
-        <v>0.80066740823136817</v>
+        <v>0.83516121956569422</v>
       </c>
       <c r="V20" s="40">
         <f t="shared" si="5"/>
-        <v>6.205172413793103</v>
+        <v>5.4392857142857141</v>
       </c>
       <c r="W20" s="43">
         <f>AVERAGE(W4:W19)</f>
@@ -3220,21 +3214,21 @@
       <c r="C26" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="102" t="s">
+      <c r="D26" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="E26" s="103"/>
-      <c r="F26" s="104"/>
+      <c r="E26" s="106"/>
+      <c r="F26" s="107"/>
       <c r="G26" s="40">
         <f>SUM(G21:G25)</f>
         <v>5</v>
       </c>
       <c r="H26" s="41">
-        <f t="shared" ref="H26:I26" si="6">SUM(H21:H25)</f>
+        <f t="shared" ref="H26:I26" si="11">SUM(H21:H25)</f>
         <v>0</v>
       </c>
       <c r="I26" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J26" s="42">
@@ -3264,7 +3258,7 @@
         <v>5</v>
       </c>
       <c r="Q26" s="41">
-        <f t="shared" ref="Q26" si="7">SUM(Q21:Q25)</f>
+        <f t="shared" ref="Q26" si="12">SUM(Q21:Q25)</f>
         <v>5</v>
       </c>
       <c r="R26" s="42">
@@ -3276,7 +3270,7 @@
         <v>5</v>
       </c>
       <c r="T26" s="41">
-        <f t="shared" ref="T26" si="8">SUM(T21:T25)</f>
+        <f t="shared" ref="T26" si="13">SUM(T21:T25)</f>
         <v>5</v>
       </c>
       <c r="U26" s="42">
@@ -3587,21 +3581,21 @@
       <c r="C31" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="D31" s="105" t="s">
+      <c r="D31" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="E31" s="106"/>
-      <c r="F31" s="107"/>
+      <c r="E31" s="109"/>
+      <c r="F31" s="110"/>
       <c r="G31" s="40">
         <f>SUM(G27:G30)</f>
         <v>4</v>
       </c>
       <c r="H31" s="41">
-        <f t="shared" ref="H31:I31" si="9">SUM(H27:H30)</f>
+        <f t="shared" ref="H31:I31" si="14">SUM(H27:H30)</f>
         <v>0</v>
       </c>
       <c r="I31" s="41">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="J31" s="42">
@@ -3631,7 +3625,7 @@
         <v>4</v>
       </c>
       <c r="Q31" s="41">
-        <f t="shared" ref="Q31" si="10">SUM(Q27:Q30)</f>
+        <f t="shared" ref="Q31" si="15">SUM(Q27:Q30)</f>
         <v>4</v>
       </c>
       <c r="R31" s="42">
@@ -3643,7 +3637,7 @@
         <v>4</v>
       </c>
       <c r="T31" s="41">
-        <f t="shared" ref="T31" si="11">SUM(T27:T30)</f>
+        <f t="shared" ref="T31" si="16">SUM(T27:T30)</f>
         <v>4</v>
       </c>
       <c r="U31" s="42">
@@ -3673,19 +3667,19 @@
       <c r="F32" s="57"/>
       <c r="G32" s="20">
         <f>+G31+G26+G20</f>
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="H32" s="21">
-        <f t="shared" ref="H32:I32" si="12">+H31+H26+H20</f>
-        <v>345</v>
+        <f t="shared" ref="H32:I32" si="17">+H31+H26+H20</f>
+        <v>220</v>
       </c>
       <c r="I32" s="21">
-        <f t="shared" si="12"/>
-        <v>63</v>
+        <f t="shared" si="17"/>
+        <v>23</v>
       </c>
       <c r="J32" s="22">
         <f t="shared" si="0"/>
-        <v>0.13432835820895522</v>
+        <v>4.8832271762208071E-2</v>
       </c>
       <c r="K32" s="20">
         <v>1</v>
@@ -3699,7 +3693,7 @@
       </c>
       <c r="N32" s="20">
         <f t="shared" si="2"/>
-        <v>1.5873015873015872E-2</v>
+        <v>4.3478260869565216E-2</v>
       </c>
       <c r="O32" s="23">
         <f>AVERAGE(O31,O20,O26)</f>
@@ -3707,31 +3701,31 @@
       </c>
       <c r="P32" s="20">
         <f>+P31+P26+P20</f>
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="Q32" s="21">
-        <f t="shared" ref="Q32" si="13">+Q31+Q26+Q20</f>
-        <v>38</v>
+        <f t="shared" ref="Q32" si="18">+Q31+Q26+Q20</f>
+        <v>44</v>
       </c>
       <c r="R32" s="22">
         <f t="shared" si="3"/>
-        <v>0.88372093023255816</v>
+        <v>0.60273972602739723</v>
       </c>
       <c r="S32" s="20">
         <f>+S31+S26+S20</f>
-        <v>233.75</v>
+        <v>236.95</v>
       </c>
       <c r="T32" s="21">
-        <f t="shared" ref="T32" si="14">+T31+T26+T20</f>
-        <v>188.95</v>
+        <f t="shared" ref="T32" si="19">+T31+T26+T20</f>
+        <v>199.375</v>
       </c>
       <c r="U32" s="22">
         <f t="shared" si="4"/>
-        <v>0.80834224598930482</v>
+        <v>0.84142224097910956</v>
       </c>
       <c r="V32" s="20">
         <f t="shared" si="5"/>
-        <v>4.9723684210526313</v>
+        <v>4.53125</v>
       </c>
       <c r="W32" s="23">
         <f>AVERAGE(W31,W20,W26)</f>
@@ -3797,36 +3791,36 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.22222222222222221</v>
+        <v>0.25925925925925924</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" s="89">
-        <v>46302</v>
-      </c>
-      <c r="G2" s="114" t="s">
+        <v>46303</v>
+      </c>
+      <c r="G2" s="117" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="115"/>
-      <c r="K2" s="111" t="s">
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="114" t="s">
         <v>48</v>
       </c>
-      <c r="L2" s="112"/>
-      <c r="M2" s="112"/>
-      <c r="N2" s="112"/>
-      <c r="O2" s="113"/>
-      <c r="P2" s="117" t="s">
+      <c r="L2" s="115"/>
+      <c r="M2" s="115"/>
+      <c r="N2" s="115"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="120" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" s="118"/>
+      <c r="Q2" s="121"/>
     </row>
     <row r="3" spans="1:18" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="25" t="s">
@@ -3895,7 +3889,7 @@
         <v>21</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E4" s="47" t="s">
         <v>22</v>
@@ -3908,34 +3902,34 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>15+13+9+11</f>
-        <v>48</v>
+        <f>15+13+9+11+10</f>
+        <v>58</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.14769230769230771</v>
+        <v>0.17846153846153845</v>
       </c>
       <c r="K4" s="7">
         <v>450</v>
       </c>
       <c r="L4" s="8">
-        <v>63.25</v>
+        <v>68.25</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.14055555555555554</v>
+        <v>0.15166666666666667</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>386.75</v>
+        <v>381.75</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>18.416666666666668</v>
+        <v>19.087499999999999</v>
       </c>
       <c r="P4" s="68">
-        <f t="shared" ref="P4:P14" si="2">L4/I4</f>
-        <v>1.3177083333333333</v>
+        <f t="shared" ref="P4:P15" si="2">L4/I4</f>
+        <v>1.1767241379310345</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3951,7 +3945,7 @@
         <v>21</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>22</v>
@@ -3964,34 +3958,34 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <f>6+5+5+3</f>
-        <v>19</v>
+        <f>6+5+5+3+3</f>
+        <v>22</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J29" si="3">IFERROR(I5/G5,0)</f>
-        <v>8.0168776371308023E-2</v>
+        <v>9.2827004219409287E-2</v>
       </c>
       <c r="K5" s="11">
         <v>350</v>
       </c>
       <c r="L5" s="12">
-        <v>33.1</v>
+        <v>37.6</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M29" si="4">IFERROR(L5/K5,0)</f>
-        <v>9.457142857142857E-2</v>
+        <v>0.10742857142857143</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>316.89999999999998</v>
+        <v>312.39999999999998</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>15.09047619047619</v>
+        <v>15.62</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>1.7421052631578948</v>
+        <v>1.7090909090909092</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -4007,7 +4001,7 @@
         <v>21</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>22</v>
@@ -4043,15 +4037,15 @@
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>15.270238095238096</v>
+        <v>16.033750000000001</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
         <v>2.094642857142857</v>
       </c>
       <c r="Q6" s="14"/>
-      <c r="R6" s="119" t="s">
-        <v>75</v>
+      <c r="R6" s="102" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
@@ -4065,7 +4059,7 @@
         <v>21</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>22</v>
@@ -4078,34 +4072,34 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>2+2+6+4</f>
-        <v>14</v>
+        <f>2+2+6+4+9</f>
+        <v>23</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>4.8611111111111112E-2</v>
+        <v>7.9861111111111105E-2</v>
       </c>
       <c r="K7" s="11">
         <v>250</v>
       </c>
       <c r="L7" s="12">
-        <v>25.65</v>
+        <v>39.1</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>0.1026</v>
+        <v>0.15640000000000001</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>224.35</v>
+        <v>210.9</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>10.683333333333334</v>
+        <v>10.545</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.8321428571428571</v>
+        <v>1.7</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4121,7 +4115,7 @@
         <v>21</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>22</v>
@@ -4134,34 +4128,34 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <f>3+6+7+6</f>
-        <v>22</v>
+        <f>3+6+7+6+6</f>
+        <v>28</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>6.1624649859943981E-2</v>
+        <v>7.8431372549019607E-2</v>
       </c>
       <c r="K8" s="11">
         <v>250</v>
       </c>
       <c r="L8" s="12">
-        <v>25.5</v>
+        <v>33.424999999999997</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>0.10199999999999999</v>
+        <v>0.13369999999999999</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N29" si="5">K8-L8</f>
-        <v>224.5</v>
+        <v>216.57499999999999</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
-        <v>10.69047619047619</v>
+        <v>10.828749999999999</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.1590909090909092</v>
+        <v>1.1937499999999999</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4177,13 +4171,13 @@
         <v>21</v>
       </c>
       <c r="D9" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G9" s="11">
         <v>150</v>
@@ -4231,7 +4225,7 @@
         <v>21</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>22</v>
@@ -4244,34 +4238,34 @@
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="12">
-        <f>3+4+4</f>
-        <v>11</v>
+        <f>3+4+4+6</f>
+        <v>17</v>
       </c>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>9.90990990990991E-2</v>
+        <v>0.15315315315315314</v>
       </c>
       <c r="K10" s="11">
         <v>2300</v>
       </c>
       <c r="L10" s="12">
-        <v>304</v>
+        <v>374</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>0.13217391304347825</v>
+        <v>0.16260869565217392</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>1996</v>
+        <v>1926</v>
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>95.047619047619051</v>
+        <v>96.3</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>27.636363636363637</v>
+        <v>22</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
@@ -4287,7 +4281,7 @@
         <v>21</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>22</v>
@@ -4322,15 +4316,15 @@
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>20.571428571428573</v>
+        <v>21.6</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Q11" s="14"/>
-      <c r="R11" s="119" t="s">
-        <v>76</v>
+      <c r="R11" s="102" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
@@ -4344,7 +4338,7 @@
         <v>21</v>
       </c>
       <c r="D12" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>22</v>
@@ -4379,15 +4373,15 @@
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>13.714285714285714</v>
+        <v>14.4</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
         <v>1.3333333333333333</v>
       </c>
       <c r="Q12" s="14"/>
-      <c r="R12" s="119" t="s">
-        <v>76</v>
+      <c r="R12" s="102" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
@@ -4401,7 +4395,7 @@
         <v>21</v>
       </c>
       <c r="D13" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>22</v>
@@ -4436,15 +4430,15 @@
       </c>
       <c r="O13" s="14">
         <f t="shared" si="6"/>
-        <v>11.714285714285714</v>
+        <v>12.3</v>
       </c>
       <c r="P13" s="71" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q13" s="14"/>
-      <c r="R13" s="119" t="s">
-        <v>76</v>
+      <c r="R13" s="102" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
@@ -4458,13 +4452,13 @@
         <v>21</v>
       </c>
       <c r="D14" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F14" s="100" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="G14" s="11">
         <v>1</v>
@@ -4491,7 +4485,7 @@
       </c>
       <c r="O14" s="14">
         <f t="shared" si="6"/>
-        <v>-4.2857142857142856</v>
+        <v>-4.5</v>
       </c>
       <c r="P14" s="71">
         <f t="shared" si="2"/>
@@ -4511,36 +4505,45 @@
         <v>21</v>
       </c>
       <c r="D15" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F15" s="100" t="s">
-        <v>64</v>
-      </c>
-      <c r="G15" s="11"/>
+        <v>76</v>
+      </c>
+      <c r="G15" s="11">
+        <v>1</v>
+      </c>
       <c r="H15" s="71"/>
-      <c r="I15" s="12"/>
+      <c r="I15" s="12">
+        <v>1</v>
+      </c>
       <c r="J15" s="69">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="11"/>
-      <c r="L15" s="12"/>
+      <c r="L15" s="12">
+        <v>75</v>
+      </c>
       <c r="M15" s="70">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N15" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="O15" s="14">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P15" s="71"/>
+        <v>-3.75</v>
+      </c>
+      <c r="P15" s="71">
+        <f t="shared" si="2"/>
+        <v>75</v>
+      </c>
       <c r="Q15" s="14"/>
       <c r="R15" s="34"/>
     </row>
@@ -4555,13 +4558,13 @@
         <v>21</v>
       </c>
       <c r="D16" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E16" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F16" s="101" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G16" s="11"/>
       <c r="H16" s="71"/>
@@ -4598,26 +4601,26 @@
       <c r="C17" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="105" t="s">
+      <c r="D17" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="106"/>
-      <c r="F17" s="107"/>
+      <c r="E17" s="109"/>
+      <c r="F17" s="110"/>
       <c r="G17" s="40">
-        <f>SUM(G4:G14)</f>
-        <v>2492</v>
+        <f>SUM(G4:G15)</f>
+        <v>2493</v>
       </c>
       <c r="H17" s="41">
         <f>SUM(H4:H13)</f>
         <v>0</v>
       </c>
       <c r="I17" s="41">
-        <f>SUM(I4:I14)</f>
-        <v>147</v>
+        <f>SUM(I4:I15)</f>
+        <v>182</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>5.8988764044943819E-2</v>
+        <v>7.300441235459286E-2</v>
       </c>
       <c r="K17" s="76">
         <f>SUM(K4:K16)</f>
@@ -4625,23 +4628,23 @@
       </c>
       <c r="L17" s="77">
         <f>SUM(L4:L16)</f>
-        <v>604.82500000000005</v>
+        <v>780.7</v>
       </c>
       <c r="M17" s="78">
         <f t="shared" si="4"/>
-        <v>0.11859313725490198</v>
+        <v>0.15307843137254903</v>
       </c>
       <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>4495.1750000000002</v>
+        <v>4319.3</v>
       </c>
       <c r="O17" s="79">
         <f t="shared" si="6"/>
-        <v>214.05595238095239</v>
+        <v>215.965</v>
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>4.1144557823129251</v>
+        <v>4.2895604395604394</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -4695,7 +4698,7 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="6"/>
-        <v>20.271428571428572</v>
+        <v>21.285</v>
       </c>
       <c r="P18" s="96">
         <f t="shared" ref="P18:P22" si="7">L18/I18</f>
@@ -4750,7 +4753,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>20.271428571428572</v>
+        <v>21.285</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4805,7 +4808,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>20.271428571428572</v>
+        <v>21.285</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4860,7 +4863,7 @@
       </c>
       <c r="O21" s="14">
         <f t="shared" si="6"/>
-        <v>20.271428571428572</v>
+        <v>21.285</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="7"/>
@@ -4915,7 +4918,7 @@
       </c>
       <c r="O22" s="94">
         <f t="shared" si="6"/>
-        <v>20.271428571428572</v>
+        <v>21.285</v>
       </c>
       <c r="P22" s="74">
         <f t="shared" si="7"/>
@@ -4936,11 +4939,11 @@
       <c r="C23" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="105" t="s">
+      <c r="D23" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="E23" s="106"/>
-      <c r="F23" s="107"/>
+      <c r="E23" s="109"/>
+      <c r="F23" s="110"/>
       <c r="G23" s="40">
         <f>SUM(G18:G22)</f>
         <v>5</v>
@@ -4973,7 +4976,7 @@
       </c>
       <c r="O23" s="79">
         <f t="shared" si="6"/>
-        <v>20.271428571428572</v>
+        <v>21.285</v>
       </c>
       <c r="P23" s="80">
         <f>L23/I23</f>
@@ -5031,7 +5034,7 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="6"/>
-        <v>20.271428571428572</v>
+        <v>21.285</v>
       </c>
       <c r="P24" s="96">
         <f t="shared" ref="P24:P27" si="9">L24/I24</f>
@@ -5086,7 +5089,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>20.271428571428572</v>
+        <v>21.285</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5141,7 +5144,7 @@
       </c>
       <c r="O26" s="14">
         <f t="shared" si="6"/>
-        <v>20.271428571428572</v>
+        <v>21.285</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="9"/>
@@ -5196,7 +5199,7 @@
       </c>
       <c r="O27" s="94">
         <f t="shared" si="6"/>
-        <v>20.271428571428572</v>
+        <v>21.285</v>
       </c>
       <c r="P27" s="74">
         <f t="shared" si="9"/>
@@ -5217,11 +5220,11 @@
       <c r="C28" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="105" t="s">
+      <c r="D28" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="E28" s="106"/>
-      <c r="F28" s="107"/>
+      <c r="E28" s="109"/>
+      <c r="F28" s="110"/>
       <c r="G28" s="40">
         <f>SUM(G24:G27)</f>
         <v>4</v>
@@ -5251,7 +5254,7 @@
       </c>
       <c r="O28" s="79">
         <f t="shared" si="6"/>
-        <v>20.271428571428572</v>
+        <v>21.285</v>
       </c>
       <c r="P28" s="80">
         <f>L28/I28</f>
@@ -5276,7 +5279,7 @@
       <c r="F29" s="57"/>
       <c r="G29" s="20">
         <f>+G28+G23+G17</f>
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="H29" s="21">
         <f t="shared" ref="H29:I29" si="11">+H28+H23+H17</f>
@@ -5284,11 +5287,11 @@
       </c>
       <c r="I29" s="21">
         <f t="shared" si="11"/>
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="J29" s="83">
         <f t="shared" si="3"/>
-        <v>6.2375049980008E-2</v>
+        <v>7.633892885691447E-2</v>
       </c>
       <c r="K29" s="84">
         <v>600</v>
@@ -5306,11 +5309,11 @@
       </c>
       <c r="O29" s="87">
         <f t="shared" si="6"/>
-        <v>20.271428571428572</v>
+        <v>21.285</v>
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>
-        <v>1.1173076923076923</v>
+        <v>0.91256544502617809</v>
       </c>
       <c r="Q29" s="23" t="e">
         <f>AVERAGE(Q28,Q17,Q23)</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D28AD26-DF38-47AC-B15B-90DBAE913E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C40E53-3D9F-4FCE-AC75-9003B1090377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="77">
   <si>
     <t>Booking</t>
   </si>
@@ -248,12 +248,6 @@
   </si>
   <si>
     <t>ABSENT</t>
-  </si>
-  <si>
-    <t>Delivery Pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Still Pending </t>
   </si>
   <si>
     <t>Abdullah Traders SD</t>
@@ -935,7 +929,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1258,6 +1252,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1593,7 +1592,7 @@
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="89">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="G2" s="117" t="s">
         <v>2</v>
@@ -1746,25 +1745,25 @@
         <v>11</v>
       </c>
       <c r="Q4" s="31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R4" s="32">
         <f>IFERROR(Q4/P4,0)</f>
-        <v>0.90909090909090906</v>
+        <v>1</v>
       </c>
       <c r="S4" s="30">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T4" s="31">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="U4" s="32">
         <f>IFERROR(T4/S4,0)</f>
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
       <c r="V4" s="90">
         <f>IFERROR(T4/Q4,0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W4" s="33"/>
       <c r="X4" s="34"/>
@@ -1820,25 +1819,25 @@
         <v>4</v>
       </c>
       <c r="Q5" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R5" s="13">
         <f t="shared" ref="R5:R32" si="3">IFERROR(Q5/P5,0)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="S5" s="11">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="T5" s="12">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="U5" s="13">
         <f t="shared" ref="U5:U32" si="4">IFERROR(T5/S5,0)</f>
-        <v>0.81818181818181823</v>
+        <v>1</v>
       </c>
       <c r="V5" s="11">
         <f t="shared" ref="V5:V32" si="5">IFERROR(T5/Q5,0)</f>
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="W5" s="14"/>
       <c r="X5" s="34"/>
@@ -1868,9 +1867,7 @@
       <c r="H6" s="71">
         <v>40</v>
       </c>
-      <c r="I6" s="12">
-        <v>0</v>
-      </c>
+      <c r="I6" s="12"/>
       <c r="J6" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1962,21 +1959,17 @@
         <v>0.89999999999999991</v>
       </c>
       <c r="O7" s="14"/>
-      <c r="P7" s="11">
-        <v>9</v>
-      </c>
-      <c r="Q7" s="12">
-        <v>9</v>
-      </c>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="12"/>
       <c r="R7" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" s="11">
-        <v>13.45</v>
+        <v>3</v>
       </c>
       <c r="T7" s="12">
-        <v>13.45</v>
+        <v>3</v>
       </c>
       <c r="U7" s="13">
         <f t="shared" si="4"/>
@@ -1984,7 +1977,7 @@
       </c>
       <c r="V7" s="11">
         <f t="shared" si="5"/>
-        <v>1.4944444444444445</v>
+        <v>0</v>
       </c>
       <c r="W7" s="14"/>
       <c r="X7" s="103"/>
@@ -2014,47 +2007,51 @@
       <c r="H8" s="71">
         <v>40</v>
       </c>
-      <c r="I8" s="12"/>
+      <c r="I8" s="12">
+        <v>6</v>
+      </c>
       <c r="J8" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="K8" s="11">
         <v>20</v>
       </c>
-      <c r="L8" s="12"/>
+      <c r="L8" s="12">
+        <v>6</v>
+      </c>
       <c r="M8" s="70">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="N8" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="14"/>
       <c r="P8" s="11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="12">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R8" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="S8" s="11">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="T8" s="12">
-        <v>7.9249999999999998</v>
+        <v>3</v>
       </c>
       <c r="U8" s="13">
         <f t="shared" si="4"/>
-        <v>0.93235294117647061</v>
+        <v>0.75</v>
       </c>
       <c r="V8" s="11">
         <f t="shared" si="5"/>
-        <v>1.3208333333333333</v>
+        <v>1</v>
       </c>
       <c r="W8" s="14"/>
       <c r="X8" s="103"/>
@@ -2150,50 +2147,54 @@
       <c r="H10" s="71">
         <v>10</v>
       </c>
-      <c r="I10" s="12"/>
+      <c r="I10" s="12">
+        <v>3</v>
+      </c>
       <c r="J10" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K10" s="11">
         <v>20</v>
       </c>
-      <c r="L10" s="12"/>
+      <c r="L10" s="12">
+        <v>66</v>
+      </c>
       <c r="M10" s="70">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N10" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O10" s="14"/>
       <c r="P10" s="11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R10" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="S10" s="11">
-        <v>69.5</v>
+        <v>52</v>
       </c>
       <c r="T10" s="12">
-        <v>69.5</v>
+        <v>46</v>
       </c>
       <c r="U10" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.88461538461538458</v>
       </c>
       <c r="V10" s="11">
         <f t="shared" si="5"/>
-        <v>11.583333333333334</v>
+        <v>23</v>
       </c>
       <c r="W10" s="14"/>
-      <c r="X10" s="103"/>
+      <c r="X10" s="122"/>
     </row>
     <row r="11" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A11" s="35" t="s">
@@ -2217,51 +2218,57 @@
       <c r="G11" s="11">
         <v>50</v>
       </c>
-      <c r="H11" s="71"/>
-      <c r="I11" s="12"/>
+      <c r="H11" s="71">
+        <v>50</v>
+      </c>
+      <c r="I11" s="12">
+        <v>26</v>
+      </c>
       <c r="J11" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="K11" s="11">
         <v>20</v>
       </c>
-      <c r="L11" s="12"/>
+      <c r="L11" s="12">
+        <v>44</v>
+      </c>
       <c r="M11" s="70">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="N11" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.6923076923076923</v>
       </c>
       <c r="O11" s="14"/>
       <c r="P11" s="11">
         <v>10</v>
       </c>
-      <c r="Q11" s="12"/>
+      <c r="Q11" s="12">
+        <v>10</v>
+      </c>
       <c r="R11" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="11">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T11" s="12">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U11" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W11" s="14"/>
-      <c r="X11" s="104" t="s">
-        <v>75</v>
-      </c>
+      <c r="X11" s="122"/>
     </row>
     <row r="12" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="35" t="s">
@@ -2285,35 +2292,43 @@
       <c r="G12" s="11">
         <v>50</v>
       </c>
-      <c r="H12" s="71"/>
-      <c r="I12" s="12"/>
+      <c r="H12" s="71">
+        <v>40</v>
+      </c>
+      <c r="I12" s="12">
+        <v>9</v>
+      </c>
       <c r="J12" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="K12" s="11">
         <v>30</v>
       </c>
-      <c r="L12" s="12"/>
+      <c r="L12" s="12">
+        <v>12</v>
+      </c>
       <c r="M12" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="N12" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="O12" s="14"/>
       <c r="P12" s="11">
-        <v>9</v>
-      </c>
-      <c r="Q12" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>0</v>
+      </c>
       <c r="R12" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S12" s="11">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="T12" s="12">
         <v>0</v>
@@ -2327,9 +2342,7 @@
         <v>0</v>
       </c>
       <c r="W12" s="14"/>
-      <c r="X12" s="104" t="s">
-        <v>75</v>
-      </c>
+      <c r="X12" s="122"/>
     </row>
     <row r="13" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A13" s="35" t="s">
@@ -2353,51 +2366,57 @@
       <c r="G13" s="11">
         <v>50</v>
       </c>
-      <c r="H13" s="71"/>
-      <c r="I13" s="12"/>
+      <c r="H13" s="71">
+        <v>40</v>
+      </c>
+      <c r="I13" s="12">
+        <v>9</v>
+      </c>
       <c r="J13" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="K13" s="11">
         <v>30</v>
       </c>
-      <c r="L13" s="12"/>
+      <c r="L13" s="12">
+        <v>11</v>
+      </c>
       <c r="M13" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.36666666666666664</v>
       </c>
       <c r="N13" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.2222222222222223</v>
       </c>
       <c r="O13" s="14"/>
       <c r="P13" s="11">
-        <v>8</v>
-      </c>
-      <c r="Q13" s="12"/>
+        <v>15</v>
+      </c>
+      <c r="Q13" s="12">
+        <v>15</v>
+      </c>
       <c r="R13" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" s="11">
         <v>15</v>
       </c>
       <c r="T13" s="12">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U13" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" s="14"/>
-      <c r="X13" s="104" t="s">
-        <v>75</v>
-      </c>
+      <c r="X13" s="122"/>
     </row>
     <row r="14" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="35" t="s">
@@ -2438,32 +2457,24 @@
         <v>0</v>
       </c>
       <c r="O14" s="14"/>
-      <c r="P14" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="12">
-        <v>1</v>
-      </c>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="12"/>
       <c r="R14" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="S14" s="11">
-        <v>90</v>
-      </c>
-      <c r="T14" s="12">
-        <v>90</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S14" s="11"/>
+      <c r="T14" s="12"/>
       <c r="U14" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="11">
         <f t="shared" si="5"/>
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="W14" s="14"/>
-      <c r="X14" s="103"/>
+      <c r="X14" s="122"/>
     </row>
     <row r="15" spans="1:24" ht="16.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15" s="35" t="s">
@@ -2714,51 +2725,59 @@
         <v>22</v>
       </c>
       <c r="F19" s="50" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G19" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="74"/>
       <c r="I19" s="37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="38">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="37">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M19" s="38">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N19" s="36">
         <f t="shared" si="2"/>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O19" s="39">
         <v>1</v>
       </c>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="37"/>
+      <c r="P19" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="37">
+        <v>1</v>
+      </c>
       <c r="R19" s="38">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S19" s="36"/>
-      <c r="T19" s="37"/>
+        <v>1</v>
+      </c>
+      <c r="S19" s="36">
+        <v>200</v>
+      </c>
+      <c r="T19" s="37">
+        <v>200</v>
+      </c>
       <c r="U19" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="36">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="W19" s="39">
         <v>1</v>
@@ -2782,35 +2801,35 @@
       <c r="F20" s="107"/>
       <c r="G20" s="40">
         <f>SUM(G4:G19)</f>
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H20" s="41">
         <f>SUM(H4:H19)</f>
-        <v>220</v>
+        <v>350</v>
       </c>
       <c r="I20" s="41">
         <f>SUM(I4:I19)</f>
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="J20" s="42">
         <f t="shared" si="0"/>
-        <v>4.9783549783549784E-2</v>
+        <v>0.16268980477223427</v>
       </c>
       <c r="K20" s="40">
         <f t="shared" ref="K20:L20" si="6">SUM(K4:K19)</f>
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L20" s="40">
         <f t="shared" si="6"/>
-        <v>227.1</v>
+        <v>166.1</v>
       </c>
       <c r="M20" s="42">
         <f t="shared" si="1"/>
-        <v>0.68818181818181812</v>
+        <v>0.5048632218844985</v>
       </c>
       <c r="N20" s="40">
         <f t="shared" si="2"/>
-        <v>9.8739130434782609</v>
+        <v>2.2146666666666666</v>
       </c>
       <c r="O20" s="43">
         <f>AVERAGE(O4:O19)</f>
@@ -2818,31 +2837,31 @@
       </c>
       <c r="P20" s="40">
         <f t="shared" ref="P20" si="7">SUM(P4:P19)</f>
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="Q20" s="41">
         <f t="shared" ref="Q20" si="8">SUM(Q4:Q19)</f>
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="R20" s="42">
         <f t="shared" si="3"/>
-        <v>0.546875</v>
+        <v>0.97872340425531912</v>
       </c>
       <c r="S20" s="40">
         <f t="shared" ref="S20" si="9">SUM(S4:S19)</f>
-        <v>227.95</v>
+        <v>301</v>
       </c>
       <c r="T20" s="41">
         <f t="shared" ref="T20" si="10">SUM(T4:T19)</f>
-        <v>190.375</v>
+        <v>294</v>
       </c>
       <c r="U20" s="42">
         <f t="shared" si="4"/>
-        <v>0.83516121956569422</v>
+        <v>0.97674418604651159</v>
       </c>
       <c r="V20" s="40">
         <f t="shared" si="5"/>
-        <v>5.4392857142857141</v>
+        <v>6.3913043478260869</v>
       </c>
       <c r="W20" s="43">
         <f>AVERAGE(W4:W19)</f>
@@ -3667,19 +3686,19 @@
       <c r="F32" s="57"/>
       <c r="G32" s="20">
         <f>+G31+G26+G20</f>
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H32" s="21">
         <f t="shared" ref="H32:I32" si="17">+H31+H26+H20</f>
-        <v>220</v>
+        <v>350</v>
       </c>
       <c r="I32" s="21">
         <f t="shared" si="17"/>
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="J32" s="22">
         <f t="shared" si="0"/>
-        <v>4.8832271762208071E-2</v>
+        <v>0.15957446808510639</v>
       </c>
       <c r="K32" s="20">
         <v>1</v>
@@ -3693,7 +3712,7 @@
       </c>
       <c r="N32" s="20">
         <f t="shared" si="2"/>
-        <v>4.3478260869565216E-2</v>
+        <v>1.3333333333333334E-2</v>
       </c>
       <c r="O32" s="23">
         <f>AVERAGE(O31,O20,O26)</f>
@@ -3701,31 +3720,31 @@
       </c>
       <c r="P32" s="20">
         <f>+P31+P26+P20</f>
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="Q32" s="21">
         <f t="shared" ref="Q32" si="18">+Q31+Q26+Q20</f>
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="R32" s="22">
         <f t="shared" si="3"/>
-        <v>0.60273972602739723</v>
+        <v>0.9821428571428571</v>
       </c>
       <c r="S32" s="20">
         <f>+S31+S26+S20</f>
-        <v>236.95</v>
+        <v>310</v>
       </c>
       <c r="T32" s="21">
         <f t="shared" ref="T32" si="19">+T31+T26+T20</f>
-        <v>199.375</v>
+        <v>303</v>
       </c>
       <c r="U32" s="22">
         <f t="shared" si="4"/>
-        <v>0.84142224097910956</v>
+        <v>0.97741935483870968</v>
       </c>
       <c r="V32" s="20">
         <f t="shared" si="5"/>
-        <v>4.53125</v>
+        <v>5.5090909090909088</v>
       </c>
       <c r="W32" s="23">
         <f>AVERAGE(W31,W20,W26)</f>
@@ -3791,18 +3810,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.25925925925925924</v>
+        <v>0.29629629629629628</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" s="89">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="G2" s="117" t="s">
         <v>34</v>
@@ -3902,34 +3921,34 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>15+13+9+11+10</f>
-        <v>58</v>
+        <f>15+13+9+11+10+11</f>
+        <v>69</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.17846153846153845</v>
+        <v>0.21230769230769231</v>
       </c>
       <c r="K4" s="7">
         <v>450</v>
       </c>
       <c r="L4" s="8">
-        <v>68.25</v>
+        <v>79.5</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.15166666666666667</v>
+        <v>0.17666666666666667</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>381.75</v>
+        <v>370.5</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>19.087499999999999</v>
+        <v>19.5</v>
       </c>
       <c r="P4" s="68">
-        <f t="shared" ref="P4:P15" si="2">L4/I4</f>
-        <v>1.1767241379310345</v>
+        <f t="shared" ref="P4:P16" si="2">L4/I4</f>
+        <v>1.1521739130434783</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3958,34 +3977,34 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <f>6+5+5+3+3</f>
-        <v>22</v>
+        <f>6+5+5+3+3+4</f>
+        <v>26</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J29" si="3">IFERROR(I5/G5,0)</f>
-        <v>9.2827004219409287E-2</v>
+        <v>0.10970464135021098</v>
       </c>
       <c r="K5" s="11">
         <v>350</v>
       </c>
       <c r="L5" s="12">
-        <v>37.6</v>
+        <v>47.6</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M29" si="4">IFERROR(L5/K5,0)</f>
-        <v>0.10742857142857143</v>
+        <v>0.13600000000000001</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>312.39999999999998</v>
+        <v>302.39999999999998</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>15.62</v>
+        <v>15.915789473684208</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>1.7090909090909092</v>
+        <v>1.8307692307692309</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -4037,7 +4056,7 @@
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>16.033750000000001</v>
+        <v>16.877631578947369</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
@@ -4095,7 +4114,7 @@
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>10.545</v>
+        <v>11.1</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
@@ -4128,34 +4147,34 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <f>3+6+7+6+6</f>
-        <v>28</v>
+        <f>3+6+7+6+6+3</f>
+        <v>31</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>7.8431372549019607E-2</v>
+        <v>8.683473389355742E-2</v>
       </c>
       <c r="K8" s="11">
         <v>250</v>
       </c>
       <c r="L8" s="12">
-        <v>33.424999999999997</v>
+        <v>37.024999999999999</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>0.13369999999999999</v>
+        <v>0.14809999999999998</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N29" si="5">K8-L8</f>
-        <v>216.57499999999999</v>
+        <v>212.97499999999999</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
-        <v>10.828749999999999</v>
+        <v>11.20921052631579</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.1937499999999999</v>
+        <v>1.1943548387096774</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4238,37 +4257,37 @@
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="12">
-        <f>3+4+4+6</f>
-        <v>17</v>
+        <f>3+4+4+6+2</f>
+        <v>19</v>
       </c>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>0.15315315315315314</v>
+        <v>0.17117117117117117</v>
       </c>
       <c r="K10" s="11">
         <v>2300</v>
       </c>
       <c r="L10" s="12">
-        <v>374</v>
+        <v>420</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>0.16260869565217392</v>
+        <v>0.18260869565217391</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>1926</v>
+        <v>1880</v>
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>96.3</v>
+        <v>98.94736842105263</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>22.105263157894736</v>
       </c>
       <c r="Q10" s="14"/>
-      <c r="R10" s="34"/>
+      <c r="R10" s="123"/>
     </row>
     <row r="11" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A11" s="35" t="s">
@@ -4316,16 +4335,14 @@
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>21.6</v>
+        <v>22.736842105263158</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Q11" s="14"/>
-      <c r="R11" s="102" t="s">
-        <v>74</v>
-      </c>
+      <c r="R11" s="124"/>
     </row>
     <row r="12" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="35" t="s">
@@ -4361,28 +4378,27 @@
         <v>300</v>
       </c>
       <c r="L12" s="12">
-        <v>12</v>
+        <f>12+15</f>
+        <v>27</v>
       </c>
       <c r="M12" s="70">
         <f t="shared" si="4"/>
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="5"/>
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>14.4</v>
+        <v>14.368421052631579</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
-        <v>1.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="Q12" s="14"/>
-      <c r="R12" s="102" t="s">
-        <v>74</v>
-      </c>
+      <c r="R12" s="124"/>
     </row>
     <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A13" s="35" t="s">
@@ -4418,28 +4434,27 @@
         <v>250</v>
       </c>
       <c r="L13" s="12">
-        <v>4</v>
+        <f>4+12</f>
+        <v>16</v>
       </c>
       <c r="M13" s="70">
         <f t="shared" si="4"/>
-        <v>1.6E-2</v>
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="5"/>
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="O13" s="14">
         <f t="shared" si="6"/>
-        <v>12.3</v>
+        <v>12.315789473684211</v>
       </c>
       <c r="P13" s="71" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q13" s="14"/>
-      <c r="R13" s="102" t="s">
-        <v>74</v>
-      </c>
+      <c r="R13" s="124"/>
     </row>
     <row r="14" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="35" t="s">
@@ -4458,7 +4473,7 @@
         <v>22</v>
       </c>
       <c r="F14" s="100" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G14" s="11">
         <v>1</v>
@@ -4485,7 +4500,7 @@
       </c>
       <c r="O14" s="14">
         <f t="shared" si="6"/>
-        <v>-4.5</v>
+        <v>-4.7368421052631575</v>
       </c>
       <c r="P14" s="71">
         <f t="shared" si="2"/>
@@ -4511,7 +4526,7 @@
         <v>22</v>
       </c>
       <c r="F15" s="100" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G15" s="11">
         <v>1</v>
@@ -4538,7 +4553,7 @@
       </c>
       <c r="O15" s="14">
         <f t="shared" si="6"/>
-        <v>-3.75</v>
+        <v>-3.9473684210526314</v>
       </c>
       <c r="P15" s="71">
         <f t="shared" si="2"/>
@@ -4568,26 +4583,33 @@
       </c>
       <c r="G16" s="11"/>
       <c r="H16" s="71"/>
-      <c r="I16" s="12"/>
+      <c r="I16" s="12">
+        <v>1</v>
+      </c>
       <c r="J16" s="69">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16" s="11"/>
-      <c r="L16" s="12"/>
+      <c r="L16" s="12">
+        <v>200</v>
+      </c>
       <c r="M16" s="70">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N16" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="O16" s="14">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P16" s="71"/>
+        <v>-10.526315789473685</v>
+      </c>
+      <c r="P16" s="71">
+        <f t="shared" si="2"/>
+        <v>200</v>
+      </c>
       <c r="Q16" s="14"/>
       <c r="R16" s="34"/>
     </row>
@@ -4615,12 +4637,12 @@
         <v>0</v>
       </c>
       <c r="I17" s="41">
-        <f>SUM(I4:I15)</f>
-        <v>182</v>
+        <f>SUM(I4:I16)</f>
+        <v>203</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>7.300441235459286E-2</v>
+        <v>8.142799839550742E-2</v>
       </c>
       <c r="K17" s="76">
         <f>SUM(K4:K16)</f>
@@ -4628,23 +4650,23 @@
       </c>
       <c r="L17" s="77">
         <f>SUM(L4:L16)</f>
-        <v>780.7</v>
+        <v>1078.55</v>
       </c>
       <c r="M17" s="78">
         <f t="shared" si="4"/>
-        <v>0.15307843137254903</v>
+        <v>0.21148039215686273</v>
       </c>
       <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>4319.3</v>
+        <v>4021.45</v>
       </c>
       <c r="O17" s="79">
         <f t="shared" si="6"/>
-        <v>215.965</v>
+        <v>211.65526315789472</v>
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>4.2895604395604394</v>
+        <v>5.313054187192118</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -4698,7 +4720,7 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="6"/>
-        <v>21.285</v>
+        <v>22.405263157894737</v>
       </c>
       <c r="P18" s="96">
         <f t="shared" ref="P18:P22" si="7">L18/I18</f>
@@ -4753,7 +4775,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>21.285</v>
+        <v>22.405263157894737</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4808,7 +4830,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>21.285</v>
+        <v>22.405263157894737</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4863,7 +4885,7 @@
       </c>
       <c r="O21" s="14">
         <f t="shared" si="6"/>
-        <v>21.285</v>
+        <v>22.405263157894737</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="7"/>
@@ -4918,7 +4940,7 @@
       </c>
       <c r="O22" s="94">
         <f t="shared" si="6"/>
-        <v>21.285</v>
+        <v>22.405263157894737</v>
       </c>
       <c r="P22" s="74">
         <f t="shared" si="7"/>
@@ -4976,7 +4998,7 @@
       </c>
       <c r="O23" s="79">
         <f t="shared" si="6"/>
-        <v>21.285</v>
+        <v>22.405263157894737</v>
       </c>
       <c r="P23" s="80">
         <f>L23/I23</f>
@@ -5034,7 +5056,7 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="6"/>
-        <v>21.285</v>
+        <v>22.405263157894737</v>
       </c>
       <c r="P24" s="96">
         <f t="shared" ref="P24:P27" si="9">L24/I24</f>
@@ -5089,7 +5111,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>21.285</v>
+        <v>22.405263157894737</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5144,7 +5166,7 @@
       </c>
       <c r="O26" s="14">
         <f t="shared" si="6"/>
-        <v>21.285</v>
+        <v>22.405263157894737</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="9"/>
@@ -5199,7 +5221,7 @@
       </c>
       <c r="O27" s="94">
         <f t="shared" si="6"/>
-        <v>21.285</v>
+        <v>22.405263157894737</v>
       </c>
       <c r="P27" s="74">
         <f t="shared" si="9"/>
@@ -5254,7 +5276,7 @@
       </c>
       <c r="O28" s="79">
         <f t="shared" si="6"/>
-        <v>21.285</v>
+        <v>22.405263157894737</v>
       </c>
       <c r="P28" s="80">
         <f>L28/I28</f>
@@ -5287,11 +5309,11 @@
       </c>
       <c r="I29" s="21">
         <f t="shared" si="11"/>
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="J29" s="83">
         <f t="shared" si="3"/>
-        <v>7.633892885691447E-2</v>
+        <v>8.4732214228617111E-2</v>
       </c>
       <c r="K29" s="84">
         <v>600</v>
@@ -5309,11 +5331,11 @@
       </c>
       <c r="O29" s="87">
         <f t="shared" si="6"/>
-        <v>21.285</v>
+        <v>22.405263157894737</v>
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>
-        <v>0.91256544502617809</v>
+        <v>0.82216981132075473</v>
       </c>
       <c r="Q29" s="23" t="e">
         <f>AVERAGE(Q28,Q17,Q23)</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C40E53-3D9F-4FCE-AC75-9003B1090377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F67B11-F5BA-46B2-B777-5316B7EFDA34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -929,7 +929,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1201,6 +1201,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1252,11 +1253,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1568,55 +1564,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G1" s="111" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="114" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
-      <c r="V1" s="115"/>
-      <c r="W1" s="116"/>
+      <c r="G1" s="112" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="115" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
+      <c r="V1" s="116"/>
+      <c r="W1" s="117"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="89">
-        <v>46305</v>
-      </c>
-      <c r="G2" s="117" t="s">
+        <v>46307</v>
+      </c>
+      <c r="G2" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="118"/>
-      <c r="I2" s="118"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="118" t="s">
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="118"/>
-      <c r="M2" s="119"/>
+      <c r="L2" s="119"/>
+      <c r="M2" s="120"/>
       <c r="N2" s="1"/>
       <c r="O2" s="2"/>
-      <c r="P2" s="117" t="s">
+      <c r="P2" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="118"/>
-      <c r="R2" s="119"/>
-      <c r="S2" s="118" t="s">
+      <c r="Q2" s="119"/>
+      <c r="R2" s="120"/>
+      <c r="S2" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="T2" s="118"/>
-      <c r="U2" s="119"/>
+      <c r="T2" s="119"/>
+      <c r="U2" s="120"/>
       <c r="V2" s="1"/>
       <c r="W2" s="2"/>
     </row>
@@ -1720,42 +1716,42 @@
         <v>40</v>
       </c>
       <c r="I4" s="12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J4" s="32">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="K4" s="30">
         <v>40</v>
       </c>
       <c r="L4" s="12">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M4" s="32">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.22500000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="N4" s="90">
         <f>IFERROR(L4/I4,0)</f>
-        <v>1.125</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="O4" s="33"/>
       <c r="P4" s="30">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q4" s="31">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R4" s="32">
         <f>IFERROR(Q4/P4,0)</f>
         <v>1</v>
       </c>
       <c r="S4" s="30">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T4" s="31">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="U4" s="32">
         <f>IFERROR(T4/S4,0)</f>
@@ -1763,7 +1759,7 @@
       </c>
       <c r="V4" s="90">
         <f>IFERROR(T4/Q4,0)</f>
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="W4" s="33"/>
       <c r="X4" s="34"/>
@@ -1794,50 +1790,50 @@
         <v>45</v>
       </c>
       <c r="I5" s="12">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J5" s="13">
         <f t="shared" ref="J5:J32" si="0">IFERROR(I5/G5,0)</f>
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="K5" s="11">
         <v>30</v>
       </c>
       <c r="L5" s="12">
-        <v>6</v>
+        <v>21.9</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M32" si="1">IFERROR(L5/K5,0)</f>
-        <v>0.2</v>
+        <v>0.73</v>
       </c>
       <c r="N5" s="71">
         <f t="shared" ref="N5:N32" si="2">IFERROR(L5/I5,0)</f>
-        <v>1.2</v>
+        <v>2.4333333333333331</v>
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q5" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R5" s="13">
         <f t="shared" ref="R5:R32" si="3">IFERROR(Q5/P5,0)</f>
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="S5" s="11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T5" s="12">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U5" s="13">
         <f t="shared" ref="U5:U32" si="4">IFERROR(T5/S5,0)</f>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="V5" s="11">
         <f t="shared" ref="V5:V32" si="5">IFERROR(T5/Q5,0)</f>
-        <v>2.5</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="W5" s="14"/>
       <c r="X5" s="34"/>
@@ -1948,36 +1944,40 @@
         <v>30</v>
       </c>
       <c r="L7" s="12">
-        <v>8.1</v>
+        <v>5.75</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="1"/>
-        <v>0.26999999999999996</v>
+        <v>0.19166666666666668</v>
       </c>
       <c r="N7" s="71">
         <f t="shared" si="2"/>
-        <v>0.89999999999999991</v>
+        <v>0.63888888888888884</v>
       </c>
       <c r="O7" s="14"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="12"/>
+      <c r="P7" s="11">
+        <v>9</v>
+      </c>
+      <c r="Q7" s="12">
+        <v>7</v>
+      </c>
       <c r="R7" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="S7" s="11">
-        <v>3</v>
+        <v>8.1</v>
       </c>
       <c r="T7" s="12">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="U7" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.71604938271604934</v>
       </c>
       <c r="V7" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.82857142857142851</v>
       </c>
       <c r="W7" s="14"/>
       <c r="X7" s="103"/>
@@ -2008,50 +2008,50 @@
         <v>40</v>
       </c>
       <c r="I8" s="12">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="K8" s="11">
         <v>20</v>
       </c>
       <c r="L8" s="12">
-        <v>6</v>
+        <v>16.7</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="1"/>
-        <v>0.3</v>
+        <v>0.83499999999999996</v>
       </c>
       <c r="N8" s="71">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.5181818181818181</v>
       </c>
       <c r="O8" s="14"/>
       <c r="P8" s="11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q8" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R8" s="13">
         <f t="shared" si="3"/>
-        <v>0.75</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="S8" s="11">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="T8" s="12">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="U8" s="13">
         <f t="shared" si="4"/>
-        <v>0.75</v>
+        <v>0.82456140350877194</v>
       </c>
       <c r="V8" s="11">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.94000000000000006</v>
       </c>
       <c r="W8" s="14"/>
       <c r="X8" s="103"/>
@@ -2148,53 +2148,53 @@
         <v>10</v>
       </c>
       <c r="I10" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J10" s="13">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="K10" s="11">
         <v>20</v>
       </c>
       <c r="L10" s="12">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="1"/>
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N10" s="71">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="O10" s="14"/>
       <c r="P10" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q10" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R10" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="S10" s="11">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="T10" s="12">
-        <v>46</v>
+        <v>65.95</v>
       </c>
       <c r="U10" s="13">
         <f t="shared" si="4"/>
-        <v>0.88461538461538458</v>
+        <v>0.99924242424242427</v>
       </c>
       <c r="V10" s="11">
         <f t="shared" si="5"/>
-        <v>23</v>
+        <v>21.983333333333334</v>
       </c>
       <c r="W10" s="14"/>
-      <c r="X10" s="122"/>
+      <c r="X10" s="103"/>
     </row>
     <row r="11" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A11" s="35" t="s">
@@ -2222,25 +2222,25 @@
         <v>50</v>
       </c>
       <c r="I11" s="12">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J11" s="13">
         <f t="shared" si="0"/>
-        <v>0.52</v>
+        <v>0.2</v>
       </c>
       <c r="K11" s="11">
         <v>20</v>
       </c>
       <c r="L11" s="12">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="1"/>
-        <v>2.2000000000000002</v>
+        <v>0.6</v>
       </c>
       <c r="N11" s="71">
         <f t="shared" si="2"/>
-        <v>1.6923076923076923</v>
+        <v>1.2</v>
       </c>
       <c r="O11" s="14"/>
       <c r="P11" s="11">
@@ -2254,10 +2254,10 @@
         <v>1</v>
       </c>
       <c r="S11" s="11">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T11" s="12">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="U11" s="13">
         <f t="shared" si="4"/>
@@ -2265,10 +2265,10 @@
       </c>
       <c r="V11" s="11">
         <f t="shared" si="5"/>
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="W11" s="14"/>
-      <c r="X11" s="122"/>
+      <c r="X11" s="103"/>
     </row>
     <row r="12" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="35" t="s">
@@ -2296,53 +2296,53 @@
         <v>40</v>
       </c>
       <c r="I12" s="12">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="J12" s="13">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>0.68</v>
       </c>
       <c r="K12" s="11">
         <v>30</v>
       </c>
       <c r="L12" s="12">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="M12" s="13">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="N12" s="11">
         <f t="shared" si="2"/>
-        <v>1.3333333333333333</v>
+        <v>1.411764705882353</v>
       </c>
       <c r="O12" s="14"/>
       <c r="P12" s="11">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q12" s="12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R12" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" s="11">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T12" s="12">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U12" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="W12" s="14"/>
-      <c r="X12" s="122"/>
+      <c r="X12" s="103"/>
     </row>
     <row r="13" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A13" s="35" t="s">
@@ -2380,32 +2380,32 @@
         <v>30</v>
       </c>
       <c r="L13" s="12">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M13" s="13">
         <f t="shared" si="1"/>
-        <v>0.36666666666666664</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="N13" s="11">
         <f t="shared" si="2"/>
-        <v>1.2222222222222223</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="O13" s="14"/>
       <c r="P13" s="11">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q13" s="12">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="R13" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="S13" s="11">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T13" s="12">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="U13" s="13">
         <f t="shared" si="4"/>
@@ -2413,10 +2413,10 @@
       </c>
       <c r="V13" s="11">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="W13" s="14"/>
-      <c r="X13" s="122"/>
+      <c r="X13" s="103"/>
     </row>
     <row r="14" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="35" t="s">
@@ -2474,7 +2474,7 @@
         <v>0</v>
       </c>
       <c r="W14" s="14"/>
-      <c r="X14" s="122"/>
+      <c r="X14" s="103"/>
     </row>
     <row r="15" spans="1:24" ht="16.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15" s="35" t="s">
@@ -2752,32 +2752,22 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O19" s="39">
-        <v>1</v>
-      </c>
-      <c r="P19" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="37">
-        <v>1</v>
-      </c>
+      <c r="O19" s="39"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="37"/>
       <c r="R19" s="38">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="S19" s="36">
-        <v>200</v>
-      </c>
-      <c r="T19" s="37">
-        <v>200</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S19" s="36"/>
+      <c r="T19" s="37"/>
       <c r="U19" s="38">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="36">
         <f t="shared" si="5"/>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="W19" s="39">
         <v>1</v>
@@ -2794,11 +2784,11 @@
       <c r="C20" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="105" t="s">
+      <c r="D20" s="106" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="106"/>
-      <c r="F20" s="107"/>
+      <c r="E20" s="107"/>
+      <c r="F20" s="108"/>
       <c r="G20" s="40">
         <f>SUM(G4:G19)</f>
         <v>461</v>
@@ -2809,11 +2799,11 @@
       </c>
       <c r="I20" s="41">
         <f>SUM(I4:I19)</f>
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="J20" s="42">
         <f t="shared" si="0"/>
-        <v>0.16268980477223427</v>
+        <v>0.2017353579175705</v>
       </c>
       <c r="K20" s="40">
         <f t="shared" ref="K20:L20" si="6">SUM(K4:K19)</f>
@@ -2821,47 +2811,47 @@
       </c>
       <c r="L20" s="40">
         <f t="shared" si="6"/>
-        <v>166.1</v>
+        <v>188.35</v>
       </c>
       <c r="M20" s="42">
         <f t="shared" si="1"/>
-        <v>0.5048632218844985</v>
+        <v>0.57249240121580547</v>
       </c>
       <c r="N20" s="40">
         <f t="shared" si="2"/>
-        <v>2.2146666666666666</v>
-      </c>
-      <c r="O20" s="43">
+        <v>2.0252688172043012</v>
+      </c>
+      <c r="O20" s="43" t="e">
         <f>AVERAGE(O4:O19)</f>
-        <v>1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P20" s="40">
         <f t="shared" ref="P20" si="7">SUM(P4:P19)</f>
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="Q20" s="41">
         <f t="shared" ref="Q20" si="8">SUM(Q4:Q19)</f>
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="R20" s="42">
         <f t="shared" si="3"/>
-        <v>0.97872340425531912</v>
+        <v>0.91379310344827591</v>
       </c>
       <c r="S20" s="40">
         <f t="shared" ref="S20" si="9">SUM(S4:S19)</f>
-        <v>301</v>
+        <v>121.8</v>
       </c>
       <c r="T20" s="41">
         <f t="shared" ref="T20" si="10">SUM(T4:T19)</f>
-        <v>294</v>
+        <v>116.45</v>
       </c>
       <c r="U20" s="42">
         <f t="shared" si="4"/>
-        <v>0.97674418604651159</v>
+        <v>0.95607553366174058</v>
       </c>
       <c r="V20" s="40">
         <f t="shared" si="5"/>
-        <v>6.3913043478260869</v>
+        <v>2.1971698113207547</v>
       </c>
       <c r="W20" s="43">
         <f>AVERAGE(W4:W19)</f>
@@ -3233,11 +3223,11 @@
       <c r="C26" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="105" t="s">
+      <c r="D26" s="106" t="s">
         <v>18</v>
       </c>
-      <c r="E26" s="106"/>
-      <c r="F26" s="107"/>
+      <c r="E26" s="107"/>
+      <c r="F26" s="108"/>
       <c r="G26" s="40">
         <f>SUM(G21:G25)</f>
         <v>5</v>
@@ -3600,11 +3590,11 @@
       <c r="C31" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="D31" s="108" t="s">
+      <c r="D31" s="109" t="s">
         <v>18</v>
       </c>
-      <c r="E31" s="109"/>
-      <c r="F31" s="110"/>
+      <c r="E31" s="110"/>
+      <c r="F31" s="111"/>
       <c r="G31" s="40">
         <f>SUM(G27:G30)</f>
         <v>4</v>
@@ -3694,11 +3684,11 @@
       </c>
       <c r="I32" s="21">
         <f t="shared" si="17"/>
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="J32" s="22">
         <f t="shared" si="0"/>
-        <v>0.15957446808510639</v>
+        <v>0.19787234042553192</v>
       </c>
       <c r="K32" s="20">
         <v>1</v>
@@ -3712,39 +3702,39 @@
       </c>
       <c r="N32" s="20">
         <f t="shared" si="2"/>
-        <v>1.3333333333333334E-2</v>
-      </c>
-      <c r="O32" s="23">
+        <v>1.0752688172043012E-2</v>
+      </c>
+      <c r="O32" s="23" t="e">
         <f>AVERAGE(O31,O20,O26)</f>
-        <v>1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P32" s="20">
         <f>+P31+P26+P20</f>
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="Q32" s="21">
         <f t="shared" ref="Q32" si="18">+Q31+Q26+Q20</f>
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="R32" s="22">
         <f t="shared" si="3"/>
-        <v>0.9821428571428571</v>
+        <v>0.92537313432835822</v>
       </c>
       <c r="S32" s="20">
         <f>+S31+S26+S20</f>
-        <v>310</v>
+        <v>130.80000000000001</v>
       </c>
       <c r="T32" s="21">
         <f t="shared" ref="T32" si="19">+T31+T26+T20</f>
-        <v>303</v>
+        <v>125.45</v>
       </c>
       <c r="U32" s="22">
         <f t="shared" si="4"/>
-        <v>0.97741935483870968</v>
+        <v>0.95909785932721703</v>
       </c>
       <c r="V32" s="20">
         <f t="shared" si="5"/>
-        <v>5.5090909090909088</v>
+        <v>2.0233870967741936</v>
       </c>
       <c r="W32" s="23">
         <f>AVERAGE(W31,W20,W26)</f>
@@ -3810,36 +3800,36 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.29629629629629628</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2" s="89">
-        <v>46304</v>
-      </c>
-      <c r="G2" s="117" t="s">
+        <v>46305</v>
+      </c>
+      <c r="G2" s="118" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="118"/>
-      <c r="I2" s="118"/>
-      <c r="J2" s="118"/>
-      <c r="K2" s="114" t="s">
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="115" t="s">
         <v>48</v>
       </c>
-      <c r="L2" s="115"/>
-      <c r="M2" s="115"/>
-      <c r="N2" s="115"/>
-      <c r="O2" s="116"/>
-      <c r="P2" s="120" t="s">
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="117"/>
+      <c r="P2" s="121" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" s="121"/>
+      <c r="Q2" s="122"/>
     </row>
     <row r="3" spans="1:18" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="25" t="s">
@@ -3921,34 +3911,34 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>15+13+9+11+10+11</f>
-        <v>69</v>
+        <f>15+13+9+11+10+11+8</f>
+        <v>77</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.21230769230769231</v>
+        <v>0.23692307692307693</v>
       </c>
       <c r="K4" s="7">
         <v>450</v>
       </c>
       <c r="L4" s="8">
-        <v>79.5</v>
+        <v>88.5</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.17666666666666667</v>
+        <v>0.19666666666666666</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>370.5</v>
+        <v>361.5</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>19.5</v>
+        <v>20.083333333333332</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P16" si="2">L4/I4</f>
-        <v>1.1521739130434783</v>
+        <v>1.1493506493506493</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3977,34 +3967,34 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <f>6+5+5+3+3+4</f>
-        <v>26</v>
+        <f>6+5+5+3+3+4+3</f>
+        <v>29</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J29" si="3">IFERROR(I5/G5,0)</f>
-        <v>0.10970464135021098</v>
+        <v>0.12236286919831224</v>
       </c>
       <c r="K5" s="11">
         <v>350</v>
       </c>
       <c r="L5" s="12">
-        <v>47.6</v>
+        <v>51.6</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M29" si="4">IFERROR(L5/K5,0)</f>
-        <v>0.13600000000000001</v>
+        <v>0.14742857142857144</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>302.39999999999998</v>
+        <v>298.39999999999998</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>15.915789473684208</v>
+        <v>16.577777777777776</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>1.8307692307692309</v>
+        <v>1.7793103448275862</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -4056,7 +4046,7 @@
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>16.877631578947369</v>
+        <v>17.81527777777778</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
@@ -4091,34 +4081,34 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>2+2+6+4+9</f>
-        <v>23</v>
+        <f>2+2+6+4+9+7</f>
+        <v>30</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>7.9861111111111105E-2</v>
+        <v>0.10416666666666667</v>
       </c>
       <c r="K7" s="11">
         <v>250</v>
       </c>
       <c r="L7" s="12">
-        <v>39.1</v>
+        <v>44.9</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>0.15640000000000001</v>
+        <v>0.17959999999999998</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>210.9</v>
+        <v>205.1</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>11.1</v>
+        <v>11.394444444444444</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.7</v>
+        <v>1.4966666666666666</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4147,34 +4137,34 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <f>3+6+7+6+6+3</f>
-        <v>31</v>
+        <f>3+6+7+6+6+3+5</f>
+        <v>36</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>8.683473389355742E-2</v>
+        <v>0.10084033613445378</v>
       </c>
       <c r="K8" s="11">
         <v>250</v>
       </c>
       <c r="L8" s="12">
-        <v>37.024999999999999</v>
+        <v>41.725000000000001</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>0.14809999999999998</v>
+        <v>0.16689999999999999</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N29" si="5">K8-L8</f>
-        <v>212.97499999999999</v>
+        <v>208.27500000000001</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
-        <v>11.20921052631579</v>
+        <v>11.570833333333333</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.1943548387096774</v>
+        <v>1.1590277777777778</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4203,11 +4193,11 @@
       </c>
       <c r="H9" s="71"/>
       <c r="I9" s="12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J9" s="69">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.6666666666666668E-2</v>
       </c>
       <c r="K9" s="11">
         <v>150</v>
@@ -4226,9 +4216,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P9" s="71" t="e">
+      <c r="P9" s="71">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="14"/>
       <c r="R9" s="34"/>
@@ -4257,37 +4247,36 @@
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="12">
-        <f>3+4+4+6+2</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>0.17117117117117117</v>
+        <v>0.1981981981981982</v>
       </c>
       <c r="K10" s="11">
         <v>2300</v>
       </c>
       <c r="L10" s="12">
-        <v>420</v>
+        <v>486.05</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>0.18260869565217391</v>
+        <v>0.21132608695652175</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>1880</v>
+        <v>1813.95</v>
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>98.94736842105263</v>
+        <v>100.77500000000001</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>22.105263157894736</v>
+        <v>22.093181818181819</v>
       </c>
       <c r="Q10" s="14"/>
-      <c r="R10" s="123"/>
+      <c r="R10" s="34"/>
     </row>
     <row r="11" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A11" s="35" t="s">
@@ -4335,14 +4324,14 @@
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>22.736842105263158</v>
+        <v>24</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Q11" s="14"/>
-      <c r="R11" s="124"/>
+      <c r="R11" s="105"/>
     </row>
     <row r="12" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="35" t="s">
@@ -4391,14 +4380,14 @@
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>14.368421052631579</v>
+        <v>15.166666666666666</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="Q12" s="14"/>
-      <c r="R12" s="124"/>
+      <c r="R12" s="105"/>
     </row>
     <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A13" s="35" t="s">
@@ -4447,14 +4436,14 @@
       </c>
       <c r="O13" s="14">
         <f t="shared" si="6"/>
-        <v>12.315789473684211</v>
+        <v>13</v>
       </c>
       <c r="P13" s="71" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q13" s="14"/>
-      <c r="R13" s="124"/>
+      <c r="R13" s="105"/>
     </row>
     <row r="14" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="35" t="s">
@@ -4500,7 +4489,7 @@
       </c>
       <c r="O14" s="14">
         <f t="shared" si="6"/>
-        <v>-4.7368421052631575</v>
+        <v>-5</v>
       </c>
       <c r="P14" s="71">
         <f t="shared" si="2"/>
@@ -4553,7 +4542,7 @@
       </c>
       <c r="O15" s="14">
         <f t="shared" si="6"/>
-        <v>-3.9473684210526314</v>
+        <v>-4.166666666666667</v>
       </c>
       <c r="P15" s="71">
         <f t="shared" si="2"/>
@@ -4604,7 +4593,7 @@
       </c>
       <c r="O16" s="14">
         <f t="shared" si="6"/>
-        <v>-10.526315789473685</v>
+        <v>-11.111111111111111</v>
       </c>
       <c r="P16" s="71">
         <f t="shared" si="2"/>
@@ -4623,11 +4612,11 @@
       <c r="C17" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="108" t="s">
+      <c r="D17" s="109" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="109"/>
-      <c r="F17" s="110"/>
+      <c r="E17" s="110"/>
+      <c r="F17" s="111"/>
       <c r="G17" s="40">
         <f>SUM(G4:G15)</f>
         <v>2493</v>
@@ -4638,11 +4627,11 @@
       </c>
       <c r="I17" s="41">
         <f>SUM(I4:I16)</f>
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>8.142799839550742E-2</v>
+        <v>9.3461692739671073E-2</v>
       </c>
       <c r="K17" s="76">
         <f>SUM(K4:K16)</f>
@@ -4650,23 +4639,23 @@
       </c>
       <c r="L17" s="77">
         <f>SUM(L4:L16)</f>
-        <v>1078.55</v>
+        <v>1168.0999999999999</v>
       </c>
       <c r="M17" s="78">
         <f t="shared" si="4"/>
-        <v>0.21148039215686273</v>
+        <v>0.2290392156862745</v>
       </c>
       <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>4021.45</v>
+        <v>3931.9</v>
       </c>
       <c r="O17" s="79">
         <f t="shared" si="6"/>
-        <v>211.65526315789472</v>
+        <v>218.4388888888889</v>
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>5.313054187192118</v>
+        <v>5.0133047210300425</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -4720,7 +4709,7 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="6"/>
-        <v>22.405263157894737</v>
+        <v>23.65</v>
       </c>
       <c r="P18" s="96">
         <f t="shared" ref="P18:P22" si="7">L18/I18</f>
@@ -4775,7 +4764,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>22.405263157894737</v>
+        <v>23.65</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4830,7 +4819,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>22.405263157894737</v>
+        <v>23.65</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4885,7 +4874,7 @@
       </c>
       <c r="O21" s="14">
         <f t="shared" si="6"/>
-        <v>22.405263157894737</v>
+        <v>23.65</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="7"/>
@@ -4940,7 +4929,7 @@
       </c>
       <c r="O22" s="94">
         <f t="shared" si="6"/>
-        <v>22.405263157894737</v>
+        <v>23.65</v>
       </c>
       <c r="P22" s="74">
         <f t="shared" si="7"/>
@@ -4961,11 +4950,11 @@
       <c r="C23" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="108" t="s">
+      <c r="D23" s="109" t="s">
         <v>18</v>
       </c>
-      <c r="E23" s="109"/>
-      <c r="F23" s="110"/>
+      <c r="E23" s="110"/>
+      <c r="F23" s="111"/>
       <c r="G23" s="40">
         <f>SUM(G18:G22)</f>
         <v>5</v>
@@ -4998,7 +4987,7 @@
       </c>
       <c r="O23" s="79">
         <f t="shared" si="6"/>
-        <v>22.405263157894737</v>
+        <v>23.65</v>
       </c>
       <c r="P23" s="80">
         <f>L23/I23</f>
@@ -5056,7 +5045,7 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="6"/>
-        <v>22.405263157894737</v>
+        <v>23.65</v>
       </c>
       <c r="P24" s="96">
         <f t="shared" ref="P24:P27" si="9">L24/I24</f>
@@ -5111,7 +5100,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>22.405263157894737</v>
+        <v>23.65</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5166,7 +5155,7 @@
       </c>
       <c r="O26" s="14">
         <f t="shared" si="6"/>
-        <v>22.405263157894737</v>
+        <v>23.65</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="9"/>
@@ -5221,7 +5210,7 @@
       </c>
       <c r="O27" s="94">
         <f t="shared" si="6"/>
-        <v>22.405263157894737</v>
+        <v>23.65</v>
       </c>
       <c r="P27" s="74">
         <f t="shared" si="9"/>
@@ -5242,11 +5231,11 @@
       <c r="C28" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="108" t="s">
+      <c r="D28" s="109" t="s">
         <v>18</v>
       </c>
-      <c r="E28" s="109"/>
-      <c r="F28" s="110"/>
+      <c r="E28" s="110"/>
+      <c r="F28" s="111"/>
       <c r="G28" s="40">
         <f>SUM(G24:G27)</f>
         <v>4</v>
@@ -5276,7 +5265,7 @@
       </c>
       <c r="O28" s="79">
         <f t="shared" si="6"/>
-        <v>22.405263157894737</v>
+        <v>23.65</v>
       </c>
       <c r="P28" s="80">
         <f>L28/I28</f>
@@ -5309,11 +5298,11 @@
       </c>
       <c r="I29" s="21">
         <f t="shared" si="11"/>
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="J29" s="83">
         <f t="shared" si="3"/>
-        <v>8.4732214228617111E-2</v>
+        <v>9.6722621902478018E-2</v>
       </c>
       <c r="K29" s="84">
         <v>600</v>
@@ -5331,11 +5320,11 @@
       </c>
       <c r="O29" s="87">
         <f t="shared" si="6"/>
-        <v>22.405263157894737</v>
+        <v>23.65</v>
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>
-        <v>0.82216981132075473</v>
+        <v>0.72024793388429753</v>
       </c>
       <c r="Q29" s="23" t="e">
         <f>AVERAGE(Q28,Q17,Q23)</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F67B11-F5BA-46B2-B777-5316B7EFDA34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A9AD18-A77D-4CA2-A011-5D3465B0366C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4193,11 +4193,11 @@
       </c>
       <c r="H9" s="71"/>
       <c r="I9" s="12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J9" s="69">
         <f t="shared" si="3"/>
-        <v>2.6666666666666668E-2</v>
+        <v>0</v>
       </c>
       <c r="K9" s="11">
         <v>150</v>
@@ -4216,9 +4216,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P9" s="71">
+      <c r="P9" s="71" t="e">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="Q9" s="14"/>
       <c r="R9" s="34"/>
@@ -4627,11 +4627,11 @@
       </c>
       <c r="I17" s="41">
         <f>SUM(I4:I16)</f>
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>9.3461692739671073E-2</v>
+        <v>9.1857200160449251E-2</v>
       </c>
       <c r="K17" s="76">
         <f>SUM(K4:K16)</f>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>5.0133047210300425</v>
+        <v>5.1008733624454141</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -5298,11 +5298,11 @@
       </c>
       <c r="I29" s="21">
         <f t="shared" si="11"/>
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="J29" s="83">
         <f t="shared" si="3"/>
-        <v>9.6722621902478018E-2</v>
+        <v>9.5123900879296563E-2</v>
       </c>
       <c r="K29" s="84">
         <v>600</v>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>
-        <v>0.72024793388429753</v>
+        <v>0.73235294117647065</v>
       </c>
       <c r="Q29" s="23" t="e">
         <f>AVERAGE(Q28,Q17,Q23)</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A9AD18-A77D-4CA2-A011-5D3465B0366C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA39C98-38EF-4704-9F2E-49C5F127828E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="78">
   <si>
     <t>Booking</t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t>Nabeel Traders SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not Delivered </t>
   </si>
 </sst>
 </file>
@@ -1588,7 +1591,7 @@
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="89">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="G2" s="118" t="s">
         <v>2</v>
@@ -1716,50 +1719,50 @@
         <v>40</v>
       </c>
       <c r="I4" s="12">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J4" s="32">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="K4" s="30">
         <v>40</v>
       </c>
       <c r="L4" s="12">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M4" s="32">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="N4" s="90">
         <f>IFERROR(L4/I4,0)</f>
-        <v>1.3333333333333333</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="O4" s="33"/>
       <c r="P4" s="30">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q4" s="31">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R4" s="32">
         <f>IFERROR(Q4/P4,0)</f>
-        <v>1</v>
+        <v>0.92307692307692313</v>
       </c>
       <c r="S4" s="30">
-        <v>9</v>
+        <v>17.850000000000001</v>
       </c>
       <c r="T4" s="31">
-        <v>9</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="U4" s="32">
         <f>IFERROR(T4/S4,0)</f>
-        <v>1</v>
+        <v>0.90196078431372551</v>
       </c>
       <c r="V4" s="90">
         <f>IFERROR(T4/Q4,0)</f>
-        <v>1.125</v>
+        <v>1.3416666666666668</v>
       </c>
       <c r="W4" s="33"/>
       <c r="X4" s="34"/>
@@ -1790,50 +1793,50 @@
         <v>45</v>
       </c>
       <c r="I5" s="12">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J5" s="13">
         <f t="shared" ref="J5:J32" si="0">IFERROR(I5/G5,0)</f>
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="K5" s="11">
         <v>30</v>
       </c>
       <c r="L5" s="12">
-        <v>21.9</v>
+        <v>13.55</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M32" si="1">IFERROR(L5/K5,0)</f>
-        <v>0.73</v>
+        <v>0.45166666666666672</v>
       </c>
       <c r="N5" s="71">
         <f t="shared" ref="N5:N32" si="2">IFERROR(L5/I5,0)</f>
-        <v>2.4333333333333331</v>
+        <v>0.67749999999999999</v>
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="11">
+        <v>7</v>
+      </c>
+      <c r="Q5" s="12">
         <v>5</v>
-      </c>
-      <c r="Q5" s="12">
-        <v>3</v>
       </c>
       <c r="R5" s="13">
         <f t="shared" ref="R5:R32" si="3">IFERROR(Q5/P5,0)</f>
-        <v>0.6</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S5" s="11">
-        <v>6</v>
+        <v>10.525</v>
       </c>
       <c r="T5" s="12">
-        <v>4</v>
+        <v>9.0250000000000004</v>
       </c>
       <c r="U5" s="13">
         <f t="shared" ref="U5:U32" si="4">IFERROR(T5/S5,0)</f>
-        <v>0.66666666666666663</v>
+        <v>0.85748218527315911</v>
       </c>
       <c r="V5" s="11">
         <f t="shared" ref="V5:V32" si="5">IFERROR(T5/Q5,0)</f>
-        <v>1.3333333333333333</v>
+        <v>1.8050000000000002</v>
       </c>
       <c r="W5" s="14"/>
       <c r="X5" s="34"/>
@@ -1863,7 +1866,9 @@
       <c r="H6" s="71">
         <v>40</v>
       </c>
-      <c r="I6" s="12"/>
+      <c r="I6" s="12">
+        <v>0</v>
+      </c>
       <c r="J6" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1934,50 +1939,50 @@
         <v>45</v>
       </c>
       <c r="I7" s="12">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="K7" s="11">
         <v>30</v>
       </c>
       <c r="L7" s="12">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="1"/>
-        <v>0.19166666666666668</v>
+        <v>0.2</v>
       </c>
       <c r="N7" s="71">
         <f t="shared" si="2"/>
-        <v>0.63888888888888884</v>
+        <v>1.5</v>
       </c>
       <c r="O7" s="14"/>
       <c r="P7" s="11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q7" s="12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R7" s="13">
         <f t="shared" si="3"/>
-        <v>0.77777777777777779</v>
+        <v>0.8</v>
       </c>
       <c r="S7" s="11">
-        <v>8.1</v>
+        <v>10.65</v>
       </c>
       <c r="T7" s="12">
-        <v>5.8</v>
+        <v>9.4749999999999996</v>
       </c>
       <c r="U7" s="13">
         <f t="shared" si="4"/>
-        <v>0.71604938271604934</v>
+        <v>0.88967136150234738</v>
       </c>
       <c r="V7" s="11">
         <f t="shared" si="5"/>
-        <v>0.82857142857142851</v>
+        <v>1.184375</v>
       </c>
       <c r="W7" s="14"/>
       <c r="X7" s="103"/>
@@ -2008,50 +2013,50 @@
         <v>40</v>
       </c>
       <c r="I8" s="12">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K8" s="11">
         <v>20</v>
       </c>
       <c r="L8" s="12">
-        <v>16.7</v>
+        <v>7.7249999999999996</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="1"/>
-        <v>0.83499999999999996</v>
+        <v>0.38624999999999998</v>
       </c>
       <c r="N8" s="71">
         <f t="shared" si="2"/>
-        <v>1.5181818181818181</v>
+        <v>1.1035714285714284</v>
       </c>
       <c r="O8" s="14"/>
       <c r="P8" s="11">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q8" s="12">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R8" s="13">
         <f t="shared" si="3"/>
-        <v>0.83333333333333337</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="S8" s="11">
-        <v>5.7</v>
+        <v>11.125</v>
       </c>
       <c r="T8" s="12">
-        <v>4.7</v>
+        <v>7.5750000000000002</v>
       </c>
       <c r="U8" s="13">
         <f t="shared" si="4"/>
-        <v>0.82456140350877194</v>
+        <v>0.68089887640449442</v>
       </c>
       <c r="V8" s="11">
         <f t="shared" si="5"/>
-        <v>0.94000000000000006</v>
+        <v>0.94687500000000002</v>
       </c>
       <c r="W8" s="14"/>
       <c r="X8" s="103"/>
@@ -2081,7 +2086,9 @@
       <c r="H9" s="71">
         <v>0</v>
       </c>
-      <c r="I9" s="12"/>
+      <c r="I9" s="12">
+        <v>0</v>
+      </c>
       <c r="J9" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2089,7 +2096,9 @@
       <c r="K9" s="11">
         <v>80</v>
       </c>
-      <c r="L9" s="12"/>
+      <c r="L9" s="12">
+        <v>0</v>
+      </c>
       <c r="M9" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2099,8 +2108,12 @@
         <v>0</v>
       </c>
       <c r="O9" s="14"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="12"/>
+      <c r="P9" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>0</v>
+      </c>
       <c r="R9" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2148,53 +2161,48 @@
         <v>10</v>
       </c>
       <c r="I10" s="12">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J10" s="13">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="K10" s="11">
         <v>20</v>
       </c>
       <c r="L10" s="12">
-        <v>60</v>
+        <f>166+66</f>
+        <v>232</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>11.6</v>
       </c>
       <c r="N10" s="71">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O10" s="14"/>
-      <c r="P10" s="11">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="12">
-        <v>3</v>
-      </c>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="12"/>
       <c r="R10" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="S10" s="11">
-        <v>66</v>
-      </c>
-      <c r="T10" s="12">
-        <v>65.95</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S10" s="11"/>
+      <c r="T10" s="12"/>
       <c r="U10" s="13">
         <f t="shared" si="4"/>
-        <v>0.99924242424242427</v>
+        <v>0</v>
       </c>
       <c r="V10" s="11">
         <f t="shared" si="5"/>
-        <v>21.983333333333334</v>
+        <v>0</v>
       </c>
       <c r="W10" s="14"/>
-      <c r="X10" s="103"/>
+      <c r="X10" s="104" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="11" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A11" s="35" t="s">
@@ -2222,25 +2230,25 @@
         <v>50</v>
       </c>
       <c r="I11" s="12">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="J11" s="13">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.52</v>
       </c>
       <c r="K11" s="11">
         <v>20</v>
       </c>
       <c r="L11" s="12">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="N11" s="71">
         <f t="shared" si="2"/>
-        <v>1.2</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="O11" s="14"/>
       <c r="P11" s="11">
@@ -2296,25 +2304,25 @@
         <v>40</v>
       </c>
       <c r="I12" s="12">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="J12" s="13">
         <f t="shared" si="0"/>
-        <v>0.68</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="K12" s="11">
         <v>30</v>
       </c>
       <c r="L12" s="12">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="M12" s="13">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="N12" s="11">
         <f t="shared" si="2"/>
-        <v>1.411764705882353</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="O12" s="14"/>
       <c r="P12" s="11">
@@ -2370,11 +2378,11 @@
         <v>40</v>
       </c>
       <c r="I13" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J13" s="13">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="K13" s="11">
         <v>30</v>
@@ -2388,7 +2396,7 @@
       </c>
       <c r="N13" s="11">
         <f t="shared" si="2"/>
-        <v>0.88888888888888884</v>
+        <v>0.8</v>
       </c>
       <c r="O13" s="14"/>
       <c r="P13" s="11">
@@ -2741,9 +2749,7 @@
       <c r="K19" s="36">
         <v>0</v>
       </c>
-      <c r="L19" s="37">
-        <v>0</v>
-      </c>
+      <c r="L19" s="37"/>
       <c r="M19" s="38">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2799,27 +2805,27 @@
       </c>
       <c r="I20" s="41">
         <f>SUM(I4:I19)</f>
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="J20" s="42">
         <f t="shared" si="0"/>
-        <v>0.2017353579175705</v>
+        <v>0.21691973969631237</v>
       </c>
       <c r="K20" s="40">
         <f t="shared" ref="K20:L20" si="6">SUM(K4:K19)</f>
         <v>329</v>
       </c>
       <c r="L20" s="40">
-        <f t="shared" si="6"/>
-        <v>188.35</v>
+        <f>SUM(L4:L19)</f>
+        <v>307.27499999999998</v>
       </c>
       <c r="M20" s="42">
         <f t="shared" si="1"/>
-        <v>0.57249240121580547</v>
+        <v>0.93396656534954403</v>
       </c>
       <c r="N20" s="40">
         <f t="shared" si="2"/>
-        <v>2.0252688172043012</v>
+        <v>3.0727499999999996</v>
       </c>
       <c r="O20" s="43" t="e">
         <f>AVERAGE(O4:O19)</f>
@@ -2827,31 +2833,31 @@
       </c>
       <c r="P20" s="40">
         <f t="shared" ref="P20" si="7">SUM(P4:P19)</f>
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="Q20" s="41">
         <f t="shared" ref="Q20" si="8">SUM(Q4:Q19)</f>
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="R20" s="42">
         <f t="shared" si="3"/>
-        <v>0.91379310344827591</v>
+        <v>0.88235294117647056</v>
       </c>
       <c r="S20" s="40">
         <f t="shared" ref="S20" si="9">SUM(S4:S19)</f>
-        <v>121.8</v>
+        <v>77.150000000000006</v>
       </c>
       <c r="T20" s="41">
         <f t="shared" ref="T20" si="10">SUM(T4:T19)</f>
-        <v>116.45</v>
+        <v>69.175000000000011</v>
       </c>
       <c r="U20" s="42">
         <f t="shared" si="4"/>
-        <v>0.95607553366174058</v>
+        <v>0.89662994167206744</v>
       </c>
       <c r="V20" s="40">
         <f t="shared" si="5"/>
-        <v>2.1971698113207547</v>
+        <v>1.1529166666666668</v>
       </c>
       <c r="W20" s="43">
         <f>AVERAGE(W4:W19)</f>
@@ -3684,11 +3690,11 @@
       </c>
       <c r="I32" s="21">
         <f t="shared" si="17"/>
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="J32" s="22">
         <f t="shared" si="0"/>
-        <v>0.19787234042553192</v>
+        <v>0.21276595744680851</v>
       </c>
       <c r="K32" s="20">
         <v>1</v>
@@ -3702,7 +3708,7 @@
       </c>
       <c r="N32" s="20">
         <f t="shared" si="2"/>
-        <v>1.0752688172043012E-2</v>
+        <v>0.01</v>
       </c>
       <c r="O32" s="23" t="e">
         <f>AVERAGE(O31,O20,O26)</f>
@@ -3710,31 +3716,31 @@
       </c>
       <c r="P32" s="20">
         <f>+P31+P26+P20</f>
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="Q32" s="21">
         <f t="shared" ref="Q32" si="18">+Q31+Q26+Q20</f>
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="R32" s="22">
         <f t="shared" si="3"/>
-        <v>0.92537313432835822</v>
+        <v>0.89610389610389607</v>
       </c>
       <c r="S32" s="20">
         <f>+S31+S26+S20</f>
-        <v>130.80000000000001</v>
+        <v>86.15</v>
       </c>
       <c r="T32" s="21">
         <f t="shared" ref="T32" si="19">+T31+T26+T20</f>
-        <v>125.45</v>
+        <v>78.175000000000011</v>
       </c>
       <c r="U32" s="22">
         <f t="shared" si="4"/>
-        <v>0.95909785932721703</v>
+        <v>0.9074289030760303</v>
       </c>
       <c r="V32" s="20">
         <f t="shared" si="5"/>
-        <v>2.0233870967741936</v>
+        <v>1.1329710144927538</v>
       </c>
       <c r="W32" s="23">
         <f>AVERAGE(W31,W20,W26)</f>
@@ -3800,18 +3806,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.33333333333333331</v>
+        <v>0.40740740740740738</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F2" s="89">
-        <v>46305</v>
+        <v>46308</v>
       </c>
       <c r="G2" s="118" t="s">
         <v>34</v>
@@ -3911,34 +3917,34 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>15+13+9+11+10+11+8</f>
-        <v>77</v>
+        <f>15+13+9+11+10+11+8+12</f>
+        <v>89</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.23692307692307693</v>
+        <v>0.27384615384615385</v>
       </c>
       <c r="K4" s="7">
         <v>450</v>
       </c>
       <c r="L4" s="8">
-        <v>88.5</v>
+        <v>113.6</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.19666666666666666</v>
+        <v>0.25244444444444442</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>361.5</v>
+        <v>336.4</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>20.083333333333332</v>
+        <v>21.024999999999999</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P16" si="2">L4/I4</f>
-        <v>1.1493506493506493</v>
+        <v>1.2764044943820223</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3967,34 +3973,34 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <f>6+5+5+3+3+4+3</f>
-        <v>29</v>
+        <f>6+5+5+3+3+4+3+5</f>
+        <v>34</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J29" si="3">IFERROR(I5/G5,0)</f>
-        <v>0.12236286919831224</v>
+        <v>0.14345991561181434</v>
       </c>
       <c r="K5" s="11">
         <v>350</v>
       </c>
       <c r="L5" s="12">
-        <v>51.6</v>
+        <v>76.525000000000006</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M29" si="4">IFERROR(L5/K5,0)</f>
-        <v>0.14742857142857144</v>
+        <v>0.21864285714285717</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>298.39999999999998</v>
+        <v>273.47500000000002</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>16.577777777777776</v>
+        <v>17.092187500000001</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>1.7793103448275862</v>
+        <v>2.2507352941176473</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -4046,7 +4052,7 @@
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>17.81527777777778</v>
+        <v>20.042187500000001</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
@@ -4081,34 +4087,34 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>2+2+6+4+9+7</f>
-        <v>30</v>
+        <f>2+2+6+4+9+7+8</f>
+        <v>38</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>0.10416666666666667</v>
+        <v>0.13194444444444445</v>
       </c>
       <c r="K7" s="11">
         <v>250</v>
       </c>
       <c r="L7" s="12">
-        <v>44.9</v>
+        <v>60.125</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>0.17959999999999998</v>
+        <v>0.24049999999999999</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>205.1</v>
+        <v>189.875</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>11.394444444444444</v>
+        <v>11.8671875</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.4966666666666666</v>
+        <v>1.5822368421052631</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4137,34 +4143,34 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <f>3+6+7+6+6+3+5</f>
-        <v>36</v>
+        <f>3+6+7+6+6+3+5+8</f>
+        <v>44</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>0.10084033613445378</v>
+        <v>0.12324929971988796</v>
       </c>
       <c r="K8" s="11">
         <v>250</v>
       </c>
       <c r="L8" s="12">
-        <v>41.725000000000001</v>
+        <v>63.7</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>0.16689999999999999</v>
+        <v>0.25480000000000003</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N29" si="5">K8-L8</f>
-        <v>208.27500000000001</v>
+        <v>186.3</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
-        <v>11.570833333333333</v>
+        <v>11.643750000000001</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.1590277777777778</v>
+        <v>1.4477272727272728</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4257,23 +4263,23 @@
         <v>2300</v>
       </c>
       <c r="L10" s="12">
-        <v>486.05</v>
+        <v>578</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>0.21132608695652175</v>
+        <v>0.25130434782608696</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>1813.95</v>
+        <v>1722</v>
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>100.77500000000001</v>
+        <v>107.625</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>22.093181818181819</v>
+        <v>26.272727272727273</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
@@ -4302,33 +4308,34 @@
       </c>
       <c r="H11" s="71"/>
       <c r="I11" s="12">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="J11" s="69">
         <f t="shared" si="3"/>
-        <v>2.7950310559006212E-2</v>
+        <v>0.2360248447204969</v>
       </c>
       <c r="K11" s="11">
         <v>450</v>
       </c>
       <c r="L11" s="12">
-        <v>18</v>
+        <f>106+16+15</f>
+        <v>137</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="4"/>
-        <v>0.04</v>
+        <v>0.30444444444444446</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="5"/>
-        <v>432</v>
+        <v>313</v>
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>19.5625</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1.8026315789473684</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="105"/>
@@ -4357,34 +4364,34 @@
       </c>
       <c r="H12" s="71"/>
       <c r="I12" s="12">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="J12" s="69">
         <f t="shared" si="3"/>
-        <v>2.8938906752411574E-2</v>
+        <v>0.22508038585209003</v>
       </c>
       <c r="K12" s="11">
         <v>300</v>
       </c>
       <c r="L12" s="12">
-        <f>12+15</f>
-        <v>27</v>
+        <f>100+8+8</f>
+        <v>116</v>
       </c>
       <c r="M12" s="70">
         <f t="shared" si="4"/>
-        <v>0.09</v>
+        <v>0.38666666666666666</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="5"/>
-        <v>273</v>
+        <v>184</v>
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>15.166666666666666</v>
+        <v>11.5</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1.6571428571428573</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="105"/>
@@ -4413,34 +4420,34 @@
       </c>
       <c r="H13" s="71"/>
       <c r="I13" s="12">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J13" s="69">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="K13" s="11">
         <v>250</v>
       </c>
       <c r="L13" s="12">
-        <f>4+12</f>
-        <v>16</v>
+        <f>50+10+10</f>
+        <v>70</v>
       </c>
       <c r="M13" s="70">
         <f t="shared" si="4"/>
-        <v>6.4000000000000001E-2</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="5"/>
-        <v>234</v>
+        <v>180</v>
       </c>
       <c r="O13" s="14">
         <f t="shared" si="6"/>
-        <v>13</v>
-      </c>
-      <c r="P13" s="71" t="e">
+        <v>11.25</v>
+      </c>
+      <c r="P13" s="71">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>1.1666666666666667</v>
       </c>
       <c r="Q13" s="14"/>
       <c r="R13" s="105"/>
@@ -4489,7 +4496,7 @@
       </c>
       <c r="O14" s="14">
         <f t="shared" si="6"/>
-        <v>-5</v>
+        <v>-5.625</v>
       </c>
       <c r="P14" s="71">
         <f t="shared" si="2"/>
@@ -4542,7 +4549,7 @@
       </c>
       <c r="O15" s="14">
         <f t="shared" si="6"/>
-        <v>-4.166666666666667</v>
+        <v>-4.6875</v>
       </c>
       <c r="P15" s="71">
         <f t="shared" si="2"/>
@@ -4581,7 +4588,7 @@
       </c>
       <c r="K16" s="11"/>
       <c r="L16" s="12">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="M16" s="70">
         <f t="shared" si="4"/>
@@ -4589,15 +4596,15 @@
       </c>
       <c r="N16" s="12">
         <f t="shared" si="5"/>
-        <v>-200</v>
+        <v>-215</v>
       </c>
       <c r="O16" s="14">
         <f t="shared" si="6"/>
-        <v>-11.111111111111111</v>
+        <v>-13.4375</v>
       </c>
       <c r="P16" s="71">
         <f t="shared" si="2"/>
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="Q16" s="14"/>
       <c r="R16" s="34"/>
@@ -4627,11 +4634,11 @@
       </c>
       <c r="I17" s="41">
         <f>SUM(I4:I16)</f>
-        <v>229</v>
+        <v>450</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>9.1857200160449251E-2</v>
+        <v>0.18050541516245489</v>
       </c>
       <c r="K17" s="76">
         <f>SUM(K4:K16)</f>
@@ -4639,23 +4646,23 @@
       </c>
       <c r="L17" s="77">
         <f>SUM(L4:L16)</f>
-        <v>1168.0999999999999</v>
+        <v>1624.2750000000001</v>
       </c>
       <c r="M17" s="78">
         <f t="shared" si="4"/>
-        <v>0.2290392156862745</v>
+        <v>0.31848529411764709</v>
       </c>
       <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>3931.9</v>
+        <v>3475.7249999999999</v>
       </c>
       <c r="O17" s="79">
         <f t="shared" si="6"/>
-        <v>218.4388888888889</v>
+        <v>217.23281249999999</v>
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>5.1008733624454141</v>
+        <v>3.6095000000000002</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -4709,7 +4716,7 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="6"/>
-        <v>23.65</v>
+        <v>26.606249999999999</v>
       </c>
       <c r="P18" s="96">
         <f t="shared" ref="P18:P22" si="7">L18/I18</f>
@@ -4764,7 +4771,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>23.65</v>
+        <v>26.606249999999999</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4819,7 +4826,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>23.65</v>
+        <v>26.606249999999999</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4874,7 +4881,7 @@
       </c>
       <c r="O21" s="14">
         <f t="shared" si="6"/>
-        <v>23.65</v>
+        <v>26.606249999999999</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="7"/>
@@ -4929,7 +4936,7 @@
       </c>
       <c r="O22" s="94">
         <f t="shared" si="6"/>
-        <v>23.65</v>
+        <v>26.606249999999999</v>
       </c>
       <c r="P22" s="74">
         <f t="shared" si="7"/>
@@ -4987,7 +4994,7 @@
       </c>
       <c r="O23" s="79">
         <f t="shared" si="6"/>
-        <v>23.65</v>
+        <v>26.606249999999999</v>
       </c>
       <c r="P23" s="80">
         <f>L23/I23</f>
@@ -5045,7 +5052,7 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="6"/>
-        <v>23.65</v>
+        <v>26.606249999999999</v>
       </c>
       <c r="P24" s="96">
         <f t="shared" ref="P24:P27" si="9">L24/I24</f>
@@ -5100,7 +5107,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>23.65</v>
+        <v>26.606249999999999</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5155,7 +5162,7 @@
       </c>
       <c r="O26" s="14">
         <f t="shared" si="6"/>
-        <v>23.65</v>
+        <v>26.606249999999999</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="9"/>
@@ -5210,7 +5217,7 @@
       </c>
       <c r="O27" s="94">
         <f t="shared" si="6"/>
-        <v>23.65</v>
+        <v>26.606249999999999</v>
       </c>
       <c r="P27" s="74">
         <f t="shared" si="9"/>
@@ -5265,7 +5272,7 @@
       </c>
       <c r="O28" s="79">
         <f t="shared" si="6"/>
-        <v>23.65</v>
+        <v>26.606249999999999</v>
       </c>
       <c r="P28" s="80">
         <f>L28/I28</f>
@@ -5298,11 +5305,11 @@
       </c>
       <c r="I29" s="21">
         <f t="shared" si="11"/>
-        <v>238</v>
+        <v>459</v>
       </c>
       <c r="J29" s="83">
         <f t="shared" si="3"/>
-        <v>9.5123900879296563E-2</v>
+        <v>0.18345323741007194</v>
       </c>
       <c r="K29" s="84">
         <v>600</v>
@@ -5320,11 +5327,11 @@
       </c>
       <c r="O29" s="87">
         <f t="shared" si="6"/>
-        <v>23.65</v>
+        <v>26.606249999999999</v>
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>
-        <v>0.73235294117647065</v>
+        <v>0.37973856209150331</v>
       </c>
       <c r="Q29" s="23" t="e">
         <f>AVERAGE(Q28,Q17,Q23)</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA39C98-38EF-4704-9F2E-49C5F127828E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5987AD-F9ED-464C-B040-B6E2E06FAD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="78">
   <si>
     <t>Booking</t>
   </si>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="89">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="G2" s="118" t="s">
         <v>2</v>
@@ -1719,25 +1719,25 @@
         <v>40</v>
       </c>
       <c r="I4" s="12">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J4" s="32">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="K4" s="30">
         <v>40</v>
       </c>
       <c r="L4" s="12">
-        <v>10</v>
+        <v>7.45</v>
       </c>
       <c r="M4" s="32">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.25</v>
+        <v>0.18625</v>
       </c>
       <c r="N4" s="90">
         <f>IFERROR(L4/I4,0)</f>
-        <v>0.90909090909090906</v>
+        <v>1.49</v>
       </c>
       <c r="O4" s="33"/>
       <c r="P4" s="30">
@@ -1765,7 +1765,9 @@
         <v>1.3416666666666668</v>
       </c>
       <c r="W4" s="33"/>
-      <c r="X4" s="34"/>
+      <c r="X4" s="104" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="5" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="35" t="s">
@@ -1793,25 +1795,25 @@
         <v>45</v>
       </c>
       <c r="I5" s="12">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J5" s="13">
         <f t="shared" ref="J5:J32" si="0">IFERROR(I5/G5,0)</f>
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="K5" s="11">
         <v>30</v>
       </c>
       <c r="L5" s="12">
-        <v>13.55</v>
+        <v>7</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M32" si="1">IFERROR(L5/K5,0)</f>
-        <v>0.45166666666666672</v>
+        <v>0.23333333333333334</v>
       </c>
       <c r="N5" s="71">
         <f t="shared" ref="N5:N32" si="2">IFERROR(L5/I5,0)</f>
-        <v>0.67749999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="11">
@@ -1839,7 +1841,9 @@
         <v>1.8050000000000002</v>
       </c>
       <c r="W5" s="14"/>
-      <c r="X5" s="34"/>
+      <c r="X5" s="104" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="6" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="35" t="s">
@@ -1866,9 +1870,7 @@
       <c r="H6" s="71">
         <v>40</v>
       </c>
-      <c r="I6" s="12">
-        <v>0</v>
-      </c>
+      <c r="I6" s="12"/>
       <c r="J6" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1939,25 +1941,25 @@
         <v>45</v>
       </c>
       <c r="I7" s="12">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K7" s="11">
         <v>30</v>
       </c>
       <c r="L7" s="12">
-        <v>6</v>
+        <v>3.05</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0.10166666666666666</v>
       </c>
       <c r="N7" s="71">
         <f t="shared" si="2"/>
-        <v>1.5</v>
+        <v>0.43571428571428567</v>
       </c>
       <c r="O7" s="14"/>
       <c r="P7" s="11">
@@ -1985,7 +1987,9 @@
         <v>1.184375</v>
       </c>
       <c r="W7" s="14"/>
-      <c r="X7" s="103"/>
+      <c r="X7" s="104" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="8" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="35" t="s">
@@ -2013,25 +2017,25 @@
         <v>40</v>
       </c>
       <c r="I8" s="12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="K8" s="11">
         <v>20</v>
       </c>
       <c r="L8" s="12">
-        <v>7.7249999999999996</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="1"/>
-        <v>0.38624999999999998</v>
+        <v>0.20750000000000002</v>
       </c>
       <c r="N8" s="71">
         <f t="shared" si="2"/>
-        <v>1.1035714285714284</v>
+        <v>0.46111111111111114</v>
       </c>
       <c r="O8" s="14"/>
       <c r="P8" s="11">
@@ -2059,7 +2063,9 @@
         <v>0.94687500000000002</v>
       </c>
       <c r="W8" s="14"/>
-      <c r="X8" s="103"/>
+      <c r="X8" s="104" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="9" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="35" t="s">
@@ -2086,9 +2092,7 @@
       <c r="H9" s="71">
         <v>0</v>
       </c>
-      <c r="I9" s="12">
-        <v>0</v>
-      </c>
+      <c r="I9" s="12"/>
       <c r="J9" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2096,9 +2100,7 @@
       <c r="K9" s="11">
         <v>80</v>
       </c>
-      <c r="L9" s="12">
-        <v>0</v>
-      </c>
+      <c r="L9" s="12"/>
       <c r="M9" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2161,11 +2163,11 @@
         <v>10</v>
       </c>
       <c r="I10" s="12">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J10" s="13">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K10" s="11">
         <v>20</v>
@@ -2180,7 +2182,7 @@
       </c>
       <c r="N10" s="71">
         <f t="shared" si="2"/>
-        <v>29</v>
+        <v>46.4</v>
       </c>
       <c r="O10" s="14"/>
       <c r="P10" s="11"/>
@@ -2230,25 +2232,25 @@
         <v>50</v>
       </c>
       <c r="I11" s="12">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J11" s="13">
         <f t="shared" si="0"/>
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="K11" s="11">
         <v>20</v>
       </c>
       <c r="L11" s="12">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="N11" s="71">
         <f t="shared" si="2"/>
-        <v>0.61538461538461542</v>
+        <v>1.52</v>
       </c>
       <c r="O11" s="14"/>
       <c r="P11" s="11">
@@ -2304,25 +2306,25 @@
         <v>40</v>
       </c>
       <c r="I12" s="12">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J12" s="13">
         <f t="shared" si="0"/>
-        <v>0.28000000000000003</v>
+        <v>0.1</v>
       </c>
       <c r="K12" s="11">
         <v>30</v>
       </c>
       <c r="L12" s="12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M12" s="13">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="N12" s="11">
         <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
+        <v>1.2</v>
       </c>
       <c r="O12" s="14"/>
       <c r="P12" s="11">
@@ -2378,25 +2380,25 @@
         <v>40</v>
       </c>
       <c r="I13" s="12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J13" s="13">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="K13" s="11">
         <v>30</v>
       </c>
       <c r="L13" s="12">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M13" s="13">
         <f t="shared" si="1"/>
-        <v>0.26666666666666666</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="N13" s="11">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="O13" s="14"/>
       <c r="P13" s="11">
@@ -2805,27 +2807,27 @@
       </c>
       <c r="I20" s="41">
         <f>SUM(I4:I19)</f>
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="J20" s="42">
         <f t="shared" si="0"/>
-        <v>0.21691973969631237</v>
+        <v>0.14533622559652928</v>
       </c>
       <c r="K20" s="40">
-        <f t="shared" ref="K20:L20" si="6">SUM(K4:K19)</f>
+        <f t="shared" ref="K20" si="6">SUM(K4:K19)</f>
         <v>329</v>
       </c>
       <c r="L20" s="40">
         <f>SUM(L4:L19)</f>
-        <v>307.27499999999998</v>
+        <v>305.64999999999998</v>
       </c>
       <c r="M20" s="42">
         <f t="shared" si="1"/>
-        <v>0.93396656534954403</v>
+        <v>0.92902735562310024</v>
       </c>
       <c r="N20" s="40">
         <f t="shared" si="2"/>
-        <v>3.0727499999999996</v>
+        <v>4.5619402985074622</v>
       </c>
       <c r="O20" s="43" t="e">
         <f>AVERAGE(O4:O19)</f>
@@ -3690,11 +3692,11 @@
       </c>
       <c r="I32" s="21">
         <f t="shared" si="17"/>
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="J32" s="22">
         <f t="shared" si="0"/>
-        <v>0.21276595744680851</v>
+        <v>0.14255319148936171</v>
       </c>
       <c r="K32" s="20">
         <v>1</v>
@@ -3708,7 +3710,7 @@
       </c>
       <c r="N32" s="20">
         <f t="shared" si="2"/>
-        <v>0.01</v>
+        <v>1.4925373134328358E-2</v>
       </c>
       <c r="O32" s="23" t="e">
         <f>AVERAGE(O31,O20,O26)</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5987AD-F9ED-464C-B040-B6E2E06FAD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D85301B-85A5-450C-9CF1-919F5239BB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="76">
   <si>
     <t>Booking</t>
   </si>
@@ -244,9 +244,6 @@
     <t>Sohail Kasoor SD</t>
   </si>
   <si>
-    <t>Absent</t>
-  </si>
-  <si>
     <t>ABSENT</t>
   </si>
   <si>
@@ -257,9 +254,6 @@
   </si>
   <si>
     <t>Nabeel Traders SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not Delivered </t>
   </si>
 </sst>
 </file>
@@ -1201,9 +1195,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1254,6 +1245,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1567,55 +1561,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G1" s="112" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="115" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
-      <c r="V1" s="116"/>
-      <c r="W1" s="117"/>
+      <c r="G1" s="111" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="114" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
+      <c r="V1" s="115"/>
+      <c r="W1" s="116"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="89">
-        <v>46310</v>
-      </c>
-      <c r="G2" s="118" t="s">
+        <v>46311</v>
+      </c>
+      <c r="G2" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="119" t="s">
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="119"/>
-      <c r="M2" s="120"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="119"/>
       <c r="N2" s="1"/>
       <c r="O2" s="2"/>
-      <c r="P2" s="118" t="s">
+      <c r="P2" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="119"/>
-      <c r="R2" s="120"/>
-      <c r="S2" s="119" t="s">
+      <c r="Q2" s="118"/>
+      <c r="R2" s="119"/>
+      <c r="S2" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="T2" s="119"/>
-      <c r="U2" s="120"/>
+      <c r="T2" s="118"/>
+      <c r="U2" s="119"/>
       <c r="V2" s="1"/>
       <c r="W2" s="2"/>
     </row>
@@ -1718,56 +1712,42 @@
       <c r="H4" s="68">
         <v>40</v>
       </c>
-      <c r="I4" s="12">
-        <v>5</v>
-      </c>
+      <c r="I4" s="12"/>
       <c r="J4" s="32">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="30">
         <v>40</v>
       </c>
-      <c r="L4" s="12">
-        <v>7.45</v>
-      </c>
+      <c r="L4" s="12"/>
       <c r="M4" s="32">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.18625</v>
+        <v>0</v>
       </c>
       <c r="N4" s="90">
         <f>IFERROR(L4/I4,0)</f>
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O4" s="33"/>
-      <c r="P4" s="30">
-        <v>13</v>
-      </c>
-      <c r="Q4" s="31">
-        <v>12</v>
-      </c>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="31"/>
       <c r="R4" s="32">
         <f>IFERROR(Q4/P4,0)</f>
-        <v>0.92307692307692313</v>
-      </c>
-      <c r="S4" s="30">
-        <v>17.850000000000001</v>
-      </c>
-      <c r="T4" s="31">
-        <v>16.100000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S4" s="30"/>
+      <c r="T4" s="31"/>
       <c r="U4" s="32">
         <f>IFERROR(T4/S4,0)</f>
-        <v>0.90196078431372551</v>
+        <v>0</v>
       </c>
       <c r="V4" s="90">
         <f>IFERROR(T4/Q4,0)</f>
-        <v>1.3416666666666668</v>
+        <v>0</v>
       </c>
       <c r="W4" s="33"/>
-      <c r="X4" s="104" t="s">
-        <v>77</v>
-      </c>
+      <c r="X4" s="122"/>
     </row>
     <row r="5" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="35" t="s">
@@ -1794,56 +1774,50 @@
       <c r="H5" s="71">
         <v>45</v>
       </c>
-      <c r="I5" s="12">
-        <v>5</v>
-      </c>
+      <c r="I5" s="12"/>
       <c r="J5" s="13">
         <f t="shared" ref="J5:J32" si="0">IFERROR(I5/G5,0)</f>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="11">
         <v>30</v>
       </c>
-      <c r="L5" s="12">
-        <v>7</v>
-      </c>
+      <c r="L5" s="12"/>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M32" si="1">IFERROR(L5/K5,0)</f>
-        <v>0.23333333333333334</v>
+        <v>0</v>
       </c>
       <c r="N5" s="71">
         <f t="shared" ref="N5:N32" si="2">IFERROR(L5/I5,0)</f>
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="11">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Q5" s="12">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="R5" s="13">
         <f t="shared" ref="R5:R32" si="3">IFERROR(Q5/P5,0)</f>
-        <v>0.7142857142857143</v>
+        <v>0.92307692307692313</v>
       </c>
       <c r="S5" s="11">
-        <v>10.525</v>
+        <v>20</v>
       </c>
       <c r="T5" s="12">
-        <v>9.0250000000000004</v>
+        <v>19</v>
       </c>
       <c r="U5" s="13">
         <f t="shared" ref="U5:U32" si="4">IFERROR(T5/S5,0)</f>
-        <v>0.85748218527315911</v>
+        <v>0.95</v>
       </c>
       <c r="V5" s="11">
         <f t="shared" ref="V5:V32" si="5">IFERROR(T5/Q5,0)</f>
-        <v>1.8050000000000002</v>
+        <v>1.5833333333333333</v>
       </c>
       <c r="W5" s="14"/>
-      <c r="X5" s="104" t="s">
-        <v>77</v>
-      </c>
+      <c r="X5" s="122"/>
     </row>
     <row r="6" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="35" t="s">
@@ -1878,9 +1852,7 @@
       <c r="K6" s="11">
         <v>25</v>
       </c>
-      <c r="L6" s="12">
-        <v>0</v>
-      </c>
+      <c r="L6" s="12"/>
       <c r="M6" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1896,12 +1868,8 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S6" s="11">
-        <v>0</v>
-      </c>
-      <c r="T6" s="12">
-        <v>0</v>
-      </c>
+      <c r="S6" s="11"/>
+      <c r="T6" s="12"/>
       <c r="U6" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -1911,9 +1879,7 @@
         <v>0</v>
       </c>
       <c r="W6" s="14"/>
-      <c r="X6" s="104" t="s">
-        <v>72</v>
-      </c>
+      <c r="X6" s="122"/>
     </row>
     <row r="7" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="35" t="s">
@@ -1940,56 +1906,50 @@
       <c r="H7" s="71">
         <v>45</v>
       </c>
-      <c r="I7" s="12">
-        <v>7</v>
-      </c>
+      <c r="I7" s="12"/>
       <c r="J7" s="13">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0</v>
       </c>
       <c r="K7" s="11">
         <v>30</v>
       </c>
-      <c r="L7" s="12">
-        <v>3.05</v>
-      </c>
+      <c r="L7" s="12"/>
       <c r="M7" s="70">
         <f t="shared" si="1"/>
-        <v>0.10166666666666666</v>
+        <v>0</v>
       </c>
       <c r="N7" s="71">
         <f t="shared" si="2"/>
-        <v>0.43571428571428567</v>
+        <v>0</v>
       </c>
       <c r="O7" s="14"/>
       <c r="P7" s="11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q7" s="12">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R7" s="13">
         <f t="shared" si="3"/>
-        <v>0.8</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S7" s="11">
-        <v>10.65</v>
+        <v>9</v>
       </c>
       <c r="T7" s="12">
-        <v>9.4749999999999996</v>
+        <v>2</v>
       </c>
       <c r="U7" s="13">
         <f t="shared" si="4"/>
-        <v>0.88967136150234738</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="V7" s="11">
         <f t="shared" si="5"/>
-        <v>1.184375</v>
+        <v>2</v>
       </c>
       <c r="W7" s="14"/>
-      <c r="X7" s="104" t="s">
-        <v>77</v>
-      </c>
+      <c r="X7" s="122"/>
     </row>
     <row r="8" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="35" t="s">
@@ -2017,55 +1977,45 @@
         <v>40</v>
       </c>
       <c r="I8" s="12">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="K8" s="11">
         <v>20</v>
       </c>
       <c r="L8" s="12">
-        <v>4.1500000000000004</v>
+        <v>22</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="1"/>
-        <v>0.20750000000000002</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="N8" s="71">
         <f t="shared" si="2"/>
-        <v>0.46111111111111114</v>
+        <v>3.6666666666666665</v>
       </c>
       <c r="O8" s="14"/>
-      <c r="P8" s="11">
-        <v>11</v>
-      </c>
-      <c r="Q8" s="12">
-        <v>8</v>
-      </c>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="12"/>
       <c r="R8" s="13">
         <f t="shared" si="3"/>
-        <v>0.72727272727272729</v>
-      </c>
-      <c r="S8" s="11">
-        <v>11.125</v>
-      </c>
-      <c r="T8" s="12">
-        <v>7.5750000000000002</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S8" s="11"/>
+      <c r="T8" s="12"/>
       <c r="U8" s="13">
         <f t="shared" si="4"/>
-        <v>0.68089887640449442</v>
+        <v>0</v>
       </c>
       <c r="V8" s="11">
         <f t="shared" si="5"/>
-        <v>0.94687500000000002</v>
+        <v>0</v>
       </c>
       <c r="W8" s="14"/>
-      <c r="X8" s="104" t="s">
-        <v>77</v>
-      </c>
+      <c r="X8" s="122"/>
     </row>
     <row r="9" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="35" t="s">
@@ -2110,22 +2060,14 @@
         <v>0</v>
       </c>
       <c r="O9" s="14"/>
-      <c r="P9" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="12">
-        <v>0</v>
-      </c>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="12"/>
       <c r="R9" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S9" s="11">
-        <v>0</v>
-      </c>
-      <c r="T9" s="12">
-        <v>0</v>
-      </c>
+      <c r="S9" s="11"/>
+      <c r="T9" s="12"/>
       <c r="U9" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -2135,7 +2077,7 @@
         <v>0</v>
       </c>
       <c r="W9" s="14"/>
-      <c r="X9" s="103"/>
+      <c r="X9" s="122"/>
     </row>
     <row r="10" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="35" t="s">
@@ -2162,27 +2104,22 @@
       <c r="H10" s="71">
         <v>10</v>
       </c>
-      <c r="I10" s="12">
-        <v>5</v>
-      </c>
+      <c r="I10" s="12"/>
       <c r="J10" s="13">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K10" s="11">
         <v>20</v>
       </c>
-      <c r="L10" s="12">
-        <f>166+66</f>
-        <v>232</v>
-      </c>
+      <c r="L10" s="12"/>
       <c r="M10" s="70">
         <f t="shared" si="1"/>
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="N10" s="71">
         <f t="shared" si="2"/>
-        <v>46.4</v>
+        <v>0</v>
       </c>
       <c r="O10" s="14"/>
       <c r="P10" s="11"/>
@@ -2202,9 +2139,7 @@
         <v>0</v>
       </c>
       <c r="W10" s="14"/>
-      <c r="X10" s="104" t="s">
-        <v>77</v>
-      </c>
+      <c r="X10" s="122"/>
     </row>
     <row r="11" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A11" s="35" t="s">
@@ -2232,25 +2167,25 @@
         <v>50</v>
       </c>
       <c r="I11" s="12">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J11" s="13">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K11" s="11">
         <v>20</v>
       </c>
       <c r="L11" s="12">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="1"/>
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="N11" s="71">
         <f t="shared" si="2"/>
-        <v>1.52</v>
+        <v>0.9</v>
       </c>
       <c r="O11" s="14"/>
       <c r="P11" s="11">
@@ -2278,7 +2213,7 @@
         <v>1.2</v>
       </c>
       <c r="W11" s="14"/>
-      <c r="X11" s="103"/>
+      <c r="X11" s="122"/>
     </row>
     <row r="12" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="35" t="s">
@@ -2306,25 +2241,25 @@
         <v>40</v>
       </c>
       <c r="I12" s="12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J12" s="13">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="K12" s="11">
         <v>30</v>
       </c>
       <c r="L12" s="12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M12" s="13">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="N12" s="11">
         <f t="shared" si="2"/>
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="O12" s="14"/>
       <c r="P12" s="11">
@@ -2379,26 +2314,22 @@
       <c r="H13" s="71">
         <v>40</v>
       </c>
-      <c r="I13" s="12">
-        <v>6</v>
-      </c>
+      <c r="I13" s="12"/>
       <c r="J13" s="13">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="K13" s="11">
         <v>30</v>
       </c>
-      <c r="L13" s="12">
-        <v>4</v>
-      </c>
+      <c r="L13" s="12"/>
       <c r="M13" s="13">
         <f t="shared" si="1"/>
-        <v>0.13333333333333333</v>
+        <v>0</v>
       </c>
       <c r="N13" s="11">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0</v>
       </c>
       <c r="O13" s="14"/>
       <c r="P13" s="11">
@@ -2735,7 +2666,7 @@
         <v>22</v>
       </c>
       <c r="F19" s="50" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G19" s="36">
         <v>0</v>
@@ -2792,11 +2723,11 @@
       <c r="C20" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="106" t="s">
+      <c r="D20" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="107"/>
-      <c r="F20" s="108"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="107"/>
       <c r="G20" s="40">
         <f>SUM(G4:G19)</f>
         <v>461</v>
@@ -2807,11 +2738,11 @@
       </c>
       <c r="I20" s="41">
         <f>SUM(I4:I19)</f>
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="J20" s="42">
         <f t="shared" si="0"/>
-        <v>0.14533622559652928</v>
+        <v>7.8091106290672452E-2</v>
       </c>
       <c r="K20" s="40">
         <f t="shared" ref="K20" si="6">SUM(K4:K19)</f>
@@ -2819,15 +2750,15 @@
       </c>
       <c r="L20" s="40">
         <f>SUM(L4:L19)</f>
-        <v>305.64999999999998</v>
+        <v>52</v>
       </c>
       <c r="M20" s="42">
         <f t="shared" si="1"/>
-        <v>0.92902735562310024</v>
+        <v>0.1580547112462006</v>
       </c>
       <c r="N20" s="40">
         <f t="shared" si="2"/>
-        <v>4.5619402985074622</v>
+        <v>1.4444444444444444</v>
       </c>
       <c r="O20" s="43" t="e">
         <f>AVERAGE(O4:O19)</f>
@@ -2835,31 +2766,31 @@
       </c>
       <c r="P20" s="40">
         <f t="shared" ref="P20" si="7">SUM(P4:P19)</f>
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="Q20" s="41">
         <f t="shared" ref="Q20" si="8">SUM(Q4:Q19)</f>
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="R20" s="42">
         <f t="shared" si="3"/>
-        <v>0.88235294117647056</v>
+        <v>0.81632653061224492</v>
       </c>
       <c r="S20" s="40">
         <f t="shared" ref="S20" si="9">SUM(S4:S19)</f>
-        <v>77.150000000000006</v>
+        <v>56</v>
       </c>
       <c r="T20" s="41">
         <f t="shared" ref="T20" si="10">SUM(T4:T19)</f>
-        <v>69.175000000000011</v>
+        <v>48</v>
       </c>
       <c r="U20" s="42">
         <f t="shared" si="4"/>
-        <v>0.89662994167206744</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="V20" s="40">
         <f t="shared" si="5"/>
-        <v>1.1529166666666668</v>
+        <v>1.2</v>
       </c>
       <c r="W20" s="43">
         <f>AVERAGE(W4:W19)</f>
@@ -3231,11 +3162,11 @@
       <c r="C26" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="106" t="s">
+      <c r="D26" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="E26" s="107"/>
-      <c r="F26" s="108"/>
+      <c r="E26" s="106"/>
+      <c r="F26" s="107"/>
       <c r="G26" s="40">
         <f>SUM(G21:G25)</f>
         <v>5</v>
@@ -3598,11 +3529,11 @@
       <c r="C31" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="D31" s="109" t="s">
+      <c r="D31" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="E31" s="110"/>
-      <c r="F31" s="111"/>
+      <c r="E31" s="109"/>
+      <c r="F31" s="110"/>
       <c r="G31" s="40">
         <f>SUM(G27:G30)</f>
         <v>4</v>
@@ -3692,11 +3623,11 @@
       </c>
       <c r="I32" s="21">
         <f t="shared" si="17"/>
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="J32" s="22">
         <f t="shared" si="0"/>
-        <v>0.14255319148936171</v>
+        <v>7.6595744680851063E-2</v>
       </c>
       <c r="K32" s="20">
         <v>1</v>
@@ -3710,7 +3641,7 @@
       </c>
       <c r="N32" s="20">
         <f t="shared" si="2"/>
-        <v>1.4925373134328358E-2</v>
+        <v>2.7777777777777776E-2</v>
       </c>
       <c r="O32" s="23" t="e">
         <f>AVERAGE(O31,O20,O26)</f>
@@ -3718,31 +3649,31 @@
       </c>
       <c r="P32" s="20">
         <f>+P31+P26+P20</f>
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="Q32" s="21">
         <f t="shared" ref="Q32" si="18">+Q31+Q26+Q20</f>
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="R32" s="22">
         <f t="shared" si="3"/>
-        <v>0.89610389610389607</v>
+        <v>0.84482758620689657</v>
       </c>
       <c r="S32" s="20">
         <f>+S31+S26+S20</f>
-        <v>86.15</v>
+        <v>65</v>
       </c>
       <c r="T32" s="21">
         <f t="shared" ref="T32" si="19">+T31+T26+T20</f>
-        <v>78.175000000000011</v>
+        <v>57</v>
       </c>
       <c r="U32" s="22">
         <f t="shared" si="4"/>
-        <v>0.9074289030760303</v>
+        <v>0.87692307692307692</v>
       </c>
       <c r="V32" s="20">
         <f t="shared" si="5"/>
-        <v>1.1329710144927538</v>
+        <v>1.1632653061224489</v>
       </c>
       <c r="W32" s="23">
         <f>AVERAGE(W31,W20,W26)</f>
@@ -3808,36 +3739,36 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.40740740740740738</v>
+        <v>0.48148148148148145</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F2" s="89">
-        <v>46308</v>
-      </c>
-      <c r="G2" s="118" t="s">
+        <v>46310</v>
+      </c>
+      <c r="G2" s="117" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="115" t="s">
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="114" t="s">
         <v>48</v>
       </c>
-      <c r="L2" s="116"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="117"/>
-      <c r="P2" s="121" t="s">
+      <c r="L2" s="115"/>
+      <c r="M2" s="115"/>
+      <c r="N2" s="115"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="120" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" s="122"/>
+      <c r="Q2" s="121"/>
     </row>
     <row r="3" spans="1:18" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="25" t="s">
@@ -3942,7 +3873,7 @@
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>21.024999999999999</v>
+        <v>24.028571428571428</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P16" si="2">L4/I4</f>
@@ -3998,7 +3929,7 @@
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>17.092187500000001</v>
+        <v>19.533928571428572</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
@@ -4054,7 +3985,7 @@
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>20.042187500000001</v>
+        <v>22.905357142857145</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
@@ -4062,7 +3993,7 @@
       </c>
       <c r="Q6" s="14"/>
       <c r="R6" s="102" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
@@ -4112,7 +4043,7 @@
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>11.8671875</v>
+        <v>13.5625</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
@@ -4168,7 +4099,7 @@
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
-        <v>11.643750000000001</v>
+        <v>13.307142857142859</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
@@ -4277,7 +4208,7 @@
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>107.625</v>
+        <v>123</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
@@ -4320,27 +4251,27 @@
         <v>450</v>
       </c>
       <c r="L11" s="12">
-        <f>106+16+15</f>
-        <v>137</v>
+        <f>106+16+15+38</f>
+        <v>175</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="4"/>
-        <v>0.30444444444444446</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="5"/>
-        <v>313</v>
+        <v>275</v>
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>19.5625</v>
+        <v>19.642857142857142</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
-        <v>1.8026315789473684</v>
+        <v>2.3026315789473686</v>
       </c>
       <c r="Q11" s="14"/>
-      <c r="R11" s="105"/>
+      <c r="R11" s="104"/>
     </row>
     <row r="12" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="35" t="s">
@@ -4376,27 +4307,27 @@
         <v>300</v>
       </c>
       <c r="L12" s="12">
-        <f>100+8+8</f>
-        <v>116</v>
+        <f>100+8+8+6</f>
+        <v>122</v>
       </c>
       <c r="M12" s="70">
         <f t="shared" si="4"/>
-        <v>0.38666666666666666</v>
+        <v>0.40666666666666668</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="5"/>
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>11.5</v>
+        <v>12.714285714285714</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
-        <v>1.6571428571428573</v>
+        <v>1.7428571428571429</v>
       </c>
       <c r="Q12" s="14"/>
-      <c r="R12" s="105"/>
+      <c r="R12" s="104"/>
     </row>
     <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A13" s="35" t="s">
@@ -4432,27 +4363,27 @@
         <v>250</v>
       </c>
       <c r="L13" s="12">
-        <f>50+10+10</f>
-        <v>70</v>
+        <f>50+10+10+4</f>
+        <v>74</v>
       </c>
       <c r="M13" s="70">
         <f t="shared" si="4"/>
-        <v>0.28000000000000003</v>
+        <v>0.29599999999999999</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="5"/>
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="O13" s="14">
         <f t="shared" si="6"/>
-        <v>11.25</v>
+        <v>12.571428571428571</v>
       </c>
       <c r="P13" s="71">
         <f t="shared" si="2"/>
-        <v>1.1666666666666667</v>
+        <v>1.2333333333333334</v>
       </c>
       <c r="Q13" s="14"/>
-      <c r="R13" s="105"/>
+      <c r="R13" s="104"/>
     </row>
     <row r="14" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="35" t="s">
@@ -4471,7 +4402,7 @@
         <v>22</v>
       </c>
       <c r="F14" s="100" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G14" s="11">
         <v>1</v>
@@ -4498,7 +4429,7 @@
       </c>
       <c r="O14" s="14">
         <f t="shared" si="6"/>
-        <v>-5.625</v>
+        <v>-6.4285714285714288</v>
       </c>
       <c r="P14" s="71">
         <f t="shared" si="2"/>
@@ -4524,7 +4455,7 @@
         <v>22</v>
       </c>
       <c r="F15" s="100" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G15" s="11">
         <v>1</v>
@@ -4551,7 +4482,7 @@
       </c>
       <c r="O15" s="14">
         <f t="shared" si="6"/>
-        <v>-4.6875</v>
+        <v>-5.3571428571428568</v>
       </c>
       <c r="P15" s="71">
         <f t="shared" si="2"/>
@@ -4602,7 +4533,7 @@
       </c>
       <c r="O16" s="14">
         <f t="shared" si="6"/>
-        <v>-13.4375</v>
+        <v>-15.357142857142858</v>
       </c>
       <c r="P16" s="71">
         <f t="shared" si="2"/>
@@ -4621,11 +4552,11 @@
       <c r="C17" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="109" t="s">
+      <c r="D17" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="110"/>
-      <c r="F17" s="111"/>
+      <c r="E17" s="109"/>
+      <c r="F17" s="110"/>
       <c r="G17" s="40">
         <f>SUM(G4:G15)</f>
         <v>2493</v>
@@ -4648,23 +4579,23 @@
       </c>
       <c r="L17" s="77">
         <f>SUM(L4:L16)</f>
-        <v>1624.2750000000001</v>
+        <v>1672.2750000000001</v>
       </c>
       <c r="M17" s="78">
         <f t="shared" si="4"/>
-        <v>0.31848529411764709</v>
+        <v>0.32789705882352943</v>
       </c>
       <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>3475.7249999999999</v>
+        <v>3427.7249999999999</v>
       </c>
       <c r="O17" s="79">
         <f t="shared" si="6"/>
-        <v>217.23281249999999</v>
+        <v>244.83750000000001</v>
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>3.6095000000000002</v>
+        <v>3.7161666666666671</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -4718,7 +4649,7 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="6"/>
-        <v>26.606249999999999</v>
+        <v>30.407142857142855</v>
       </c>
       <c r="P18" s="96">
         <f t="shared" ref="P18:P22" si="7">L18/I18</f>
@@ -4773,7 +4704,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>26.606249999999999</v>
+        <v>30.407142857142855</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4828,7 +4759,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>26.606249999999999</v>
+        <v>30.407142857142855</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4883,7 +4814,7 @@
       </c>
       <c r="O21" s="14">
         <f t="shared" si="6"/>
-        <v>26.606249999999999</v>
+        <v>30.407142857142855</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="7"/>
@@ -4938,7 +4869,7 @@
       </c>
       <c r="O22" s="94">
         <f t="shared" si="6"/>
-        <v>26.606249999999999</v>
+        <v>30.407142857142855</v>
       </c>
       <c r="P22" s="74">
         <f t="shared" si="7"/>
@@ -4959,11 +4890,11 @@
       <c r="C23" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="109" t="s">
+      <c r="D23" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="E23" s="110"/>
-      <c r="F23" s="111"/>
+      <c r="E23" s="109"/>
+      <c r="F23" s="110"/>
       <c r="G23" s="40">
         <f>SUM(G18:G22)</f>
         <v>5</v>
@@ -4996,7 +4927,7 @@
       </c>
       <c r="O23" s="79">
         <f t="shared" si="6"/>
-        <v>26.606249999999999</v>
+        <v>30.407142857142855</v>
       </c>
       <c r="P23" s="80">
         <f>L23/I23</f>
@@ -5054,7 +4985,7 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="6"/>
-        <v>26.606249999999999</v>
+        <v>30.407142857142855</v>
       </c>
       <c r="P24" s="96">
         <f t="shared" ref="P24:P27" si="9">L24/I24</f>
@@ -5109,7 +5040,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>26.606249999999999</v>
+        <v>30.407142857142855</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5164,7 +5095,7 @@
       </c>
       <c r="O26" s="14">
         <f t="shared" si="6"/>
-        <v>26.606249999999999</v>
+        <v>30.407142857142855</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="9"/>
@@ -5219,7 +5150,7 @@
       </c>
       <c r="O27" s="94">
         <f t="shared" si="6"/>
-        <v>26.606249999999999</v>
+        <v>30.407142857142855</v>
       </c>
       <c r="P27" s="74">
         <f t="shared" si="9"/>
@@ -5240,11 +5171,11 @@
       <c r="C28" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="109" t="s">
+      <c r="D28" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="E28" s="110"/>
-      <c r="F28" s="111"/>
+      <c r="E28" s="109"/>
+      <c r="F28" s="110"/>
       <c r="G28" s="40">
         <f>SUM(G24:G27)</f>
         <v>4</v>
@@ -5274,7 +5205,7 @@
       </c>
       <c r="O28" s="79">
         <f t="shared" si="6"/>
-        <v>26.606249999999999</v>
+        <v>30.407142857142855</v>
       </c>
       <c r="P28" s="80">
         <f>L28/I28</f>
@@ -5329,7 +5260,7 @@
       </c>
       <c r="O29" s="87">
         <f t="shared" si="6"/>
-        <v>26.606249999999999</v>
+        <v>30.407142857142855</v>
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D85301B-85A5-450C-9CF1-919F5239BB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D7267F-C3B0-4C01-955D-F423DA493231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="77">
   <si>
     <t>Booking</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>Nabeel Traders SD</t>
+  </si>
+  <si>
+    <t>Closed</t>
   </si>
 </sst>
 </file>
@@ -303,6 +306,7 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Arial Unicode MS"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -926,7 +930,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1245,9 +1249,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1585,7 +1586,7 @@
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="89">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="G2" s="117" t="s">
         <v>2</v>
@@ -1712,42 +1713,54 @@
       <c r="H4" s="68">
         <v>40</v>
       </c>
-      <c r="I4" s="12"/>
+      <c r="I4" s="12">
+        <v>10</v>
+      </c>
       <c r="J4" s="32">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K4" s="30">
         <v>40</v>
       </c>
-      <c r="L4" s="12"/>
+      <c r="L4" s="12">
+        <v>11.5</v>
+      </c>
       <c r="M4" s="32">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0</v>
+        <v>0.28749999999999998</v>
       </c>
       <c r="N4" s="90">
         <f>IFERROR(L4/I4,0)</f>
-        <v>0</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="O4" s="33"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="31"/>
+      <c r="P4" s="30">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="31">
+        <v>14</v>
+      </c>
       <c r="R4" s="32">
         <f>IFERROR(Q4/P4,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S4" s="30"/>
-      <c r="T4" s="31"/>
+        <v>1</v>
+      </c>
+      <c r="S4" s="30">
+        <v>14</v>
+      </c>
+      <c r="T4" s="31">
+        <v>14</v>
+      </c>
       <c r="U4" s="32">
         <f>IFERROR(T4/S4,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="90">
         <f>IFERROR(T4/Q4,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" s="33"/>
-      <c r="X4" s="122"/>
+      <c r="X4" s="103"/>
     </row>
     <row r="5" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="35" t="s">
@@ -1774,50 +1787,54 @@
       <c r="H5" s="71">
         <v>45</v>
       </c>
-      <c r="I5" s="12"/>
+      <c r="I5" s="12">
+        <v>20</v>
+      </c>
       <c r="J5" s="13">
         <f t="shared" ref="J5:J32" si="0">IFERROR(I5/G5,0)</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K5" s="11">
         <v>30</v>
       </c>
-      <c r="L5" s="12"/>
+      <c r="L5" s="12">
+        <v>12.025</v>
+      </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M32" si="1">IFERROR(L5/K5,0)</f>
-        <v>0</v>
+        <v>0.40083333333333332</v>
       </c>
       <c r="N5" s="71">
         <f t="shared" ref="N5:N32" si="2">IFERROR(L5/I5,0)</f>
-        <v>0</v>
+        <v>0.60125000000000006</v>
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="11">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Q5" s="12">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="R5" s="13">
         <f t="shared" ref="R5:R32" si="3">IFERROR(Q5/P5,0)</f>
-        <v>0.92307692307692313</v>
+        <v>0.95</v>
       </c>
       <c r="S5" s="11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" s="12">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="U5" s="13">
         <f t="shared" ref="U5:U32" si="4">IFERROR(T5/S5,0)</f>
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="V5" s="11">
         <f t="shared" ref="V5:V32" si="5">IFERROR(T5/Q5,0)</f>
-        <v>1.5833333333333333</v>
+        <v>0.47368421052631576</v>
       </c>
       <c r="W5" s="14"/>
-      <c r="X5" s="122"/>
+      <c r="X5" s="103"/>
     </row>
     <row r="6" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="35" t="s">
@@ -1844,7 +1861,9 @@
       <c r="H6" s="71">
         <v>40</v>
       </c>
-      <c r="I6" s="12"/>
+      <c r="I6" s="12">
+        <v>0</v>
+      </c>
       <c r="J6" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1852,7 +1871,9 @@
       <c r="K6" s="11">
         <v>25</v>
       </c>
-      <c r="L6" s="12"/>
+      <c r="L6" s="12">
+        <v>0</v>
+      </c>
       <c r="M6" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1879,7 +1900,9 @@
         <v>0</v>
       </c>
       <c r="W6" s="14"/>
-      <c r="X6" s="122"/>
+      <c r="X6" s="103" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="7" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="35" t="s">
@@ -1906,50 +1929,54 @@
       <c r="H7" s="71">
         <v>45</v>
       </c>
-      <c r="I7" s="12"/>
+      <c r="I7" s="12">
+        <v>7</v>
+      </c>
       <c r="J7" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K7" s="11">
         <v>30</v>
       </c>
-      <c r="L7" s="12"/>
+      <c r="L7" s="12">
+        <v>8.6750000000000007</v>
+      </c>
       <c r="M7" s="70">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.28916666666666668</v>
       </c>
       <c r="N7" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.2392857142857143</v>
       </c>
       <c r="O7" s="14"/>
       <c r="P7" s="11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q7" s="12">
         <v>1</v>
       </c>
       <c r="R7" s="13">
         <f t="shared" si="3"/>
-        <v>0.1111111111111111</v>
+        <v>0.1</v>
       </c>
       <c r="S7" s="11">
         <v>9</v>
       </c>
       <c r="T7" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U7" s="13">
         <f t="shared" si="4"/>
-        <v>0.22222222222222221</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="V7" s="11">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W7" s="14"/>
-      <c r="X7" s="122"/>
+      <c r="X7" s="103"/>
     </row>
     <row r="8" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="35" t="s">
@@ -1987,35 +2014,43 @@
         <v>20</v>
       </c>
       <c r="L8" s="12">
-        <v>22</v>
+        <v>22.45</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="1"/>
-        <v>1.1000000000000001</v>
+        <v>1.1225000000000001</v>
       </c>
       <c r="N8" s="71">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.7416666666666667</v>
       </c>
       <c r="O8" s="14"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="12"/>
+      <c r="P8" s="11">
+        <v>8</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>7</v>
+      </c>
       <c r="R8" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S8" s="11"/>
-      <c r="T8" s="12"/>
+        <v>0.875</v>
+      </c>
+      <c r="S8" s="11">
+        <v>8</v>
+      </c>
+      <c r="T8" s="12">
+        <v>6</v>
+      </c>
       <c r="U8" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="V8" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="W8" s="14"/>
-      <c r="X8" s="122"/>
+      <c r="X8" s="103"/>
     </row>
     <row r="9" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="35" t="s">
@@ -2042,7 +2077,9 @@
       <c r="H9" s="71">
         <v>0</v>
       </c>
-      <c r="I9" s="12"/>
+      <c r="I9" s="12">
+        <v>0</v>
+      </c>
       <c r="J9" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2050,7 +2087,9 @@
       <c r="K9" s="11">
         <v>80</v>
       </c>
-      <c r="L9" s="12"/>
+      <c r="L9" s="12">
+        <v>0</v>
+      </c>
       <c r="M9" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2077,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="W9" s="14"/>
-      <c r="X9" s="122"/>
+      <c r="X9" s="103"/>
     </row>
     <row r="10" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="35" t="s">
@@ -2104,42 +2143,54 @@
       <c r="H10" s="71">
         <v>10</v>
       </c>
-      <c r="I10" s="12"/>
+      <c r="I10" s="12">
+        <v>7</v>
+      </c>
       <c r="J10" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="K10" s="11">
         <v>20</v>
       </c>
-      <c r="L10" s="12"/>
+      <c r="L10" s="12">
+        <v>110</v>
+      </c>
       <c r="M10" s="70">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N10" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>15.714285714285714</v>
       </c>
       <c r="O10" s="14"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="12"/>
+      <c r="P10" s="11">
+        <v>11</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>7</v>
+      </c>
       <c r="R10" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S10" s="11"/>
-      <c r="T10" s="12"/>
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="S10" s="11">
+        <v>250</v>
+      </c>
+      <c r="T10" s="12">
+        <v>215</v>
+      </c>
       <c r="U10" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="V10" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>30.714285714285715</v>
       </c>
       <c r="W10" s="14"/>
-      <c r="X10" s="122"/>
+      <c r="X10" s="103"/>
     </row>
     <row r="11" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A11" s="35" t="s">
@@ -2213,7 +2264,7 @@
         <v>1.2</v>
       </c>
       <c r="W11" s="14"/>
-      <c r="X11" s="122"/>
+      <c r="X11" s="103"/>
     </row>
     <row r="12" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="35" t="s">
@@ -2314,22 +2365,26 @@
       <c r="H13" s="71">
         <v>40</v>
       </c>
-      <c r="I13" s="12"/>
+      <c r="I13" s="12">
+        <v>6</v>
+      </c>
       <c r="J13" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="K13" s="11">
         <v>30</v>
       </c>
-      <c r="L13" s="12"/>
+      <c r="L13" s="12">
+        <v>5</v>
+      </c>
       <c r="M13" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="N13" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="O13" s="14"/>
       <c r="P13" s="11">
@@ -2692,21 +2747,29 @@
         <v>0</v>
       </c>
       <c r="O19" s="39"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="37"/>
+      <c r="P19" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="37">
+        <v>1</v>
+      </c>
       <c r="R19" s="38">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S19" s="36"/>
-      <c r="T19" s="37"/>
+        <v>1</v>
+      </c>
+      <c r="S19" s="36">
+        <v>196</v>
+      </c>
+      <c r="T19" s="37">
+        <v>196</v>
+      </c>
       <c r="U19" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="36">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="W19" s="39">
         <v>1</v>
@@ -2738,11 +2801,11 @@
       </c>
       <c r="I20" s="41">
         <f>SUM(I4:I19)</f>
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="J20" s="42">
         <f t="shared" si="0"/>
-        <v>7.8091106290672452E-2</v>
+        <v>0.18655097613882862</v>
       </c>
       <c r="K20" s="40">
         <f t="shared" ref="K20" si="6">SUM(K4:K19)</f>
@@ -2750,15 +2813,15 @@
       </c>
       <c r="L20" s="40">
         <f>SUM(L4:L19)</f>
-        <v>52</v>
+        <v>199.65</v>
       </c>
       <c r="M20" s="42">
         <f t="shared" si="1"/>
-        <v>0.1580547112462006</v>
+        <v>0.60683890577507604</v>
       </c>
       <c r="N20" s="40">
         <f t="shared" si="2"/>
-        <v>1.4444444444444444</v>
+        <v>2.3215116279069767</v>
       </c>
       <c r="O20" s="43" t="e">
         <f>AVERAGE(O4:O19)</f>
@@ -2766,31 +2829,31 @@
       </c>
       <c r="P20" s="40">
         <f t="shared" ref="P20" si="7">SUM(P4:P19)</f>
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="Q20" s="41">
         <f t="shared" ref="Q20" si="8">SUM(Q4:Q19)</f>
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="R20" s="42">
         <f t="shared" si="3"/>
-        <v>0.81632653061224492</v>
+        <v>0.8351648351648352</v>
       </c>
       <c r="S20" s="40">
         <f t="shared" ref="S20" si="9">SUM(S4:S19)</f>
-        <v>56</v>
+        <v>514</v>
       </c>
       <c r="T20" s="41">
         <f t="shared" ref="T20" si="10">SUM(T4:T19)</f>
-        <v>48</v>
+        <v>468</v>
       </c>
       <c r="U20" s="42">
         <f t="shared" si="4"/>
-        <v>0.8571428571428571</v>
+        <v>0.91050583657587547</v>
       </c>
       <c r="V20" s="40">
         <f t="shared" si="5"/>
-        <v>1.2</v>
+        <v>6.1578947368421053</v>
       </c>
       <c r="W20" s="43">
         <f>AVERAGE(W4:W19)</f>
@@ -3623,11 +3686,11 @@
       </c>
       <c r="I32" s="21">
         <f t="shared" si="17"/>
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="J32" s="22">
         <f t="shared" si="0"/>
-        <v>7.6595744680851063E-2</v>
+        <v>0.18297872340425531</v>
       </c>
       <c r="K32" s="20">
         <v>1</v>
@@ -3641,7 +3704,7 @@
       </c>
       <c r="N32" s="20">
         <f t="shared" si="2"/>
-        <v>2.7777777777777776E-2</v>
+        <v>1.1627906976744186E-2</v>
       </c>
       <c r="O32" s="23" t="e">
         <f>AVERAGE(O31,O20,O26)</f>
@@ -3649,31 +3712,31 @@
       </c>
       <c r="P32" s="20">
         <f>+P31+P26+P20</f>
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="Q32" s="21">
         <f t="shared" ref="Q32" si="18">+Q31+Q26+Q20</f>
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="R32" s="22">
         <f t="shared" si="3"/>
-        <v>0.84482758620689657</v>
+        <v>0.85</v>
       </c>
       <c r="S32" s="20">
         <f>+S31+S26+S20</f>
-        <v>65</v>
+        <v>523</v>
       </c>
       <c r="T32" s="21">
         <f t="shared" ref="T32" si="19">+T31+T26+T20</f>
-        <v>57</v>
+        <v>477</v>
       </c>
       <c r="U32" s="22">
         <f t="shared" si="4"/>
-        <v>0.87692307692307692</v>
+        <v>0.91204588910133844</v>
       </c>
       <c r="V32" s="20">
         <f t="shared" si="5"/>
-        <v>1.1632653061224489</v>
+        <v>5.6117647058823525</v>
       </c>
       <c r="W32" s="23">
         <f>AVERAGE(W31,W20,W26)</f>
@@ -3739,18 +3802,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.48148148148148145</v>
+        <v>0.51851851851851849</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" s="89">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="G2" s="117" t="s">
         <v>34</v>
@@ -3850,34 +3913,34 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>15+13+9+11+10+11+8+12</f>
-        <v>89</v>
+        <f>15+13+9+11+10+11+8+12+12</f>
+        <v>101</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.27384615384615385</v>
+        <v>0.31076923076923074</v>
       </c>
       <c r="K4" s="7">
         <v>450</v>
       </c>
       <c r="L4" s="8">
-        <v>113.6</v>
+        <v>127.05</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.25244444444444442</v>
+        <v>0.28233333333333333</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>336.4</v>
+        <v>322.95</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>24.028571428571428</v>
+        <v>24.842307692307692</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P16" si="2">L4/I4</f>
-        <v>1.2764044943820223</v>
+        <v>1.2579207920792079</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3906,34 +3969,34 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <f>6+5+5+3+3+4+3+5</f>
-        <v>34</v>
+        <f>6+5+5+3+3+4+3+5+10+19</f>
+        <v>63</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J29" si="3">IFERROR(I5/G5,0)</f>
-        <v>0.14345991561181434</v>
+        <v>0.26582278481012656</v>
       </c>
       <c r="K5" s="11">
         <v>350</v>
       </c>
       <c r="L5" s="12">
-        <v>76.525000000000006</v>
+        <v>88.075000000000003</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M29" si="4">IFERROR(L5/K5,0)</f>
-        <v>0.21864285714285717</v>
+        <v>0.25164285714285717</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>273.47500000000002</v>
+        <v>261.92500000000001</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>19.533928571428572</v>
+        <v>20.148076923076925</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>2.2507352941176473</v>
+        <v>1.3980158730158732</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -3962,12 +4025,11 @@
       </c>
       <c r="H6" s="71"/>
       <c r="I6" s="12">
-        <f>6+4+4</f>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J6" s="69">
         <f t="shared" si="3"/>
-        <v>5.6000000000000001E-2</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="K6" s="11">
         <v>350</v>
@@ -3985,11 +4047,11 @@
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>22.905357142857145</v>
+        <v>24.667307692307695</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
-        <v>2.094642857142857</v>
+        <v>1.5434210526315788</v>
       </c>
       <c r="Q6" s="14"/>
       <c r="R6" s="102" t="s">
@@ -4020,34 +4082,34 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>2+2+6+4+9+7+8</f>
-        <v>38</v>
+        <f>2+2+6+4+9+7+8+1</f>
+        <v>39</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>0.13194444444444445</v>
+        <v>0.13541666666666666</v>
       </c>
       <c r="K7" s="11">
         <v>250</v>
       </c>
       <c r="L7" s="12">
-        <v>60.125</v>
+        <v>61.274999999999999</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>0.24049999999999999</v>
+        <v>0.24509999999999998</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>189.875</v>
+        <v>188.72499999999999</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>13.5625</v>
+        <v>14.517307692307693</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.5822368421052631</v>
+        <v>1.5711538461538461</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4076,34 +4138,34 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <f>3+6+7+6+6+3+5+8</f>
-        <v>44</v>
+        <f>3+6+7+6+6+3+5+8+6</f>
+        <v>50</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>0.12324929971988796</v>
+        <v>0.14005602240896359</v>
       </c>
       <c r="K8" s="11">
         <v>250</v>
       </c>
       <c r="L8" s="12">
-        <v>63.7</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>0.25480000000000003</v>
+        <v>0.27960000000000002</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N29" si="5">K8-L8</f>
-        <v>186.3</v>
+        <v>180.1</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
-        <v>13.307142857142859</v>
+        <v>13.853846153846153</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.4477272727272728</v>
+        <v>1.3980000000000001</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4186,33 +4248,33 @@
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="12">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>0.1981981981981982</v>
+        <v>0.25225225225225223</v>
       </c>
       <c r="K10" s="11">
         <v>2300</v>
       </c>
       <c r="L10" s="12">
-        <v>578</v>
+        <v>774</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>0.25130434782608696</v>
+        <v>0.33652173913043476</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>1722</v>
+        <v>1526</v>
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>123</v>
+        <v>117.38461538461539</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>26.272727272727273</v>
+        <v>27.642857142857142</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
@@ -4241,34 +4303,34 @@
       </c>
       <c r="H11" s="71"/>
       <c r="I11" s="12">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J11" s="69">
         <f t="shared" si="3"/>
-        <v>0.2360248447204969</v>
+        <v>0.25465838509316768</v>
       </c>
       <c r="K11" s="11">
         <v>450</v>
       </c>
       <c r="L11" s="12">
-        <f>106+16+15+38</f>
-        <v>175</v>
+        <f>106+16+15+38+16</f>
+        <v>191</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="4"/>
-        <v>0.3888888888888889</v>
+        <v>0.42444444444444446</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="5"/>
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>19.642857142857142</v>
+        <v>19.923076923076923</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
-        <v>2.3026315789473686</v>
+        <v>2.3292682926829267</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="104"/>
@@ -4297,34 +4359,34 @@
       </c>
       <c r="H12" s="71"/>
       <c r="I12" s="12">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J12" s="69">
         <f t="shared" si="3"/>
-        <v>0.22508038585209003</v>
+        <v>0.25723472668810288</v>
       </c>
       <c r="K12" s="11">
         <v>300</v>
       </c>
       <c r="L12" s="12">
-        <f>100+8+8+6</f>
-        <v>122</v>
+        <f>100+8+8+6+8</f>
+        <v>130</v>
       </c>
       <c r="M12" s="70">
         <f t="shared" si="4"/>
-        <v>0.40666666666666668</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="5"/>
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>12.714285714285714</v>
+        <v>13.076923076923077</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
-        <v>1.7428571428571429</v>
+        <v>1.625</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="104"/>
@@ -4353,34 +4415,34 @@
       </c>
       <c r="H13" s="71"/>
       <c r="I13" s="12">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="J13" s="69">
         <f t="shared" si="3"/>
-        <v>0.42857142857142855</v>
+        <v>0.48571428571428571</v>
       </c>
       <c r="K13" s="11">
         <v>250</v>
       </c>
       <c r="L13" s="12">
-        <f>50+10+10+4</f>
-        <v>74</v>
+        <f>50+10+10+4+5</f>
+        <v>79</v>
       </c>
       <c r="M13" s="70">
         <f t="shared" si="4"/>
-        <v>0.29599999999999999</v>
+        <v>0.316</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="5"/>
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="O13" s="14">
         <f t="shared" si="6"/>
-        <v>12.571428571428571</v>
+        <v>13.153846153846153</v>
       </c>
       <c r="P13" s="71">
         <f t="shared" si="2"/>
-        <v>1.2333333333333334</v>
+        <v>1.161764705882353</v>
       </c>
       <c r="Q13" s="14"/>
       <c r="R13" s="104"/>
@@ -4415,21 +4477,23 @@
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="K14" s="11"/>
+      <c r="K14" s="11">
+        <v>100</v>
+      </c>
       <c r="L14" s="12">
         <v>90</v>
       </c>
       <c r="M14" s="70">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="N14" s="12">
         <f t="shared" si="5"/>
-        <v>-90</v>
+        <v>10</v>
       </c>
       <c r="O14" s="14">
         <f t="shared" si="6"/>
-        <v>-6.4285714285714288</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="P14" s="71">
         <f t="shared" si="2"/>
@@ -4468,21 +4532,23 @@
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="K15" s="11"/>
+      <c r="K15" s="11">
+        <v>100</v>
+      </c>
       <c r="L15" s="12">
         <v>75</v>
       </c>
       <c r="M15" s="70">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="N15" s="12">
         <f t="shared" si="5"/>
-        <v>-75</v>
+        <v>25</v>
       </c>
       <c r="O15" s="14">
         <f t="shared" si="6"/>
-        <v>-5.3571428571428568</v>
+        <v>1.9230769230769231</v>
       </c>
       <c r="P15" s="71">
         <f t="shared" si="2"/>
@@ -4521,7 +4587,7 @@
       </c>
       <c r="K16" s="11"/>
       <c r="L16" s="12">
-        <v>215</v>
+        <v>430</v>
       </c>
       <c r="M16" s="70">
         <f t="shared" si="4"/>
@@ -4529,15 +4595,15 @@
       </c>
       <c r="N16" s="12">
         <f t="shared" si="5"/>
-        <v>-215</v>
+        <v>-430</v>
       </c>
       <c r="O16" s="14">
         <f t="shared" si="6"/>
-        <v>-15.357142857142858</v>
+        <v>-33.07692307692308</v>
       </c>
       <c r="P16" s="71">
         <f t="shared" si="2"/>
-        <v>215</v>
+        <v>430</v>
       </c>
       <c r="Q16" s="14"/>
       <c r="R16" s="34"/>
@@ -4567,35 +4633,35 @@
       </c>
       <c r="I17" s="41">
         <f>SUM(I4:I16)</f>
-        <v>450</v>
+        <v>533</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>0.18050541516245489</v>
+        <v>0.21379863618130765</v>
       </c>
       <c r="K17" s="76">
         <f>SUM(K4:K16)</f>
-        <v>5100</v>
+        <v>5300</v>
       </c>
       <c r="L17" s="77">
         <f>SUM(L4:L16)</f>
-        <v>1672.2750000000001</v>
+        <v>2144.625</v>
       </c>
       <c r="M17" s="78">
         <f t="shared" si="4"/>
-        <v>0.32789705882352943</v>
+        <v>0.40464622641509435</v>
       </c>
       <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>3427.7249999999999</v>
+        <v>3155.375</v>
       </c>
       <c r="O17" s="79">
         <f t="shared" si="6"/>
-        <v>244.83750000000001</v>
+        <v>242.72115384615384</v>
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>3.7161666666666671</v>
+        <v>4.0236866791744843</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -4649,7 +4715,7 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="6"/>
-        <v>30.407142857142855</v>
+        <v>32.746153846153845</v>
       </c>
       <c r="P18" s="96">
         <f t="shared" ref="P18:P22" si="7">L18/I18</f>
@@ -4704,7 +4770,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>30.407142857142855</v>
+        <v>32.746153846153845</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4759,7 +4825,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>30.407142857142855</v>
+        <v>32.746153846153845</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4814,7 +4880,7 @@
       </c>
       <c r="O21" s="14">
         <f t="shared" si="6"/>
-        <v>30.407142857142855</v>
+        <v>32.746153846153845</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="7"/>
@@ -4869,7 +4935,7 @@
       </c>
       <c r="O22" s="94">
         <f t="shared" si="6"/>
-        <v>30.407142857142855</v>
+        <v>32.746153846153845</v>
       </c>
       <c r="P22" s="74">
         <f t="shared" si="7"/>
@@ -4927,7 +4993,7 @@
       </c>
       <c r="O23" s="79">
         <f t="shared" si="6"/>
-        <v>30.407142857142855</v>
+        <v>32.746153846153845</v>
       </c>
       <c r="P23" s="80">
         <f>L23/I23</f>
@@ -4985,7 +5051,7 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="6"/>
-        <v>30.407142857142855</v>
+        <v>32.746153846153845</v>
       </c>
       <c r="P24" s="96">
         <f t="shared" ref="P24:P27" si="9">L24/I24</f>
@@ -5040,7 +5106,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>30.407142857142855</v>
+        <v>32.746153846153845</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5095,7 +5161,7 @@
       </c>
       <c r="O26" s="14">
         <f t="shared" si="6"/>
-        <v>30.407142857142855</v>
+        <v>32.746153846153845</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="9"/>
@@ -5150,7 +5216,7 @@
       </c>
       <c r="O27" s="94">
         <f t="shared" si="6"/>
-        <v>30.407142857142855</v>
+        <v>32.746153846153845</v>
       </c>
       <c r="P27" s="74">
         <f t="shared" si="9"/>
@@ -5205,7 +5271,7 @@
       </c>
       <c r="O28" s="79">
         <f t="shared" si="6"/>
-        <v>30.407142857142855</v>
+        <v>32.746153846153845</v>
       </c>
       <c r="P28" s="80">
         <f>L28/I28</f>
@@ -5238,11 +5304,11 @@
       </c>
       <c r="I29" s="21">
         <f t="shared" si="11"/>
-        <v>459</v>
+        <v>542</v>
       </c>
       <c r="J29" s="83">
         <f t="shared" si="3"/>
-        <v>0.18345323741007194</v>
+        <v>0.21662669864108713</v>
       </c>
       <c r="K29" s="84">
         <v>600</v>
@@ -5260,11 +5326,11 @@
       </c>
       <c r="O29" s="87">
         <f t="shared" si="6"/>
-        <v>30.407142857142855</v>
+        <v>32.746153846153845</v>
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>
-        <v>0.37973856209150331</v>
+        <v>0.3215867158671587</v>
       </c>
       <c r="Q29" s="23" t="e">
         <f>AVERAGE(Q28,Q17,Q23)</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D7267F-C3B0-4C01-955D-F423DA493231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDAF63FC-C279-4F00-BD2D-14CA119768A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -3802,18 +3802,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.51851851851851849</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" s="89">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="G2" s="117" t="s">
         <v>34</v>
@@ -3913,34 +3913,34 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>15+13+9+11+10+11+8+12+12</f>
-        <v>101</v>
+        <f>15+13+9+11+10+11+8+12+12+8</f>
+        <v>109</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.31076923076923074</v>
+        <v>0.33538461538461539</v>
       </c>
       <c r="K4" s="7">
         <v>450</v>
       </c>
       <c r="L4" s="8">
-        <v>127.05</v>
+        <v>135.05000000000001</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.28233333333333333</v>
+        <v>0.30011111111111116</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>322.95</v>
+        <v>314.95</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>24.842307692307692</v>
+        <v>26.245833333333334</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P16" si="2">L4/I4</f>
-        <v>1.2579207920792079</v>
+        <v>1.2389908256880735</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3969,34 +3969,34 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <f>6+5+5+3+3+4+3+5+10+19</f>
-        <v>63</v>
+        <f>6+5+5+3+3+4+3+5+10+19+20</f>
+        <v>83</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J29" si="3">IFERROR(I5/G5,0)</f>
-        <v>0.26582278481012656</v>
+        <v>0.35021097046413502</v>
       </c>
       <c r="K5" s="11">
         <v>350</v>
       </c>
       <c r="L5" s="12">
-        <v>88.075000000000003</v>
+        <v>100.1</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M29" si="4">IFERROR(L5/K5,0)</f>
-        <v>0.25164285714285717</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>261.92500000000001</v>
+        <v>249.9</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>20.148076923076925</v>
+        <v>20.824999999999999</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>1.3980158730158732</v>
+        <v>1.2060240963855422</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>24.667307692307695</v>
+        <v>26.722916666666666</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
@@ -4082,34 +4082,34 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>2+2+6+4+9+7+8+1</f>
-        <v>39</v>
+        <f>2+2+6+4+9+7+8+1+6</f>
+        <v>45</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>0.13541666666666666</v>
+        <v>0.15625</v>
       </c>
       <c r="K7" s="11">
         <v>250</v>
       </c>
       <c r="L7" s="12">
-        <v>61.274999999999999</v>
+        <v>68.95</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>0.24509999999999998</v>
+        <v>0.27579999999999999</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>188.72499999999999</v>
+        <v>181.05</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>14.517307692307693</v>
+        <v>15.0875</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.5711538461538461</v>
+        <v>1.5322222222222224</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4138,34 +4138,34 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <f>3+6+7+6+6+3+5+8+6</f>
-        <v>50</v>
+        <f>3+6+7+6+6+3+5+8+6+4</f>
+        <v>54</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>0.14005602240896359</v>
+        <v>0.15126050420168066</v>
       </c>
       <c r="K8" s="11">
         <v>250</v>
       </c>
       <c r="L8" s="12">
-        <v>69.900000000000006</v>
+        <v>84.9</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>0.27960000000000002</v>
+        <v>0.33960000000000001</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N29" si="5">K8-L8</f>
-        <v>180.1</v>
+        <v>165.1</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
-        <v>13.853846153846153</v>
+        <v>13.758333333333333</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.3980000000000001</v>
+        <v>1.5722222222222224</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4248,33 +4248,34 @@
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="12">
-        <v>28</v>
+        <f>28+9</f>
+        <v>37</v>
       </c>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>0.25225225225225223</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="K10" s="11">
         <v>2300</v>
       </c>
       <c r="L10" s="12">
-        <v>774</v>
+        <v>948</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>0.33652173913043476</v>
+        <v>0.41217391304347828</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>1526</v>
+        <v>1352</v>
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>117.38461538461539</v>
+        <v>112.66666666666667</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>27.642857142857142</v>
+        <v>25.621621621621621</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
@@ -4313,24 +4314,24 @@
         <v>450</v>
       </c>
       <c r="L11" s="12">
-        <f>106+16+15+38+16</f>
-        <v>191</v>
+        <f>106+16+15+38+16+18</f>
+        <v>209</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="4"/>
-        <v>0.42444444444444446</v>
+        <v>0.46444444444444444</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="5"/>
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>19.923076923076923</v>
+        <v>20.083333333333332</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
-        <v>2.3292682926829267</v>
+        <v>2.5487804878048781</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="104"/>
@@ -4369,24 +4370,24 @@
         <v>300</v>
       </c>
       <c r="L12" s="12">
-        <f>100+8+8+6+8</f>
-        <v>130</v>
+        <f>100+8+8+6+8+8</f>
+        <v>138</v>
       </c>
       <c r="M12" s="70">
         <f t="shared" si="4"/>
-        <v>0.43333333333333335</v>
+        <v>0.46</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="5"/>
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>13.076923076923077</v>
+        <v>13.5</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
-        <v>1.625</v>
+        <v>1.7250000000000001</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="104"/>
@@ -4425,24 +4426,24 @@
         <v>250</v>
       </c>
       <c r="L13" s="12">
-        <f>50+10+10+4+5</f>
-        <v>79</v>
+        <f>50+10+10+4+5+5</f>
+        <v>84</v>
       </c>
       <c r="M13" s="70">
         <f t="shared" si="4"/>
-        <v>0.316</v>
+        <v>0.33600000000000002</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="5"/>
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="O13" s="14">
         <f t="shared" si="6"/>
-        <v>13.153846153846153</v>
+        <v>13.833333333333334</v>
       </c>
       <c r="P13" s="71">
         <f t="shared" si="2"/>
-        <v>1.161764705882353</v>
+        <v>1.2352941176470589</v>
       </c>
       <c r="Q13" s="14"/>
       <c r="R13" s="104"/>
@@ -4493,7 +4494,7 @@
       </c>
       <c r="O14" s="14">
         <f t="shared" si="6"/>
-        <v>0.76923076923076927</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="P14" s="71">
         <f t="shared" si="2"/>
@@ -4548,7 +4549,7 @@
       </c>
       <c r="O15" s="14">
         <f t="shared" si="6"/>
-        <v>1.9230769230769231</v>
+        <v>2.0833333333333335</v>
       </c>
       <c r="P15" s="71">
         <f t="shared" si="2"/>
@@ -4599,7 +4600,7 @@
       </c>
       <c r="O16" s="14">
         <f t="shared" si="6"/>
-        <v>-33.07692307692308</v>
+        <v>-35.833333333333336</v>
       </c>
       <c r="P16" s="71">
         <f t="shared" si="2"/>
@@ -4633,11 +4634,11 @@
       </c>
       <c r="I17" s="41">
         <f>SUM(I4:I16)</f>
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>0.21379863618130765</v>
+        <v>0.23265142398716407</v>
       </c>
       <c r="K17" s="76">
         <f>SUM(K4:K16)</f>
@@ -4645,23 +4646,23 @@
       </c>
       <c r="L17" s="77">
         <f>SUM(L4:L16)</f>
-        <v>2144.625</v>
+        <v>2392.3249999999998</v>
       </c>
       <c r="M17" s="78">
         <f t="shared" si="4"/>
-        <v>0.40464622641509435</v>
+        <v>0.45138207547169806</v>
       </c>
       <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>3155.375</v>
+        <v>2907.6750000000002</v>
       </c>
       <c r="O17" s="79">
         <f t="shared" si="6"/>
-        <v>242.72115384615384</v>
+        <v>242.30625000000001</v>
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>4.0236866791744843</v>
+        <v>4.1246982758620687</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -4715,7 +4716,7 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="6"/>
-        <v>32.746153846153845</v>
+        <v>35.475000000000001</v>
       </c>
       <c r="P18" s="96">
         <f t="shared" ref="P18:P22" si="7">L18/I18</f>
@@ -4770,7 +4771,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>32.746153846153845</v>
+        <v>35.475000000000001</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4825,7 +4826,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>32.746153846153845</v>
+        <v>35.475000000000001</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4880,7 +4881,7 @@
       </c>
       <c r="O21" s="14">
         <f t="shared" si="6"/>
-        <v>32.746153846153845</v>
+        <v>35.475000000000001</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="7"/>
@@ -4935,7 +4936,7 @@
       </c>
       <c r="O22" s="94">
         <f t="shared" si="6"/>
-        <v>32.746153846153845</v>
+        <v>35.475000000000001</v>
       </c>
       <c r="P22" s="74">
         <f t="shared" si="7"/>
@@ -4993,7 +4994,7 @@
       </c>
       <c r="O23" s="79">
         <f t="shared" si="6"/>
-        <v>32.746153846153845</v>
+        <v>35.475000000000001</v>
       </c>
       <c r="P23" s="80">
         <f>L23/I23</f>
@@ -5051,7 +5052,7 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="6"/>
-        <v>32.746153846153845</v>
+        <v>35.475000000000001</v>
       </c>
       <c r="P24" s="96">
         <f t="shared" ref="P24:P27" si="9">L24/I24</f>
@@ -5106,7 +5107,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>32.746153846153845</v>
+        <v>35.475000000000001</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5161,7 +5162,7 @@
       </c>
       <c r="O26" s="14">
         <f t="shared" si="6"/>
-        <v>32.746153846153845</v>
+        <v>35.475000000000001</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="9"/>
@@ -5216,7 +5217,7 @@
       </c>
       <c r="O27" s="94">
         <f t="shared" si="6"/>
-        <v>32.746153846153845</v>
+        <v>35.475000000000001</v>
       </c>
       <c r="P27" s="74">
         <f t="shared" si="9"/>
@@ -5271,7 +5272,7 @@
       </c>
       <c r="O28" s="79">
         <f t="shared" si="6"/>
-        <v>32.746153846153845</v>
+        <v>35.475000000000001</v>
       </c>
       <c r="P28" s="80">
         <f>L28/I28</f>
@@ -5304,11 +5305,11 @@
       </c>
       <c r="I29" s="21">
         <f t="shared" si="11"/>
-        <v>542</v>
+        <v>589</v>
       </c>
       <c r="J29" s="83">
         <f t="shared" si="3"/>
-        <v>0.21662669864108713</v>
+        <v>0.23541167066346921</v>
       </c>
       <c r="K29" s="84">
         <v>600</v>
@@ -5326,11 +5327,11 @@
       </c>
       <c r="O29" s="87">
         <f t="shared" si="6"/>
-        <v>32.746153846153845</v>
+        <v>35.475000000000001</v>
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>
-        <v>0.3215867158671587</v>
+        <v>0.29592529711375215</v>
       </c>
       <c r="Q29" s="23" t="e">
         <f>AVERAGE(Q28,Q17,Q23)</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDAF63FC-C279-4F00-BD2D-14CA119768A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6707FF-DEC4-425F-A093-68DDF7B6F44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3802,18 +3802,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.55555555555555558</v>
+        <v>0.59259259259259256</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F2" s="89">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="G2" s="117" t="s">
         <v>34</v>
@@ -3913,34 +3913,34 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>15+13+9+11+10+11+8+12+12+8</f>
-        <v>109</v>
+        <f>15+13+9+11+10+11+8+12+12+8+10</f>
+        <v>119</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.33538461538461539</v>
+        <v>0.36615384615384616</v>
       </c>
       <c r="K4" s="7">
         <v>450</v>
       </c>
       <c r="L4" s="8">
-        <v>135.05000000000001</v>
+        <v>159.05000000000001</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.30011111111111116</v>
+        <v>0.35344444444444445</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>314.95</v>
+        <v>290.95</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>26.245833333333334</v>
+        <v>26.45</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P16" si="2">L4/I4</f>
-        <v>1.2389908256880735</v>
+        <v>1.3365546218487396</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3969,34 +3969,34 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <f>6+5+5+3+3+4+3+5+10+19+20</f>
-        <v>83</v>
+        <f>6+5+5+3+3+4+3+5+10+19+20+23</f>
+        <v>106</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J29" si="3">IFERROR(I5/G5,0)</f>
-        <v>0.35021097046413502</v>
+        <v>0.4472573839662447</v>
       </c>
       <c r="K5" s="11">
         <v>350</v>
       </c>
       <c r="L5" s="12">
-        <v>100.1</v>
+        <v>109.1</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M29" si="4">IFERROR(L5/K5,0)</f>
-        <v>0.28599999999999998</v>
+        <v>0.31171428571428572</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>249.9</v>
+        <v>240.9</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>20.824999999999999</v>
+        <v>21.900000000000002</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>1.2060240963855422</v>
+        <v>1.0292452830188679</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>26.722916666666666</v>
+        <v>29.152272727272727</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
@@ -4082,34 +4082,34 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>2+2+6+4+9+7+8+1+6</f>
-        <v>45</v>
+        <f>2+2+6+4+9+7+8+1+6+6</f>
+        <v>51</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>0.15625</v>
+        <v>0.17708333333333334</v>
       </c>
       <c r="K7" s="11">
         <v>250</v>
       </c>
       <c r="L7" s="12">
-        <v>68.95</v>
+        <v>76.174999999999997</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>0.27579999999999999</v>
+        <v>0.30469999999999997</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>181.05</v>
+        <v>173.82499999999999</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>15.0875</v>
+        <v>15.802272727272726</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.5322222222222224</v>
+        <v>1.4936274509803922</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4138,34 +4138,34 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <f>3+6+7+6+6+3+5+8+6+4</f>
-        <v>54</v>
+        <f>3+6+7+6+6+3+5+8+6+4+6</f>
+        <v>60</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>0.15126050420168066</v>
+        <v>0.16806722689075632</v>
       </c>
       <c r="K8" s="11">
         <v>250</v>
       </c>
       <c r="L8" s="12">
-        <v>84.9</v>
+        <v>88.85</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>0.33960000000000001</v>
+        <v>0.35539999999999999</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N29" si="5">K8-L8</f>
-        <v>165.1</v>
+        <v>161.15</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
-        <v>13.758333333333333</v>
+        <v>14.65</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.5722222222222224</v>
+        <v>1.4808333333333332</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4248,34 +4248,34 @@
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="12">
-        <f>28+9</f>
-        <v>37</v>
+        <f>28+9+9</f>
+        <v>46</v>
       </c>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>0.33333333333333331</v>
+        <v>0.4144144144144144</v>
       </c>
       <c r="K10" s="11">
         <v>2300</v>
       </c>
       <c r="L10" s="12">
-        <v>948</v>
+        <v>1103</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>0.41217391304347828</v>
+        <v>0.47956521739130437</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>1352</v>
+        <v>1197</v>
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>112.66666666666667</v>
+        <v>108.81818181818181</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>25.621621621621621</v>
+        <v>23.978260869565219</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
@@ -4314,24 +4314,24 @@
         <v>450</v>
       </c>
       <c r="L11" s="12">
-        <f>106+16+15+38+16+18</f>
-        <v>209</v>
+        <f>106+16+15+38+16+18+9</f>
+        <v>218</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="4"/>
-        <v>0.46444444444444444</v>
+        <v>0.48444444444444446</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="5"/>
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>20.083333333333332</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
-        <v>2.5487804878048781</v>
+        <v>2.6585365853658538</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="104"/>
@@ -4370,24 +4370,24 @@
         <v>300</v>
       </c>
       <c r="L12" s="12">
-        <f>100+8+8+6+8+8</f>
-        <v>138</v>
+        <f>100+8+8+6+8+8+6</f>
+        <v>144</v>
       </c>
       <c r="M12" s="70">
         <f t="shared" si="4"/>
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="5"/>
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>13.5</v>
+        <v>14.181818181818182</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
-        <v>1.7250000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="104"/>
@@ -4426,24 +4426,24 @@
         <v>250</v>
       </c>
       <c r="L13" s="12">
-        <f>50+10+10+4+5+5</f>
-        <v>84</v>
+        <f>50+10+10+4+5+5+3.5</f>
+        <v>87.5</v>
       </c>
       <c r="M13" s="70">
         <f t="shared" si="4"/>
-        <v>0.33600000000000002</v>
+        <v>0.35</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="5"/>
-        <v>166</v>
+        <v>162.5</v>
       </c>
       <c r="O13" s="14">
         <f t="shared" si="6"/>
-        <v>13.833333333333334</v>
+        <v>14.772727272727273</v>
       </c>
       <c r="P13" s="71">
         <f t="shared" si="2"/>
-        <v>1.2352941176470589</v>
+        <v>1.286764705882353</v>
       </c>
       <c r="Q13" s="14"/>
       <c r="R13" s="104"/>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="O14" s="14">
         <f t="shared" si="6"/>
-        <v>0.83333333333333337</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="P14" s="71">
         <f t="shared" si="2"/>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="O15" s="14">
         <f t="shared" si="6"/>
-        <v>2.0833333333333335</v>
+        <v>2.2727272727272729</v>
       </c>
       <c r="P15" s="71">
         <f t="shared" si="2"/>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="O16" s="14">
         <f t="shared" si="6"/>
-        <v>-35.833333333333336</v>
+        <v>-39.090909090909093</v>
       </c>
       <c r="P16" s="71">
         <f t="shared" si="2"/>
@@ -4634,11 +4634,11 @@
       </c>
       <c r="I17" s="41">
         <f>SUM(I4:I16)</f>
-        <v>580</v>
+        <v>634</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>0.23265142398716407</v>
+        <v>0.25431207380665866</v>
       </c>
       <c r="K17" s="76">
         <f>SUM(K4:K16)</f>
@@ -4646,23 +4646,23 @@
       </c>
       <c r="L17" s="77">
         <f>SUM(L4:L16)</f>
-        <v>2392.3249999999998</v>
+        <v>2610</v>
       </c>
       <c r="M17" s="78">
         <f t="shared" si="4"/>
-        <v>0.45138207547169806</v>
+        <v>0.49245283018867925</v>
       </c>
       <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>2907.6750000000002</v>
+        <v>2690</v>
       </c>
       <c r="O17" s="79">
         <f t="shared" si="6"/>
-        <v>242.30625000000001</v>
+        <v>244.54545454545453</v>
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>4.1246982758620687</v>
+        <v>4.1167192429022084</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="6"/>
-        <v>35.475000000000001</v>
+        <v>38.699999999999996</v>
       </c>
       <c r="P18" s="96">
         <f t="shared" ref="P18:P22" si="7">L18/I18</f>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>35.475000000000001</v>
+        <v>38.699999999999996</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>35.475000000000001</v>
+        <v>38.699999999999996</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="O21" s="14">
         <f t="shared" si="6"/>
-        <v>35.475000000000001</v>
+        <v>38.699999999999996</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="7"/>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="O22" s="94">
         <f t="shared" si="6"/>
-        <v>35.475000000000001</v>
+        <v>38.699999999999996</v>
       </c>
       <c r="P22" s="74">
         <f t="shared" si="7"/>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="O23" s="79">
         <f t="shared" si="6"/>
-        <v>35.475000000000001</v>
+        <v>38.699999999999996</v>
       </c>
       <c r="P23" s="80">
         <f>L23/I23</f>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="6"/>
-        <v>35.475000000000001</v>
+        <v>38.699999999999996</v>
       </c>
       <c r="P24" s="96">
         <f t="shared" ref="P24:P27" si="9">L24/I24</f>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>35.475000000000001</v>
+        <v>38.699999999999996</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="O26" s="14">
         <f t="shared" si="6"/>
-        <v>35.475000000000001</v>
+        <v>38.699999999999996</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="9"/>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="O27" s="94">
         <f t="shared" si="6"/>
-        <v>35.475000000000001</v>
+        <v>38.699999999999996</v>
       </c>
       <c r="P27" s="74">
         <f t="shared" si="9"/>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="O28" s="79">
         <f t="shared" si="6"/>
-        <v>35.475000000000001</v>
+        <v>38.699999999999996</v>
       </c>
       <c r="P28" s="80">
         <f>L28/I28</f>
@@ -5305,11 +5305,11 @@
       </c>
       <c r="I29" s="21">
         <f t="shared" si="11"/>
-        <v>589</v>
+        <v>643</v>
       </c>
       <c r="J29" s="83">
         <f t="shared" si="3"/>
-        <v>0.23541167066346921</v>
+        <v>0.25699440447641886</v>
       </c>
       <c r="K29" s="84">
         <v>600</v>
@@ -5327,11 +5327,11 @@
       </c>
       <c r="O29" s="87">
         <f t="shared" si="6"/>
-        <v>35.475000000000001</v>
+        <v>38.699999999999996</v>
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>
-        <v>0.29592529711375215</v>
+        <v>0.27107309486780717</v>
       </c>
       <c r="Q29" s="23" t="e">
         <f>AVERAGE(Q28,Q17,Q23)</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6707FF-DEC4-425F-A093-68DDF7B6F44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{074496B6-BF39-40F7-9C62-E005F59D196F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -3802,18 +3802,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.59259259259259256</v>
+        <v>0.62962962962962965</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" s="89">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="G2" s="117" t="s">
         <v>34</v>
@@ -3913,34 +3913,34 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>15+13+9+11+10+11+8+12+12+8+10</f>
-        <v>119</v>
+        <f>15+13+9+11+10+11+8+12+12+8+10+12</f>
+        <v>131</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.36615384615384616</v>
+        <v>0.40307692307692305</v>
       </c>
       <c r="K4" s="7">
         <v>450</v>
       </c>
       <c r="L4" s="8">
-        <v>159.05000000000001</v>
+        <v>173.7</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.35344444444444445</v>
+        <v>0.38599999999999995</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>290.95</v>
+        <v>276.3</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>26.45</v>
+        <v>27.630000000000003</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P16" si="2">L4/I4</f>
-        <v>1.3365546218487396</v>
+        <v>1.3259541984732823</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3969,34 +3969,34 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <f>6+5+5+3+3+4+3+5+10+19+20+23</f>
-        <v>106</v>
+        <f>6+5+5+3+3+4+3+5+10+19+20+23+20</f>
+        <v>126</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J29" si="3">IFERROR(I5/G5,0)</f>
-        <v>0.4472573839662447</v>
+        <v>0.53164556962025311</v>
       </c>
       <c r="K5" s="11">
         <v>350</v>
       </c>
       <c r="L5" s="12">
-        <v>109.1</v>
+        <v>118.3</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M29" si="4">IFERROR(L5/K5,0)</f>
-        <v>0.31171428571428572</v>
+        <v>0.33799999999999997</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>240.9</v>
+        <v>231.7</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>21.900000000000002</v>
+        <v>23.169999999999998</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>1.0292452830188679</v>
+        <v>0.93888888888888888</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>29.152272727272727</v>
+        <v>32.067500000000003</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
@@ -4082,34 +4082,34 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>2+2+6+4+9+7+8+1+6+6</f>
-        <v>51</v>
+        <f>2+2+6+4+9+7+8+1+6+6+8</f>
+        <v>59</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>0.17708333333333334</v>
+        <v>0.2048611111111111</v>
       </c>
       <c r="K7" s="11">
         <v>250</v>
       </c>
       <c r="L7" s="12">
-        <v>76.174999999999997</v>
+        <v>83.525000000000006</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>0.30469999999999997</v>
+        <v>0.33410000000000001</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>173.82499999999999</v>
+        <v>166.47499999999999</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>15.802272727272726</v>
+        <v>16.647500000000001</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.4936274509803922</v>
+        <v>1.4156779661016949</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
-        <v>14.65</v>
+        <v>16.115000000000002</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
@@ -4248,34 +4248,34 @@
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="12">
-        <f>28+9+9</f>
-        <v>46</v>
+        <f>28+9+9+5</f>
+        <v>51</v>
       </c>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>0.4144144144144144</v>
+        <v>0.45945945945945948</v>
       </c>
       <c r="K10" s="11">
         <v>2300</v>
       </c>
       <c r="L10" s="12">
-        <v>1103</v>
+        <v>1150</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>0.47956521739130437</v>
+        <v>0.5</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>1197</v>
+        <v>1150</v>
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>108.81818181818181</v>
+        <v>115</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>23.978260869565219</v>
+        <v>22.549019607843139</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
@@ -4304,34 +4304,35 @@
       </c>
       <c r="H11" s="71"/>
       <c r="I11" s="12">
-        <v>82</v>
+        <f>82+12</f>
+        <v>94</v>
       </c>
       <c r="J11" s="69">
         <f t="shared" si="3"/>
-        <v>0.25465838509316768</v>
+        <v>0.29192546583850931</v>
       </c>
       <c r="K11" s="11">
         <v>450</v>
       </c>
       <c r="L11" s="12">
-        <f>106+16+15+38+16+18+9</f>
-        <v>218</v>
+        <f>106+16+15+38+16+18+9+16</f>
+        <v>234</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="4"/>
-        <v>0.48444444444444446</v>
+        <v>0.52</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="5"/>
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>21.09090909090909</v>
+        <v>21.6</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
-        <v>2.6585365853658538</v>
+        <v>2.4893617021276597</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="104"/>
@@ -4360,34 +4361,35 @@
       </c>
       <c r="H12" s="71"/>
       <c r="I12" s="12">
-        <v>80</v>
+        <f>80+8</f>
+        <v>88</v>
       </c>
       <c r="J12" s="69">
         <f t="shared" si="3"/>
-        <v>0.25723472668810288</v>
+        <v>0.28295819935691319</v>
       </c>
       <c r="K12" s="11">
         <v>300</v>
       </c>
       <c r="L12" s="12">
-        <f>100+8+8+6+8+8+6</f>
-        <v>144</v>
+        <f>100+8+8+6+8+8+6+8</f>
+        <v>152</v>
       </c>
       <c r="M12" s="70">
         <f t="shared" si="4"/>
-        <v>0.48</v>
+        <v>0.50666666666666671</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="5"/>
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>14.181818181818182</v>
+        <v>14.8</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
-        <v>1.8</v>
+        <v>1.7272727272727273</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="104"/>
@@ -4416,34 +4418,35 @@
       </c>
       <c r="H13" s="71"/>
       <c r="I13" s="12">
-        <v>68</v>
+        <f>68+10</f>
+        <v>78</v>
       </c>
       <c r="J13" s="69">
         <f t="shared" si="3"/>
-        <v>0.48571428571428571</v>
+        <v>0.55714285714285716</v>
       </c>
       <c r="K13" s="11">
         <v>250</v>
       </c>
       <c r="L13" s="12">
-        <f>50+10+10+4+5+5+3.5</f>
-        <v>87.5</v>
+        <f>50+10+10+4+5+5+3.5+8</f>
+        <v>95.5</v>
       </c>
       <c r="M13" s="70">
         <f t="shared" si="4"/>
-        <v>0.35</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="5"/>
-        <v>162.5</v>
+        <v>154.5</v>
       </c>
       <c r="O13" s="14">
         <f t="shared" si="6"/>
-        <v>14.772727272727273</v>
+        <v>15.45</v>
       </c>
       <c r="P13" s="71">
         <f t="shared" si="2"/>
-        <v>1.286764705882353</v>
+        <v>1.2243589743589745</v>
       </c>
       <c r="Q13" s="14"/>
       <c r="R13" s="104"/>
@@ -4494,7 +4497,7 @@
       </c>
       <c r="O14" s="14">
         <f t="shared" si="6"/>
-        <v>0.90909090909090906</v>
+        <v>1</v>
       </c>
       <c r="P14" s="71">
         <f t="shared" si="2"/>
@@ -4549,7 +4552,7 @@
       </c>
       <c r="O15" s="14">
         <f t="shared" si="6"/>
-        <v>2.2727272727272729</v>
+        <v>2.5</v>
       </c>
       <c r="P15" s="71">
         <f t="shared" si="2"/>
@@ -4579,32 +4582,28 @@
       </c>
       <c r="G16" s="11"/>
       <c r="H16" s="71"/>
-      <c r="I16" s="12">
-        <v>1</v>
-      </c>
+      <c r="I16" s="12"/>
       <c r="J16" s="69">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16" s="11"/>
-      <c r="L16" s="12">
-        <v>430</v>
-      </c>
+      <c r="L16" s="12"/>
       <c r="M16" s="70">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N16" s="12">
         <f t="shared" si="5"/>
-        <v>-430</v>
+        <v>0</v>
       </c>
       <c r="O16" s="14">
         <f t="shared" si="6"/>
-        <v>-39.090909090909093</v>
-      </c>
-      <c r="P16" s="71">
+        <v>0</v>
+      </c>
+      <c r="P16" s="71" t="e">
         <f t="shared" si="2"/>
-        <v>430</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="Q16" s="14"/>
       <c r="R16" s="34"/>
@@ -4634,11 +4633,11 @@
       </c>
       <c r="I17" s="41">
         <f>SUM(I4:I16)</f>
-        <v>634</v>
+        <v>708</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>0.25431207380665866</v>
+        <v>0.28399518652226236</v>
       </c>
       <c r="K17" s="76">
         <f>SUM(K4:K16)</f>
@@ -4646,23 +4645,23 @@
       </c>
       <c r="L17" s="77">
         <f>SUM(L4:L16)</f>
-        <v>2610</v>
+        <v>2290.1999999999998</v>
       </c>
       <c r="M17" s="78">
         <f t="shared" si="4"/>
-        <v>0.49245283018867925</v>
+        <v>0.43211320754716975</v>
       </c>
       <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>2690</v>
+        <v>3009.8</v>
       </c>
       <c r="O17" s="79">
         <f t="shared" si="6"/>
-        <v>244.54545454545453</v>
+        <v>300.98</v>
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>4.1167192429022084</v>
+        <v>3.2347457627118641</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -4716,7 +4715,7 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="6"/>
-        <v>38.699999999999996</v>
+        <v>42.57</v>
       </c>
       <c r="P18" s="96">
         <f t="shared" ref="P18:P22" si="7">L18/I18</f>
@@ -4771,7 +4770,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>38.699999999999996</v>
+        <v>42.57</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4826,7 +4825,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>38.699999999999996</v>
+        <v>42.57</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4881,7 +4880,7 @@
       </c>
       <c r="O21" s="14">
         <f t="shared" si="6"/>
-        <v>38.699999999999996</v>
+        <v>42.57</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="7"/>
@@ -4936,7 +4935,7 @@
       </c>
       <c r="O22" s="94">
         <f t="shared" si="6"/>
-        <v>38.699999999999996</v>
+        <v>42.57</v>
       </c>
       <c r="P22" s="74">
         <f t="shared" si="7"/>
@@ -4994,7 +4993,7 @@
       </c>
       <c r="O23" s="79">
         <f t="shared" si="6"/>
-        <v>38.699999999999996</v>
+        <v>42.57</v>
       </c>
       <c r="P23" s="80">
         <f>L23/I23</f>
@@ -5052,7 +5051,7 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="6"/>
-        <v>38.699999999999996</v>
+        <v>42.57</v>
       </c>
       <c r="P24" s="96">
         <f t="shared" ref="P24:P27" si="9">L24/I24</f>
@@ -5107,7 +5106,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>38.699999999999996</v>
+        <v>42.57</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5162,7 +5161,7 @@
       </c>
       <c r="O26" s="14">
         <f t="shared" si="6"/>
-        <v>38.699999999999996</v>
+        <v>42.57</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="9"/>
@@ -5217,7 +5216,7 @@
       </c>
       <c r="O27" s="94">
         <f t="shared" si="6"/>
-        <v>38.699999999999996</v>
+        <v>42.57</v>
       </c>
       <c r="P27" s="74">
         <f t="shared" si="9"/>
@@ -5272,7 +5271,7 @@
       </c>
       <c r="O28" s="79">
         <f t="shared" si="6"/>
-        <v>38.699999999999996</v>
+        <v>42.57</v>
       </c>
       <c r="P28" s="80">
         <f>L28/I28</f>
@@ -5305,11 +5304,11 @@
       </c>
       <c r="I29" s="21">
         <f t="shared" si="11"/>
-        <v>643</v>
+        <v>717</v>
       </c>
       <c r="J29" s="83">
         <f t="shared" si="3"/>
-        <v>0.25699440447641886</v>
+        <v>0.28657074340527577</v>
       </c>
       <c r="K29" s="84">
         <v>600</v>
@@ -5327,11 +5326,11 @@
       </c>
       <c r="O29" s="87">
         <f t="shared" si="6"/>
-        <v>38.699999999999996</v>
+        <v>42.57</v>
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>
-        <v>0.27107309486780717</v>
+        <v>0.24309623430962346</v>
       </c>
       <c r="Q29" s="23" t="e">
         <f>AVERAGE(Q28,Q17,Q23)</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{074496B6-BF39-40F7-9C62-E005F59D196F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2734DB01-A343-4821-B943-1343784D80BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3802,18 +3802,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.62962962962962965</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" s="89">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="G2" s="117" t="s">
         <v>34</v>
@@ -3913,34 +3913,34 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>15+13+9+11+10+11+8+12+12+8+10+12</f>
-        <v>131</v>
+        <f>15+13+9+11+10+11+8+12+12+8+10+12+7</f>
+        <v>138</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.40307692307692305</v>
+        <v>0.42461538461538462</v>
       </c>
       <c r="K4" s="7">
         <v>450</v>
       </c>
       <c r="L4" s="8">
-        <v>173.7</v>
+        <v>197.7</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.38599999999999995</v>
+        <v>0.4393333333333333</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>276.3</v>
+        <v>252.3</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>27.630000000000003</v>
+        <v>28.033333333333335</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P16" si="2">L4/I4</f>
-        <v>1.3259541984732823</v>
+        <v>1.4326086956521737</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3969,34 +3969,34 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <f>6+5+5+3+3+4+3+5+10+19+20+23+20</f>
-        <v>126</v>
+        <f>6+5+5+3+3+4+3+5+10+19+20+23+20+14</f>
+        <v>140</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J29" si="3">IFERROR(I5/G5,0)</f>
-        <v>0.53164556962025311</v>
+        <v>0.59071729957805907</v>
       </c>
       <c r="K5" s="11">
         <v>350</v>
       </c>
       <c r="L5" s="12">
-        <v>118.3</v>
+        <v>126.675</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M29" si="4">IFERROR(L5/K5,0)</f>
-        <v>0.33799999999999997</v>
+        <v>0.36192857142857143</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>231.7</v>
+        <v>223.32499999999999</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>23.169999999999998</v>
+        <v>24.813888888888886</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>0.93888888888888888</v>
+        <v>0.90482142857142855</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>32.067500000000003</v>
+        <v>35.63055555555556</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
@@ -4082,34 +4082,34 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>2+2+6+4+9+7+8+1+6+6+8</f>
-        <v>59</v>
+        <f>2+2+6+4+9+7+8+1+6+6+8+4</f>
+        <v>63</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>0.2048611111111111</v>
+        <v>0.21875</v>
       </c>
       <c r="K7" s="11">
         <v>250</v>
       </c>
       <c r="L7" s="12">
-        <v>83.525000000000006</v>
+        <v>92.125</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>0.33410000000000001</v>
+        <v>0.36849999999999999</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>166.47499999999999</v>
+        <v>157.875</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>16.647500000000001</v>
+        <v>17.541666666666668</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.4156779661016949</v>
+        <v>1.4623015873015872</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4138,34 +4138,34 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <f>3+6+7+6+6+3+5+8+6+4+6</f>
-        <v>60</v>
+        <f>3+6+7+6+6+3+5+8+6+4+6+10</f>
+        <v>70</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>0.16806722689075632</v>
+        <v>0.19607843137254902</v>
       </c>
       <c r="K8" s="11">
         <v>250</v>
       </c>
       <c r="L8" s="12">
-        <v>88.85</v>
+        <v>100.7</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>0.35539999999999999</v>
+        <v>0.40279999999999999</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N29" si="5">K8-L8</f>
-        <v>161.15</v>
+        <v>149.30000000000001</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
-        <v>16.115000000000002</v>
+        <v>16.588888888888889</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.4808333333333332</v>
+        <v>1.4385714285714286</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4248,34 +4248,34 @@
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="12">
-        <f>28+9+9+5</f>
-        <v>51</v>
+        <f>28+9+9+5+6</f>
+        <v>57</v>
       </c>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>0.45945945945945948</v>
+        <v>0.51351351351351349</v>
       </c>
       <c r="K10" s="11">
         <v>2300</v>
       </c>
       <c r="L10" s="12">
-        <v>1150</v>
+        <v>1322</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>0.5</v>
+        <v>0.57478260869565212</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>1150</v>
+        <v>978</v>
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>115</v>
+        <v>108.66666666666667</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>22.549019607843139</v>
+        <v>23.192982456140349</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
@@ -4315,24 +4315,24 @@
         <v>450</v>
       </c>
       <c r="L11" s="12">
-        <f>106+16+15+38+16+18+9+16</f>
-        <v>234</v>
+        <f>106+16+15+38+16+18+9+16+11</f>
+        <v>245</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="4"/>
-        <v>0.52</v>
+        <v>0.5444444444444444</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="5"/>
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>21.6</v>
+        <v>22.777777777777779</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
-        <v>2.4893617021276597</v>
+        <v>2.6063829787234041</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="104"/>
@@ -4372,24 +4372,24 @@
         <v>300</v>
       </c>
       <c r="L12" s="12">
-        <f>100+8+8+6+8+8+6+8</f>
-        <v>152</v>
+        <f>100+8+8+6+8+8+6+8+11</f>
+        <v>163</v>
       </c>
       <c r="M12" s="70">
         <f t="shared" si="4"/>
-        <v>0.50666666666666671</v>
+        <v>0.54333333333333333</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="5"/>
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>14.8</v>
+        <v>15.222222222222221</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
-        <v>1.7272727272727273</v>
+        <v>1.8522727272727273</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="104"/>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="O13" s="14">
         <f t="shared" si="6"/>
-        <v>15.45</v>
+        <v>17.166666666666668</v>
       </c>
       <c r="P13" s="71">
         <f t="shared" si="2"/>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="O14" s="14">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>1.1111111111111112</v>
       </c>
       <c r="P14" s="71">
         <f t="shared" si="2"/>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O15" s="14">
         <f t="shared" si="6"/>
-        <v>2.5</v>
+        <v>2.7777777777777777</v>
       </c>
       <c r="P15" s="71">
         <f t="shared" si="2"/>
@@ -4633,11 +4633,11 @@
       </c>
       <c r="I17" s="41">
         <f>SUM(I4:I16)</f>
-        <v>708</v>
+        <v>749</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>0.28399518652226236</v>
+        <v>0.30044123545928603</v>
       </c>
       <c r="K17" s="76">
         <f>SUM(K4:K16)</f>
@@ -4645,23 +4645,23 @@
       </c>
       <c r="L17" s="77">
         <f>SUM(L4:L16)</f>
-        <v>2290.1999999999998</v>
+        <v>2537.0250000000001</v>
       </c>
       <c r="M17" s="78">
         <f t="shared" si="4"/>
-        <v>0.43211320754716975</v>
+        <v>0.47868396226415094</v>
       </c>
       <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>3009.8</v>
+        <v>2762.9749999999999</v>
       </c>
       <c r="O17" s="79">
         <f t="shared" si="6"/>
-        <v>300.98</v>
+        <v>306.99722222222221</v>
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>3.2347457627118641</v>
+        <v>3.3872162883845127</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="6"/>
-        <v>42.57</v>
+        <v>47.3</v>
       </c>
       <c r="P18" s="96">
         <f t="shared" ref="P18:P22" si="7">L18/I18</f>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>42.57</v>
+        <v>47.3</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>42.57</v>
+        <v>47.3</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="O21" s="14">
         <f t="shared" si="6"/>
-        <v>42.57</v>
+        <v>47.3</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="7"/>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="O22" s="94">
         <f t="shared" si="6"/>
-        <v>42.57</v>
+        <v>47.3</v>
       </c>
       <c r="P22" s="74">
         <f t="shared" si="7"/>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="O23" s="79">
         <f t="shared" si="6"/>
-        <v>42.57</v>
+        <v>47.3</v>
       </c>
       <c r="P23" s="80">
         <f>L23/I23</f>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="6"/>
-        <v>42.57</v>
+        <v>47.3</v>
       </c>
       <c r="P24" s="96">
         <f t="shared" ref="P24:P27" si="9">L24/I24</f>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>42.57</v>
+        <v>47.3</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="O26" s="14">
         <f t="shared" si="6"/>
-        <v>42.57</v>
+        <v>47.3</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="9"/>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="O27" s="94">
         <f t="shared" si="6"/>
-        <v>42.57</v>
+        <v>47.3</v>
       </c>
       <c r="P27" s="74">
         <f t="shared" si="9"/>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="O28" s="79">
         <f t="shared" si="6"/>
-        <v>42.57</v>
+        <v>47.3</v>
       </c>
       <c r="P28" s="80">
         <f>L28/I28</f>
@@ -5304,11 +5304,11 @@
       </c>
       <c r="I29" s="21">
         <f t="shared" si="11"/>
-        <v>717</v>
+        <v>758</v>
       </c>
       <c r="J29" s="83">
         <f t="shared" si="3"/>
-        <v>0.28657074340527577</v>
+        <v>0.30295763389288571</v>
       </c>
       <c r="K29" s="84">
         <v>600</v>
@@ -5326,11 +5326,11 @@
       </c>
       <c r="O29" s="87">
         <f t="shared" si="6"/>
-        <v>42.57</v>
+        <v>47.3</v>
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>
-        <v>0.24309623430962346</v>
+        <v>0.22994722955145119</v>
       </c>
       <c r="Q29" s="23" t="e">
         <f>AVERAGE(Q28,Q17,Q23)</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2734DB01-A343-4821-B943-1343784D80BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5435E919-C678-459C-A3A5-20D9B75B20B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3802,18 +3802,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.66666666666666663</v>
+        <v>0.70370370370370372</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" s="89">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="G2" s="117" t="s">
         <v>34</v>
@@ -3913,34 +3913,34 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>15+13+9+11+10+11+8+12+12+8+10+12+7</f>
-        <v>138</v>
+        <f>15+13+9+11+10+11+8+12+12+8+10+12+7+29</f>
+        <v>167</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.42461538461538462</v>
+        <v>0.51384615384615384</v>
       </c>
       <c r="K4" s="7">
         <v>450</v>
       </c>
       <c r="L4" s="8">
-        <v>197.7</v>
+        <v>228.45</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.4393333333333333</v>
+        <v>0.5076666666666666</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>252.3</v>
+        <v>221.55</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>28.033333333333335</v>
+        <v>27.693750000000001</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P16" si="2">L4/I4</f>
-        <v>1.4326086956521737</v>
+        <v>1.3679640718562873</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3969,34 +3969,34 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <f>6+5+5+3+3+4+3+5+10+19+20+23+20+14</f>
-        <v>140</v>
+        <f>6+5+5+3+3+4+3+5+10+19+20+23+20+14+13</f>
+        <v>153</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J29" si="3">IFERROR(I5/G5,0)</f>
-        <v>0.59071729957805907</v>
+        <v>0.64556962025316456</v>
       </c>
       <c r="K5" s="11">
         <v>350</v>
       </c>
       <c r="L5" s="12">
-        <v>126.675</v>
+        <v>141.42500000000001</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M29" si="4">IFERROR(L5/K5,0)</f>
-        <v>0.36192857142857143</v>
+        <v>0.40407142857142858</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>223.32499999999999</v>
+        <v>208.57499999999999</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>24.813888888888886</v>
+        <v>26.071874999999999</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>0.90482142857142855</v>
+        <v>0.92434640522875822</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>35.63055555555556</v>
+        <v>40.084375000000001</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
@@ -4082,34 +4082,34 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>2+2+6+4+9+7+8+1+6+6+8+4</f>
-        <v>63</v>
+        <f>2+2+6+4+9+7+8+1+6+6+8+4+4</f>
+        <v>67</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>0.21875</v>
+        <v>0.2326388888888889</v>
       </c>
       <c r="K7" s="11">
         <v>250</v>
       </c>
       <c r="L7" s="12">
-        <v>92.125</v>
+        <v>96.474999999999994</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>0.36849999999999999</v>
+        <v>0.38589999999999997</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>157.875</v>
+        <v>153.52500000000001</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>17.541666666666668</v>
+        <v>19.190625000000001</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.4623015873015872</v>
+        <v>1.4399253731343282</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4138,34 +4138,34 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <f>3+6+7+6+6+3+5+8+6+4+6+10</f>
-        <v>70</v>
+        <f>3+6+7+6+6+3+5+8+6+4+6+10+10</f>
+        <v>80</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>0.19607843137254902</v>
+        <v>0.22408963585434175</v>
       </c>
       <c r="K8" s="11">
         <v>250</v>
       </c>
       <c r="L8" s="12">
-        <v>100.7</v>
+        <v>112.95</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>0.40279999999999999</v>
+        <v>0.45180000000000003</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N29" si="5">K8-L8</f>
-        <v>149.30000000000001</v>
+        <v>137.05000000000001</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
-        <v>16.588888888888889</v>
+        <v>17.131250000000001</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.4385714285714286</v>
+        <v>1.411875</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4248,34 +4248,34 @@
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="12">
-        <f>28+9+9+5+6</f>
-        <v>57</v>
+        <f>28+9+9+5+6+4</f>
+        <v>61</v>
       </c>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>0.51351351351351349</v>
+        <v>0.5495495495495496</v>
       </c>
       <c r="K10" s="11">
         <v>2300</v>
       </c>
       <c r="L10" s="12">
-        <v>1322</v>
+        <v>1504</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>0.57478260869565212</v>
+        <v>0.65391304347826085</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>978</v>
+        <v>796</v>
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>108.66666666666667</v>
+        <v>99.5</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>23.192982456140349</v>
+        <v>24.655737704918032</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
@@ -4304,35 +4304,35 @@
       </c>
       <c r="H11" s="71"/>
       <c r="I11" s="12">
-        <f>82+12</f>
-        <v>94</v>
+        <f>82+12+14</f>
+        <v>108</v>
       </c>
       <c r="J11" s="69">
         <f t="shared" si="3"/>
-        <v>0.29192546583850931</v>
+        <v>0.33540372670807456</v>
       </c>
       <c r="K11" s="11">
         <v>450</v>
       </c>
       <c r="L11" s="12">
-        <f>106+16+15+38+16+18+9+16+11</f>
-        <v>245</v>
+        <f>106+16+15+38+16+18+9+16+11+14</f>
+        <v>259</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="4"/>
-        <v>0.5444444444444444</v>
+        <v>0.5755555555555556</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="5"/>
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>22.777777777777779</v>
+        <v>23.875</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
-        <v>2.6063829787234041</v>
+        <v>2.3981481481481484</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="104"/>
@@ -4361,35 +4361,35 @@
       </c>
       <c r="H12" s="71"/>
       <c r="I12" s="12">
-        <f>80+8</f>
-        <v>88</v>
+        <f>80+8+10</f>
+        <v>98</v>
       </c>
       <c r="J12" s="69">
         <f t="shared" si="3"/>
-        <v>0.28295819935691319</v>
+        <v>0.31511254019292606</v>
       </c>
       <c r="K12" s="11">
         <v>300</v>
       </c>
       <c r="L12" s="12">
-        <f>100+8+8+6+8+8+6+8+11</f>
-        <v>163</v>
+        <f>100+8+8+6+8+8+6+8+11+8</f>
+        <v>171</v>
       </c>
       <c r="M12" s="70">
         <f t="shared" si="4"/>
-        <v>0.54333333333333333</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="5"/>
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>15.222222222222221</v>
+        <v>16.125</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
-        <v>1.8522727272727273</v>
+        <v>1.7448979591836735</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="104"/>
@@ -4418,35 +4418,35 @@
       </c>
       <c r="H13" s="71"/>
       <c r="I13" s="12">
-        <f>68+10</f>
-        <v>78</v>
+        <f>68+10+4</f>
+        <v>82</v>
       </c>
       <c r="J13" s="69">
         <f t="shared" si="3"/>
-        <v>0.55714285714285716</v>
+        <v>0.58571428571428574</v>
       </c>
       <c r="K13" s="11">
         <v>250</v>
       </c>
       <c r="L13" s="12">
-        <f>50+10+10+4+5+5+3.5+8</f>
-        <v>95.5</v>
+        <f>50+10+10+4+5+5+3.5+8+4</f>
+        <v>99.5</v>
       </c>
       <c r="M13" s="70">
         <f t="shared" si="4"/>
-        <v>0.38200000000000001</v>
+        <v>0.39800000000000002</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="5"/>
-        <v>154.5</v>
+        <v>150.5</v>
       </c>
       <c r="O13" s="14">
         <f t="shared" si="6"/>
-        <v>17.166666666666668</v>
+        <v>18.8125</v>
       </c>
       <c r="P13" s="71">
         <f t="shared" si="2"/>
-        <v>1.2243589743589745</v>
+        <v>1.2134146341463414</v>
       </c>
       <c r="Q13" s="14"/>
       <c r="R13" s="104"/>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="O14" s="14">
         <f t="shared" si="6"/>
-        <v>1.1111111111111112</v>
+        <v>1.25</v>
       </c>
       <c r="P14" s="71">
         <f t="shared" si="2"/>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O15" s="14">
         <f t="shared" si="6"/>
-        <v>2.7777777777777777</v>
+        <v>3.125</v>
       </c>
       <c r="P15" s="71">
         <f t="shared" si="2"/>
@@ -4633,11 +4633,11 @@
       </c>
       <c r="I17" s="41">
         <f>SUM(I4:I16)</f>
-        <v>749</v>
+        <v>837</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>0.30044123545928603</v>
+        <v>0.33574007220216606</v>
       </c>
       <c r="K17" s="76">
         <f>SUM(K4:K16)</f>
@@ -4645,23 +4645,23 @@
       </c>
       <c r="L17" s="77">
         <f>SUM(L4:L16)</f>
-        <v>2537.0250000000001</v>
+        <v>2807.125</v>
       </c>
       <c r="M17" s="78">
         <f t="shared" si="4"/>
-        <v>0.47868396226415094</v>
+        <v>0.52964622641509429</v>
       </c>
       <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>2762.9749999999999</v>
+        <v>2492.875</v>
       </c>
       <c r="O17" s="79">
         <f t="shared" si="6"/>
-        <v>306.99722222222221</v>
+        <v>311.609375</v>
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>3.3872162883845127</v>
+        <v>3.3537933094384709</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="6"/>
-        <v>47.3</v>
+        <v>53.212499999999999</v>
       </c>
       <c r="P18" s="96">
         <f t="shared" ref="P18:P22" si="7">L18/I18</f>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>47.3</v>
+        <v>53.212499999999999</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>47.3</v>
+        <v>53.212499999999999</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="O21" s="14">
         <f t="shared" si="6"/>
-        <v>47.3</v>
+        <v>53.212499999999999</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="7"/>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="O22" s="94">
         <f t="shared" si="6"/>
-        <v>47.3</v>
+        <v>53.212499999999999</v>
       </c>
       <c r="P22" s="74">
         <f t="shared" si="7"/>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="O23" s="79">
         <f t="shared" si="6"/>
-        <v>47.3</v>
+        <v>53.212499999999999</v>
       </c>
       <c r="P23" s="80">
         <f>L23/I23</f>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="6"/>
-        <v>47.3</v>
+        <v>53.212499999999999</v>
       </c>
       <c r="P24" s="96">
         <f t="shared" ref="P24:P27" si="9">L24/I24</f>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>47.3</v>
+        <v>53.212499999999999</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="O26" s="14">
         <f t="shared" si="6"/>
-        <v>47.3</v>
+        <v>53.212499999999999</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="9"/>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="O27" s="94">
         <f t="shared" si="6"/>
-        <v>47.3</v>
+        <v>53.212499999999999</v>
       </c>
       <c r="P27" s="74">
         <f t="shared" si="9"/>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="O28" s="79">
         <f t="shared" si="6"/>
-        <v>47.3</v>
+        <v>53.212499999999999</v>
       </c>
       <c r="P28" s="80">
         <f>L28/I28</f>
@@ -5304,11 +5304,11 @@
       </c>
       <c r="I29" s="21">
         <f t="shared" si="11"/>
-        <v>758</v>
+        <v>846</v>
       </c>
       <c r="J29" s="83">
         <f t="shared" si="3"/>
-        <v>0.30295763389288571</v>
+        <v>0.33812949640287771</v>
       </c>
       <c r="K29" s="84">
         <v>600</v>
@@ -5326,11 +5326,11 @@
       </c>
       <c r="O29" s="87">
         <f t="shared" si="6"/>
-        <v>47.3</v>
+        <v>53.212499999999999</v>
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>
-        <v>0.22994722955145119</v>
+        <v>0.20602836879432626</v>
       </c>
       <c r="Q29" s="23" t="e">
         <f>AVERAGE(Q28,Q17,Q23)</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5435E919-C678-459C-A3A5-20D9B75B20B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7AC1029-E5D4-4929-A01C-C6E1158078D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3802,18 +3802,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.70370370370370372</v>
+        <v>0.7407407407407407</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" s="89">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="G2" s="117" t="s">
         <v>34</v>
@@ -3913,34 +3913,34 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>15+13+9+11+10+11+8+12+12+8+10+12+7+29</f>
-        <v>167</v>
+        <f>15+13+9+11+10+11+8+12+12+8+10+12+7+29+20</f>
+        <v>187</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.51384615384615384</v>
+        <v>0.57538461538461538</v>
       </c>
       <c r="K4" s="7">
         <v>450</v>
       </c>
       <c r="L4" s="8">
-        <v>228.45</v>
+        <v>247.2</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.5076666666666666</v>
+        <v>0.54933333333333334</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>221.55</v>
+        <v>202.8</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>27.693750000000001</v>
+        <v>28.971428571428572</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P16" si="2">L4/I4</f>
-        <v>1.3679640718562873</v>
+        <v>1.3219251336898394</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3969,34 +3969,34 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <f>6+5+5+3+3+4+3+5+10+19+20+23+20+14+13</f>
-        <v>153</v>
+        <f>6+5+5+3+3+4+3+5+10+19+20+23+20+14+13+14</f>
+        <v>167</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J29" si="3">IFERROR(I5/G5,0)</f>
-        <v>0.64556962025316456</v>
+        <v>0.70464135021097052</v>
       </c>
       <c r="K5" s="11">
         <v>350</v>
       </c>
       <c r="L5" s="12">
-        <v>141.42500000000001</v>
+        <v>146.44999999999999</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M29" si="4">IFERROR(L5/K5,0)</f>
-        <v>0.40407142857142858</v>
+        <v>0.41842857142857137</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>208.57499999999999</v>
+        <v>203.55</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>26.071874999999999</v>
+        <v>29.078571428571429</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>0.92434640522875822</v>
+        <v>0.87694610778443105</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>40.084375000000001</v>
+        <v>45.81071428571429</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
@@ -4082,34 +4082,34 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>2+2+6+4+9+7+8+1+6+6+8+4+4</f>
-        <v>67</v>
+        <f>2+2+6+4+9+7+8+1+6+6+8+4+4+5</f>
+        <v>72</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>0.2326388888888889</v>
+        <v>0.25</v>
       </c>
       <c r="K7" s="11">
         <v>250</v>
       </c>
       <c r="L7" s="12">
-        <v>96.474999999999994</v>
+        <v>113.325</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>0.38589999999999997</v>
+        <v>0.45330000000000004</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>153.52500000000001</v>
+        <v>136.67500000000001</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>19.190625000000001</v>
+        <v>19.525000000000002</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.4399253731343282</v>
+        <v>1.5739583333333333</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4138,34 +4138,34 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <f>3+6+7+6+6+3+5+8+6+4+6+10+10</f>
-        <v>80</v>
+        <f>3+6+7+6+6+3+5+8+6+4+6+10+10+9</f>
+        <v>89</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>0.22408963585434175</v>
+        <v>0.24929971988795518</v>
       </c>
       <c r="K8" s="11">
         <v>250</v>
       </c>
       <c r="L8" s="12">
-        <v>112.95</v>
+        <v>120.55</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>0.45180000000000003</v>
+        <v>0.48219999999999996</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N29" si="5">K8-L8</f>
-        <v>137.05000000000001</v>
+        <v>129.44999999999999</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
-        <v>17.131250000000001</v>
+        <v>18.49285714285714</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.411875</v>
+        <v>1.354494382022472</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4248,34 +4248,34 @@
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="12">
-        <f>28+9+9+5+6+4</f>
-        <v>61</v>
+        <f>28+9+9+5+6+4+3</f>
+        <v>64</v>
       </c>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>0.5495495495495496</v>
+        <v>0.57657657657657657</v>
       </c>
       <c r="K10" s="11">
         <v>2300</v>
       </c>
       <c r="L10" s="12">
-        <v>1504</v>
+        <v>1555.95</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>0.65391304347826085</v>
+        <v>0.67649999999999999</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>796</v>
+        <v>744.05</v>
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>99.5</v>
+        <v>106.29285714285713</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>24.655737704918032</v>
+        <v>24.311718750000001</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
@@ -4304,35 +4304,35 @@
       </c>
       <c r="H11" s="71"/>
       <c r="I11" s="12">
-        <f>82+12+14</f>
-        <v>108</v>
+        <f>82+12+14+10</f>
+        <v>118</v>
       </c>
       <c r="J11" s="69">
         <f t="shared" si="3"/>
-        <v>0.33540372670807456</v>
+        <v>0.36645962732919257</v>
       </c>
       <c r="K11" s="11">
         <v>450</v>
       </c>
       <c r="L11" s="12">
-        <f>106+16+15+38+16+18+9+16+11+14</f>
-        <v>259</v>
+        <f>106+16+15+38+16+18+9+16+11+14+12</f>
+        <v>271</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="4"/>
-        <v>0.5755555555555556</v>
+        <v>0.60222222222222221</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="5"/>
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>23.875</v>
+        <v>25.571428571428573</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
-        <v>2.3981481481481484</v>
+        <v>2.2966101694915255</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="104"/>
@@ -4361,35 +4361,35 @@
       </c>
       <c r="H12" s="71"/>
       <c r="I12" s="12">
-        <f>80+8+10</f>
-        <v>98</v>
+        <f>80+8+10+8</f>
+        <v>106</v>
       </c>
       <c r="J12" s="69">
         <f t="shared" si="3"/>
-        <v>0.31511254019292606</v>
+        <v>0.34083601286173631</v>
       </c>
       <c r="K12" s="11">
         <v>300</v>
       </c>
       <c r="L12" s="12">
-        <f>100+8+8+6+8+8+6+8+11+8</f>
-        <v>171</v>
+        <f>100+8+8+6+8+8+6+8+11+8+12</f>
+        <v>183</v>
       </c>
       <c r="M12" s="70">
         <f t="shared" si="4"/>
-        <v>0.56999999999999995</v>
+        <v>0.61</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="5"/>
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>16.125</v>
+        <v>16.714285714285715</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
-        <v>1.7448979591836735</v>
+        <v>1.7264150943396226</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="104"/>
@@ -4418,35 +4418,35 @@
       </c>
       <c r="H13" s="71"/>
       <c r="I13" s="12">
-        <f>68+10+4</f>
-        <v>82</v>
+        <f>68+10+4+5</f>
+        <v>87</v>
       </c>
       <c r="J13" s="69">
         <f t="shared" si="3"/>
-        <v>0.58571428571428574</v>
+        <v>0.62142857142857144</v>
       </c>
       <c r="K13" s="11">
         <v>250</v>
       </c>
       <c r="L13" s="12">
-        <f>50+10+10+4+5+5+3.5+8+4</f>
-        <v>99.5</v>
+        <f>50+10+10+4+5+5+3.5+8+4+10</f>
+        <v>109.5</v>
       </c>
       <c r="M13" s="70">
         <f t="shared" si="4"/>
-        <v>0.39800000000000002</v>
+        <v>0.438</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="5"/>
-        <v>150.5</v>
+        <v>140.5</v>
       </c>
       <c r="O13" s="14">
         <f t="shared" si="6"/>
-        <v>18.8125</v>
+        <v>20.071428571428573</v>
       </c>
       <c r="P13" s="71">
         <f t="shared" si="2"/>
-        <v>1.2134146341463414</v>
+        <v>1.2586206896551724</v>
       </c>
       <c r="Q13" s="14"/>
       <c r="R13" s="104"/>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="O14" s="14">
         <f t="shared" si="6"/>
-        <v>1.25</v>
+        <v>1.4285714285714286</v>
       </c>
       <c r="P14" s="71">
         <f t="shared" si="2"/>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O15" s="14">
         <f t="shared" si="6"/>
-        <v>3.125</v>
+        <v>3.5714285714285716</v>
       </c>
       <c r="P15" s="71">
         <f t="shared" si="2"/>
@@ -4633,11 +4633,11 @@
       </c>
       <c r="I17" s="41">
         <f>SUM(I4:I16)</f>
-        <v>837</v>
+        <v>911</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>0.33574007220216606</v>
+        <v>0.36542318491776976</v>
       </c>
       <c r="K17" s="76">
         <f>SUM(K4:K16)</f>
@@ -4645,23 +4645,23 @@
       </c>
       <c r="L17" s="77">
         <f>SUM(L4:L16)</f>
-        <v>2807.125</v>
+        <v>2941.3</v>
       </c>
       <c r="M17" s="78">
         <f t="shared" si="4"/>
-        <v>0.52964622641509429</v>
+        <v>0.55496226415094341</v>
       </c>
       <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>2492.875</v>
+        <v>2358.6999999999998</v>
       </c>
       <c r="O17" s="79">
         <f t="shared" si="6"/>
-        <v>311.609375</v>
+        <v>336.95714285714286</v>
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>3.3537933094384709</v>
+        <v>3.2286498353457742</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="6"/>
-        <v>53.212499999999999</v>
+        <v>60.81428571428571</v>
       </c>
       <c r="P18" s="96">
         <f t="shared" ref="P18:P22" si="7">L18/I18</f>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>53.212499999999999</v>
+        <v>60.81428571428571</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>53.212499999999999</v>
+        <v>60.81428571428571</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="O21" s="14">
         <f t="shared" si="6"/>
-        <v>53.212499999999999</v>
+        <v>60.81428571428571</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="7"/>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="O22" s="94">
         <f t="shared" si="6"/>
-        <v>53.212499999999999</v>
+        <v>60.81428571428571</v>
       </c>
       <c r="P22" s="74">
         <f t="shared" si="7"/>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="O23" s="79">
         <f t="shared" si="6"/>
-        <v>53.212499999999999</v>
+        <v>60.81428571428571</v>
       </c>
       <c r="P23" s="80">
         <f>L23/I23</f>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="6"/>
-        <v>53.212499999999999</v>
+        <v>60.81428571428571</v>
       </c>
       <c r="P24" s="96">
         <f t="shared" ref="P24:P27" si="9">L24/I24</f>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>53.212499999999999</v>
+        <v>60.81428571428571</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="O26" s="14">
         <f t="shared" si="6"/>
-        <v>53.212499999999999</v>
+        <v>60.81428571428571</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="9"/>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="O27" s="94">
         <f t="shared" si="6"/>
-        <v>53.212499999999999</v>
+        <v>60.81428571428571</v>
       </c>
       <c r="P27" s="74">
         <f t="shared" si="9"/>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="O28" s="79">
         <f t="shared" si="6"/>
-        <v>53.212499999999999</v>
+        <v>60.81428571428571</v>
       </c>
       <c r="P28" s="80">
         <f>L28/I28</f>
@@ -5304,11 +5304,11 @@
       </c>
       <c r="I29" s="21">
         <f t="shared" si="11"/>
-        <v>846</v>
+        <v>920</v>
       </c>
       <c r="J29" s="83">
         <f t="shared" si="3"/>
-        <v>0.33812949640287771</v>
+        <v>0.36770583533173462</v>
       </c>
       <c r="K29" s="84">
         <v>600</v>
@@ -5326,11 +5326,11 @@
       </c>
       <c r="O29" s="87">
         <f t="shared" si="6"/>
-        <v>53.212499999999999</v>
+        <v>60.81428571428571</v>
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>
-        <v>0.20602836879432626</v>
+        <v>0.18945652173913044</v>
       </c>
       <c r="Q29" s="23" t="e">
         <f>AVERAGE(Q28,Q17,Q23)</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7AC1029-E5D4-4929-A01C-C6E1158078D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90CE5632-2A4C-4039-B7DC-601F2EA04726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3802,18 +3802,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.7407407407407407</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" s="89">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="G2" s="117" t="s">
         <v>34</v>
@@ -3913,34 +3913,34 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>15+13+9+11+10+11+8+12+12+8+10+12+7+29+20</f>
-        <v>187</v>
+        <f>15+13+9+11+10+11+8+12+12+8+10+12+7+29+20+17</f>
+        <v>204</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.57538461538461538</v>
+        <v>0.62769230769230766</v>
       </c>
       <c r="K4" s="7">
         <v>450</v>
       </c>
       <c r="L4" s="8">
-        <v>247.2</v>
+        <v>259.95</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.54933333333333334</v>
+        <v>0.57766666666666666</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>202.8</v>
+        <v>190.05</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>28.971428571428572</v>
+        <v>31.675000000000001</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P16" si="2">L4/I4</f>
-        <v>1.3219251336898394</v>
+        <v>1.2742647058823529</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>29.078571428571429</v>
+        <v>33.925000000000004</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>45.81071428571429</v>
+        <v>53.445833333333333</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
@@ -4082,34 +4082,34 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>2+2+6+4+9+7+8+1+6+6+8+4+4+5</f>
-        <v>72</v>
+        <f>2+2+6+4+9+7+8+1+6+6+8+4+4+5+8</f>
+        <v>80</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.27777777777777779</v>
       </c>
       <c r="K7" s="11">
         <v>250</v>
       </c>
       <c r="L7" s="12">
-        <v>113.325</v>
+        <v>121.325</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>0.45330000000000004</v>
+        <v>0.48530000000000001</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>136.67500000000001</v>
+        <v>128.67500000000001</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>19.525000000000002</v>
+        <v>21.445833333333336</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.5739583333333333</v>
+        <v>1.5165625</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4138,34 +4138,34 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <f>3+6+7+6+6+3+5+8+6+4+6+10+10+9</f>
-        <v>89</v>
+        <f>3+6+7+6+6+3+5+8+6+4+6+10+10+9+5</f>
+        <v>94</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>0.24929971988795518</v>
+        <v>0.26330532212885155</v>
       </c>
       <c r="K8" s="11">
         <v>250</v>
       </c>
       <c r="L8" s="12">
-        <v>120.55</v>
+        <v>128</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>0.48219999999999996</v>
+        <v>0.51200000000000001</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N29" si="5">K8-L8</f>
-        <v>129.44999999999999</v>
+        <v>122</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
-        <v>18.49285714285714</v>
+        <v>20.333333333333332</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.354494382022472</v>
+        <v>1.3617021276595744</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4248,34 +4248,34 @@
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="12">
-        <f>28+9+9+5+6+4+3</f>
-        <v>64</v>
+        <f>28+9+9+5+6+4+3+5</f>
+        <v>69</v>
       </c>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>0.57657657657657657</v>
+        <v>0.6216216216216216</v>
       </c>
       <c r="K10" s="11">
         <v>2300</v>
       </c>
       <c r="L10" s="12">
-        <v>1555.95</v>
+        <v>1655</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>0.67649999999999999</v>
+        <v>0.7195652173913043</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>744.05</v>
+        <v>645</v>
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>106.29285714285713</v>
+        <v>107.5</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>24.311718750000001</v>
+        <v>23.985507246376812</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
@@ -4304,35 +4304,35 @@
       </c>
       <c r="H11" s="71"/>
       <c r="I11" s="12">
-        <f>82+12+14+10</f>
-        <v>118</v>
+        <f>82+12+14+10+10</f>
+        <v>128</v>
       </c>
       <c r="J11" s="69">
         <f t="shared" si="3"/>
-        <v>0.36645962732919257</v>
+        <v>0.39751552795031053</v>
       </c>
       <c r="K11" s="11">
         <v>450</v>
       </c>
       <c r="L11" s="12">
-        <f>106+16+15+38+16+18+9+16+11+14+12</f>
-        <v>271</v>
+        <f>106+16+15+38+16+18+9+16+11+14+12+8</f>
+        <v>279</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="4"/>
-        <v>0.60222222222222221</v>
+        <v>0.62</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="5"/>
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>25.571428571428573</v>
+        <v>28.5</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
-        <v>2.2966101694915255</v>
+        <v>2.1796875</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="104"/>
@@ -4361,35 +4361,35 @@
       </c>
       <c r="H12" s="71"/>
       <c r="I12" s="12">
-        <f>80+8+10+8</f>
-        <v>106</v>
+        <f>80+8+10+8+12</f>
+        <v>118</v>
       </c>
       <c r="J12" s="69">
         <f t="shared" si="3"/>
-        <v>0.34083601286173631</v>
+        <v>0.37942122186495175</v>
       </c>
       <c r="K12" s="11">
         <v>300</v>
       </c>
       <c r="L12" s="12">
-        <f>100+8+8+6+8+8+6+8+11+8+12</f>
-        <v>183</v>
+        <f>100+8+8+6+8+8+6+8+11+8+12+23</f>
+        <v>206</v>
       </c>
       <c r="M12" s="70">
         <f t="shared" si="4"/>
-        <v>0.61</v>
+        <v>0.68666666666666665</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="5"/>
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>16.714285714285715</v>
+        <v>15.666666666666666</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
-        <v>1.7264150943396226</v>
+        <v>1.7457627118644068</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="104"/>
@@ -4418,35 +4418,35 @@
       </c>
       <c r="H13" s="71"/>
       <c r="I13" s="12">
-        <f>68+10+4+5</f>
-        <v>87</v>
+        <f>68+10+4+5+8</f>
+        <v>95</v>
       </c>
       <c r="J13" s="69">
         <f t="shared" si="3"/>
-        <v>0.62142857142857144</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="K13" s="11">
         <v>250</v>
       </c>
       <c r="L13" s="12">
-        <f>50+10+10+4+5+5+3.5+8+4+10</f>
-        <v>109.5</v>
+        <f>50+10+10+4+5+5+3.5+8+4+10+5</f>
+        <v>114.5</v>
       </c>
       <c r="M13" s="70">
         <f t="shared" si="4"/>
-        <v>0.438</v>
+        <v>0.45800000000000002</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="5"/>
-        <v>140.5</v>
+        <v>135.5</v>
       </c>
       <c r="O13" s="14">
         <f t="shared" si="6"/>
-        <v>20.071428571428573</v>
+        <v>22.583333333333332</v>
       </c>
       <c r="P13" s="71">
         <f t="shared" si="2"/>
-        <v>1.2586206896551724</v>
+        <v>1.2052631578947368</v>
       </c>
       <c r="Q13" s="14"/>
       <c r="R13" s="104"/>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="O14" s="14">
         <f t="shared" si="6"/>
-        <v>1.4285714285714286</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="P14" s="71">
         <f t="shared" si="2"/>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O15" s="14">
         <f t="shared" si="6"/>
-        <v>3.5714285714285716</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="P15" s="71">
         <f t="shared" si="2"/>
@@ -4633,11 +4633,11 @@
       </c>
       <c r="I17" s="41">
         <f>SUM(I4:I16)</f>
-        <v>911</v>
+        <v>976</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>0.36542318491776976</v>
+        <v>0.39149618933012437</v>
       </c>
       <c r="K17" s="76">
         <f>SUM(K4:K16)</f>
@@ -4645,23 +4645,23 @@
       </c>
       <c r="L17" s="77">
         <f>SUM(L4:L16)</f>
-        <v>2941.3</v>
+        <v>3104.55</v>
       </c>
       <c r="M17" s="78">
         <f t="shared" si="4"/>
-        <v>0.55496226415094341</v>
+        <v>0.58576415094339629</v>
       </c>
       <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>2358.6999999999998</v>
+        <v>2195.4499999999998</v>
       </c>
       <c r="O17" s="79">
         <f t="shared" si="6"/>
-        <v>336.95714285714286</v>
+        <v>365.9083333333333</v>
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>3.2286498353457742</v>
+        <v>3.1808913934426233</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="6"/>
-        <v>60.81428571428571</v>
+        <v>70.95</v>
       </c>
       <c r="P18" s="96">
         <f t="shared" ref="P18:P22" si="7">L18/I18</f>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>60.81428571428571</v>
+        <v>70.95</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>60.81428571428571</v>
+        <v>70.95</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="O21" s="14">
         <f t="shared" si="6"/>
-        <v>60.81428571428571</v>
+        <v>70.95</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="7"/>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="O22" s="94">
         <f t="shared" si="6"/>
-        <v>60.81428571428571</v>
+        <v>70.95</v>
       </c>
       <c r="P22" s="74">
         <f t="shared" si="7"/>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="O23" s="79">
         <f t="shared" si="6"/>
-        <v>60.81428571428571</v>
+        <v>70.95</v>
       </c>
       <c r="P23" s="80">
         <f>L23/I23</f>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="6"/>
-        <v>60.81428571428571</v>
+        <v>70.95</v>
       </c>
       <c r="P24" s="96">
         <f t="shared" ref="P24:P27" si="9">L24/I24</f>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>60.81428571428571</v>
+        <v>70.95</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="O26" s="14">
         <f t="shared" si="6"/>
-        <v>60.81428571428571</v>
+        <v>70.95</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="9"/>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="O27" s="94">
         <f t="shared" si="6"/>
-        <v>60.81428571428571</v>
+        <v>70.95</v>
       </c>
       <c r="P27" s="74">
         <f t="shared" si="9"/>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="O28" s="79">
         <f t="shared" si="6"/>
-        <v>60.81428571428571</v>
+        <v>70.95</v>
       </c>
       <c r="P28" s="80">
         <f>L28/I28</f>
@@ -5304,11 +5304,11 @@
       </c>
       <c r="I29" s="21">
         <f t="shared" si="11"/>
-        <v>920</v>
+        <v>985</v>
       </c>
       <c r="J29" s="83">
         <f t="shared" si="3"/>
-        <v>0.36770583533173462</v>
+        <v>0.39368505195843323</v>
       </c>
       <c r="K29" s="84">
         <v>600</v>
@@ -5326,11 +5326,11 @@
       </c>
       <c r="O29" s="87">
         <f t="shared" si="6"/>
-        <v>60.81428571428571</v>
+        <v>70.95</v>
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>
-        <v>0.18945652173913044</v>
+        <v>0.17695431472081219</v>
       </c>
       <c r="Q29" s="23" t="e">
         <f>AVERAGE(Q28,Q17,Q23)</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90CE5632-2A4C-4039-B7DC-601F2EA04726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EADE0765-E87E-4D61-A4F4-1BC7E9A52210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3802,18 +3802,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.77777777777777779</v>
+        <v>0.81481481481481477</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" s="89">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="G2" s="117" t="s">
         <v>34</v>
@@ -3913,34 +3913,34 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>15+13+9+11+10+11+8+12+12+8+10+12+7+29+20+17</f>
-        <v>204</v>
+        <f>15+13+9+11+10+11+8+12+12+8+10+12+7+29+20+17+13</f>
+        <v>217</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.62769230769230766</v>
+        <v>0.6676923076923077</v>
       </c>
       <c r="K4" s="7">
         <v>450</v>
       </c>
       <c r="L4" s="8">
-        <v>259.95</v>
+        <v>273.95</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.57766666666666666</v>
+        <v>0.60877777777777775</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>190.05</v>
+        <v>176.05</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>31.675000000000001</v>
+        <v>35.21</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P16" si="2">L4/I4</f>
-        <v>1.2742647058823529</v>
+        <v>1.262442396313364</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3969,34 +3969,34 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <f>6+5+5+3+3+4+3+5+10+19+20+23+20+14+13+14</f>
-        <v>167</v>
+        <f>6+5+5+3+3+4+3+5+10+19+20+23+20+14+13+14+7</f>
+        <v>174</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J29" si="3">IFERROR(I5/G5,0)</f>
-        <v>0.70464135021097052</v>
+        <v>0.73417721518987344</v>
       </c>
       <c r="K5" s="11">
         <v>350</v>
       </c>
       <c r="L5" s="12">
-        <v>146.44999999999999</v>
+        <v>157.47499999999999</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M29" si="4">IFERROR(L5/K5,0)</f>
-        <v>0.41842857142857137</v>
+        <v>0.4499285714285714</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>203.55</v>
+        <v>192.52500000000001</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>33.925000000000004</v>
+        <v>38.505000000000003</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>0.87694610778443105</v>
+        <v>0.90502873563218389</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>53.445833333333333</v>
+        <v>64.135000000000005</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
@@ -4082,34 +4082,34 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>2+2+6+4+9+7+8+1+6+6+8+4+4+5+8</f>
-        <v>80</v>
+        <f>2+2+6+4+9+7+8+1+6+6+8+4+4+5+8+5</f>
+        <v>85</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>0.27777777777777779</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="K7" s="11">
         <v>250</v>
       </c>
       <c r="L7" s="12">
-        <v>121.325</v>
+        <v>129.85</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>0.48530000000000001</v>
+        <v>0.51939999999999997</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>128.67500000000001</v>
+        <v>120.15</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>21.445833333333336</v>
+        <v>24.03</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.5165625</v>
+        <v>1.5276470588235294</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
-        <v>20.333333333333332</v>
+        <v>24.4</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
@@ -4248,34 +4248,34 @@
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="12">
-        <f>28+9+9+5+6+4+3+5</f>
-        <v>69</v>
+        <f>28+9+9+5+6+4+3+5+2</f>
+        <v>71</v>
       </c>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>0.6216216216216216</v>
+        <v>0.63963963963963966</v>
       </c>
       <c r="K10" s="11">
         <v>2300</v>
       </c>
       <c r="L10" s="12">
-        <v>1655</v>
+        <v>1668</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>0.7195652173913043</v>
+        <v>0.72521739130434781</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>645</v>
+        <v>632</v>
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>107.5</v>
+        <v>126.4</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>23.985507246376812</v>
+        <v>23.492957746478872</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
@@ -4304,35 +4304,35 @@
       </c>
       <c r="H11" s="71"/>
       <c r="I11" s="12">
-        <f>82+12+14+10+10</f>
-        <v>128</v>
+        <f>82+12+14+10+10+12</f>
+        <v>140</v>
       </c>
       <c r="J11" s="69">
         <f t="shared" si="3"/>
-        <v>0.39751552795031053</v>
+        <v>0.43478260869565216</v>
       </c>
       <c r="K11" s="11">
         <v>450</v>
       </c>
       <c r="L11" s="12">
-        <f>106+16+15+38+16+18+9+16+11+14+12+8</f>
-        <v>279</v>
+        <f>106+16+15+38+16+18+9+16+11+14+12+8+14</f>
+        <v>293</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="4"/>
-        <v>0.62</v>
+        <v>0.65111111111111108</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="5"/>
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>28.5</v>
+        <v>31.4</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
-        <v>2.1796875</v>
+        <v>2.092857142857143</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="104"/>
@@ -4361,35 +4361,35 @@
       </c>
       <c r="H12" s="71"/>
       <c r="I12" s="12">
-        <f>80+8+10+8+12</f>
-        <v>118</v>
+        <f>80+8+10+8+12+15</f>
+        <v>133</v>
       </c>
       <c r="J12" s="69">
         <f t="shared" si="3"/>
-        <v>0.37942122186495175</v>
+        <v>0.42765273311897106</v>
       </c>
       <c r="K12" s="11">
         <v>300</v>
       </c>
       <c r="L12" s="12">
-        <f>100+8+8+6+8+8+6+8+11+8+12+23</f>
-        <v>206</v>
+        <f>100+8+8+6+8+8+6+8+11+8+12+23+15</f>
+        <v>221</v>
       </c>
       <c r="M12" s="70">
         <f t="shared" si="4"/>
-        <v>0.68666666666666665</v>
+        <v>0.73666666666666669</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="5"/>
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>15.666666666666666</v>
+        <v>15.8</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
-        <v>1.7457627118644068</v>
+        <v>1.6616541353383458</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="104"/>
@@ -4418,35 +4418,35 @@
       </c>
       <c r="H13" s="71"/>
       <c r="I13" s="12">
-        <f>68+10+4+5+8</f>
-        <v>95</v>
+        <f>68+10+4+5+8+8</f>
+        <v>103</v>
       </c>
       <c r="J13" s="69">
         <f t="shared" si="3"/>
-        <v>0.6785714285714286</v>
+        <v>0.73571428571428577</v>
       </c>
       <c r="K13" s="11">
         <v>250</v>
       </c>
       <c r="L13" s="12">
-        <f>50+10+10+4+5+5+3.5+8+4+10+5</f>
-        <v>114.5</v>
+        <f>50+10+10+4+5+5+3.5+8+4+10+5+8</f>
+        <v>122.5</v>
       </c>
       <c r="M13" s="70">
         <f t="shared" si="4"/>
-        <v>0.45800000000000002</v>
+        <v>0.49</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="5"/>
-        <v>135.5</v>
+        <v>127.5</v>
       </c>
       <c r="O13" s="14">
         <f t="shared" si="6"/>
-        <v>22.583333333333332</v>
+        <v>25.5</v>
       </c>
       <c r="P13" s="71">
         <f t="shared" si="2"/>
-        <v>1.2052631578947368</v>
+        <v>1.1893203883495145</v>
       </c>
       <c r="Q13" s="14"/>
       <c r="R13" s="104"/>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="O14" s="14">
         <f t="shared" si="6"/>
-        <v>1.6666666666666667</v>
+        <v>2</v>
       </c>
       <c r="P14" s="71">
         <f t="shared" si="2"/>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O15" s="14">
         <f t="shared" si="6"/>
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="P15" s="71">
         <f t="shared" si="2"/>
@@ -4633,11 +4633,11 @@
       </c>
       <c r="I17" s="41">
         <f>SUM(I4:I16)</f>
-        <v>976</v>
+        <v>1038</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>0.39149618933012437</v>
+        <v>0.41636582430806257</v>
       </c>
       <c r="K17" s="76">
         <f>SUM(K4:K16)</f>
@@ -4645,23 +4645,23 @@
       </c>
       <c r="L17" s="77">
         <f>SUM(L4:L16)</f>
-        <v>3104.55</v>
+        <v>3188.1</v>
       </c>
       <c r="M17" s="78">
         <f t="shared" si="4"/>
-        <v>0.58576415094339629</v>
+        <v>0.6015283018867924</v>
       </c>
       <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>2195.4499999999998</v>
+        <v>2111.9</v>
       </c>
       <c r="O17" s="79">
         <f t="shared" si="6"/>
-        <v>365.9083333333333</v>
+        <v>422.38</v>
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>3.1808913934426233</v>
+        <v>3.0713872832369939</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P18" s="96">
         <f t="shared" ref="P18:P22" si="7">L18/I18</f>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="O21" s="14">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="7"/>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="O22" s="94">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P22" s="74">
         <f t="shared" si="7"/>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="O23" s="79">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P23" s="80">
         <f>L23/I23</f>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P24" s="96">
         <f t="shared" ref="P24:P27" si="9">L24/I24</f>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="O26" s="14">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="9"/>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="O27" s="94">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P27" s="74">
         <f t="shared" si="9"/>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="O28" s="79">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P28" s="80">
         <f>L28/I28</f>
@@ -5304,11 +5304,11 @@
       </c>
       <c r="I29" s="21">
         <f t="shared" si="11"/>
-        <v>985</v>
+        <v>1047</v>
       </c>
       <c r="J29" s="83">
         <f t="shared" si="3"/>
-        <v>0.39368505195843323</v>
+        <v>0.41846522781774581</v>
       </c>
       <c r="K29" s="84">
         <v>600</v>
@@ -5326,11 +5326,11 @@
       </c>
       <c r="O29" s="87">
         <f t="shared" si="6"/>
-        <v>70.95</v>
+        <v>85.14</v>
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>
-        <v>0.17695431472081219</v>
+        <v>0.16647564469914042</v>
       </c>
       <c r="Q29" s="23" t="e">
         <f>AVERAGE(Q28,Q17,Q23)</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EADE0765-E87E-4D61-A4F4-1BC7E9A52210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20FC8C2C-C6E8-401D-893C-73F0CCA1B4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3802,18 +3802,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.81481481481481477</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2" s="89">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="G2" s="117" t="s">
         <v>34</v>
@@ -3913,34 +3913,34 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>15+13+9+11+10+11+8+12+12+8+10+12+7+29+20+17+13</f>
-        <v>217</v>
+        <f>15+13+9+11+10+11+8+12+12+8+10+12+7+29+20+17+13+11</f>
+        <v>228</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.6676923076923077</v>
+        <v>0.70153846153846156</v>
       </c>
       <c r="K4" s="7">
         <v>450</v>
       </c>
       <c r="L4" s="8">
-        <v>273.95</v>
+        <v>277.45</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.60877777777777775</v>
+        <v>0.61655555555555552</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>176.05</v>
+        <v>172.55</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>35.21</v>
+        <v>57.516666666666673</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P16" si="2">L4/I4</f>
-        <v>1.262442396313364</v>
+        <v>1.2168859649122807</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3969,34 +3969,34 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <f>6+5+5+3+3+4+3+5+10+19+20+23+20+14+13+14+7</f>
-        <v>174</v>
+        <f>6+5+5+3+3+4+3+5+10+19+20+23+20+14+13+14+7+16</f>
+        <v>190</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J29" si="3">IFERROR(I5/G5,0)</f>
-        <v>0.73417721518987344</v>
+        <v>0.80168776371308015</v>
       </c>
       <c r="K5" s="11">
         <v>350</v>
       </c>
       <c r="L5" s="12">
-        <v>157.47499999999999</v>
+        <v>170.42500000000001</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M29" si="4">IFERROR(L5/K5,0)</f>
-        <v>0.4499285714285714</v>
+        <v>0.48692857142857149</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>192.52500000000001</v>
+        <v>179.57499999999999</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>38.505000000000003</v>
+        <v>59.858333333333327</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>0.90502873563218389</v>
+        <v>0.89697368421052637</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>64.135000000000005</v>
+        <v>106.89166666666667</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
@@ -4082,34 +4082,34 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>2+2+6+4+9+7+8+1+6+6+8+4+4+5+8+5</f>
-        <v>85</v>
+        <f>2+2+6+4+9+7+8+1+6+6+8+4+4+5+8+5+6</f>
+        <v>91</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>0.2951388888888889</v>
+        <v>0.31597222222222221</v>
       </c>
       <c r="K7" s="11">
         <v>250</v>
       </c>
       <c r="L7" s="12">
-        <v>129.85</v>
+        <v>137.22499999999999</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>0.51939999999999997</v>
+        <v>0.54889999999999994</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>120.15</v>
+        <v>112.77500000000001</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>24.03</v>
+        <v>37.591666666666669</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.5276470588235294</v>
+        <v>1.5079670329670329</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4138,34 +4138,34 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <f>3+6+7+6+6+3+5+8+6+4+6+10+10+9+5</f>
-        <v>94</v>
+        <f>3+6+7+6+6+3+5+8+6+4+6+10+10+9+5+4</f>
+        <v>98</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>0.26330532212885155</v>
+        <v>0.27450980392156865</v>
       </c>
       <c r="K8" s="11">
         <v>250</v>
       </c>
       <c r="L8" s="12">
-        <v>128</v>
+        <v>130.15</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>0.51200000000000001</v>
+        <v>0.52060000000000006</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N29" si="5">K8-L8</f>
-        <v>122</v>
+        <v>119.85</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
-        <v>24.4</v>
+        <v>39.949999999999996</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.3617021276595744</v>
+        <v>1.328061224489796</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4248,34 +4248,34 @@
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="12">
-        <f>28+9+9+5+6+4+3+5+2</f>
-        <v>71</v>
+        <f>28+9+9+5+6+4+3+5+2+5</f>
+        <v>76</v>
       </c>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>0.63963963963963966</v>
+        <v>0.68468468468468469</v>
       </c>
       <c r="K10" s="11">
         <v>2300</v>
       </c>
       <c r="L10" s="12">
-        <v>1668</v>
+        <v>1752</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>0.72521739130434781</v>
+        <v>0.76173913043478259</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>632</v>
+        <v>548</v>
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>126.4</v>
+        <v>182.66666666666666</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>23.492957746478872</v>
+        <v>23.05263157894737</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
@@ -4304,35 +4304,35 @@
       </c>
       <c r="H11" s="71"/>
       <c r="I11" s="12">
-        <f>82+12+14+10+10+12</f>
-        <v>140</v>
+        <f>82+12+14+10+10+12+12</f>
+        <v>152</v>
       </c>
       <c r="J11" s="69">
         <f t="shared" si="3"/>
-        <v>0.43478260869565216</v>
+        <v>0.47204968944099379</v>
       </c>
       <c r="K11" s="11">
         <v>450</v>
       </c>
       <c r="L11" s="12">
-        <f>106+16+15+38+16+18+9+16+11+14+12+8+14</f>
-        <v>293</v>
+        <f>106+16+15+38+16+18+9+16+11+14+12+8+14+15</f>
+        <v>308</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="4"/>
-        <v>0.65111111111111108</v>
+        <v>0.68444444444444441</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="5"/>
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>31.4</v>
+        <v>47.333333333333336</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
-        <v>2.092857142857143</v>
+        <v>2.0263157894736841</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="104"/>
@@ -4361,35 +4361,35 @@
       </c>
       <c r="H12" s="71"/>
       <c r="I12" s="12">
-        <f>80+8+10+8+12+15</f>
-        <v>133</v>
+        <f>80+8+10+8+12+15+10</f>
+        <v>143</v>
       </c>
       <c r="J12" s="69">
         <f t="shared" si="3"/>
-        <v>0.42765273311897106</v>
+        <v>0.45980707395498394</v>
       </c>
       <c r="K12" s="11">
         <v>300</v>
       </c>
       <c r="L12" s="12">
-        <f>100+8+8+6+8+8+6+8+11+8+12+23+15</f>
-        <v>221</v>
+        <f>100+8+8+6+8+8+6+8+11+8+12+23+15+12</f>
+        <v>233</v>
       </c>
       <c r="M12" s="70">
         <f t="shared" si="4"/>
-        <v>0.73666666666666669</v>
+        <v>0.77666666666666662</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="5"/>
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>15.8</v>
+        <v>22.333333333333332</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
-        <v>1.6616541353383458</v>
+        <v>1.6293706293706294</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="104"/>
@@ -4418,35 +4418,35 @@
       </c>
       <c r="H13" s="71"/>
       <c r="I13" s="12">
-        <f>68+10+4+5+8+8</f>
-        <v>103</v>
+        <f>68+10+4+5+8+8+4</f>
+        <v>107</v>
       </c>
       <c r="J13" s="69">
         <f t="shared" si="3"/>
-        <v>0.73571428571428577</v>
+        <v>0.76428571428571423</v>
       </c>
       <c r="K13" s="11">
         <v>250</v>
       </c>
       <c r="L13" s="12">
-        <f>50+10+10+4+5+5+3.5+8+4+10+5+8</f>
-        <v>122.5</v>
+        <f>50+10+10+4+5+5+3.5+8+4+10+5+8+4</f>
+        <v>126.5</v>
       </c>
       <c r="M13" s="70">
         <f t="shared" si="4"/>
-        <v>0.49</v>
+        <v>0.50600000000000001</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="5"/>
-        <v>127.5</v>
+        <v>123.5</v>
       </c>
       <c r="O13" s="14">
         <f t="shared" si="6"/>
-        <v>25.5</v>
+        <v>41.166666666666664</v>
       </c>
       <c r="P13" s="71">
         <f t="shared" si="2"/>
-        <v>1.1893203883495145</v>
+        <v>1.1822429906542056</v>
       </c>
       <c r="Q13" s="14"/>
       <c r="R13" s="104"/>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="O14" s="14">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3.3333333333333335</v>
       </c>
       <c r="P14" s="71">
         <f t="shared" si="2"/>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O15" s="14">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>8.3333333333333339</v>
       </c>
       <c r="P15" s="71">
         <f t="shared" si="2"/>
@@ -4633,11 +4633,11 @@
       </c>
       <c r="I17" s="41">
         <f>SUM(I4:I16)</f>
-        <v>1038</v>
+        <v>1106</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>0.41636582430806257</v>
+        <v>0.44364219815483352</v>
       </c>
       <c r="K17" s="76">
         <f>SUM(K4:K16)</f>
@@ -4645,23 +4645,23 @@
       </c>
       <c r="L17" s="77">
         <f>SUM(L4:L16)</f>
-        <v>3188.1</v>
+        <v>3329.0749999999998</v>
       </c>
       <c r="M17" s="78">
         <f t="shared" si="4"/>
-        <v>0.6015283018867924</v>
+        <v>0.628127358490566</v>
       </c>
       <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>2111.9</v>
+        <v>1970.9250000000002</v>
       </c>
       <c r="O17" s="79">
         <f t="shared" si="6"/>
-        <v>422.38</v>
+        <v>656.97500000000002</v>
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>3.0713872832369939</v>
+        <v>3.0100135623869799</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>141.9</v>
       </c>
       <c r="P18" s="96">
         <f t="shared" ref="P18:P22" si="7">L18/I18</f>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>141.9</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>141.9</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="O21" s="14">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>141.9</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="7"/>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="O22" s="94">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>141.9</v>
       </c>
       <c r="P22" s="74">
         <f t="shared" si="7"/>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="O23" s="79">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>141.9</v>
       </c>
       <c r="P23" s="80">
         <f>L23/I23</f>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>141.9</v>
       </c>
       <c r="P24" s="96">
         <f t="shared" ref="P24:P27" si="9">L24/I24</f>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>141.9</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="O26" s="14">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>141.9</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="9"/>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="O27" s="94">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>141.9</v>
       </c>
       <c r="P27" s="74">
         <f t="shared" si="9"/>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="O28" s="79">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>141.9</v>
       </c>
       <c r="P28" s="80">
         <f>L28/I28</f>
@@ -5304,11 +5304,11 @@
       </c>
       <c r="I29" s="21">
         <f t="shared" si="11"/>
-        <v>1047</v>
+        <v>1115</v>
       </c>
       <c r="J29" s="83">
         <f t="shared" si="3"/>
-        <v>0.41846522781774581</v>
+        <v>0.44564348521183056</v>
       </c>
       <c r="K29" s="84">
         <v>600</v>
@@ -5326,11 +5326,11 @@
       </c>
       <c r="O29" s="87">
         <f t="shared" si="6"/>
-        <v>85.14</v>
+        <v>141.9</v>
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>
-        <v>0.16647564469914042</v>
+        <v>0.15632286995515696</v>
       </c>
       <c r="Q29" s="23" t="e">
         <f>AVERAGE(Q28,Q17,Q23)</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20FC8C2C-C6E8-401D-893C-73F0CCA1B4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2951B154-0505-463F-8BFA-E01145AC9D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3802,18 +3802,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.88888888888888884</v>
+        <v>0.96296296296296291</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" s="89">
-        <v>46322</v>
+        <v>46324</v>
       </c>
       <c r="G2" s="117" t="s">
         <v>34</v>
@@ -3913,34 +3913,34 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>15+13+9+11+10+11+8+12+12+8+10+12+7+29+20+17+13+11</f>
-        <v>228</v>
+        <f>15+13+9+11+10+11+8+12+12+8+10+12+7+29+20+17+13+11+8+14</f>
+        <v>250</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.70153846153846156</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="K4" s="7">
         <v>450</v>
       </c>
       <c r="L4" s="8">
-        <v>277.45</v>
+        <v>306.2</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.61655555555555552</v>
+        <v>0.68044444444444441</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>172.55</v>
+        <v>143.80000000000001</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>57.516666666666673</v>
+        <v>143.80000000000001</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P16" si="2">L4/I4</f>
-        <v>1.2168859649122807</v>
+        <v>1.2247999999999999</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3969,34 +3969,34 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <f>6+5+5+3+3+4+3+5+10+19+20+23+20+14+13+14+7+16</f>
-        <v>190</v>
+        <f>6+5+5+3+3+4+3+5+10+19+20+23+20+14+13+14+7+16+22+15</f>
+        <v>227</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J29" si="3">IFERROR(I5/G5,0)</f>
-        <v>0.80168776371308015</v>
+        <v>0.95780590717299574</v>
       </c>
       <c r="K5" s="11">
         <v>350</v>
       </c>
       <c r="L5" s="12">
-        <v>170.42500000000001</v>
+        <v>191.25</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M29" si="4">IFERROR(L5/K5,0)</f>
-        <v>0.48692857142857149</v>
+        <v>0.54642857142857137</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>179.57499999999999</v>
+        <v>158.75</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="1"/>
-        <v>59.858333333333327</v>
+        <v>158.75</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>0.89697368421052637</v>
+        <v>0.84251101321585908</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="O6" s="14">
         <f t="shared" si="1"/>
-        <v>106.89166666666667</v>
+        <v>320.67500000000001</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
@@ -4082,34 +4082,34 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>2+2+6+4+9+7+8+1+6+6+8+4+4+5+8+5+6</f>
-        <v>91</v>
+        <f>2+2+6+4+9+7+8+1+6+6+8+4+4+5+8+5+6+5+2</f>
+        <v>98</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>0.31597222222222221</v>
+        <v>0.34027777777777779</v>
       </c>
       <c r="K7" s="11">
         <v>250</v>
       </c>
       <c r="L7" s="12">
-        <v>137.22499999999999</v>
+        <v>146.02500000000001</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>0.54889999999999994</v>
+        <v>0.58410000000000006</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>112.77500000000001</v>
+        <v>103.97499999999999</v>
       </c>
       <c r="O7" s="14">
         <f t="shared" si="1"/>
-        <v>37.591666666666669</v>
+        <v>103.97499999999999</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.5079670329670329</v>
+        <v>1.4900510204081634</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4138,34 +4138,34 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <f>3+6+7+6+6+3+5+8+6+4+6+10+10+9+5+4</f>
-        <v>98</v>
+        <f>3+6+7+6+6+3+5+8+6+4+6+10+10+9+5+4+7+7</f>
+        <v>112</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>0.27450980392156865</v>
+        <v>0.31372549019607843</v>
       </c>
       <c r="K8" s="11">
         <v>250</v>
       </c>
       <c r="L8" s="12">
-        <v>130.15</v>
+        <v>139.4</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>0.52060000000000006</v>
+        <v>0.55759999999999998</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N29" si="5">K8-L8</f>
-        <v>119.85</v>
+        <v>110.6</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
-        <v>39.949999999999996</v>
+        <v>110.6</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.328061224489796</v>
+        <v>1.2446428571428572</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4248,34 +4248,34 @@
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="12">
-        <f>28+9+9+5+6+4+3+5+2+5</f>
-        <v>76</v>
+        <f>28+9+9+5+6+4+3+5+2+5+3+2</f>
+        <v>81</v>
       </c>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>0.68468468468468469</v>
+        <v>0.72972972972972971</v>
       </c>
       <c r="K10" s="11">
         <v>2300</v>
       </c>
       <c r="L10" s="12">
-        <v>1752</v>
+        <v>1819</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>0.76173913043478259</v>
+        <v>0.79086956521739127</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>548</v>
+        <v>481</v>
       </c>
       <c r="O10" s="14">
         <f t="shared" si="6"/>
-        <v>182.66666666666666</v>
+        <v>481</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>23.05263157894737</v>
+        <v>22.456790123456791</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
@@ -4315,24 +4315,24 @@
         <v>450</v>
       </c>
       <c r="L11" s="12">
-        <f>106+16+15+38+16+18+9+16+11+14+12+8+14+15</f>
-        <v>308</v>
+        <f>106+16+15+38+16+18+9+16+11+14+12+8+14+15+10+12</f>
+        <v>330</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="4"/>
-        <v>0.68444444444444441</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="5"/>
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="O11" s="14">
         <f t="shared" si="6"/>
-        <v>47.333333333333336</v>
+        <v>120</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
-        <v>2.0263157894736841</v>
+        <v>2.1710526315789473</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="104"/>
@@ -4372,24 +4372,24 @@
         <v>300</v>
       </c>
       <c r="L12" s="12">
-        <f>100+8+8+6+8+8+6+8+11+8+12+23+15+12</f>
-        <v>233</v>
+        <f>100+8+8+6+8+8+6+8+11+8+12+23+15+12+8+15</f>
+        <v>256</v>
       </c>
       <c r="M12" s="70">
         <f t="shared" si="4"/>
-        <v>0.77666666666666662</v>
+        <v>0.85333333333333339</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="5"/>
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="O12" s="14">
         <f t="shared" si="6"/>
-        <v>22.333333333333332</v>
+        <v>44</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
-        <v>1.6293706293706294</v>
+        <v>1.7902097902097902</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="104"/>
@@ -4429,24 +4429,24 @@
         <v>250</v>
       </c>
       <c r="L13" s="12">
-        <f>50+10+10+4+5+5+3.5+8+4+10+5+8+4</f>
-        <v>126.5</v>
+        <f>50+10+10+4+5+5+3.5+8+4+10+5+8+4+4+3</f>
+        <v>133.5</v>
       </c>
       <c r="M13" s="70">
         <f t="shared" si="4"/>
-        <v>0.50600000000000001</v>
+        <v>0.53400000000000003</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="5"/>
-        <v>123.5</v>
+        <v>116.5</v>
       </c>
       <c r="O13" s="14">
         <f t="shared" si="6"/>
-        <v>41.166666666666664</v>
+        <v>116.5</v>
       </c>
       <c r="P13" s="71">
         <f t="shared" si="2"/>
-        <v>1.1822429906542056</v>
+        <v>1.2476635514018692</v>
       </c>
       <c r="Q13" s="14"/>
       <c r="R13" s="104"/>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="O14" s="14">
         <f t="shared" si="6"/>
-        <v>3.3333333333333335</v>
+        <v>10</v>
       </c>
       <c r="P14" s="71">
         <f t="shared" si="2"/>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O15" s="14">
         <f t="shared" si="6"/>
-        <v>8.3333333333333339</v>
+        <v>25</v>
       </c>
       <c r="P15" s="71">
         <f t="shared" si="2"/>
@@ -4582,7 +4582,9 @@
       </c>
       <c r="G16" s="11"/>
       <c r="H16" s="71"/>
-      <c r="I16" s="12"/>
+      <c r="I16" s="12">
+        <v>1</v>
+      </c>
       <c r="J16" s="69">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4601,9 +4603,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P16" s="71" t="e">
+      <c r="P16" s="71">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="14"/>
       <c r="R16" s="34"/>
@@ -4633,11 +4635,11 @@
       </c>
       <c r="I17" s="41">
         <f>SUM(I4:I16)</f>
-        <v>1106</v>
+        <v>1192</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>0.44364219815483352</v>
+        <v>0.47813878860810266</v>
       </c>
       <c r="K17" s="76">
         <f>SUM(K4:K16)</f>
@@ -4645,23 +4647,23 @@
       </c>
       <c r="L17" s="77">
         <f>SUM(L4:L16)</f>
-        <v>3329.0749999999998</v>
+        <v>3515.7</v>
       </c>
       <c r="M17" s="78">
         <f t="shared" si="4"/>
-        <v>0.628127358490566</v>
+        <v>0.66333962264150936</v>
       </c>
       <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>1970.9250000000002</v>
+        <v>1784.3000000000002</v>
       </c>
       <c r="O17" s="79">
         <f t="shared" si="6"/>
-        <v>656.97500000000002</v>
+        <v>1784.3000000000002</v>
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>3.0100135623869799</v>
+        <v>2.9494127516778521</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -4715,7 +4717,7 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="6"/>
-        <v>141.9</v>
+        <v>425.7</v>
       </c>
       <c r="P18" s="96">
         <f t="shared" ref="P18:P22" si="7">L18/I18</f>
@@ -4770,7 +4772,7 @@
       </c>
       <c r="O19" s="14">
         <f t="shared" si="6"/>
-        <v>141.9</v>
+        <v>425.7</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4825,7 +4827,7 @@
       </c>
       <c r="O20" s="14">
         <f t="shared" si="6"/>
-        <v>141.9</v>
+        <v>425.7</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4880,7 +4882,7 @@
       </c>
       <c r="O21" s="14">
         <f t="shared" si="6"/>
-        <v>141.9</v>
+        <v>425.7</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="7"/>
@@ -4935,7 +4937,7 @@
       </c>
       <c r="O22" s="94">
         <f t="shared" si="6"/>
-        <v>141.9</v>
+        <v>425.7</v>
       </c>
       <c r="P22" s="74">
         <f t="shared" si="7"/>
@@ -4993,7 +4995,7 @@
       </c>
       <c r="O23" s="79">
         <f t="shared" si="6"/>
-        <v>141.9</v>
+        <v>425.7</v>
       </c>
       <c r="P23" s="80">
         <f>L23/I23</f>
@@ -5051,7 +5053,7 @@
       </c>
       <c r="O24" s="10">
         <f t="shared" si="6"/>
-        <v>141.9</v>
+        <v>425.7</v>
       </c>
       <c r="P24" s="96">
         <f t="shared" ref="P24:P27" si="9">L24/I24</f>
@@ -5106,7 +5108,7 @@
       </c>
       <c r="O25" s="14">
         <f t="shared" si="6"/>
-        <v>141.9</v>
+        <v>425.7</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5161,7 +5163,7 @@
       </c>
       <c r="O26" s="14">
         <f t="shared" si="6"/>
-        <v>141.9</v>
+        <v>425.7</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="9"/>
@@ -5216,7 +5218,7 @@
       </c>
       <c r="O27" s="94">
         <f t="shared" si="6"/>
-        <v>141.9</v>
+        <v>425.7</v>
       </c>
       <c r="P27" s="74">
         <f t="shared" si="9"/>
@@ -5271,7 +5273,7 @@
       </c>
       <c r="O28" s="79">
         <f t="shared" si="6"/>
-        <v>141.9</v>
+        <v>425.7</v>
       </c>
       <c r="P28" s="80">
         <f>L28/I28</f>
@@ -5304,11 +5306,11 @@
       </c>
       <c r="I29" s="21">
         <f t="shared" si="11"/>
-        <v>1115</v>
+        <v>1201</v>
       </c>
       <c r="J29" s="83">
         <f t="shared" si="3"/>
-        <v>0.44564348521183056</v>
+        <v>0.48001598721023181</v>
       </c>
       <c r="K29" s="84">
         <v>600</v>
@@ -5326,11 +5328,11 @@
       </c>
       <c r="O29" s="87">
         <f t="shared" si="6"/>
-        <v>141.9</v>
+        <v>425.7</v>
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>
-        <v>0.15632286995515696</v>
+        <v>0.14512905911740218</v>
       </c>
       <c r="Q29" s="23" t="e">
         <f>AVERAGE(Q28,Q17,Q23)</f>

--- a/OCT_2026/Reports/Sales Reporting Depricated.xlsx
+++ b/OCT_2026/Reports/Sales Reporting Depricated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2951B154-0505-463F-8BFA-E01145AC9D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB167B5-5A89-44A2-847E-95D846DB369B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3802,18 +3802,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" s="62">
         <f>+B2/A2</f>
-        <v>0.96296296296296291</v>
+        <v>1</v>
       </c>
       <c r="D2" s="91">
         <f>+A2-B2</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="89">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="G2" s="117" t="s">
         <v>34</v>
@@ -3913,34 +3913,34 @@
       </c>
       <c r="H4" s="68"/>
       <c r="I4" s="31">
-        <f>15+13+9+11+10+11+8+12+12+8+10+12+7+29+20+17+13+11+8+14</f>
-        <v>250</v>
+        <f>15+13+9+11+10+11+8+12+12+8+10+12+7+29+20+17+13+11+8+14+27</f>
+        <v>277</v>
       </c>
       <c r="J4" s="67">
         <f>IFERROR(I4/G4,0)</f>
-        <v>0.76923076923076927</v>
+        <v>0.85230769230769232</v>
       </c>
       <c r="K4" s="7">
         <v>450</v>
       </c>
       <c r="L4" s="8">
-        <v>306.2</v>
+        <v>326</v>
       </c>
       <c r="M4" s="82">
         <f>IFERROR(L4/K4,0)</f>
-        <v>0.68044444444444441</v>
+        <v>0.72444444444444445</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" ref="N4:N7" si="0">K4-L4</f>
-        <v>143.80000000000001</v>
-      </c>
-      <c r="O4" s="10">
+        <v>124</v>
+      </c>
+      <c r="O4" s="10" t="e">
         <f t="shared" ref="O4:O7" si="1">N4/$D$2</f>
-        <v>143.80000000000001</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ref="P4:P16" si="2">L4/I4</f>
-        <v>1.2247999999999999</v>
+        <v>1.1768953068592058</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="34"/>
@@ -3969,34 +3969,34 @@
       </c>
       <c r="H5" s="71"/>
       <c r="I5" s="12">
-        <f>6+5+5+3+3+4+3+5+10+19+20+23+20+14+13+14+7+16+22+15</f>
-        <v>227</v>
+        <f>6+5+5+3+3+4+3+5+10+19+20+23+20+14+13+14+7+16+22+15+6</f>
+        <v>233</v>
       </c>
       <c r="J5" s="69">
         <f t="shared" ref="J5:J29" si="3">IFERROR(I5/G5,0)</f>
-        <v>0.95780590717299574</v>
+        <v>0.9831223628691983</v>
       </c>
       <c r="K5" s="11">
         <v>350</v>
       </c>
       <c r="L5" s="12">
-        <v>191.25</v>
+        <v>196.45</v>
       </c>
       <c r="M5" s="70">
         <f t="shared" ref="M5:M29" si="4">IFERROR(L5/K5,0)</f>
-        <v>0.54642857142857137</v>
+        <v>0.56128571428571428</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
-        <v>158.75</v>
-      </c>
-      <c r="O5" s="14">
+        <v>153.55000000000001</v>
+      </c>
+      <c r="O5" s="14" t="e">
         <f t="shared" si="1"/>
-        <v>158.75</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P5" s="71">
         <f t="shared" si="2"/>
-        <v>0.84251101321585908</v>
+        <v>0.84313304721030036</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="34"/>
@@ -4045,9 +4045,9 @@
         <f t="shared" si="0"/>
         <v>320.67500000000001</v>
       </c>
-      <c r="O6" s="14">
+      <c r="O6" s="14" t="e">
         <f t="shared" si="1"/>
-        <v>320.67500000000001</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" si="2"/>
@@ -4082,34 +4082,34 @@
       </c>
       <c r="H7" s="71"/>
       <c r="I7" s="12">
-        <f>2+2+6+4+9+7+8+1+6+6+8+4+4+5+8+5+6+5+2</f>
-        <v>98</v>
+        <f>2+2+6+4+9+7+8+1+6+6+8+4+4+5+8+5+6+5+2+4</f>
+        <v>102</v>
       </c>
       <c r="J7" s="69">
         <f t="shared" si="3"/>
-        <v>0.34027777777777779</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="K7" s="11">
         <v>250</v>
       </c>
       <c r="L7" s="12">
-        <v>146.02500000000001</v>
+        <v>155.02500000000001</v>
       </c>
       <c r="M7" s="70">
         <f t="shared" si="4"/>
-        <v>0.58410000000000006</v>
+        <v>0.62009999999999998</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>103.97499999999999</v>
-      </c>
-      <c r="O7" s="14">
+        <v>94.974999999999994</v>
+      </c>
+      <c r="O7" s="14" t="e">
         <f t="shared" si="1"/>
-        <v>103.97499999999999</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="2"/>
-        <v>1.4900510204081634</v>
+        <v>1.5198529411764707</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="34"/>
@@ -4138,34 +4138,34 @@
       </c>
       <c r="H8" s="71"/>
       <c r="I8" s="12">
-        <f>3+6+7+6+6+3+5+8+6+4+6+10+10+9+5+4+7+7</f>
-        <v>112</v>
+        <f>3+6+7+6+6+3+5+8+6+4+6+10+10+9+5+4+7+7+10</f>
+        <v>122</v>
       </c>
       <c r="J8" s="69">
         <f t="shared" si="3"/>
-        <v>0.31372549019607843</v>
+        <v>0.34173669467787116</v>
       </c>
       <c r="K8" s="11">
         <v>250</v>
       </c>
       <c r="L8" s="12">
-        <v>139.4</v>
+        <v>144.15</v>
       </c>
       <c r="M8" s="70">
         <f t="shared" si="4"/>
-        <v>0.55759999999999998</v>
+        <v>0.5766</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N29" si="5">K8-L8</f>
-        <v>110.6</v>
-      </c>
-      <c r="O8" s="14">
+        <v>105.85</v>
+      </c>
+      <c r="O8" s="14" t="e">
         <f t="shared" ref="O8:O29" si="6">N8/$D$2</f>
-        <v>110.6</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="2"/>
-        <v>1.2446428571428572</v>
+        <v>1.1815573770491803</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="34"/>
@@ -4213,9 +4213,9 @@
       <c r="N9" s="12">
         <v>0</v>
       </c>
-      <c r="O9" s="14">
+      <c r="O9" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P9" s="71" t="e">
         <f t="shared" si="2"/>
@@ -4248,34 +4248,34 @@
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="12">
-        <f>28+9+9+5+6+4+3+5+2+5+3+2</f>
-        <v>81</v>
+        <f>28+9+9+5+6+4+3+5+2+5+3+2+12</f>
+        <v>93</v>
       </c>
       <c r="J10" s="69">
         <f t="shared" si="3"/>
-        <v>0.72972972972972971</v>
+        <v>0.83783783783783783</v>
       </c>
       <c r="K10" s="11">
         <v>2300</v>
       </c>
       <c r="L10" s="12">
-        <v>1819</v>
+        <v>1896</v>
       </c>
       <c r="M10" s="70">
         <f t="shared" si="4"/>
-        <v>0.79086956521739127</v>
+        <v>0.82434782608695656</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="5"/>
-        <v>481</v>
-      </c>
-      <c r="O10" s="14">
+        <v>404</v>
+      </c>
+      <c r="O10" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>481</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="2"/>
-        <v>22.456790123456791</v>
+        <v>20.387096774193548</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="34"/>
@@ -4304,35 +4304,35 @@
       </c>
       <c r="H11" s="71"/>
       <c r="I11" s="12">
-        <f>82+12+14+10+10+12+12</f>
-        <v>152</v>
+        <f>82+12+14+10+10+12+12+14</f>
+        <v>166</v>
       </c>
       <c r="J11" s="69">
         <f t="shared" si="3"/>
-        <v>0.47204968944099379</v>
+        <v>0.51552795031055898</v>
       </c>
       <c r="K11" s="11">
         <v>450</v>
       </c>
       <c r="L11" s="12">
-        <f>106+16+15+38+16+18+9+16+11+14+12+8+14+15+10+12</f>
-        <v>330</v>
+        <f>106+16+15+38+16+18+9+16+11+14+12+8+14+15+10+12+14</f>
+        <v>344</v>
       </c>
       <c r="M11" s="70">
         <f t="shared" si="4"/>
-        <v>0.73333333333333328</v>
+        <v>0.76444444444444448</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="5"/>
-        <v>120</v>
-      </c>
-      <c r="O11" s="14">
+        <v>106</v>
+      </c>
+      <c r="O11" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="2"/>
-        <v>2.1710526315789473</v>
+        <v>2.072289156626506</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="104"/>
@@ -4361,35 +4361,35 @@
       </c>
       <c r="H12" s="71"/>
       <c r="I12" s="12">
-        <f>80+8+10+8+12+15+10</f>
-        <v>143</v>
+        <f>80+8+10+8+12+15+10+12</f>
+        <v>155</v>
       </c>
       <c r="J12" s="69">
         <f t="shared" si="3"/>
-        <v>0.45980707395498394</v>
+        <v>0.49839228295819937</v>
       </c>
       <c r="K12" s="11">
         <v>300</v>
       </c>
       <c r="L12" s="12">
-        <f>100+8+8+6+8+8+6+8+11+8+12+23+15+12+8+15</f>
-        <v>256</v>
+        <f>100+8+8+6+8+8+6+8+11+8+12+23+15+12+8+15+12</f>
+        <v>268</v>
       </c>
       <c r="M12" s="70">
         <f t="shared" si="4"/>
-        <v>0.85333333333333339</v>
+        <v>0.89333333333333331</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="5"/>
-        <v>44</v>
-      </c>
-      <c r="O12" s="14">
+        <v>32</v>
+      </c>
+      <c r="O12" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>44</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="2"/>
-        <v>1.7902097902097902</v>
+        <v>1.7290322580645161</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="104"/>
@@ -4418,35 +4418,35 @@
       </c>
       <c r="H13" s="71"/>
       <c r="I13" s="12">
-        <f>68+10+4+5+8+8+4</f>
-        <v>107</v>
+        <f>68+10+4+5+8+8+4+4</f>
+        <v>111</v>
       </c>
       <c r="J13" s="69">
         <f t="shared" si="3"/>
-        <v>0.76428571428571423</v>
+        <v>0.79285714285714282</v>
       </c>
       <c r="K13" s="11">
         <v>250</v>
       </c>
       <c r="L13" s="12">
-        <f>50+10+10+4+5+5+3.5+8+4+10+5+8+4+4+3</f>
-        <v>133.5</v>
+        <f>50+10+10+4+5+5+3.5+8+4+10+5+8+4+4+3+8</f>
+        <v>141.5</v>
       </c>
       <c r="M13" s="70">
         <f t="shared" si="4"/>
-        <v>0.53400000000000003</v>
+        <v>0.56599999999999995</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="5"/>
-        <v>116.5</v>
-      </c>
-      <c r="O13" s="14">
+        <v>108.5</v>
+      </c>
+      <c r="O13" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>116.5</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P13" s="71">
         <f t="shared" si="2"/>
-        <v>1.2476635514018692</v>
+        <v>1.2747747747747749</v>
       </c>
       <c r="Q13" s="14"/>
       <c r="R13" s="104"/>
@@ -4495,9 +4495,9 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="O14" s="14">
+      <c r="O14" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P14" s="71">
         <f t="shared" si="2"/>
@@ -4550,9 +4550,9 @@
         <f t="shared" si="5"/>
         <v>25</v>
       </c>
-      <c r="O15" s="14">
+      <c r="O15" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P15" s="71">
         <f t="shared" si="2"/>
@@ -4599,9 +4599,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O16" s="14">
+      <c r="O16" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P16" s="71">
         <f t="shared" si="2"/>
@@ -4635,11 +4635,11 @@
       </c>
       <c r="I17" s="41">
         <f>SUM(I4:I16)</f>
-        <v>1192</v>
+        <v>1281</v>
       </c>
       <c r="J17" s="75">
         <f t="shared" si="3"/>
-        <v>0.47813878860810266</v>
+        <v>0.51383874849578826</v>
       </c>
       <c r="K17" s="76">
         <f>SUM(K4:K16)</f>
@@ -4647,23 +4647,23 @@
       </c>
       <c r="L17" s="77">
         <f>SUM(L4:L16)</f>
-        <v>3515.7</v>
+        <v>3665.45</v>
       </c>
       <c r="M17" s="78">
         <f t="shared" si="4"/>
-        <v>0.66333962264150936</v>
+        <v>0.6915943396226415</v>
       </c>
       <c r="N17" s="77">
         <f t="shared" si="5"/>
-        <v>1784.3000000000002</v>
-      </c>
-      <c r="O17" s="79">
+        <v>1634.5500000000002</v>
+      </c>
+      <c r="O17" s="79" t="e">
         <f t="shared" si="6"/>
-        <v>1784.3000000000002</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P17" s="80">
         <f>L17/I17</f>
-        <v>2.9494127516778521</v>
+        <v>2.8613973458235753</v>
       </c>
       <c r="Q17" s="43" t="e">
         <f>AVERAGE(Q4:Q16)</f>
@@ -4715,9 +4715,9 @@
         <f t="shared" si="5"/>
         <v>425.7</v>
       </c>
-      <c r="O18" s="10">
+      <c r="O18" s="10" t="e">
         <f t="shared" si="6"/>
-        <v>425.7</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P18" s="96">
         <f t="shared" ref="P18:P22" si="7">L18/I18</f>
@@ -4770,9 +4770,9 @@
         <f t="shared" si="5"/>
         <v>425.7</v>
       </c>
-      <c r="O19" s="14">
+      <c r="O19" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>425.7</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="7"/>
@@ -4825,9 +4825,9 @@
         <f t="shared" si="5"/>
         <v>425.7</v>
       </c>
-      <c r="O20" s="14">
+      <c r="O20" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>425.7</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="7"/>
@@ -4880,9 +4880,9 @@
         <f t="shared" si="5"/>
         <v>425.7</v>
       </c>
-      <c r="O21" s="14">
+      <c r="O21" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>425.7</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="7"/>
@@ -4935,9 +4935,9 @@
         <f t="shared" si="5"/>
         <v>425.7</v>
       </c>
-      <c r="O22" s="94">
+      <c r="O22" s="94" t="e">
         <f t="shared" si="6"/>
-        <v>425.7</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P22" s="74">
         <f t="shared" si="7"/>
@@ -4993,9 +4993,9 @@
         <f t="shared" si="5"/>
         <v>425.7</v>
       </c>
-      <c r="O23" s="79">
+      <c r="O23" s="79" t="e">
         <f t="shared" si="6"/>
-        <v>425.7</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P23" s="80">
         <f>L23/I23</f>
@@ -5051,9 +5051,9 @@
         <f t="shared" si="5"/>
         <v>425.7</v>
       </c>
-      <c r="O24" s="10">
+      <c r="O24" s="10" t="e">
         <f t="shared" si="6"/>
-        <v>425.7</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P24" s="96">
         <f t="shared" ref="P24:P27" si="9">L24/I24</f>
@@ -5106,9 +5106,9 @@
         <f t="shared" si="5"/>
         <v>425.7</v>
       </c>
-      <c r="O25" s="14">
+      <c r="O25" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>425.7</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="9"/>
@@ -5161,9 +5161,9 @@
         <f t="shared" si="5"/>
         <v>425.7</v>
       </c>
-      <c r="O26" s="14">
+      <c r="O26" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>425.7</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="9"/>
@@ -5216,9 +5216,9 @@
         <f t="shared" si="5"/>
         <v>425.7</v>
       </c>
-      <c r="O27" s="94">
+      <c r="O27" s="94" t="e">
         <f t="shared" si="6"/>
-        <v>425.7</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P27" s="74">
         <f t="shared" si="9"/>
@@ -5271,9 +5271,9 @@
         <f t="shared" si="5"/>
         <v>425.7</v>
       </c>
-      <c r="O28" s="79">
+      <c r="O28" s="79" t="e">
         <f t="shared" si="6"/>
-        <v>425.7</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P28" s="80">
         <f>L28/I28</f>
@@ -5306,11 +5306,11 @@
       </c>
       <c r="I29" s="21">
         <f t="shared" si="11"/>
-        <v>1201</v>
+        <v>1290</v>
       </c>
       <c r="J29" s="83">
         <f t="shared" si="3"/>
-        <v>0.48001598721023181</v>
+        <v>0.5155875299760192</v>
       </c>
       <c r="K29" s="84">
         <v>600</v>
@@ -5326,13 +5326,13 @@
         <f t="shared" si="5"/>
         <v>425.7</v>
       </c>
-      <c r="O29" s="87">
+      <c r="O29" s="87" t="e">
         <f t="shared" si="6"/>
-        <v>425.7</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P29" s="88">
         <f>L29/I29</f>
-        <v>0.14512905911740218</v>
+        <v>0.13511627906976745</v>
       </c>
       <c r="Q29" s="23" t="e">
         <f>AVERAGE(Q28,Q17,Q23)</f>
